--- a/data/italy/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,3898 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:FG5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_10</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_10</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_11</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_11</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_12</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_12</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_13</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_13</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_10</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_10</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_11</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_11</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_12</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_12</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_13</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_13</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_14</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_14</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_14</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_14</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_15</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GbSDQoj8</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>pizzignacco semuel</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>OrlLWHno</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>izzo armando</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>8hN0kFPe</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>mari pablo</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>lOTx2Yho</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>caldirola luca</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>lb7jSwtb</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>birindelli samuele</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Wj6lXM52</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>pessina matteo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>ABbkAWNr</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>bondo warren</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>dbshNo9J</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>kiriakopoulos giorgos</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>txSCnXec</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>maldini daniel</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>G6Sr2L01</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>dany mota</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>MRq91oVQ</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>petagna andrea</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>SMgpBuOO</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>poluzzi giacomo</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>YsPOdXfT</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>giorgini andrea</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>ARUkhedr</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ceppitelli luca</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2empGF74</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>masiello andrea</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>AwaLb1Br</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>molina salvatore</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>6u5S22DT</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>mallamo alessandro</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Y7lNxZKs</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>arrigoni tommaso</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>E57MEmuc</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>kurtic jasmin</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>GYpRZEj3</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>davi simone</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>IF4kfees</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>odogwu raphael</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>SxUQm619</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>casiraghi daniele</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>Ysk36pE4</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>bettella davide</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>hM9I17fh</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>caprari gianluca</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>jBspTfmj</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>carboni andrea</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>AuwJZqXT</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>d alessandro marco</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>ShD3fHfH</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>d ambrosio danilo</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>hfhlvfwf</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>machin jose</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>6i5Fwg4m</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>maric mirko</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>EirLWWbG</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>mazza andrea</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>8t5OxIB9</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>pereira pedro</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>dbqlLrFU</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>sensi stefano</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>KWK0U27f</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>sorrentino alessandro</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>vPBB8Jle</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>valoti mattia</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0WK0EKMu</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>vignato samuel</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>nqlptEJn</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>cagnano andrea</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>G4Bn6Wm8</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>cisco andrea</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>EwwZyir4</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>crespi valerio</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>re3fD4ft</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>drago giacomo</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>8jRONImG</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>kofler raphael</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>YyHMPSdo</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>lonardi lorenzo</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>AwAumAMJ</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>martini jacopo</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>Yce2AIsg</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>merkaj silvio</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>UVuDC3HF</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>pietrangeli nicola</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>dYVzSibc</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>praszelik mateusz</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>ClOmlbUN</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>rover matteo</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>WluibOr9</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>tait fabian</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>MixK5s5G</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>tscholl jakob</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>Ia5CwlDC</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>vimercati alessandro</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>hM9I17fh</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>caprari gianluca</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>hM9I17fh</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>caprari gianluca</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>txSCnXec</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>maldini daniel</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>8t5OxIB9</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>pereira pedro</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>8t5OxIB9</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>pereira pedro</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>lb7jSwtb</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>birindelli samuele</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>6i5Fwg4m</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>maric mirko</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>6i5Fwg4m</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>maric mirko</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>MRq91oVQ</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>petagna andrea</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>dbqlLrFU</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>sensi stefano</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>dbqlLrFU</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>sensi stefano</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Wj6lXM52</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>pessina matteo</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>EwwZyir4</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>crespi valerio</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>EwwZyir4</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>crespi valerio</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>IF4kfees</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>odogwu raphael</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>Yce2AIsg</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>merkaj silvio</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>Yce2AIsg</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>merkaj silvio</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>SxUQm619</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>casiraghi daniele</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>dYVzSibc</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>praszelik mateusz</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>dYVzSibc</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>praszelik mateusz</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>6u5S22DT</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>mallamo alessandro</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr"/>
+      <c r="EM2" t="inlineStr"/>
+      <c r="EN2" t="inlineStr"/>
+      <c r="EO2" t="inlineStr"/>
+      <c r="EP2" t="inlineStr"/>
+      <c r="EQ2" t="inlineStr"/>
+      <c r="ER2" t="inlineStr"/>
+      <c r="ES2" t="inlineStr"/>
+      <c r="ET2" t="inlineStr"/>
+      <c r="EU2" t="inlineStr"/>
+      <c r="EV2" t="inlineStr"/>
+      <c r="EW2" t="inlineStr"/>
+      <c r="EX2" t="inlineStr"/>
+      <c r="EY2" t="inlineStr"/>
+      <c r="EZ2" t="inlineStr"/>
+      <c r="FA2" t="inlineStr"/>
+      <c r="FB2" t="inlineStr"/>
+      <c r="FC2" t="inlineStr"/>
+      <c r="FD2" t="inlineStr"/>
+      <c r="FE2" t="inlineStr"/>
+      <c r="FF2" t="inlineStr"/>
+      <c r="FG2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MHD6IelJ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>leali nicola</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>tW6pCCm8</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vogliacco alessandro</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>vgmL526e</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>bani mattia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EFmPm0Qo</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>de winter koni</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>l4xhn6hC</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>caricol aaron</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2XPmtx2l</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>frendrup morten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4InuIizr</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>badelj milan</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ei7zkE0o</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>thorsby morten</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>zLlOcqw4</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>sabelli stefano</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>8l36RdAF</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>messias junior</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>AazXYT3h</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>vitinha</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>ATMse0OQ</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>motta edoardo</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>bkpO1UAs</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>fiamozzi riccardo</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>baFaIqPm</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>meroni andrea</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Ug0GqtE0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>rozzio paolo</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>46jUu380</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>cavallini giacomo</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>jumC8deM</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>sersanti alessandro</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>lfpEEa5J</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>cigarini luca</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>SpsFliY4</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>ignacchiti lorenzo</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0bwMG5SF</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>vergara antonio</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>QqCsQcU5</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>gondo cedric</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>UZADb54K</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>maggio matteo</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>U5DbE1A7</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>accornero federico</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>Q1Sl1XK4</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>ahanor honest</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>25uHtnwl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>bohinen emil</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>QopKhlIm</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>ekhator jeff</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>hzTcOuoN</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>fini seydou</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>vZY7FZwP</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>gollini pierluigi</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>GGkyU0bT</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>malinovsky ruslan</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>fwaRyAka</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>masini patrizio</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>lnhcFnwg</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>papadopoulos christos</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>SWwXbklm</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>pittino tommaso</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>MsjFcjtJ</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>sommariva daniele</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>Qydfoeer</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>vasquez johan</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>xjWe0TTo</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>zanoli alessandro</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>vei7O2U9</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>donelli matteo</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>08RKxF9J</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>libutti lorenzo</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>8WxIdbec</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>nahounou yannis</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>CEu5J6N8</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>okwonkwo orji</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>67w6mUGh</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>reinhart tobias</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>UenvOQL5</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>sposito alex</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>dh1QqfhO</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>stramaccioni diego</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>zPvo9nZ2</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>urso oliver</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>d0WK1pb6</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>vido luca</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr"/>
+      <c r="CM3" t="inlineStr"/>
+      <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="inlineStr"/>
+      <c r="CP3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr"/>
+      <c r="CR3" t="inlineStr"/>
+      <c r="CS3" t="inlineStr"/>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>GGkyU0bT</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>malinovsky ruslan</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>GGkyU0bT</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>malinovsky ruslan</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>4InuIizr</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>badelj milan</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>xjWe0TTo</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>zanoli alessandro</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>xjWe0TTo</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>zanoli alessandro</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>zLlOcqw4</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>sabelli stefano</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>QopKhlIm</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>ekhator jeff</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>QopKhlIm</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>ekhator jeff</t>
+        </is>
+      </c>
+      <c r="DL3" t="inlineStr">
+        <is>
+          <t>AazXYT3h</t>
+        </is>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>vitinha</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>hzTcOuoN</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>fini seydou</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>hzTcOuoN</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
+          <t>fini seydou</t>
+        </is>
+      </c>
+      <c r="DR3" t="inlineStr">
+        <is>
+          <t>8l36RdAF</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
+          <t>messias junior</t>
+        </is>
+      </c>
+      <c r="DT3" t="inlineStr">
+        <is>
+          <t>67w6mUGh</t>
+        </is>
+      </c>
+      <c r="DU3" t="inlineStr">
+        <is>
+          <t>reinhart tobias</t>
+        </is>
+      </c>
+      <c r="DV3" t="inlineStr">
+        <is>
+          <t>67w6mUGh</t>
+        </is>
+      </c>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>reinhart tobias</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>lfpEEa5J</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>cigarini luca</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>CEu5J6N8</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>okwonkwo orji</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>CEu5J6N8</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>okwonkwo orji</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>UZADb54K</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>maggio matteo</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>08RKxF9J</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>libutti lorenzo</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>08RKxF9J</t>
+        </is>
+      </c>
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>libutti lorenzo</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>jumC8deM</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>sersanti alessandro</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
+        <is>
+          <t>d0WK1pb6</t>
+        </is>
+      </c>
+      <c r="EM3" t="inlineStr">
+        <is>
+          <t>vido luca</t>
+        </is>
+      </c>
+      <c r="EN3" t="inlineStr">
+        <is>
+          <t>d0WK1pb6</t>
+        </is>
+      </c>
+      <c r="EO3" t="inlineStr">
+        <is>
+          <t>vido luca</t>
+        </is>
+      </c>
+      <c r="EP3" t="inlineStr">
+        <is>
+          <t>bkpO1UAs</t>
+        </is>
+      </c>
+      <c r="EQ3" t="inlineStr">
+        <is>
+          <t>fiamozzi riccardo</t>
+        </is>
+      </c>
+      <c r="ER3" t="inlineStr">
+        <is>
+          <t>zPvo9nZ2</t>
+        </is>
+      </c>
+      <c r="ES3" t="inlineStr">
+        <is>
+          <t>urso oliver</t>
+        </is>
+      </c>
+      <c r="ET3" t="inlineStr">
+        <is>
+          <t>zPvo9nZ2</t>
+        </is>
+      </c>
+      <c r="EU3" t="inlineStr">
+        <is>
+          <t>urso oliver</t>
+        </is>
+      </c>
+      <c r="EV3" t="inlineStr">
+        <is>
+          <t>46jUu380</t>
+        </is>
+      </c>
+      <c r="EW3" t="inlineStr">
+        <is>
+          <t>cavallini giacomo</t>
+        </is>
+      </c>
+      <c r="EX3" t="inlineStr"/>
+      <c r="EY3" t="inlineStr"/>
+      <c r="EZ3" t="inlineStr"/>
+      <c r="FA3" t="inlineStr"/>
+      <c r="FB3" t="inlineStr"/>
+      <c r="FC3" t="inlineStr"/>
+      <c r="FD3" t="inlineStr"/>
+      <c r="FE3" t="inlineStr"/>
+      <c r="FF3" t="inlineStr"/>
+      <c r="FG3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>dnnqk0iD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gr6T6rIt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>okoye maduks</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4nmFi4El</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>perez nehuen</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0CykEP51</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>bijol jaka</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2PHfEmDr</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>gianetti lautaro</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6XCZJG4M</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ehizibue kingsley</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2oBl3y29</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lovric sandi</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ChzBGkMR</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>payero martin</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>KEZVn6fB</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>kamara hassane</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>SMbMSc26</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>thauvin florian</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2kXZSD2S</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>brenner</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>UVyQpa9t</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>lucca lorenzo</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>E7mOU6ff</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>iannarilli antony</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4CQoUvoA</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>cancellotti tommaso</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>r7TIOlXj</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>armellino marco</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>t23s6fm4</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>frascatore paolo</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>KOKJAtq7</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>tribuzzi alessio</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>YwwYfXn7</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>palmiero luca</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>UXbPSRqh</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>sounas dimitris</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>4pCR0JnU</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>rocca michele</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>CYq0fk4G</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>liotti daniele</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>KMmfYvvf</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>patierno cosimo</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>pEpm6Yvi</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>gori gabriele</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>QgfEnOwH</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>abankwah james</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>b5XwSo4Q</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>bravo iker</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>SKxz4XFS</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>davis keinan</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>t8htBdkK</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>ebosele festy</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0SEEBeWj</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>esteves goncalo lago pontes</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>42ADo7dd</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>kabasele christian</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>UDGFZQv8</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>karlstrom jesper</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>dWZccSvp</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>padelli daniele</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>pObeJZYN</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>palma matteo</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>ba7y6F3c</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>samardzic lazar</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>6JqatiEa</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>silvestri marco</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>QHRhjNJJ</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>zarraga oier</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>GAzjxceh</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>zemura jordan</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>jmK9pHmm</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>arzillo vincenzo</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>txZro8GK</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>benedetti simone</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>nwuJgSGk</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>cancellieri damiano</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>CQBR5B92</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>d ausilio michele</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>lt2qSjLr</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>de cristofaro antonio</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>jgqeZ2zA</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>fusco salvatore</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>6sSiUjMJ</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>guarnieri mattia</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>zibNnQ1D</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>llano manuel</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>trVxivFo</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>marson leonardo</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>KrOKz4Yj</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>pizzella luca</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>4rD2qMLm</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>russo raffaele</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>EZN6Bu3i</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>sannipoli daniel</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>YLLycp6S</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>toscano marco</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>xAvF8BUe</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>vano michele</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>UDGFZQv8</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>karlstrom jesper</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>UDGFZQv8</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>karlstrom jesper</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>ChzBGkMR</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>payero martin</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
+          <t>ba7y6F3c</t>
+        </is>
+      </c>
+      <c r="DC4" t="inlineStr">
+        <is>
+          <t>samardzic lazar</t>
+        </is>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>ba7y6F3c</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>samardzic lazar</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
+        <is>
+          <t>SMbMSc26</t>
+        </is>
+      </c>
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>thauvin florian</t>
+        </is>
+      </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>QHRhjNJJ</t>
+        </is>
+      </c>
+      <c r="DI4" t="inlineStr">
+        <is>
+          <t>zarraga oier</t>
+        </is>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>QHRhjNJJ</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>zarraga oier</t>
+        </is>
+      </c>
+      <c r="DL4" t="inlineStr">
+        <is>
+          <t>2kXZSD2S</t>
+        </is>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>brenner</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>SKxz4XFS</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>davis keinan</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>SKxz4XFS</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
+          <t>davis keinan</t>
+        </is>
+      </c>
+      <c r="DR4" t="inlineStr">
+        <is>
+          <t>UVyQpa9t</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
+          <t>lucca lorenzo</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>CQBR5B92</t>
+        </is>
+      </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t>d ausilio michele</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
+          <t>CQBR5B92</t>
+        </is>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>d ausilio michele</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>UXbPSRqh</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>sounas dimitris</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>4rD2qMLm</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>russo raffaele</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>4rD2qMLm</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
+          <t>russo raffaele</t>
+        </is>
+      </c>
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t>KMmfYvvf</t>
+        </is>
+      </c>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t>patierno cosimo</t>
+        </is>
+      </c>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>nwuJgSGk</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>cancellieri damiano</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>nwuJgSGk</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>cancellieri damiano</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
+        <is>
+          <t>CYq0fk4G</t>
+        </is>
+      </c>
+      <c r="EK4" t="inlineStr">
+        <is>
+          <t>liotti daniele</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
+        <is>
+          <t>xAvF8BUe</t>
+        </is>
+      </c>
+      <c r="EM4" t="inlineStr">
+        <is>
+          <t>vano michele</t>
+        </is>
+      </c>
+      <c r="EN4" t="inlineStr">
+        <is>
+          <t>xAvF8BUe</t>
+        </is>
+      </c>
+      <c r="EO4" t="inlineStr">
+        <is>
+          <t>vano michele</t>
+        </is>
+      </c>
+      <c r="EP4" t="inlineStr">
+        <is>
+          <t>pEpm6Yvi</t>
+        </is>
+      </c>
+      <c r="EQ4" t="inlineStr">
+        <is>
+          <t>gori gabriele</t>
+        </is>
+      </c>
+      <c r="ER4" t="inlineStr">
+        <is>
+          <t>lt2qSjLr</t>
+        </is>
+      </c>
+      <c r="ES4" t="inlineStr">
+        <is>
+          <t>de cristofaro antonio</t>
+        </is>
+      </c>
+      <c r="ET4" t="inlineStr">
+        <is>
+          <t>lt2qSjLr</t>
+        </is>
+      </c>
+      <c r="EU4" t="inlineStr">
+        <is>
+          <t>de cristofaro antonio</t>
+        </is>
+      </c>
+      <c r="EV4" t="inlineStr">
+        <is>
+          <t>4pCR0JnU</t>
+        </is>
+      </c>
+      <c r="EW4" t="inlineStr">
+        <is>
+          <t>rocca michele</t>
+        </is>
+      </c>
+      <c r="EX4" t="inlineStr">
+        <is>
+          <t>42ADo7dd</t>
+        </is>
+      </c>
+      <c r="EY4" t="inlineStr">
+        <is>
+          <t>kabasele christian</t>
+        </is>
+      </c>
+      <c r="EZ4" t="inlineStr">
+        <is>
+          <t>42ADo7dd</t>
+        </is>
+      </c>
+      <c r="FA4" t="inlineStr">
+        <is>
+          <t>kabasele christian</t>
+        </is>
+      </c>
+      <c r="FB4" t="inlineStr">
+        <is>
+          <t>4nmFi4El</t>
+        </is>
+      </c>
+      <c r="FC4" t="inlineStr">
+        <is>
+          <t>perez nehuen</t>
+        </is>
+      </c>
+      <c r="FD4" t="inlineStr"/>
+      <c r="FE4" t="inlineStr"/>
+      <c r="FF4" t="inlineStr"/>
+      <c r="FG4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>d2BR3Upb</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>satalino giacomo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IsGWKIMq</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>toljan jeremy</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>M5l0hplp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>odenthal cas</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ILuvGx81</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>romagna filippo</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dQ1Evunq</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>doig josh</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>nodnKnAs</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obiang pedro</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>jPrEU8Tr</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>boloca daniel</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Q1wMNrxU</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>bajrami nedim</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>EF3UYlr3</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>thorstvedt kristian</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>EZVZoGs8</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>lauriente armand</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>f3tdpb62</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>mulattieri samuele</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0dqCCCd6</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>kastrati elhan</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>80gdKWOF</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>salvi alessandro</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>KQJr2C6I</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>pavan nicola</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>jiFEodbj</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>angeli matteo</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>IooWgdIk</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>masciangelo edoardo</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Q7OEUsLS</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>vita alessio</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>04FCiMFb</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>casolari federico</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>SnRbZOrK</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>amatucci francesco</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>K0AtvAAP</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>desogus jacopo</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>zaRWiIq6</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>baldini enrico</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>2LoNIGf3</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>rabbi simone</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>4Of5akc5</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>antiste janis</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>6392aYqP</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>caligara fabrizio</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>retVSWHL</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>kumi justin</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>t4NSHrlh</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>lipani luca</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>QiWQsVa5</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>lovato matteo</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>KpyQQSsm</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>miranda kevin</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>UmzKM5tM</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>missori filippo</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>fDRMwkTQ</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>moro luca</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>IJwHBntK</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>paz yeferson</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>KEyUOiHh</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>piccinini stefano</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>C0qz46Jj</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>pieragnolo edoardo</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>lpzv4KJf</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>racic uros</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>MLQScsMb</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>russo alessandro</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>l2Rt2EsD</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>branca simone</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>O4VaVa69</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>carissoni lorenzo</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>hUTyvgJA</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>cassano claudio</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>v5Kz7B89</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>cecchetto andrea</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>EVzPaGzl</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>d alessio francesco</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>424Mngue</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>djibril akim</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>f3UWa8ss</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>magrassi andrea</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>2JxynqKk</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>maistrello tommy</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>GpcVQVTI</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>maniero luca</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>2ixP48b6</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>negro stefano</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>I3kYfG62</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>rizza alessio</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>SOKhXWeD</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>sottini edoardo</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>2qCcTkgp</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>tessiore andrea</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr"/>
+      <c r="CU5" t="inlineStr"/>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>2B5YqXFG</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>volpato cristian</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>2B5YqXFG</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>volpato cristian</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>Q1wMNrxU</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>bajrami nedim</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
+          <t>t4NSHrlh</t>
+        </is>
+      </c>
+      <c r="DC5" t="inlineStr">
+        <is>
+          <t>lipani luca</t>
+        </is>
+      </c>
+      <c r="DD5" t="inlineStr">
+        <is>
+          <t>t4NSHrlh</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>lipani luca</t>
+        </is>
+      </c>
+      <c r="DF5" t="inlineStr">
+        <is>
+          <t>nodnKnAs</t>
+        </is>
+      </c>
+      <c r="DG5" t="inlineStr">
+        <is>
+          <t>obiang pedro</t>
+        </is>
+      </c>
+      <c r="DH5" t="inlineStr">
+        <is>
+          <t>6392aYqP</t>
+        </is>
+      </c>
+      <c r="DI5" t="inlineStr">
+        <is>
+          <t>caligara fabrizio</t>
+        </is>
+      </c>
+      <c r="DJ5" t="inlineStr">
+        <is>
+          <t>6392aYqP</t>
+        </is>
+      </c>
+      <c r="DK5" t="inlineStr">
+        <is>
+          <t>caligara fabrizio</t>
+        </is>
+      </c>
+      <c r="DL5" t="inlineStr">
+        <is>
+          <t>EF3UYlr3</t>
+        </is>
+      </c>
+      <c r="DM5" t="inlineStr">
+        <is>
+          <t>thorstvedt kristian</t>
+        </is>
+      </c>
+      <c r="DN5" t="inlineStr">
+        <is>
+          <t>fDRMwkTQ</t>
+        </is>
+      </c>
+      <c r="DO5" t="inlineStr">
+        <is>
+          <t>moro luca</t>
+        </is>
+      </c>
+      <c r="DP5" t="inlineStr">
+        <is>
+          <t>fDRMwkTQ</t>
+        </is>
+      </c>
+      <c r="DQ5" t="inlineStr">
+        <is>
+          <t>moro luca</t>
+        </is>
+      </c>
+      <c r="DR5" t="inlineStr">
+        <is>
+          <t>f3tdpb62</t>
+        </is>
+      </c>
+      <c r="DS5" t="inlineStr">
+        <is>
+          <t>mulattieri samuele</t>
+        </is>
+      </c>
+      <c r="DT5" t="inlineStr">
+        <is>
+          <t>hUTyvgJA</t>
+        </is>
+      </c>
+      <c r="DU5" t="inlineStr">
+        <is>
+          <t>cassano claudio</t>
+        </is>
+      </c>
+      <c r="DV5" t="inlineStr">
+        <is>
+          <t>hUTyvgJA</t>
+        </is>
+      </c>
+      <c r="DW5" t="inlineStr">
+        <is>
+          <t>cassano claudio</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>zaRWiIq6</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>baldini enrico</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>f3UWa8ss</t>
+        </is>
+      </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>magrassi andrea</t>
+        </is>
+      </c>
+      <c r="EB5" t="inlineStr">
+        <is>
+          <t>f3UWa8ss</t>
+        </is>
+      </c>
+      <c r="EC5" t="inlineStr">
+        <is>
+          <t>magrassi andrea</t>
+        </is>
+      </c>
+      <c r="ED5" t="inlineStr">
+        <is>
+          <t>K0AtvAAP</t>
+        </is>
+      </c>
+      <c r="EE5" t="inlineStr">
+        <is>
+          <t>desogus jacopo</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr">
+        <is>
+          <t>l2Rt2EsD</t>
+        </is>
+      </c>
+      <c r="EG5" t="inlineStr">
+        <is>
+          <t>branca simone</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
+          <t>l2Rt2EsD</t>
+        </is>
+      </c>
+      <c r="EI5" t="inlineStr">
+        <is>
+          <t>branca simone</t>
+        </is>
+      </c>
+      <c r="EJ5" t="inlineStr">
+        <is>
+          <t>04FCiMFb</t>
+        </is>
+      </c>
+      <c r="EK5" t="inlineStr">
+        <is>
+          <t>casolari federico</t>
+        </is>
+      </c>
+      <c r="EL5" t="inlineStr">
+        <is>
+          <t>2ixP48b6</t>
+        </is>
+      </c>
+      <c r="EM5" t="inlineStr">
+        <is>
+          <t>negro stefano</t>
+        </is>
+      </c>
+      <c r="EN5" t="inlineStr">
+        <is>
+          <t>2ixP48b6</t>
+        </is>
+      </c>
+      <c r="EO5" t="inlineStr">
+        <is>
+          <t>negro stefano</t>
+        </is>
+      </c>
+      <c r="EP5" t="inlineStr">
+        <is>
+          <t>KQJr2C6I</t>
+        </is>
+      </c>
+      <c r="EQ5" t="inlineStr">
+        <is>
+          <t>pavan nicola</t>
+        </is>
+      </c>
+      <c r="ER5" t="inlineStr">
+        <is>
+          <t>2JxynqKk</t>
+        </is>
+      </c>
+      <c r="ES5" t="inlineStr">
+        <is>
+          <t>maistrello tommy</t>
+        </is>
+      </c>
+      <c r="ET5" t="inlineStr">
+        <is>
+          <t>2JxynqKk</t>
+        </is>
+      </c>
+      <c r="EU5" t="inlineStr">
+        <is>
+          <t>maistrello tommy</t>
+        </is>
+      </c>
+      <c r="EV5" t="inlineStr">
+        <is>
+          <t>2LoNIGf3</t>
+        </is>
+      </c>
+      <c r="EW5" t="inlineStr">
+        <is>
+          <t>rabbi simone</t>
+        </is>
+      </c>
+      <c r="EX5" t="inlineStr">
+        <is>
+          <t>QiWQsVa5</t>
+        </is>
+      </c>
+      <c r="EY5" t="inlineStr">
+        <is>
+          <t>lovato matteo</t>
+        </is>
+      </c>
+      <c r="EZ5" t="inlineStr">
+        <is>
+          <t>QiWQsVa5</t>
+        </is>
+      </c>
+      <c r="FA5" t="inlineStr">
+        <is>
+          <t>lovato matteo</t>
+        </is>
+      </c>
+      <c r="FB5" t="inlineStr">
+        <is>
+          <t>EZVZoGs8</t>
+        </is>
+      </c>
+      <c r="FC5" t="inlineStr">
+        <is>
+          <t>lauriente armand</t>
+        </is>
+      </c>
+      <c r="FD5" t="inlineStr">
+        <is>
+          <t>prHV7Xpt</t>
+        </is>
+      </c>
+      <c r="FE5" t="inlineStr">
+        <is>
+          <t>russo flavio</t>
+        </is>
+      </c>
+      <c r="FF5" t="inlineStr">
+        <is>
+          <t>2B5YqXFG</t>
+        </is>
+      </c>
+      <c r="FG5" t="inlineStr">
+        <is>
+          <t>volpato cristian</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/italy/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,4016 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:FM5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_10</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_10</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_11</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_11</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_10</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_10</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_11</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_11</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_12</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_12</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_12</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_12</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4bDDVvmT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>suzuki zion</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SUqEqOY3</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>coulibaly woyo</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6RV5Qaot</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>balogh botond</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>x0EJsbc8</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>circati alessandro</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>l8UQT6rE</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>valeri emanuele</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>6NqFKJLp</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>estevez nahuel</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Qw9q7XhE</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>bernabe adrian</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>zwvX5g6l</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>man dennis</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>ITcHEtOG</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>sohm simon</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>OOFN5OX4</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>mihaila valentin</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>08MpRWg8</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>bonny ange yoan</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>S6gN2QNC</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>maignan mike</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>OKPvQBOR</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>calabria davide</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>AZn3ZNeI</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>tomori fikayo</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Qm2DVwBO</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>pavlovic strahinja</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>ATurLHr0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>hernandez theo</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>f17EnPl3</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>reijnders tijani</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>ETMctXs4</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>musah yunus</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>vTuaEfRq</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>pulisic christian</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>6DpURWF8</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>loftus cheek ruben</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>AqOPWN5s</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>leao rafael</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>EDhpumvd</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>okafor noah</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>vL30lp6C</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>almqvist pontus</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>zm9nBPNL</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>camara drissa</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>GvtmmdSl</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>cancellieri matteo</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>ba10fZZI</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>chichizola leandro</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>j33di9cK</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>corvi edoardo</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>40jzLivE</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>cyprien wylan</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>b7eKMEEo</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>del prato enrico</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>hO2RGEGC</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>hainaut antoine</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>Eo7P7oks</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>haj mohamed</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>WU5civJO</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>kowalski mateusz</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>GOYmE8zM</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>mikolajewski daniel</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>KS8ySjGG</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>bennacer ismael</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>niW1cP0k</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>chukwueze samuel</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>zBkSUAjf</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>emerson royal</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>dn3cCK1H</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>fofana youssouf</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>Sl6O3rbN</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>gabbia matteo</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>viIS0FT7</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>jovic luka</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>bwgnNY5o</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>raveyre noah</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>n5cPVwks</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>saelemaekers alexis</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>4lL9syGa</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>terracciano filippo</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>0vSsR1xI</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>thiaw malick</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>h8lbX15I</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>torriani lorenzo</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>GvtmmdSl</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>cancellieri matteo</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>GvtmmdSl</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>cancellieri matteo</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>ITcHEtOG</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>sohm simon</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>b7eKMEEo</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>del prato enrico</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>b7eKMEEo</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>del prato enrico</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>OOFN5OX4</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>mihaila valentin</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>40jzLivE</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>cyprien wylan</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>40jzLivE</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>cyprien wylan</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>6NqFKJLp</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>estevez nahuel</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>vL30lp6C</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>almqvist pontus</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>vL30lp6C</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>almqvist pontus</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>zwvX5g6l</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>man dennis</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>dn3cCK1H</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>fofana youssouf</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>dn3cCK1H</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>fofana youssouf</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>ETMctXs4</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>musah yunus</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>zBkSUAjf</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>emerson royal</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>zBkSUAjf</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>emerson royal</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>OKPvQBOR</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>calabria davide</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>niW1cP0k</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>chukwueze samuel</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>niW1cP0k</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>chukwueze samuel</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>vTuaEfRq</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>pulisic christian</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>viIS0FT7</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>jovic luka</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>viIS0FT7</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>jovic luka</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>EDhpumvd</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>okafor noah</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>KSn7To32</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>benedyczak adrian</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>fNdypn5G</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>charpentier gabriel</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>Sv3By8Ki</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>di chiara gianluca</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>bcZkPxo4</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>hernani</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>48K74eTp</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>osorio yordan</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>8UwHPuvH</t>
+        </is>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>florenzi alessandro</t>
+        </is>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>fmkHs3aU</t>
+        </is>
+      </c>
+      <c r="EU2" t="inlineStr">
+        <is>
+          <t>morata alvaro</t>
+        </is>
+      </c>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>EiVDoV04</t>
+        </is>
+      </c>
+      <c r="EW2" t="inlineStr">
+        <is>
+          <t>sportiello marco</t>
+        </is>
+      </c>
+      <c r="EX2" t="inlineStr"/>
+      <c r="EY2" t="inlineStr"/>
+      <c r="EZ2" t="inlineStr"/>
+      <c r="FA2" t="inlineStr"/>
+      <c r="FB2" t="inlineStr"/>
+      <c r="FC2" t="inlineStr"/>
+      <c r="FD2" t="inlineStr"/>
+      <c r="FE2" t="inlineStr"/>
+      <c r="FF2" t="inlineStr"/>
+      <c r="FG2" t="inlineStr"/>
+      <c r="FH2" t="inlineStr"/>
+      <c r="FI2" t="inlineStr"/>
+      <c r="FJ2" t="inlineStr"/>
+      <c r="FK2" t="inlineStr"/>
+      <c r="FL2" t="inlineStr"/>
+      <c r="FM2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Gr6T6rIt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>okoye maduks</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4nmFi4El</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>perez nehuen</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0CykEP51</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>bijol jaka</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2PHfEmDr</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>gianetti lautaro</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6XCZJG4M</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ehizibue kingsley</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>UDGFZQv8</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>karlstrom jesper</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ChzBGkMR</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>payero martin</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>KEZVn6fB</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>kamara hassane</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>SMbMSc26</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>thauvin florian</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2kXZSD2S</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>brenner</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>UVyQpa9t</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>lucca lorenzo</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>C6m92DF7</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>provedel ivan</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>WlqJxlIT</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>lazzari manuel</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>WAb3qgda</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>casale nicolo</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Wr49C0j4</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>romagnoli alessio</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>tC46HZrA</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>marusic adam</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>6ZesE86o</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>guendouzi matteo</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>AVysqrBE</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>vecino matias</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>AF8BqWgI</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>dele bashiru fisayo</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>Uma3vLeI</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>noslin tijjani</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>ET4rsqIP</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>castellanos valentin</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>MJ7sACQ8</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>zaccagni mattia</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>QgfEnOwH</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>abankwah james</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>b5XwSo4Q</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>bravo iker</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>SKxz4XFS</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>davis keinan</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>t8htBdkK</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>ebosele festy</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>4W6Geckd</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>ekkelenkamp jurgen</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>42ADo7dd</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>kabasele christian</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>GdjB2qGA</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>kristensen thomas</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2oBl3y29</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>lovric sandi</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>dWZccSvp</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>padelli daniele</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>6JqatiEa</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>silvestri marco</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>QHRhjNJJ</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>zarraga oier</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>ALBpOZPH</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>castrovilli gaetano</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>IcuAZWW1</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>cataldi danilo</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>zk0Q52W2</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>dia boulaye</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>2PZTBiII</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>furlanetto alessio</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>8z6PLSII</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>hysaj elseid</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>d0vohCHH</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>isaksen gustav</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>vVGAhOFI</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>mandas christos</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>YXwSY2Ef</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>patric</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>0f1tMqQl</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>pedro</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>bPQZKve0</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>rovella nicolo</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>pY6E7S2D</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>tavares nuno</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>2oBl3y29</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>lovric sandi</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>2oBl3y29</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>lovric sandi</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>ChzBGkMR</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>payero martin</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>4W6Geckd</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>ekkelenkamp jurgen</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>4W6Geckd</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>ekkelenkamp jurgen</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>2kXZSD2S</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>brenner</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>42ADo7dd</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>kabasele christian</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>42ADo7dd</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>kabasele christian</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>2PHfEmDr</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>gianetti lautaro</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>QHRhjNJJ</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>zarraga oier</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>QHRhjNJJ</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>zarraga oier</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>SMbMSc26</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>thauvin florian</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>YXwSY2Ef</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>patric</t>
+        </is>
+      </c>
+      <c r="DL3" t="inlineStr">
+        <is>
+          <t>YXwSY2Ef</t>
+        </is>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>patric</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>WAb3qgda</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>casale nicolo</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>zk0Q52W2</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
+          <t>dia boulaye</t>
+        </is>
+      </c>
+      <c r="DR3" t="inlineStr">
+        <is>
+          <t>zk0Q52W2</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
+          <t>dia boulaye</t>
+        </is>
+      </c>
+      <c r="DT3" t="inlineStr">
+        <is>
+          <t>AF8BqWgI</t>
+        </is>
+      </c>
+      <c r="DU3" t="inlineStr">
+        <is>
+          <t>dele bashiru fisayo</t>
+        </is>
+      </c>
+      <c r="DV3" t="inlineStr">
+        <is>
+          <t>d0vohCHH</t>
+        </is>
+      </c>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>isaksen gustav</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>d0vohCHH</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>isaksen gustav</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>Uma3vLeI</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>noslin tijjani</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>8z6PLSII</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>hysaj elseid</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>8z6PLSII</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>hysaj elseid</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>tC46HZrA</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>marusic adam</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>WpIsmaGl</t>
+        </is>
+      </c>
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>deulofeu gerard</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>MXSXXNLr</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>ebosse enzo</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
+        <is>
+          <t>O8lwaueL</t>
+        </is>
+      </c>
+      <c r="EM3" t="inlineStr">
+        <is>
+          <t>pizarro damian</t>
+        </is>
+      </c>
+      <c r="EN3" t="inlineStr">
+        <is>
+          <t>QgGt7V0d</t>
+        </is>
+      </c>
+      <c r="EO3" t="inlineStr">
+        <is>
+          <t>sanchez alexis</t>
+        </is>
+      </c>
+      <c r="EP3" t="inlineStr"/>
+      <c r="EQ3" t="inlineStr"/>
+      <c r="ER3" t="inlineStr">
+        <is>
+          <t>dQqXDhtf</t>
+        </is>
+      </c>
+      <c r="ES3" t="inlineStr">
+        <is>
+          <t>gila mario</t>
+        </is>
+      </c>
+      <c r="ET3" t="inlineStr">
+        <is>
+          <t>WKey0InR</t>
+        </is>
+      </c>
+      <c r="EU3" t="inlineStr">
+        <is>
+          <t>pellegrini luca</t>
+        </is>
+      </c>
+      <c r="EV3" t="inlineStr"/>
+      <c r="EW3" t="inlineStr"/>
+      <c r="EX3" t="inlineStr">
+        <is>
+          <t>GAzjxceh</t>
+        </is>
+      </c>
+      <c r="EY3" t="inlineStr">
+        <is>
+          <t>zemura jordan</t>
+        </is>
+      </c>
+      <c r="EZ3" t="inlineStr">
+        <is>
+          <t>vij66lN7</t>
+        </is>
+      </c>
+      <c r="FA3" t="inlineStr">
+        <is>
+          <t>tchaouna loum</t>
+        </is>
+      </c>
+      <c r="FB3" t="inlineStr">
+        <is>
+          <t>SKxz4XFS</t>
+        </is>
+      </c>
+      <c r="FC3" t="inlineStr">
+        <is>
+          <t>davis keinan</t>
+        </is>
+      </c>
+      <c r="FD3" t="inlineStr">
+        <is>
+          <t>SKxz4XFS</t>
+        </is>
+      </c>
+      <c r="FE3" t="inlineStr">
+        <is>
+          <t>davis keinan</t>
+        </is>
+      </c>
+      <c r="FF3" t="inlineStr">
+        <is>
+          <t>UVyQpa9t</t>
+        </is>
+      </c>
+      <c r="FG3" t="inlineStr">
+        <is>
+          <t>lucca lorenzo</t>
+        </is>
+      </c>
+      <c r="FH3" t="inlineStr">
+        <is>
+          <t>vij66lN7</t>
+        </is>
+      </c>
+      <c r="FI3" t="inlineStr">
+        <is>
+          <t>tchaouna loum</t>
+        </is>
+      </c>
+      <c r="FJ3" t="inlineStr">
+        <is>
+          <t>vij66lN7</t>
+        </is>
+      </c>
+      <c r="FK3" t="inlineStr">
+        <is>
+          <t>tchaouna loum</t>
+        </is>
+      </c>
+      <c r="FL3" t="inlineStr">
+        <is>
+          <t>MJ7sACQ8</t>
+        </is>
+      </c>
+      <c r="FM3" t="inlineStr">
+        <is>
+          <t>zaccagni mattia</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SMgpBuOO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>poluzzi giacomo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>YsPOdXfT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>giorgini andrea</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ARUkhedr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ceppitelli luca</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2empGF74</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>masiello andrea</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>AwaLb1Br</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>molina salvatore</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Y7lNxZKs</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>arrigoni tommaso</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>dYVzSibc</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>praszelik mateusz</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>GYpRZEj3</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>davi simone</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>6u5S22DT</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>mallamo alessandro</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>SxUQm619</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>casiraghi daniele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>IF4kfees</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>odogwu raphael</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>dvzcWaun</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>sepe luigi</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>pW9YKtJc</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>daniliuc flavius</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>b5OLGEKk</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>bronn dylan</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>lWANALyo</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>velthuis tijs</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>OMiJz5gi</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>njoh lilian</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0rM28Wn3</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>tello andres</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>4jCqyBoe</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>amatucci lorenzo</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>8lqSIsQI</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>valencia diego</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>IiIBwl8s</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>kallon yayah</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>IN4rltwr</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>simy</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>4QLzJGnH</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>tongya franco</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>nqlptEJn</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>cagnano andrea</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>G4Bn6Wm8</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>cisco andrea</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>EwwZyir4</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>crespi valerio</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>MLiynlN2</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>davi federico</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>re3fD4ft</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>drago giacomo</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>8jRONImG</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>kofler raphael</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>E57MEmuc</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>kurtic jasmin</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>AwAumAMJ</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>martini jacopo</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>Yce2AIsg</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>merkaj silvio</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>UVuDC3HF</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>pietrangeli nicola</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>ClOmlbUN</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>rover matteo</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>2NEiLzlK</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>braaf jayden</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>GGJ3Opji</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>bradaric domagoj</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>raWfPms5</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>corriere francesco</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>v14eQOOO</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>di vico rocco</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>l0e0BnSA</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>fiorillo vincenzo</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>EFz3cpqf</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>gentile davide</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>I7FmJUQk</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>iervolino antonio pio</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>2uPbwswk</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>ruggeri fabio</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>KEdDR3M7</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>soriano roberto</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>UkKychK3</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>verde daniele</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr"/>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>E57MEmuc</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>kurtic jasmin</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>E57MEmuc</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>kurtic jasmin</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>dYVzSibc</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>praszelik mateusz</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>Yce2AIsg</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>merkaj silvio</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>Yce2AIsg</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>merkaj silvio</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>IF4kfees</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>odogwu raphael</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>WluibOr9</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>tait fabian</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>WluibOr9</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>tait fabian</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
+          <t>6u5S22DT</t>
+        </is>
+      </c>
+      <c r="DC4" t="inlineStr">
+        <is>
+          <t>mallamo alessandro</t>
+        </is>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>ClOmlbUN</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>rover matteo</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
+        <is>
+          <t>ClOmlbUN</t>
+        </is>
+      </c>
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>rover matteo</t>
+        </is>
+      </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>SxUQm619</t>
+        </is>
+      </c>
+      <c r="DI4" t="inlineStr">
+        <is>
+          <t>casiraghi daniele</t>
+        </is>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>2NEiLzlK</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>braaf jayden</t>
+        </is>
+      </c>
+      <c r="DL4" t="inlineStr">
+        <is>
+          <t>2NEiLzlK</t>
+        </is>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>braaf jayden</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>8lqSIsQI</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>valencia diego</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>UkKychK3</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
+          <t>verde daniele</t>
+        </is>
+      </c>
+      <c r="DR4" t="inlineStr">
+        <is>
+          <t>UkKychK3</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
+          <t>verde daniele</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>IiIBwl8s</t>
+        </is>
+      </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t>kallon yayah</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
+          <t>KEdDR3M7</t>
+        </is>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>soriano roberto</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>KEdDR3M7</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>soriano roberto</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>0rM28Wn3</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>tello andres</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>EFz3cpqf</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
+          <t>gentile davide</t>
+        </is>
+      </c>
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t>EFz3cpqf</t>
+        </is>
+      </c>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t>gentile davide</t>
+        </is>
+      </c>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>pW9YKtJc</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>daniliuc flavius</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr"/>
+      <c r="EI4" t="inlineStr"/>
+      <c r="EJ4" t="inlineStr"/>
+      <c r="EK4" t="inlineStr"/>
+      <c r="EL4" t="inlineStr"/>
+      <c r="EM4" t="inlineStr"/>
+      <c r="EN4" t="inlineStr"/>
+      <c r="EO4" t="inlineStr"/>
+      <c r="EP4" t="inlineStr"/>
+      <c r="EQ4" t="inlineStr"/>
+      <c r="ER4" t="inlineStr"/>
+      <c r="ES4" t="inlineStr"/>
+      <c r="ET4" t="inlineStr"/>
+      <c r="EU4" t="inlineStr"/>
+      <c r="EV4" t="inlineStr"/>
+      <c r="EW4" t="inlineStr"/>
+      <c r="EX4" t="inlineStr">
+        <is>
+          <t>WluibOr9</t>
+        </is>
+      </c>
+      <c r="EY4" t="inlineStr">
+        <is>
+          <t>tait fabian</t>
+        </is>
+      </c>
+      <c r="EZ4" t="inlineStr"/>
+      <c r="FA4" t="inlineStr"/>
+      <c r="FB4" t="inlineStr">
+        <is>
+          <t>MLiynlN2</t>
+        </is>
+      </c>
+      <c r="FC4" t="inlineStr">
+        <is>
+          <t>davi federico</t>
+        </is>
+      </c>
+      <c r="FD4" t="inlineStr">
+        <is>
+          <t>MLiynlN2</t>
+        </is>
+      </c>
+      <c r="FE4" t="inlineStr">
+        <is>
+          <t>davi federico</t>
+        </is>
+      </c>
+      <c r="FF4" t="inlineStr">
+        <is>
+          <t>AwaLb1Br</t>
+        </is>
+      </c>
+      <c r="FG4" t="inlineStr">
+        <is>
+          <t>molina salvatore</t>
+        </is>
+      </c>
+      <c r="FH4" t="inlineStr">
+        <is>
+          <t>v14eQOOO</t>
+        </is>
+      </c>
+      <c r="FI4" t="inlineStr">
+        <is>
+          <t>di vico rocco</t>
+        </is>
+      </c>
+      <c r="FJ4" t="inlineStr">
+        <is>
+          <t>v14eQOOO</t>
+        </is>
+      </c>
+      <c r="FK4" t="inlineStr">
+        <is>
+          <t>di vico rocco</t>
+        </is>
+      </c>
+      <c r="FL4" t="inlineStr">
+        <is>
+          <t>4QLzJGnH</t>
+        </is>
+      </c>
+      <c r="FM4" t="inlineStr">
+        <is>
+          <t>tongya franco</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>zVciSbuM</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>gagno riccardo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>h2x8H16h</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>caldara mattia</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>lrTyTrDK</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>zaro giovanni</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>IDD8ySMl</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>pergreffi antonio</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>n5TCLpkU</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>cotali matteo</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>4IL28fC8</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>santoro simone</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>OxkBKxKc</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>gerli fabio</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>WzfIQAtT</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>battistella thomas</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>K2oPRv02</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>palumbo antonio</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Wv6b1jk0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>gliozzi ettore</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>GpH8L1Ag</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>mendes pedro</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>vJSWqc3U</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>radunovic boris</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>vRCJaryd</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>pucino raffaele</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>joCeChcm</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>vicari francesco</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2J5yEYd4</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>obaretin nosa edward</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>bFSFG3sT</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>olivieri andrea</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>UFsffxn9</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>maita mattia</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Gl31cksa</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>benali ahmad</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>2DjEKsjr</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>dorval mehdi</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>WAWziD2c</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>manzari giacomo</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>KKpjmCfA</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>sibilli giuseppe</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>Q9PDryv2</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>novakovich andrija</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>ldqJAYF7</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>abiuso fabio</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>6PTxZBhB</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>beyuku bowutankoyi gady pierre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Msrf6Ec9</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>botteghin</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>hfvxnHLb</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>bozhanaj kleis</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>AcHn4RA5</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>cauz cristian</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>UkRwQ194</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>defrel gregoire</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>OQxnsO9U</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>di pardo alessandro</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>f1smwzJc</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>duca edoardo</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>GxGwdpWd</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>idrissi riyad</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>dnZSvEME</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>magnino luca</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>EBfOOAYg</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>mondele lukas</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>KOt4gbkL</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>astrologo andrea</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>zsBl6R0S</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>bellomo nicola</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>d64ZXgzb</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>faggi filippo</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>x4AiZlG7</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>favasuli costantino</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>lEiQbqRi</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>lasagna kevin</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>2DRxNUHG</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>lulic karlo</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>K4ftNDkl</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>mantovani valerio</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>YLm7hvBc</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>matino emmanuele</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>zHYBgcIp</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>morachioli gregorio</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>t0rMk0s7</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>pissardo marco</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>WMM2MKsk</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>ricci giacomo</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>dnZSvEME</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>magnino luca</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>dnZSvEME</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>magnino luca</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>WzfIQAtT</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>battistella thomas</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>OQxnsO9U</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>di pardo alessandro</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>OQxnsO9U</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>di pardo alessandro</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>IDD8ySMl</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>pergreffi antonio</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>GxGwdpWd</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>idrissi riyad</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>GxGwdpWd</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>idrissi riyad</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
+          <t>n5TCLpkU</t>
+        </is>
+      </c>
+      <c r="DC5" t="inlineStr">
+        <is>
+          <t>cotali matteo</t>
+        </is>
+      </c>
+      <c r="DD5" t="inlineStr">
+        <is>
+          <t>UkRwQ194</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>defrel gregoire</t>
+        </is>
+      </c>
+      <c r="DF5" t="inlineStr">
+        <is>
+          <t>UkRwQ194</t>
+        </is>
+      </c>
+      <c r="DG5" t="inlineStr">
+        <is>
+          <t>defrel gregoire</t>
+        </is>
+      </c>
+      <c r="DH5" t="inlineStr">
+        <is>
+          <t>K2oPRv02</t>
+        </is>
+      </c>
+      <c r="DI5" t="inlineStr">
+        <is>
+          <t>palumbo antonio</t>
+        </is>
+      </c>
+      <c r="DJ5" t="inlineStr">
+        <is>
+          <t>WMM2MKsk</t>
+        </is>
+      </c>
+      <c r="DK5" t="inlineStr">
+        <is>
+          <t>ricci giacomo</t>
+        </is>
+      </c>
+      <c r="DL5" t="inlineStr">
+        <is>
+          <t>WMM2MKsk</t>
+        </is>
+      </c>
+      <c r="DM5" t="inlineStr">
+        <is>
+          <t>ricci giacomo</t>
+        </is>
+      </c>
+      <c r="DN5" t="inlineStr">
+        <is>
+          <t>2DjEKsjr</t>
+        </is>
+      </c>
+      <c r="DO5" t="inlineStr">
+        <is>
+          <t>dorval mehdi</t>
+        </is>
+      </c>
+      <c r="DP5" t="inlineStr">
+        <is>
+          <t>lEiQbqRi</t>
+        </is>
+      </c>
+      <c r="DQ5" t="inlineStr">
+        <is>
+          <t>lasagna kevin</t>
+        </is>
+      </c>
+      <c r="DR5" t="inlineStr">
+        <is>
+          <t>lEiQbqRi</t>
+        </is>
+      </c>
+      <c r="DS5" t="inlineStr">
+        <is>
+          <t>lasagna kevin</t>
+        </is>
+      </c>
+      <c r="DT5" t="inlineStr">
+        <is>
+          <t>Q9PDryv2</t>
+        </is>
+      </c>
+      <c r="DU5" t="inlineStr">
+        <is>
+          <t>novakovich andrija</t>
+        </is>
+      </c>
+      <c r="DV5" t="inlineStr">
+        <is>
+          <t>x4AiZlG7</t>
+        </is>
+      </c>
+      <c r="DW5" t="inlineStr">
+        <is>
+          <t>favasuli costantino</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>x4AiZlG7</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>favasuli costantino</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>WAWziD2c</t>
+        </is>
+      </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>manzari giacomo</t>
+        </is>
+      </c>
+      <c r="EB5" t="inlineStr">
+        <is>
+          <t>2DRxNUHG</t>
+        </is>
+      </c>
+      <c r="EC5" t="inlineStr">
+        <is>
+          <t>lulic karlo</t>
+        </is>
+      </c>
+      <c r="ED5" t="inlineStr">
+        <is>
+          <t>2DRxNUHG</t>
+        </is>
+      </c>
+      <c r="EE5" t="inlineStr">
+        <is>
+          <t>lulic karlo</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr">
+        <is>
+          <t>UFsffxn9</t>
+        </is>
+      </c>
+      <c r="EG5" t="inlineStr">
+        <is>
+          <t>maita mattia</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr"/>
+      <c r="EI5" t="inlineStr"/>
+      <c r="EJ5" t="inlineStr"/>
+      <c r="EK5" t="inlineStr"/>
+      <c r="EL5" t="inlineStr"/>
+      <c r="EM5" t="inlineStr"/>
+      <c r="EN5" t="inlineStr"/>
+      <c r="EO5" t="inlineStr"/>
+      <c r="EP5" t="inlineStr"/>
+      <c r="EQ5" t="inlineStr"/>
+      <c r="ER5" t="inlineStr"/>
+      <c r="ES5" t="inlineStr"/>
+      <c r="ET5" t="inlineStr"/>
+      <c r="EU5" t="inlineStr"/>
+      <c r="EV5" t="inlineStr"/>
+      <c r="EW5" t="inlineStr"/>
+      <c r="EX5" t="inlineStr">
+        <is>
+          <t>ChuL5A4p</t>
+        </is>
+      </c>
+      <c r="EY5" t="inlineStr">
+        <is>
+          <t>sassi jacopo</t>
+        </is>
+      </c>
+      <c r="EZ5" t="inlineStr">
+        <is>
+          <t>YgsNSpKb</t>
+        </is>
+      </c>
+      <c r="FA5" t="inlineStr">
+        <is>
+          <t>sgarbi lorenzo</t>
+        </is>
+      </c>
+      <c r="FB5" t="inlineStr">
+        <is>
+          <t>Msrf6Ec9</t>
+        </is>
+      </c>
+      <c r="FC5" t="inlineStr">
+        <is>
+          <t>botteghin</t>
+        </is>
+      </c>
+      <c r="FD5" t="inlineStr">
+        <is>
+          <t>Msrf6Ec9</t>
+        </is>
+      </c>
+      <c r="FE5" t="inlineStr">
+        <is>
+          <t>botteghin</t>
+        </is>
+      </c>
+      <c r="FF5" t="inlineStr">
+        <is>
+          <t>Wv6b1jk0</t>
+        </is>
+      </c>
+      <c r="FG5" t="inlineStr">
+        <is>
+          <t>gliozzi ettore</t>
+        </is>
+      </c>
+      <c r="FH5" t="inlineStr">
+        <is>
+          <t>YgsNSpKb</t>
+        </is>
+      </c>
+      <c r="FI5" t="inlineStr">
+        <is>
+          <t>sgarbi lorenzo</t>
+        </is>
+      </c>
+      <c r="FJ5" t="inlineStr">
+        <is>
+          <t>YgsNSpKb</t>
+        </is>
+      </c>
+      <c r="FK5" t="inlineStr">
+        <is>
+          <t>sgarbi lorenzo</t>
+        </is>
+      </c>
+      <c r="FL5" t="inlineStr">
+        <is>
+          <t>bFSFG3sT</t>
+        </is>
+      </c>
+      <c r="FM5" t="inlineStr">
+        <is>
+          <t>olivieri andrea</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/italy/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FM5"/>
+  <dimension ref="A1:FS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -761,3678 +761,8554 @@
       </c>
       <c r="BP1" s="1" t="inlineStr">
         <is>
+          <t>id_player_sub_home_12</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_12</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
           <t>id_player_sub_away_1</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_1</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_2</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_2</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_3</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_3</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_4</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_4</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_5</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_5</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_6</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_6</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_7</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_7</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_8</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_8</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_9</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_9</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_10</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_10</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_11</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_11</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_12</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_12</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_13</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_13</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_1</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_1</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_2</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_2</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_3</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_3</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_4</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_4</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_5</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_5</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_6</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_6</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_7</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_7</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_8</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_8</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_9</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_9</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_10</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_10</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_11</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_11</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_12</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_12</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_1</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_1</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_2</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_2</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_3</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_3</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_4</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_4</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_5</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_5</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_6</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_6</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_7</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_7</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_8</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_8</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_9</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_9</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_10</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_10</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_11</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_11</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_12</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_12</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_1</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_1</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_2</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_2</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_13</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_13</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_14</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_14</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_3</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_3</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_4</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_home_12</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_home_12</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_12</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_12</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_15</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_15</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_13</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_13</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_14</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_14</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_15</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_15</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4bDDVvmT</t>
+          <t>Wz2bzMVI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>suzuki zion</t>
+          <t>terracciano pietro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SUqEqOY3</t>
+          <t>xfB3Fqzl</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>coulibaly woyo</t>
+          <t>comuzzo pietro</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>6RV5Qaot</t>
+          <t>boIt2f70</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>balogh botond</t>
+          <t>ranieri luca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>x0EJsbc8</t>
+          <t>h81ElhF9</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>circati alessandro</t>
+          <t>biraghi cristiano</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>l8UQT6rE</t>
+          <t>6qJwoGCI</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>valeri emanuele</t>
+          <t>dodo</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6NqFKJLp</t>
+          <t>r5WUFzf3</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>estevez nahuel</t>
+          <t>amrabat sofyan</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Qw9q7XhE</t>
+          <t>nc2mg7is</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>bernabe adrian</t>
+          <t>richardson amir</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>zwvX5g6l</t>
+          <t>Ghafo5hk</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>man dennis</t>
+          <t>parisi fabiano</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>ITcHEtOG</t>
+          <t>CAayjMI3</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>sohm simon</t>
+          <t>barak antonin</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>OOFN5OX4</t>
+          <t>6ZevPMzQ</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>mihaila valentin</t>
+          <t>kouame cristian</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>08MpRWg8</t>
+          <t>QPclX9Uq</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>bonny ange yoan</t>
+          <t>kean moise</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>S6gN2QNC</t>
+          <t>Q7KOnM07</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>maignan mike</t>
+          <t>joronen jesse</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>OKPvQBOR</t>
+          <t>6PYQeLsa</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>calabria davide</t>
+          <t>idzes jay</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>AZn3ZNeI</t>
+          <t>087BaXQf</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>tomori fikayo</t>
+          <t>altare giorgio</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Qm2DVwBO</t>
+          <t>h6p8JLua</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>pavlovic strahinja</t>
+          <t>sverko marin</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ATurLHr0</t>
+          <t>nHot9WLH</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>hernandez theo</t>
+          <t>candela antonio</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>f17EnPl3</t>
+          <t>hpae2jw4</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>reijnders tijani</t>
+          <t>andersen magnus kofod</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>ETMctXs4</t>
+          <t>tjm4dqgg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>musah yunus</t>
+          <t>duncan alfred</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>vTuaEfRq</t>
+          <t>SAVw0168</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>pulisic christian</t>
+          <t>zampano francesco</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>6DpURWF8</t>
+          <t>4EDOAeYC</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>loftus cheek ruben</t>
+          <t>ellertsson mikael egill</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>AqOPWN5s</t>
+          <t>EiLy1nCa</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>leao rafael</t>
+          <t>oristanio gaetano</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>EDhpumvd</t>
+          <t>AcMGD9Nj</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>okafor noah</t>
+          <t>gytkjaer christian</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>vL30lp6C</t>
+          <t>4jLAxE3g</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>almqvist pontus</t>
+          <t>beltran lucas</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>zm9nBPNL</t>
+          <t>r5YvrtEQ</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>camara drissa</t>
+          <t>bianco alessandro</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>GvtmmdSl</t>
+          <t>QcPvNKjR</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>cancellieri matteo</t>
+          <t>brekalo josip</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>ba10fZZI</t>
+          <t>d2DTOQlc</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>chichizola leandro</t>
+          <t>colpani andrea</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>j33di9cK</t>
+          <t>d6AEQ6OD</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>corvi edoardo</t>
+          <t>de gea david</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>40jzLivE</t>
+          <t>bHF8YI0f</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>cyprien wylan</t>
+          <t>fortini niccolo</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>b7eKMEEo</t>
+          <t>pn7nWiwS</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>del prato enrico</t>
+          <t>infantino gino</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>hO2RGEGC</t>
+          <t>CrxJQ1Q8</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>hainaut antoine</t>
+          <t>kayode michael</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>Eo7P7oks</t>
+          <t>v9oBM840</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>haj mohamed</t>
+          <t>mandragora rolando</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>WU5civJO</t>
+          <t>OxtBmUSA</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>kowalski mateusz</t>
+          <t>martinelli tommaso</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>GOYmE8zM</t>
+          <t>KOGWbJk6</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>mikolajewski daniel</t>
+          <t>martinez lucas</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>KS8ySjGG</t>
+          <t>rkQyXmLB</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>bennacer ismael</t>
+          <t>sottil riccardo</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>niW1cP0k</t>
+          <t>UJyCwMHF</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>chukwueze samuel</t>
+          <t>crnigoj domen</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>zBkSUAjf</t>
+          <t>dfIWSyf9</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>emerson royal</t>
+          <t>doumbia issa</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>dn3cCK1H</t>
+          <t>dCPh9H60</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>fofana youssouf</t>
+          <t>el haddad saad</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>Sl6O3rbN</t>
+          <t>M9b7IZRg</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>gabbia matteo</t>
+          <t>grandi matteo</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>viIS0FT7</t>
+          <t>h2WGwSuO</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>jovic luka</t>
+          <t>haps ridgeciano</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>bwgnNY5o</t>
+          <t>8EOkxnms</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>raveyre noah</t>
+          <t>lella nunzio</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>n5cPVwks</t>
+          <t>M9Nbe4EG</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>saelemaekers alexis</t>
+          <t>lucchesi lorenzo</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4lL9syGa</t>
+          <t>rJcy0auH</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>terracciano filippo</t>
+          <t>nicolussi hans</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0vSsR1xI</t>
+          <t>zNDPrjy8</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>thiaw malick</t>
+          <t>pierini nicholas</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>h8lbX15I</t>
+          <t>Yq9XdF2N</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>torriani lorenzo</t>
+          <t>raimondo antonio</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>GvtmmdSl</t>
+          <t>lj2aOZGT</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>cancellieri matteo</t>
+          <t>sagrado richie</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>GvtmmdSl</t>
+          <t>vsFwl9Sg</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>cancellieri matteo</t>
+          <t>stankovic filip</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>ITcHEtOG</t>
+          <t>d6gJghfB</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>sohm simon</t>
+          <t>svoboda michael</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>b7eKMEEo</t>
+          <t>d2DTOQlc</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>del prato enrico</t>
+          <t>colpani andrea</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>b7eKMEEo</t>
+          <t>d2DTOQlc</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>del prato enrico</t>
+          <t>colpani andrea</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>OOFN5OX4</t>
+          <t>CAayjMI3</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>mihaila valentin</t>
+          <t>barak antonin</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>40jzLivE</t>
+          <t>rkQyXmLB</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>cyprien wylan</t>
+          <t>sottil riccardo</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>40jzLivE</t>
+          <t>rkQyXmLB</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>cyprien wylan</t>
+          <t>sottil riccardo</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>6NqFKJLp</t>
+          <t>6ZevPMzQ</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>estevez nahuel</t>
+          <t>kouame cristian</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>vL30lp6C</t>
+          <t>KOGWbJk6</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>almqvist pontus</t>
+          <t>martinez lucas</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>vL30lp6C</t>
+          <t>KOGWbJk6</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>almqvist pontus</t>
+          <t>martinez lucas</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>zwvX5g6l</t>
+          <t>xfB3Fqzl</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>man dennis</t>
+          <t>comuzzo pietro</t>
         </is>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>dn3cCK1H</t>
+          <t>v9oBM840</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>fofana youssouf</t>
+          <t>mandragora rolando</t>
         </is>
       </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>dn3cCK1H</t>
+          <t>v9oBM840</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>fofana youssouf</t>
+          <t>mandragora rolando</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>ETMctXs4</t>
+          <t>nc2mg7is</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>musah yunus</t>
+          <t>richardson amir</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>zBkSUAjf</t>
+          <t>4jLAxE3g</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>emerson royal</t>
+          <t>beltran lucas</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>zBkSUAjf</t>
+          <t>4jLAxE3g</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>emerson royal</t>
+          <t>beltran lucas</t>
         </is>
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>OKPvQBOR</t>
+          <t>QPclX9Uq</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
         <is>
-          <t>calabria davide</t>
+          <t>kean moise</t>
         </is>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>niW1cP0k</t>
+          <t>zNDPrjy8</t>
         </is>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>chukwueze samuel</t>
+          <t>pierini nicholas</t>
         </is>
       </c>
       <c r="DX2" t="inlineStr">
         <is>
-          <t>niW1cP0k</t>
+          <t>zNDPrjy8</t>
         </is>
       </c>
       <c r="DY2" t="inlineStr">
         <is>
-          <t>chukwueze samuel</t>
+          <t>pierini nicholas</t>
         </is>
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
-          <t>vTuaEfRq</t>
+          <t>EiLy1nCa</t>
         </is>
       </c>
       <c r="EA2" t="inlineStr">
         <is>
-          <t>pulisic christian</t>
+          <t>oristanio gaetano</t>
         </is>
       </c>
       <c r="EB2" t="inlineStr">
         <is>
-          <t>viIS0FT7</t>
+          <t>Yq9XdF2N</t>
         </is>
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>jovic luka</t>
+          <t>raimondo antonio</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
         <is>
-          <t>viIS0FT7</t>
+          <t>Yq9XdF2N</t>
         </is>
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>jovic luka</t>
+          <t>raimondo antonio</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>EDhpumvd</t>
+          <t>AcMGD9Nj</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>okafor noah</t>
+          <t>gytkjaer christian</t>
         </is>
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>KSn7To32</t>
+          <t>rJcy0auH</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
         <is>
-          <t>benedyczak adrian</t>
+          <t>nicolussi hans</t>
         </is>
       </c>
       <c r="EJ2" t="inlineStr">
         <is>
-          <t>fNdypn5G</t>
+          <t>rJcy0auH</t>
         </is>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>charpentier gabriel</t>
+          <t>nicolussi hans</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>Sv3By8Ki</t>
+          <t>hpae2jw4</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>di chiara gianluca</t>
+          <t>andersen magnus kofod</t>
         </is>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>bcZkPxo4</t>
+          <t>d6gJghfB</t>
         </is>
       </c>
       <c r="EO2" t="inlineStr">
         <is>
-          <t>hernani</t>
+          <t>svoboda michael</t>
         </is>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>48K74eTp</t>
+          <t>d6gJghfB</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>osorio yordan</t>
+          <t>svoboda michael</t>
         </is>
       </c>
       <c r="ER2" t="inlineStr">
         <is>
-          <t>8UwHPuvH</t>
+          <t>6PYQeLsa</t>
         </is>
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>florenzi alessandro</t>
+          <t>idzes jay</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>fmkHs3aU</t>
+          <t>dfIWSyf9</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
         <is>
-          <t>morata alvaro</t>
+          <t>doumbia issa</t>
         </is>
       </c>
       <c r="EV2" t="inlineStr">
         <is>
-          <t>EiVDoV04</t>
+          <t>dfIWSyf9</t>
         </is>
       </c>
       <c r="EW2" t="inlineStr">
         <is>
-          <t>sportiello marco</t>
-        </is>
-      </c>
-      <c r="EX2" t="inlineStr"/>
-      <c r="EY2" t="inlineStr"/>
-      <c r="EZ2" t="inlineStr"/>
-      <c r="FA2" t="inlineStr"/>
-      <c r="FB2" t="inlineStr"/>
-      <c r="FC2" t="inlineStr"/>
-      <c r="FD2" t="inlineStr"/>
-      <c r="FE2" t="inlineStr"/>
-      <c r="FF2" t="inlineStr"/>
-      <c r="FG2" t="inlineStr"/>
-      <c r="FH2" t="inlineStr"/>
-      <c r="FI2" t="inlineStr"/>
-      <c r="FJ2" t="inlineStr"/>
-      <c r="FK2" t="inlineStr"/>
+          <t>doumbia issa</t>
+        </is>
+      </c>
+      <c r="EX2" t="inlineStr">
+        <is>
+          <t>4EDOAeYC</t>
+        </is>
+      </c>
+      <c r="EY2" t="inlineStr">
+        <is>
+          <t>ellertsson mikael egill</t>
+        </is>
+      </c>
+      <c r="EZ2" t="inlineStr">
+        <is>
+          <t>bHCOu1Tl</t>
+        </is>
+      </c>
+      <c r="FA2" t="inlineStr">
+        <is>
+          <t>gudmundsson albert</t>
+        </is>
+      </c>
+      <c r="FB2" t="inlineStr">
+        <is>
+          <t>OSXlKkv9</t>
+        </is>
+      </c>
+      <c r="FC2" t="inlineStr">
+        <is>
+          <t>pongracic marin</t>
+        </is>
+      </c>
+      <c r="FD2" t="inlineStr">
+        <is>
+          <t>tpMja0bC</t>
+        </is>
+      </c>
+      <c r="FE2" t="inlineStr">
+        <is>
+          <t>bjarkason bjarki steinn</t>
+        </is>
+      </c>
+      <c r="FF2" t="inlineStr">
+        <is>
+          <t>bVamjfgm</t>
+        </is>
+      </c>
+      <c r="FG2" t="inlineStr">
+        <is>
+          <t>busio gianluca</t>
+        </is>
+      </c>
+      <c r="FH2" t="inlineStr">
+        <is>
+          <t>4UOgBotB</t>
+        </is>
+      </c>
+      <c r="FI2" t="inlineStr">
+        <is>
+          <t>jajalo mato</t>
+        </is>
+      </c>
+      <c r="FJ2" t="inlineStr">
+        <is>
+          <t>WfrgzpCh</t>
+        </is>
+      </c>
+      <c r="FK2" t="inlineStr">
+        <is>
+          <t>pohjanpalo joel</t>
+        </is>
+      </c>
       <c r="FL2" t="inlineStr"/>
       <c r="FM2" t="inlineStr"/>
+      <c r="FN2" t="inlineStr"/>
+      <c r="FO2" t="inlineStr"/>
+      <c r="FP2" t="inlineStr"/>
+      <c r="FQ2" t="inlineStr"/>
+      <c r="FR2" t="inlineStr"/>
+      <c r="FS2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gr6T6rIt</t>
+          <t>Mw0wd0xM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>okoye maduks</t>
+          <t>milinkovic savic vanja</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4nmFi4El</t>
+          <t>nRc0fR5f</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>perez nehuen</t>
+          <t>tameze adrien</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0CykEP51</t>
+          <t>4f3WP5vm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>bijol jaka</t>
+          <t>coco saul</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2PHfEmDr</t>
+          <t>fsw4UmgM</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>gianetti lautaro</t>
+          <t>masina adam</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6XCZJG4M</t>
+          <t>YirekWMs</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ehizibue kingsley</t>
+          <t>vojvoda mergim</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>UDGFZQv8</t>
+          <t>KShlcp4N</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>karlstrom jesper</t>
+          <t>linetty karol</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ChzBGkMR</t>
+          <t>thdNLRpt</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>payero martin</t>
+          <t>ricci samuele</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>KEZVn6fB</t>
+          <t>vqZMiS0h</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>kamara hassane</t>
+          <t>illic ivan</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>SMbMSc26</t>
+          <t>OvtFAISo</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>thauvin florian</t>
+          <t>lazaro valentino</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2kXZSD2S</t>
+          <t>4C0YmOaJ</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>brenner</t>
+          <t>adams che</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>UVyQpa9t</t>
+          <t>v7zQxVoD</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>lucca lorenzo</t>
+          <t>zapata duvan</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>C6m92DF7</t>
+          <t>8WujtCJF</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>provedel ivan</t>
+          <t>carnesecchi marco</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>WlqJxlIT</t>
+          <t>pW01mTt9</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>lazzari manuel</t>
+          <t>djimsiti berat</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>WAb3qgda</t>
+          <t>SUUtwXea</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>casale nicolo</t>
+          <t>de roon marten</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Wr49C0j4</t>
+          <t>hz4zWEIG</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>romagnoli alessio</t>
+          <t>hien isak</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>tC46HZrA</t>
+          <t>G6AuiwvH</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>marusic adam</t>
+          <t>zappacosta davide</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6ZesE86o</t>
+          <t>fqEsbNyA</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>guendouzi matteo</t>
+          <t>ederson</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>AVysqrBE</t>
+          <t>ld4iyqYa</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>vecino matias</t>
+          <t>pasalic mario</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>AF8BqWgI</t>
+          <t>0WPEP3LT</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>dele bashiru fisayo</t>
+          <t>ruggeri matteo</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>Uma3vLeI</t>
+          <t>lt87Q6nj</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>noslin tijjani</t>
+          <t>brescianini marco</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>ET4rsqIP</t>
+          <t>2eOa3r1T</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>castellanos valentin</t>
+          <t>de ketelaere charles</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>MJ7sACQ8</t>
+          <t>Grhjz8pS</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>zaccagni mattia</t>
+          <t>retegui mateo</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>QgfEnOwH</t>
+          <t>GStMS8cB</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>abankwah james</t>
+          <t>bianay balcot come</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>b5XwSo4Q</t>
+          <t>hM1aIsWB</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>bravo iker</t>
+          <t>ciammaglichella aaron</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>SKxz4XFS</t>
+          <t>0KOxlW5f</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>davis keinan</t>
+          <t>dellavalle alessandro</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>t8htBdkK</t>
+          <t>AsEOFfdr</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>ebosele festy</t>
+          <t>dembele ali</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>4W6Geckd</t>
+          <t>zZcNEj5Q</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>ekkelenkamp jurgen</t>
+          <t>donnarumma antonio</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>42ADo7dd</t>
+          <t>rHtTa12H</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>kabasele christian</t>
+          <t>horvath krisztofer</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>GdjB2qGA</t>
+          <t>OQYJ3VXT</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>kristensen thomas</t>
+          <t>karamoh yann</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2oBl3y29</t>
+          <t>vwnI8wkF</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>lovric sandi</t>
+          <t>nije eybi</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>dWZccSvp</t>
+          <t>vR4315G2</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>padelli daniele</t>
+          <t>paleari alberto</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>6JqatiEa</t>
+          <t>ltnVl6l2</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>silvestri marco</t>
+          <t>pedersen marcus</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>QHRhjNJJ</t>
+          <t>v3hpfVmF</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>zarraga oier</t>
+          <t>pellegri pietro</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>ALBpOZPH</t>
+          <t>jNePUJ0b</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>castrovilli gaetano</t>
+          <t>sanabria antonio</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>IcuAZWW1</t>
+          <t>E9X5pB6I</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>cataldi danilo</t>
+          <t>cassa federico</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>zk0Q52W2</t>
+          <t>jivNliqi</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>dia boulaye</t>
+          <t>del lungo tommaso</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>2PZTBiII</t>
+          <t>nD7QhgLn</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>furlanetto alessio</t>
+          <t>godfrey ben</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>8z6PLSII</t>
+          <t>Y3misx2c</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>hysaj elseid</t>
+          <t>manzoni alberto</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>d0vohCHH</t>
+          <t>zB5O8dXn</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>isaksen gustav</t>
+          <t>musso juan</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>vVGAhOFI</t>
+          <t>Y3DYaDdP</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>mandas christos</t>
+          <t>palestra marco</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>YXwSY2Ef</t>
+          <t>MqtvdNVj</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>patric</t>
+          <t>riccio lorenzo</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0f1tMqQl</t>
+          <t>tdfrZ6nG</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>pedro</t>
+          <t>rossi francesco</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>bPQZKve0</t>
+          <t>ba7y6F3c</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>rovella nicolo</t>
+          <t>samardzic lazar</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>pY6E7S2D</t>
+          <t>lWXuL6ki</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>tavares nuno</t>
+          <t>tornaghi pietro</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>2oBl3y29</t>
+          <t>0G7MtHBl</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>lovric sandi</t>
-        </is>
-      </c>
-      <c r="CN3" t="inlineStr">
-        <is>
-          <t>2oBl3y29</t>
-        </is>
-      </c>
-      <c r="CO3" t="inlineStr">
-        <is>
-          <t>lovric sandi</t>
-        </is>
-      </c>
-      <c r="CP3" t="inlineStr">
-        <is>
-          <t>ChzBGkMR</t>
-        </is>
-      </c>
-      <c r="CQ3" t="inlineStr">
-        <is>
-          <t>payero martin</t>
-        </is>
-      </c>
+          <t>zaniolo nicolo</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="inlineStr"/>
+      <c r="CP3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr"/>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>4W6Geckd</t>
+          <t>AsEOFfdr</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>ekkelenkamp jurgen</t>
+          <t>dembele ali</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>4W6Geckd</t>
+          <t>AsEOFfdr</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>ekkelenkamp jurgen</t>
+          <t>dembele ali</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>2kXZSD2S</t>
+          <t>nRc0fR5f</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>brenner</t>
+          <t>tameze adrien</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>42ADo7dd</t>
+          <t>4vTK4LUr</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>kabasele christian</t>
+          <t>sosa borna</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>42ADo7dd</t>
+          <t>4vTK4LUr</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>kabasele christian</t>
+          <t>sosa borna</t>
         </is>
       </c>
       <c r="DB3" t="inlineStr">
         <is>
-          <t>2PHfEmDr</t>
+          <t>YirekWMs</t>
         </is>
       </c>
       <c r="DC3" t="inlineStr">
         <is>
-          <t>gianetti lautaro</t>
+          <t>vojvoda mergim</t>
         </is>
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>QHRhjNJJ</t>
+          <t>OQYJ3VXT</t>
         </is>
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>zarraga oier</t>
+          <t>karamoh yann</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr">
         <is>
-          <t>QHRhjNJJ</t>
+          <t>OQYJ3VXT</t>
         </is>
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>zarraga oier</t>
+          <t>karamoh yann</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>SMbMSc26</t>
+          <t>4C0YmOaJ</t>
         </is>
       </c>
       <c r="DI3" t="inlineStr">
         <is>
-          <t>thauvin florian</t>
+          <t>adams che</t>
         </is>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>YXwSY2Ef</t>
+          <t>hM1aIsWB</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>patric</t>
+          <t>ciammaglichella aaron</t>
         </is>
       </c>
       <c r="DL3" t="inlineStr">
         <is>
-          <t>YXwSY2Ef</t>
+          <t>hM1aIsWB</t>
         </is>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>patric</t>
+          <t>ciammaglichella aaron</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>WAb3qgda</t>
+          <t>thdNLRpt</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>casale nicolo</t>
-        </is>
-      </c>
-      <c r="DP3" t="inlineStr">
-        <is>
-          <t>zk0Q52W2</t>
-        </is>
-      </c>
-      <c r="DQ3" t="inlineStr">
-        <is>
-          <t>dia boulaye</t>
-        </is>
-      </c>
-      <c r="DR3" t="inlineStr">
-        <is>
-          <t>zk0Q52W2</t>
-        </is>
-      </c>
-      <c r="DS3" t="inlineStr">
-        <is>
-          <t>dia boulaye</t>
-        </is>
-      </c>
-      <c r="DT3" t="inlineStr">
-        <is>
-          <t>AF8BqWgI</t>
-        </is>
-      </c>
-      <c r="DU3" t="inlineStr">
-        <is>
-          <t>dele bashiru fisayo</t>
-        </is>
-      </c>
+          <t>ricci samuele</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr"/>
+      <c r="DQ3" t="inlineStr"/>
+      <c r="DR3" t="inlineStr"/>
+      <c r="DS3" t="inlineStr"/>
+      <c r="DT3" t="inlineStr"/>
+      <c r="DU3" t="inlineStr"/>
       <c r="DV3" t="inlineStr">
         <is>
-          <t>d0vohCHH</t>
+          <t>ba7y6F3c</t>
         </is>
       </c>
       <c r="DW3" t="inlineStr">
         <is>
-          <t>isaksen gustav</t>
+          <t>samardzic lazar</t>
         </is>
       </c>
       <c r="DX3" t="inlineStr">
         <is>
-          <t>d0vohCHH</t>
+          <t>ba7y6F3c</t>
         </is>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>isaksen gustav</t>
+          <t>samardzic lazar</t>
         </is>
       </c>
       <c r="DZ3" t="inlineStr">
         <is>
-          <t>Uma3vLeI</t>
+          <t>lt87Q6nj</t>
         </is>
       </c>
       <c r="EA3" t="inlineStr">
         <is>
-          <t>noslin tijjani</t>
+          <t>brescianini marco</t>
         </is>
       </c>
       <c r="EB3" t="inlineStr">
         <is>
-          <t>8z6PLSII</t>
+          <t>0G7MtHBl</t>
         </is>
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>hysaj elseid</t>
+          <t>zaniolo nicolo</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>8z6PLSII</t>
+          <t>0G7MtHBl</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>hysaj elseid</t>
+          <t>zaniolo nicolo</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>tC46HZrA</t>
+          <t>Grhjz8pS</t>
         </is>
       </c>
       <c r="EG3" t="inlineStr">
         <is>
-          <t>marusic adam</t>
+          <t>retegui mateo</t>
         </is>
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>WpIsmaGl</t>
+          <t>Y3DYaDdP</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
         <is>
-          <t>deulofeu gerard</t>
+          <t>palestra marco</t>
         </is>
       </c>
       <c r="EJ3" t="inlineStr">
         <is>
-          <t>MXSXXNLr</t>
+          <t>Y3DYaDdP</t>
         </is>
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>ebosse enzo</t>
+          <t>palestra marco</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr">
         <is>
-          <t>O8lwaueL</t>
+          <t>hz4zWEIG</t>
         </is>
       </c>
       <c r="EM3" t="inlineStr">
         <is>
-          <t>pizarro damian</t>
+          <t>hien isak</t>
         </is>
       </c>
       <c r="EN3" t="inlineStr">
         <is>
-          <t>QgGt7V0d</t>
+          <t>Y3misx2c</t>
         </is>
       </c>
       <c r="EO3" t="inlineStr">
         <is>
-          <t>sanchez alexis</t>
-        </is>
-      </c>
-      <c r="EP3" t="inlineStr"/>
-      <c r="EQ3" t="inlineStr"/>
+          <t>manzoni alberto</t>
+        </is>
+      </c>
+      <c r="EP3" t="inlineStr">
+        <is>
+          <t>Y3misx2c</t>
+        </is>
+      </c>
+      <c r="EQ3" t="inlineStr">
+        <is>
+          <t>manzoni alberto</t>
+        </is>
+      </c>
       <c r="ER3" t="inlineStr">
         <is>
-          <t>dQqXDhtf</t>
+          <t>2eOa3r1T</t>
         </is>
       </c>
       <c r="ES3" t="inlineStr">
         <is>
-          <t>gila mario</t>
+          <t>de ketelaere charles</t>
         </is>
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>WKey0InR</t>
+          <t>E9X5pB6I</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr">
         <is>
-          <t>pellegrini luca</t>
-        </is>
-      </c>
-      <c r="EV3" t="inlineStr"/>
-      <c r="EW3" t="inlineStr"/>
+          <t>cassa federico</t>
+        </is>
+      </c>
+      <c r="EV3" t="inlineStr">
+        <is>
+          <t>E9X5pB6I</t>
+        </is>
+      </c>
+      <c r="EW3" t="inlineStr">
+        <is>
+          <t>cassa federico</t>
+        </is>
+      </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>GAzjxceh</t>
+          <t>fqEsbNyA</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>zemura jordan</t>
+          <t>ederson</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>vij66lN7</t>
+          <t>vkek8Ais</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
-          <t>tchaouna loum</t>
+          <t>gineitis gvidas</t>
         </is>
       </c>
       <c r="FB3" t="inlineStr">
         <is>
-          <t>SKxz4XFS</t>
+          <t>bmU7ExmH</t>
         </is>
       </c>
       <c r="FC3" t="inlineStr">
         <is>
-          <t>davis keinan</t>
+          <t>savva zannetos</t>
         </is>
       </c>
       <c r="FD3" t="inlineStr">
         <is>
-          <t>SKxz4XFS</t>
+          <t>8xFYnbEi</t>
         </is>
       </c>
       <c r="FE3" t="inlineStr">
         <is>
-          <t>davis keinan</t>
+          <t>kolasinac sead</t>
         </is>
       </c>
       <c r="FF3" t="inlineStr">
         <is>
-          <t>UVyQpa9t</t>
+          <t>hvC4gron</t>
         </is>
       </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>lucca lorenzo</t>
+          <t>scalvini giorgio</t>
         </is>
       </c>
       <c r="FH3" t="inlineStr">
         <is>
-          <t>vij66lN7</t>
+          <t>vDgQxOYl</t>
         </is>
       </c>
       <c r="FI3" t="inlineStr">
         <is>
-          <t>tchaouna loum</t>
+          <t>scamacca gianluca</t>
         </is>
       </c>
       <c r="FJ3" t="inlineStr">
         <is>
-          <t>vij66lN7</t>
+          <t>QB1RMomj</t>
         </is>
       </c>
       <c r="FK3" t="inlineStr">
         <is>
-          <t>tchaouna loum</t>
+          <t>toloi rafael</t>
         </is>
       </c>
       <c r="FL3" t="inlineStr">
         <is>
-          <t>MJ7sACQ8</t>
+          <t>t2MszR74</t>
         </is>
       </c>
       <c r="FM3" t="inlineStr">
         <is>
-          <t>zaccagni mattia</t>
+          <t>sazonov saba</t>
+        </is>
+      </c>
+      <c r="FN3" t="inlineStr">
+        <is>
+          <t>4vTK4LUr</t>
+        </is>
+      </c>
+      <c r="FO3" t="inlineStr">
+        <is>
+          <t>sosa borna</t>
+        </is>
+      </c>
+      <c r="FP3" t="inlineStr">
+        <is>
+          <t>ARdXOcOJ</t>
+        </is>
+      </c>
+      <c r="FQ3" t="inlineStr">
+        <is>
+          <t>schuurs perr</t>
+        </is>
+      </c>
+      <c r="FR3" t="inlineStr">
+        <is>
+          <t>4ryWOtME</t>
+        </is>
+      </c>
+      <c r="FS3" t="inlineStr">
+        <is>
+          <t>vlasic nikola</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CjGqFjre</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SMgpBuOO</t>
+          <t>4zA5n1UG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>poluzzi giacomo</t>
+          <t>sommer yann</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>YsPOdXfT</t>
+          <t>xxuEya3O</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>giorgini andrea</t>
+          <t>pavard benjamin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ARUkhedr</t>
+          <t>SrhnSpzL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ceppitelli luca</t>
+          <t>acerbi francesco</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2empGF74</t>
+          <t>On4TkPTN</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>masiello andrea</t>
+          <t>bastoni alessandro</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AwaLb1Br</t>
+          <t>WbNknKk3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>molina salvatore</t>
+          <t>darmian matteo</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Y7lNxZKs</t>
+          <t>W0yrjzz2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>arrigoni tommaso</t>
+          <t>barella nicolo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>dYVzSibc</t>
+          <t>IRQeP5FJ</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>praszelik mateusz</t>
+          <t>calhanoglu hakan</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>GYpRZEj3</t>
+          <t>KKi1DwHC</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>davi simone</t>
+          <t>mkhitaryan henrikh</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>6u5S22DT</t>
+          <t>W6lypZn3</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>mallamo alessandro</t>
+          <t>dimarco federico</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>SxUQm619</t>
+          <t>hMMX02Fm</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>casiraghi daniele</t>
+          <t>thuram marcus</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>IF4kfees</t>
+          <t>E9UW7Gv8</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>odogwu raphael</t>
+          <t>taremi mehdi</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>dvzcWaun</t>
+          <t>OCJ3DqzU</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>sepe luigi</t>
+          <t>falcone wladimiro</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>pW9YKtJc</t>
+          <t>lxAucZ4d</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>daniliuc flavius</t>
+          <t>gendrey valentin</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>b5OLGEKk</t>
+          <t>25Z8Kyb5</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>bronn dylan</t>
+          <t>baschirotto federico</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>lWANALyo</t>
+          <t>QJJ3NUdE</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>velthuis tijs</t>
+          <t>gaspar kialonga</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>OMiJz5gi</t>
+          <t>GxXIRkFl</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>njoh lilian</t>
+          <t>gallo antonino</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0rM28Wn3</t>
+          <t>2PPgUVm4</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>tello andres</t>
+          <t>ramadani ylber</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4jCqyBoe</t>
+          <t>fZXLQLKC</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>amatucci lorenzo</t>
+          <t>pierret balthazar</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>8lqSIsQI</t>
+          <t>IoRXiRdq</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>valencia diego</t>
+          <t>banda lameck</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>IiIBwl8s</t>
+          <t>bNNOGcFF</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>kallon yayah</t>
+          <t>rafia hamza</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>IN4rltwr</t>
+          <t>Sf4eaXAH</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>simy</t>
+          <t>dorgu patrick</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>4QLzJGnH</t>
+          <t>4CvqRml2</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>tongya franco</t>
+          <t>krstovic nikola</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>nqlptEJn</t>
+          <t>WvR2ASLR</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>cagnano andrea</t>
+          <t>arnautovic marko</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>G4Bn6Wm8</t>
+          <t>hzUi0u2S</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>cisco andrea</t>
+          <t>asllani kristjan</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>EwwZyir4</t>
+          <t>b3kUQZ4h</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>crespi valerio</t>
+          <t>bisseck yann aurel</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>MLiynlN2</t>
+          <t>QZQkZOWj</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>davi federico</t>
+          <t>carlos augusto</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>re3fD4ft</t>
+          <t>IkcGiQBb</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>drago giacomo</t>
+          <t>correa joaquin</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>8jRONImG</t>
+          <t>IuWFfk7l</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>kofler raphael</t>
+          <t>di gennaro raffaele</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>E57MEmuc</t>
+          <t>QR0j1ejk</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>kurtic jasmin</t>
+          <t>dumfries denzel</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>AwAumAMJ</t>
+          <t>G0zPj5Ba</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>martini jacopo</t>
+          <t>fontanarosa alessandro</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>Yce2AIsg</t>
+          <t>WlVuvCqU</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>merkaj silvio</t>
+          <t>frattesi davide</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>UVuDC3HF</t>
+          <t>n5XVsSqd</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>pietrangeli nicola</t>
+          <t>martinez josep</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>ClOmlbUN</t>
+          <t>dlFNZSvb</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>rover matteo</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>2NEiLzlK</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>braaf jayden</t>
-        </is>
-      </c>
+          <t>zielinski piotr</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>GGJ3Opji</t>
+          <t>4fbjCD7B</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>bradaric domagoj</t>
+          <t>berisha medon</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>raWfPms5</t>
+          <t>WEh0KZMT</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>corriere francesco</t>
+          <t>borbei alexandru</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>v14eQOOO</t>
+          <t>vVyq9D0S</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>di vico rocco</t>
+          <t>burnete catalin</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>l0e0BnSA</t>
+          <t>nccbKjdO</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>fiorillo vincenzo</t>
+          <t>coulibaly lassana</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>EFz3cpqf</t>
+          <t>I9wPkuuh</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>gentile davide</t>
+          <t>fruchtl christian</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>I7FmJUQk</t>
+          <t>QsP2aUC4</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>iervolino antonio pio</t>
+          <t>helgason thorir</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>2uPbwswk</t>
+          <t>bygrxvpg</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>ruggeri fabio</t>
+          <t>marchwinski filip</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>KEdDR3M7</t>
+          <t>xOh4r9KI</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>soriano roberto</t>
+          <t>mcjannet ed</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>UkKychK3</t>
+          <t>lQ1WQFtO</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>verde daniele</t>
-        </is>
-      </c>
-      <c r="CJ4" t="inlineStr"/>
-      <c r="CK4" t="inlineStr"/>
+          <t>oudin remi</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>04Pk3MMd</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>pelmard andy</t>
+        </is>
+      </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>E57MEmuc</t>
+          <t>APPhFofM</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>kurtic jasmin</t>
+          <t>pierotti santiago</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>E57MEmuc</t>
+          <t>xhN6Eae7</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>kurtic jasmin</t>
+          <t>samooja jasper</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>dYVzSibc</t>
+          <t>lUc5MiUn</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>praszelik mateusz</t>
+          <t>tete morente</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>Yce2AIsg</t>
+          <t>QZQkZOWj</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>merkaj silvio</t>
+          <t>carlos augusto</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>Yce2AIsg</t>
+          <t>QZQkZOWj</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>merkaj silvio</t>
+          <t>carlos augusto</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>IF4kfees</t>
+          <t>W6lypZn3</t>
         </is>
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>odogwu raphael</t>
+          <t>dimarco federico</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>WluibOr9</t>
+          <t>QR0j1ejk</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>tait fabian</t>
+          <t>dumfries denzel</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>WluibOr9</t>
+          <t>QR0j1ejk</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>tait fabian</t>
+          <t>dumfries denzel</t>
         </is>
       </c>
       <c r="DB4" t="inlineStr">
         <is>
-          <t>6u5S22DT</t>
+          <t>WbNknKk3</t>
         </is>
       </c>
       <c r="DC4" t="inlineStr">
         <is>
-          <t>mallamo alessandro</t>
+          <t>darmian matteo</t>
         </is>
       </c>
       <c r="DD4" t="inlineStr">
         <is>
-          <t>ClOmlbUN</t>
+          <t>WlVuvCqU</t>
         </is>
       </c>
       <c r="DE4" t="inlineStr">
         <is>
-          <t>rover matteo</t>
+          <t>frattesi davide</t>
         </is>
       </c>
       <c r="DF4" t="inlineStr">
         <is>
-          <t>ClOmlbUN</t>
+          <t>WlVuvCqU</t>
         </is>
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>rover matteo</t>
+          <t>frattesi davide</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>SxUQm619</t>
+          <t>W0yrjzz2</t>
         </is>
       </c>
       <c r="DI4" t="inlineStr">
         <is>
-          <t>casiraghi daniele</t>
+          <t>barella nicolo</t>
         </is>
       </c>
       <c r="DJ4" t="inlineStr">
         <is>
-          <t>2NEiLzlK</t>
+          <t>WvR2ASLR</t>
         </is>
       </c>
       <c r="DK4" t="inlineStr">
         <is>
-          <t>braaf jayden</t>
+          <t>arnautovic marko</t>
         </is>
       </c>
       <c r="DL4" t="inlineStr">
         <is>
-          <t>2NEiLzlK</t>
+          <t>WvR2ASLR</t>
         </is>
       </c>
       <c r="DM4" t="inlineStr">
         <is>
-          <t>braaf jayden</t>
+          <t>arnautovic marko</t>
         </is>
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>8lqSIsQI</t>
+          <t>hMMX02Fm</t>
         </is>
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>valencia diego</t>
+          <t>thuram marcus</t>
         </is>
       </c>
       <c r="DP4" t="inlineStr">
         <is>
-          <t>UkKychK3</t>
+          <t>hzUi0u2S</t>
         </is>
       </c>
       <c r="DQ4" t="inlineStr">
         <is>
-          <t>verde daniele</t>
+          <t>asllani kristjan</t>
         </is>
       </c>
       <c r="DR4" t="inlineStr">
         <is>
-          <t>UkKychK3</t>
+          <t>hzUi0u2S</t>
         </is>
       </c>
       <c r="DS4" t="inlineStr">
         <is>
-          <t>verde daniele</t>
+          <t>asllani kristjan</t>
         </is>
       </c>
       <c r="DT4" t="inlineStr">
         <is>
-          <t>IiIBwl8s</t>
+          <t>IRQeP5FJ</t>
         </is>
       </c>
       <c r="DU4" t="inlineStr">
         <is>
-          <t>kallon yayah</t>
+          <t>calhanoglu hakan</t>
         </is>
       </c>
       <c r="DV4" t="inlineStr">
         <is>
-          <t>KEdDR3M7</t>
+          <t>APPhFofM</t>
         </is>
       </c>
       <c r="DW4" t="inlineStr">
         <is>
-          <t>soriano roberto</t>
+          <t>pierotti santiago</t>
         </is>
       </c>
       <c r="DX4" t="inlineStr">
         <is>
-          <t>KEdDR3M7</t>
+          <t>APPhFofM</t>
         </is>
       </c>
       <c r="DY4" t="inlineStr">
         <is>
-          <t>soriano roberto</t>
+          <t>pierotti santiago</t>
         </is>
       </c>
       <c r="DZ4" t="inlineStr">
         <is>
-          <t>0rM28Wn3</t>
+          <t>bNNOGcFF</t>
         </is>
       </c>
       <c r="EA4" t="inlineStr">
         <is>
-          <t>tello andres</t>
+          <t>rafia hamza</t>
         </is>
       </c>
       <c r="EB4" t="inlineStr">
         <is>
-          <t>EFz3cpqf</t>
+          <t>lUc5MiUn</t>
         </is>
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>gentile davide</t>
+          <t>tete morente</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
         <is>
-          <t>EFz3cpqf</t>
+          <t>lUc5MiUn</t>
         </is>
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>gentile davide</t>
+          <t>tete morente</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>pW9YKtJc</t>
+          <t>IoRXiRdq</t>
         </is>
       </c>
       <c r="EG4" t="inlineStr">
         <is>
-          <t>daniliuc flavius</t>
-        </is>
-      </c>
-      <c r="EH4" t="inlineStr"/>
-      <c r="EI4" t="inlineStr"/>
-      <c r="EJ4" t="inlineStr"/>
-      <c r="EK4" t="inlineStr"/>
-      <c r="EL4" t="inlineStr"/>
-      <c r="EM4" t="inlineStr"/>
-      <c r="EN4" t="inlineStr"/>
-      <c r="EO4" t="inlineStr"/>
-      <c r="EP4" t="inlineStr"/>
-      <c r="EQ4" t="inlineStr"/>
-      <c r="ER4" t="inlineStr"/>
-      <c r="ES4" t="inlineStr"/>
+          <t>banda lameck</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>4fbjCD7B</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>berisha medon</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
+        <is>
+          <t>4fbjCD7B</t>
+        </is>
+      </c>
+      <c r="EK4" t="inlineStr">
+        <is>
+          <t>berisha medon</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
+        <is>
+          <t>fZXLQLKC</t>
+        </is>
+      </c>
+      <c r="EM4" t="inlineStr">
+        <is>
+          <t>pierret balthazar</t>
+        </is>
+      </c>
+      <c r="EN4" t="inlineStr">
+        <is>
+          <t>nccbKjdO</t>
+        </is>
+      </c>
+      <c r="EO4" t="inlineStr">
+        <is>
+          <t>coulibaly lassana</t>
+        </is>
+      </c>
+      <c r="EP4" t="inlineStr">
+        <is>
+          <t>nccbKjdO</t>
+        </is>
+      </c>
+      <c r="EQ4" t="inlineStr">
+        <is>
+          <t>coulibaly lassana</t>
+        </is>
+      </c>
+      <c r="ER4" t="inlineStr">
+        <is>
+          <t>4CvqRml2</t>
+        </is>
+      </c>
+      <c r="ES4" t="inlineStr">
+        <is>
+          <t>krstovic nikola</t>
+        </is>
+      </c>
       <c r="ET4" t="inlineStr"/>
       <c r="EU4" t="inlineStr"/>
       <c r="EV4" t="inlineStr"/>
       <c r="EW4" t="inlineStr"/>
-      <c r="EX4" t="inlineStr">
-        <is>
-          <t>WluibOr9</t>
-        </is>
-      </c>
-      <c r="EY4" t="inlineStr">
-        <is>
-          <t>tait fabian</t>
-        </is>
-      </c>
-      <c r="EZ4" t="inlineStr"/>
-      <c r="FA4" t="inlineStr"/>
+      <c r="EX4" t="inlineStr"/>
+      <c r="EY4" t="inlineStr"/>
+      <c r="EZ4" t="inlineStr">
+        <is>
+          <t>G62SXlFI</t>
+        </is>
+      </c>
+      <c r="FA4" t="inlineStr">
+        <is>
+          <t>buchanan tajon</t>
+        </is>
+      </c>
       <c r="FB4" t="inlineStr">
         <is>
-          <t>MLiynlN2</t>
+          <t>8Cf0NM4a</t>
         </is>
       </c>
       <c r="FC4" t="inlineStr">
         <is>
-          <t>davi federico</t>
+          <t>de vrij stefan</t>
         </is>
       </c>
       <c r="FD4" t="inlineStr">
         <is>
-          <t>MLiynlN2</t>
+          <t>0xAp4q1P</t>
         </is>
       </c>
       <c r="FE4" t="inlineStr">
         <is>
-          <t>davi federico</t>
+          <t>gonzalez joan</t>
         </is>
       </c>
       <c r="FF4" t="inlineStr">
         <is>
-          <t>AwaLb1Br</t>
+          <t>lIjZ6yI2</t>
         </is>
       </c>
       <c r="FG4" t="inlineStr">
         <is>
-          <t>molina salvatore</t>
+          <t>kaba mohamed</t>
         </is>
       </c>
       <c r="FH4" t="inlineStr">
         <is>
-          <t>v14eQOOO</t>
+          <t>8xArOHfB</t>
         </is>
       </c>
       <c r="FI4" t="inlineStr">
         <is>
-          <t>di vico rocco</t>
-        </is>
-      </c>
-      <c r="FJ4" t="inlineStr">
-        <is>
-          <t>v14eQOOO</t>
-        </is>
-      </c>
-      <c r="FK4" t="inlineStr">
-        <is>
-          <t>di vico rocco</t>
-        </is>
-      </c>
-      <c r="FL4" t="inlineStr">
-        <is>
-          <t>4QLzJGnH</t>
-        </is>
-      </c>
-      <c r="FM4" t="inlineStr">
-        <is>
-          <t>tongya franco</t>
-        </is>
-      </c>
+          <t>sansone nicola</t>
+        </is>
+      </c>
+      <c r="FJ4" t="inlineStr"/>
+      <c r="FK4" t="inlineStr"/>
+      <c r="FL4" t="inlineStr"/>
+      <c r="FM4" t="inlineStr"/>
+      <c r="FN4" t="inlineStr"/>
+      <c r="FO4" t="inlineStr"/>
+      <c r="FP4" t="inlineStr">
+        <is>
+          <t>QHk1CXUh</t>
+        </is>
+      </c>
+      <c r="FQ4" t="inlineStr">
+        <is>
+          <t>martinez lautaro</t>
+        </is>
+      </c>
+      <c r="FR4" t="inlineStr"/>
+      <c r="FS4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4CX22Dbk</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>zVciSbuM</t>
+          <t>GbSDQoj8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gagno riccardo</t>
+          <t>pizzignacco semuel</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>h2x8H16h</t>
+          <t>OrlLWHno</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>caldara mattia</t>
+          <t>izzo armando</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>lrTyTrDK</t>
+          <t>8hN0kFPe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>zaro giovanni</t>
+          <t>mari pablo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>IDD8ySMl</t>
+          <t>lOTx2Yho</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>pergreffi antonio</t>
+          <t>caldirola luca</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>n5TCLpkU</t>
+          <t>lb7jSwtb</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>cotali matteo</t>
+          <t>birindelli samuele</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4IL28fC8</t>
+          <t>Wj6lXM52</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>santoro simone</t>
+          <t>pessina matteo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>OxkBKxKc</t>
+          <t>ABbkAWNr</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>gerli fabio</t>
+          <t>bondo warren</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>WzfIQAtT</t>
+          <t>dbshNo9J</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>battistella thomas</t>
+          <t>kiriakopoulos giorgos</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>K2oPRv02</t>
+          <t>txSCnXec</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>palumbo antonio</t>
+          <t>maldini daniel</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Wv6b1jk0</t>
+          <t>G6Sr2L01</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>gliozzi ettore</t>
+          <t>dany mota</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>GpH8L1Ag</t>
+          <t>MRq91oVQ</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>mendes pedro</t>
+          <t>petagna andrea</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>vJSWqc3U</t>
+          <t>vZY7FZwP</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>radunovic boris</t>
+          <t>gollini pierluigi</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>vRCJaryd</t>
+          <t>EFmPm0Qo</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>pucino raffaele</t>
+          <t>de winter koni</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>joCeChcm</t>
+          <t>vgmL526e</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>vicari francesco</t>
+          <t>bani mattia</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2J5yEYd4</t>
+          <t>Qydfoeer</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>obaretin nosa edward</t>
+          <t>vasquez johan</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>bFSFG3sT</t>
+          <t>zLlOcqw4</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>olivieri andrea</t>
+          <t>sabelli stefano</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>UFsffxn9</t>
+          <t>8l36RdAF</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>maita mattia</t>
+          <t>messias junior</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Gl31cksa</t>
+          <t>4InuIizr</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>benali ahmad</t>
+          <t>badelj milan</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2DjEKsjr</t>
+          <t>2XPmtx2l</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>dorval mehdi</t>
+          <t>frendrup morten</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>WAWziD2c</t>
+          <t>l4xhn6hC</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>manzari giacomo</t>
+          <t>caricol aaron</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>KKpjmCfA</t>
+          <t>AazXYT3h</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>sibilli giuseppe</t>
+          <t>vitinha</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>Q9PDryv2</t>
+          <t>O4qi5hfc</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>novakovich andrija</t>
+          <t>pinamonti andrea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>ldqJAYF7</t>
+          <t>KtFXzdCA</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>abiuso fabio</t>
+          <t>bifulco davide</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>6PTxZBhB</t>
+          <t>hM9I17fh</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>beyuku bowutankoyi gady pierre</t>
+          <t>caprari gianluca</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Msrf6Ec9</t>
+          <t>jBspTfmj</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>botteghin</t>
+          <t>carboni andrea</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>hfvxnHLb</t>
+          <t>AuwJZqXT</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>bozhanaj kleis</t>
+          <t>d alessandro marco</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>AcHn4RA5</t>
+          <t>ShD3fHfH</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>cauz cristian</t>
+          <t>d ambrosio danilo</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>UkRwQ194</t>
+          <t>ri4T3rvJ</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>defrel gregoire</t>
+          <t>djuric milan</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>OQxnsO9U</t>
+          <t>lh4Ryd2l</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>di pardo alessandro</t>
+          <t>forson omari</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>f1smwzJc</t>
+          <t>f1Ft78yl</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>duca edoardo</t>
+          <t>gagliardini roberto</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>GxGwdpWd</t>
+          <t>EirLWWbG</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>idrissi riyad</t>
+          <t>mazza andrea</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>dnZSvEME</t>
+          <t>8t5OxIB9</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>magnino luca</t>
+          <t>pereira pedro</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>EBfOOAYg</t>
+          <t>GdRRPoEK</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>mondele lukas</t>
+          <t>turati stefano</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>KOt4gbkL</t>
+          <t>vPBB8Jle</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>astrologo andrea</t>
+          <t>valoti mattia</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>zsBl6R0S</t>
+          <t>U5DbE1A7</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>bellomo nicola</t>
+          <t>accornero federico</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>d64ZXgzb</t>
+          <t>Q1Sl1XK4</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>faggi filippo</t>
+          <t>ahanor honest</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>x4AiZlG7</t>
+          <t>25uHtnwl</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>favasuli costantino</t>
+          <t>bohinen emil</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>lEiQbqRi</t>
+          <t>QopKhlIm</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>lasagna kevin</t>
+          <t>ekhator jeff</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2DRxNUHG</t>
+          <t>CtdcoETk</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>lulic karlo</t>
+          <t>ekuban caleb</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>K4ftNDkl</t>
+          <t>MHD6IelJ</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>mantovani valerio</t>
+          <t>leali nicola</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>YLm7hvBc</t>
+          <t>GGkyU0bT</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>matino emmanuele</t>
+          <t>malinovsky ruslan</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>zHYBgcIp</t>
+          <t>6BUzxLAe</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>morachioli gregorio</t>
+          <t>marcandalli alessandro</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>t0rMk0s7</t>
+          <t>fwaRyAka</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>pissardo marco</t>
+          <t>masini patrizio</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>WMM2MKsk</t>
+          <t>MsjFcjtJ</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>ricci giacomo</t>
+          <t>sommariva daniele</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>dnZSvEME</t>
+          <t>Ei7zkE0o</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>magnino luca</t>
+          <t>thorsby morten</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>dnZSvEME</t>
+          <t>tW6pCCm8</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>magnino luca</t>
+          <t>vogliacco alessandro</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>WzfIQAtT</t>
+          <t>xjWe0TTo</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>battistella thomas</t>
+          <t>zanoli alessandro</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>OQxnsO9U</t>
+          <t>ri4T3rvJ</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>di pardo alessandro</t>
+          <t>djuric milan</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>OQxnsO9U</t>
+          <t>ri4T3rvJ</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>di pardo alessandro</t>
+          <t>djuric milan</t>
         </is>
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>IDD8ySMl</t>
+          <t>MRq91oVQ</t>
         </is>
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>pergreffi antonio</t>
+          <t>petagna andrea</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>GxGwdpWd</t>
+          <t>hM9I17fh</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>idrissi riyad</t>
+          <t>caprari gianluca</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>GxGwdpWd</t>
+          <t>hM9I17fh</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>idrissi riyad</t>
+          <t>caprari gianluca</t>
         </is>
       </c>
       <c r="DB5" t="inlineStr">
         <is>
-          <t>n5TCLpkU</t>
+          <t>txSCnXec</t>
         </is>
       </c>
       <c r="DC5" t="inlineStr">
         <is>
-          <t>cotali matteo</t>
+          <t>maldini daniel</t>
         </is>
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>UkRwQ194</t>
+          <t>f1Ft78yl</t>
         </is>
       </c>
       <c r="DE5" t="inlineStr">
         <is>
-          <t>defrel gregoire</t>
+          <t>gagliardini roberto</t>
         </is>
       </c>
       <c r="DF5" t="inlineStr">
         <is>
-          <t>UkRwQ194</t>
+          <t>f1Ft78yl</t>
         </is>
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>defrel gregoire</t>
+          <t>gagliardini roberto</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>K2oPRv02</t>
+          <t>OrlLWHno</t>
         </is>
       </c>
       <c r="DI5" t="inlineStr">
         <is>
-          <t>palumbo antonio</t>
+          <t>izzo armando</t>
         </is>
       </c>
       <c r="DJ5" t="inlineStr">
         <is>
-          <t>WMM2MKsk</t>
+          <t>0WK0EKMu</t>
         </is>
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>ricci giacomo</t>
+          <t>vignato samuel</t>
         </is>
       </c>
       <c r="DL5" t="inlineStr">
         <is>
-          <t>WMM2MKsk</t>
+          <t>0WK0EKMu</t>
         </is>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>ricci giacomo</t>
+          <t>vignato samuel</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>2DjEKsjr</t>
+          <t>G6Sr2L01</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>dorval mehdi</t>
+          <t>dany mota</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
         <is>
-          <t>lEiQbqRi</t>
+          <t>8t5OxIB9</t>
         </is>
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
-          <t>lasagna kevin</t>
+          <t>pereira pedro</t>
         </is>
       </c>
       <c r="DR5" t="inlineStr">
         <is>
-          <t>lEiQbqRi</t>
+          <t>8t5OxIB9</t>
         </is>
       </c>
       <c r="DS5" t="inlineStr">
         <is>
-          <t>lasagna kevin</t>
+          <t>pereira pedro</t>
         </is>
       </c>
       <c r="DT5" t="inlineStr">
         <is>
-          <t>Q9PDryv2</t>
+          <t>lb7jSwtb</t>
         </is>
       </c>
       <c r="DU5" t="inlineStr">
         <is>
-          <t>novakovich andrija</t>
+          <t>birindelli samuele</t>
         </is>
       </c>
       <c r="DV5" t="inlineStr">
         <is>
-          <t>x4AiZlG7</t>
+          <t>tW6pCCm8</t>
         </is>
       </c>
       <c r="DW5" t="inlineStr">
         <is>
-          <t>favasuli costantino</t>
+          <t>vogliacco alessandro</t>
         </is>
       </c>
       <c r="DX5" t="inlineStr">
         <is>
-          <t>x4AiZlG7</t>
+          <t>tW6pCCm8</t>
         </is>
       </c>
       <c r="DY5" t="inlineStr">
         <is>
-          <t>favasuli costantino</t>
+          <t>vogliacco alessandro</t>
         </is>
       </c>
       <c r="DZ5" t="inlineStr">
         <is>
-          <t>WAWziD2c</t>
+          <t>vgmL526e</t>
         </is>
       </c>
       <c r="EA5" t="inlineStr">
         <is>
-          <t>manzari giacomo</t>
+          <t>bani mattia</t>
         </is>
       </c>
       <c r="EB5" t="inlineStr">
         <is>
-          <t>2DRxNUHG</t>
+          <t>xjWe0TTo</t>
         </is>
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>lulic karlo</t>
+          <t>zanoli alessandro</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>2DRxNUHG</t>
+          <t>xjWe0TTo</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>lulic karlo</t>
+          <t>zanoli alessandro</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>UFsffxn9</t>
+          <t>zLlOcqw4</t>
         </is>
       </c>
       <c r="EG5" t="inlineStr">
         <is>
-          <t>maita mattia</t>
-        </is>
-      </c>
-      <c r="EH5" t="inlineStr"/>
-      <c r="EI5" t="inlineStr"/>
-      <c r="EJ5" t="inlineStr"/>
-      <c r="EK5" t="inlineStr"/>
-      <c r="EL5" t="inlineStr"/>
-      <c r="EM5" t="inlineStr"/>
-      <c r="EN5" t="inlineStr"/>
-      <c r="EO5" t="inlineStr"/>
-      <c r="EP5" t="inlineStr"/>
-      <c r="EQ5" t="inlineStr"/>
-      <c r="ER5" t="inlineStr"/>
-      <c r="ES5" t="inlineStr"/>
-      <c r="ET5" t="inlineStr"/>
-      <c r="EU5" t="inlineStr"/>
-      <c r="EV5" t="inlineStr"/>
-      <c r="EW5" t="inlineStr"/>
+          <t>sabelli stefano</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
+          <t>GGkyU0bT</t>
+        </is>
+      </c>
+      <c r="EI5" t="inlineStr">
+        <is>
+          <t>malinovsky ruslan</t>
+        </is>
+      </c>
+      <c r="EJ5" t="inlineStr">
+        <is>
+          <t>GGkyU0bT</t>
+        </is>
+      </c>
+      <c r="EK5" t="inlineStr">
+        <is>
+          <t>malinovsky ruslan</t>
+        </is>
+      </c>
+      <c r="EL5" t="inlineStr">
+        <is>
+          <t>AazXYT3h</t>
+        </is>
+      </c>
+      <c r="EM5" t="inlineStr">
+        <is>
+          <t>vitinha</t>
+        </is>
+      </c>
+      <c r="EN5" t="inlineStr">
+        <is>
+          <t>Ei7zkE0o</t>
+        </is>
+      </c>
+      <c r="EO5" t="inlineStr">
+        <is>
+          <t>thorsby morten</t>
+        </is>
+      </c>
+      <c r="EP5" t="inlineStr">
+        <is>
+          <t>Ei7zkE0o</t>
+        </is>
+      </c>
+      <c r="EQ5" t="inlineStr">
+        <is>
+          <t>thorsby morten</t>
+        </is>
+      </c>
+      <c r="ER5" t="inlineStr">
+        <is>
+          <t>4InuIizr</t>
+        </is>
+      </c>
+      <c r="ES5" t="inlineStr">
+        <is>
+          <t>badelj milan</t>
+        </is>
+      </c>
+      <c r="ET5" t="inlineStr">
+        <is>
+          <t>CtdcoETk</t>
+        </is>
+      </c>
+      <c r="EU5" t="inlineStr">
+        <is>
+          <t>ekuban caleb</t>
+        </is>
+      </c>
+      <c r="EV5" t="inlineStr">
+        <is>
+          <t>CtdcoETk</t>
+        </is>
+      </c>
+      <c r="EW5" t="inlineStr">
+        <is>
+          <t>ekuban caleb</t>
+        </is>
+      </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t>ChuL5A4p</t>
+          <t>O4qi5hfc</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
         <is>
-          <t>sassi jacopo</t>
+          <t>pinamonti andrea</t>
         </is>
       </c>
       <c r="EZ5" t="inlineStr">
         <is>
-          <t>YgsNSpKb</t>
+          <t>p8mcxZnq</t>
         </is>
       </c>
       <c r="FA5" t="inlineStr">
         <is>
-          <t>sgarbi lorenzo</t>
+          <t>ciurria patrick</t>
         </is>
       </c>
       <c r="FB5" t="inlineStr">
         <is>
-          <t>Msrf6Ec9</t>
+          <t>ENDYjGK9</t>
         </is>
       </c>
       <c r="FC5" t="inlineStr">
         <is>
-          <t>botteghin</t>
+          <t>cragno alessio</t>
         </is>
       </c>
       <c r="FD5" t="inlineStr">
         <is>
-          <t>Msrf6Ec9</t>
+          <t>fTOU6yR2</t>
         </is>
       </c>
       <c r="FE5" t="inlineStr">
         <is>
-          <t>botteghin</t>
+          <t>ankeye david</t>
         </is>
       </c>
       <c r="FF5" t="inlineStr">
         <is>
-          <t>Wv6b1jk0</t>
+          <t>WOffNMWA</t>
         </is>
       </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>gliozzi ettore</t>
+          <t>matturro romero alan</t>
         </is>
       </c>
       <c r="FH5" t="inlineStr">
         <is>
-          <t>YgsNSpKb</t>
+          <t>63jp0ZJd</t>
         </is>
       </c>
       <c r="FI5" t="inlineStr">
         <is>
-          <t>sgarbi lorenzo</t>
-        </is>
-      </c>
-      <c r="FJ5" t="inlineStr">
-        <is>
-          <t>YgsNSpKb</t>
-        </is>
-      </c>
-      <c r="FK5" t="inlineStr">
-        <is>
-          <t>sgarbi lorenzo</t>
-        </is>
-      </c>
+          <t>norton cuffy brooke</t>
+        </is>
+      </c>
+      <c r="FJ5" t="inlineStr"/>
+      <c r="FK5" t="inlineStr"/>
       <c r="FL5" t="inlineStr">
         <is>
-          <t>bFSFG3sT</t>
+          <t>0WK0EKMu</t>
         </is>
       </c>
       <c r="FM5" t="inlineStr">
         <is>
-          <t>olivieri andrea</t>
-        </is>
-      </c>
+          <t>vignato samuel</t>
+        </is>
+      </c>
+      <c r="FN5" t="inlineStr"/>
+      <c r="FO5" t="inlineStr"/>
+      <c r="FP5" t="inlineStr">
+        <is>
+          <t>hfhlvfwf</t>
+        </is>
+      </c>
+      <c r="FQ5" t="inlineStr">
+        <is>
+          <t>machin jose</t>
+        </is>
+      </c>
+      <c r="FR5" t="inlineStr">
+        <is>
+          <t>dbqlLrFU</t>
+        </is>
+      </c>
+      <c r="FS5" t="inlineStr">
+        <is>
+          <t>sensi stefano</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>j5xET4RO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>lezzerini luca</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>d8G4xPEs</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>dickmann lorenzo</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>WluTc7aK</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>cistana andrea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SlzlBsGu</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>adorni davide</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6PM5vQQo</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>jallow alexander</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0OrcBvqE</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>galazzi nicolas</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>SKC8z0LF</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>bisoli dimitri</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>dtE4EsL3</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>verreth matthias</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>UBJZLl4T</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>bertagnoli massimo</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kh4HwK0A</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>borrelli gennaro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>pGN9fQkH</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>olzer giacomo</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0dqCCCd6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>kastrati elhan</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>O4VaVa69</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>carissoni lorenzo</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>KQJr2C6I</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>pavan nicola</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>jiFEodbj</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>angeli matteo</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>IooWgdIk</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>masciangelo edoardo</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>SnRbZOrK</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>amatucci francesco</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>04FCiMFb</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>casolari federico</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>l2Rt2EsD</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>branca simone</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>Q7OEUsLS</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>vita alessio</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>2LoNIGf3</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>rabbi simone</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>K0AtvAAP</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>desogus jacopo</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>Kv1RND3R</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>andrenacci lorenzo</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>zaHOeeSS</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>besaggio michele</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>xC9rbYUF</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>bianchi flavio</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>tGcjYXdg</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>bjarnason birkir</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>bX0itvNd</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>buhagiar trent</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>WIETgwMu</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>corrado niccolo</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>nH4bnBjF</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>fogliata riccardo</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>Czj6Fpfh</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>juric ante matej</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>Ama1rbYr</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>muca zylyf</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>bTRbEf8c</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>nuamah patrick</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>Mw804hef</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>paghera fabrizio</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>OIah8ITR</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>papetti andrea</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>hUTyvgJA</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>cassano claudio</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>EVzPaGzl</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>d alessio francesco</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>424Mngue</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>djibril akim</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>f3UWa8ss</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>magrassi andrea</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>GpcVQVTI</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>maniero luca</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>dbk2r5CD</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>pandolfi luca</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>Q741cgiO</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>ravasio mario</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>I3kYfG62</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>rizza alessio</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>80gdKWOF</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>salvi alessandro</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>SOKhXWeD</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>sottini edoardo</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>2qCcTkgp</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>tessiore andrea</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr"/>
+      <c r="CO6" t="inlineStr"/>
+      <c r="CP6" t="inlineStr"/>
+      <c r="CQ6" t="inlineStr"/>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>zaHOeeSS</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>besaggio michele</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>zaHOeeSS</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>besaggio michele</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>UBJZLl4T</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>bertagnoli massimo</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>Czj6Fpfh</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>juric ante matej</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>Czj6Fpfh</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>juric ante matej</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
+          <t>0OrcBvqE</t>
+        </is>
+      </c>
+      <c r="DC6" t="inlineStr">
+        <is>
+          <t>galazzi nicolas</t>
+        </is>
+      </c>
+      <c r="DD6" t="inlineStr">
+        <is>
+          <t>tGcjYXdg</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>bjarnason birkir</t>
+        </is>
+      </c>
+      <c r="DF6" t="inlineStr">
+        <is>
+          <t>tGcjYXdg</t>
+        </is>
+      </c>
+      <c r="DG6" t="inlineStr">
+        <is>
+          <t>bjarnason birkir</t>
+        </is>
+      </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>pGN9fQkH</t>
+        </is>
+      </c>
+      <c r="DI6" t="inlineStr">
+        <is>
+          <t>olzer giacomo</t>
+        </is>
+      </c>
+      <c r="DJ6" t="inlineStr">
+        <is>
+          <t>WIETgwMu</t>
+        </is>
+      </c>
+      <c r="DK6" t="inlineStr">
+        <is>
+          <t>corrado niccolo</t>
+        </is>
+      </c>
+      <c r="DL6" t="inlineStr">
+        <is>
+          <t>WIETgwMu</t>
+        </is>
+      </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>corrado niccolo</t>
+        </is>
+      </c>
+      <c r="DN6" t="inlineStr">
+        <is>
+          <t>Kh4HwK0A</t>
+        </is>
+      </c>
+      <c r="DO6" t="inlineStr">
+        <is>
+          <t>borrelli gennaro</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>xC9rbYUF</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
+          <t>bianchi flavio</t>
+        </is>
+      </c>
+      <c r="DR6" t="inlineStr">
+        <is>
+          <t>xC9rbYUF</t>
+        </is>
+      </c>
+      <c r="DS6" t="inlineStr">
+        <is>
+          <t>bianchi flavio</t>
+        </is>
+      </c>
+      <c r="DT6" t="inlineStr">
+        <is>
+          <t>d8G4xPEs</t>
+        </is>
+      </c>
+      <c r="DU6" t="inlineStr">
+        <is>
+          <t>dickmann lorenzo</t>
+        </is>
+      </c>
+      <c r="DV6" t="inlineStr">
+        <is>
+          <t>80gdKWOF</t>
+        </is>
+      </c>
+      <c r="DW6" t="inlineStr">
+        <is>
+          <t>salvi alessandro</t>
+        </is>
+      </c>
+      <c r="DX6" t="inlineStr">
+        <is>
+          <t>80gdKWOF</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>salvi alessandro</t>
+        </is>
+      </c>
+      <c r="DZ6" t="inlineStr">
+        <is>
+          <t>K0AtvAAP</t>
+        </is>
+      </c>
+      <c r="EA6" t="inlineStr">
+        <is>
+          <t>desogus jacopo</t>
+        </is>
+      </c>
+      <c r="EB6" t="inlineStr">
+        <is>
+          <t>SOKhXWeD</t>
+        </is>
+      </c>
+      <c r="EC6" t="inlineStr">
+        <is>
+          <t>sottini edoardo</t>
+        </is>
+      </c>
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t>SOKhXWeD</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t>sottini edoardo</t>
+        </is>
+      </c>
+      <c r="EF6" t="inlineStr">
+        <is>
+          <t>IooWgdIk</t>
+        </is>
+      </c>
+      <c r="EG6" t="inlineStr">
+        <is>
+          <t>masciangelo edoardo</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t>Q741cgiO</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>ravasio mario</t>
+        </is>
+      </c>
+      <c r="EJ6" t="inlineStr">
+        <is>
+          <t>Q741cgiO</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr">
+        <is>
+          <t>ravasio mario</t>
+        </is>
+      </c>
+      <c r="EL6" t="inlineStr">
+        <is>
+          <t>2LoNIGf3</t>
+        </is>
+      </c>
+      <c r="EM6" t="inlineStr">
+        <is>
+          <t>rabbi simone</t>
+        </is>
+      </c>
+      <c r="EN6" t="inlineStr">
+        <is>
+          <t>EVzPaGzl</t>
+        </is>
+      </c>
+      <c r="EO6" t="inlineStr">
+        <is>
+          <t>d alessio francesco</t>
+        </is>
+      </c>
+      <c r="EP6" t="inlineStr">
+        <is>
+          <t>EVzPaGzl</t>
+        </is>
+      </c>
+      <c r="EQ6" t="inlineStr">
+        <is>
+          <t>d alessio francesco</t>
+        </is>
+      </c>
+      <c r="ER6" t="inlineStr">
+        <is>
+          <t>l2Rt2EsD</t>
+        </is>
+      </c>
+      <c r="ES6" t="inlineStr">
+        <is>
+          <t>branca simone</t>
+        </is>
+      </c>
+      <c r="ET6" t="inlineStr"/>
+      <c r="EU6" t="inlineStr"/>
+      <c r="EV6" t="inlineStr"/>
+      <c r="EW6" t="inlineStr"/>
+      <c r="EX6" t="inlineStr"/>
+      <c r="EY6" t="inlineStr"/>
+      <c r="EZ6" t="inlineStr"/>
+      <c r="FA6" t="inlineStr"/>
+      <c r="FB6" t="inlineStr"/>
+      <c r="FC6" t="inlineStr"/>
+      <c r="FD6" t="inlineStr"/>
+      <c r="FE6" t="inlineStr"/>
+      <c r="FF6" t="inlineStr"/>
+      <c r="FG6" t="inlineStr"/>
+      <c r="FH6" t="inlineStr"/>
+      <c r="FI6" t="inlineStr"/>
+      <c r="FJ6" t="inlineStr"/>
+      <c r="FK6" t="inlineStr"/>
+      <c r="FL6" t="inlineStr"/>
+      <c r="FM6" t="inlineStr"/>
+      <c r="FN6" t="inlineStr"/>
+      <c r="FO6" t="inlineStr"/>
+      <c r="FP6" t="inlineStr"/>
+      <c r="FQ6" t="inlineStr"/>
+      <c r="FR6" t="inlineStr"/>
+      <c r="FS6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pEUDpBZR</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>fulignati andrea</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>QD7M0ATr</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>antov valentin</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>rZo8WmF7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ravanelli luca</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>8hcuiE2b</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>bianchetti matteo</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>j7T2rzph</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>barbieri tommaso</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AoykjoMB</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>pickel charles</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4KEjxptI</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>castagnetti michele</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>zX8VztZq</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>vandeputte jari</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>xIUCaSh4</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>sernicola leonardo</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>pEYPJXO8</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>bonazzoli federico</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>MeskQr4l</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>de luca manuel</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>QJM49URT</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>bleve marco</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>bmwzhd5k</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>coppolaro mauro</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>GAOlIzwG</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>illanes julian</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>tMqmOicE</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>imperiale marco</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>AT5jymNl</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>zanon simone</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>ddvz0tcQ</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>capezzi leonardo</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>dne3gePB</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>schiavi nicolas</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>hn4q1pAA</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>cicconi manuel</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>zPp0s4d5</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>panico giuseppe</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>C0IePhv1</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>finotto mattia</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>t6Pgd1eg</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>zuelli emanuele</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>GCL4UYe3</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>falletti cesar</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>xpN4ICmj</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>johnsen dennis</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>fLyWlO5j</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>lochoshvili luka</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>KI9lXC0P</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>majer zan</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>UspinGse</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>milanese tommaso</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>r3yChj3j</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>moretti lorenzo</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>tdJlhP53</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>nasti marco</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>pdJ2qg8l</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>quagliata giacomo</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>8IlcJpOd</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>saro gianluca</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>QunHCDU2</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>tsadjout frank</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>vJItNu2r</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>vazquez franco</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>rglBThG1</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>zanimacchia luca</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>SEwp6Uhi</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>belloni niccolo</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>dfo0RTSJ</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>capello alessandro</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>z92952s6</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>cerri leonardo</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>Kd5zFbti</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>cherubini luigi</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>t8Q8Iav7</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>della latta simone</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>AgoFEXP9</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>giovane samuel</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>hrU2YLMp</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>mazzini stefano</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>Ak6MHnNb</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>motolese mattia</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>xM8qrrze</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>oliana filippo</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>xhitsOAj</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>palermo ryduan</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>hpPoJ5jN</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>palmieri riccardo</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>bV4825W6</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>scheffer mateo</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr"/>
+      <c r="CQ7" t="inlineStr"/>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>vJItNu2r</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
+        <is>
+          <t>vazquez franco</t>
+        </is>
+      </c>
+      <c r="CT7" t="inlineStr">
+        <is>
+          <t>vJItNu2r</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>vazquez franco</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>pEYPJXO8</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>bonazzoli federico</t>
+        </is>
+      </c>
+      <c r="CX7" t="inlineStr">
+        <is>
+          <t>xpN4ICmj</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>johnsen dennis</t>
+        </is>
+      </c>
+      <c r="CZ7" t="inlineStr">
+        <is>
+          <t>xpN4ICmj</t>
+        </is>
+      </c>
+      <c r="DA7" t="inlineStr">
+        <is>
+          <t>johnsen dennis</t>
+        </is>
+      </c>
+      <c r="DB7" t="inlineStr">
+        <is>
+          <t>zX8VztZq</t>
+        </is>
+      </c>
+      <c r="DC7" t="inlineStr">
+        <is>
+          <t>vandeputte jari</t>
+        </is>
+      </c>
+      <c r="DD7" t="inlineStr">
+        <is>
+          <t>tdJlhP53</t>
+        </is>
+      </c>
+      <c r="DE7" t="inlineStr">
+        <is>
+          <t>nasti marco</t>
+        </is>
+      </c>
+      <c r="DF7" t="inlineStr">
+        <is>
+          <t>tdJlhP53</t>
+        </is>
+      </c>
+      <c r="DG7" t="inlineStr">
+        <is>
+          <t>nasti marco</t>
+        </is>
+      </c>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>MeskQr4l</t>
+        </is>
+      </c>
+      <c r="DI7" t="inlineStr">
+        <is>
+          <t>de luca manuel</t>
+        </is>
+      </c>
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>rglBThG1</t>
+        </is>
+      </c>
+      <c r="DK7" t="inlineStr">
+        <is>
+          <t>zanimacchia luca</t>
+        </is>
+      </c>
+      <c r="DL7" t="inlineStr">
+        <is>
+          <t>rglBThG1</t>
+        </is>
+      </c>
+      <c r="DM7" t="inlineStr">
+        <is>
+          <t>zanimacchia luca</t>
+        </is>
+      </c>
+      <c r="DN7" t="inlineStr">
+        <is>
+          <t>j7T2rzph</t>
+        </is>
+      </c>
+      <c r="DO7" t="inlineStr">
+        <is>
+          <t>barbieri tommaso</t>
+        </is>
+      </c>
+      <c r="DP7" t="inlineStr">
+        <is>
+          <t>fLyWlO5j</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
+          <t>lochoshvili luka</t>
+        </is>
+      </c>
+      <c r="DR7" t="inlineStr">
+        <is>
+          <t>fLyWlO5j</t>
+        </is>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
+          <t>lochoshvili luka</t>
+        </is>
+      </c>
+      <c r="DT7" t="inlineStr">
+        <is>
+          <t>QD7M0ATr</t>
+        </is>
+      </c>
+      <c r="DU7" t="inlineStr">
+        <is>
+          <t>antov valentin</t>
+        </is>
+      </c>
+      <c r="DV7" t="inlineStr">
+        <is>
+          <t>hpPoJ5jN</t>
+        </is>
+      </c>
+      <c r="DW7" t="inlineStr">
+        <is>
+          <t>palmieri riccardo</t>
+        </is>
+      </c>
+      <c r="DX7" t="inlineStr">
+        <is>
+          <t>hpPoJ5jN</t>
+        </is>
+      </c>
+      <c r="DY7" t="inlineStr">
+        <is>
+          <t>palmieri riccardo</t>
+        </is>
+      </c>
+      <c r="DZ7" t="inlineStr">
+        <is>
+          <t>t6Pgd1eg</t>
+        </is>
+      </c>
+      <c r="EA7" t="inlineStr">
+        <is>
+          <t>zuelli emanuele</t>
+        </is>
+      </c>
+      <c r="EB7" t="inlineStr">
+        <is>
+          <t>AgoFEXP9</t>
+        </is>
+      </c>
+      <c r="EC7" t="inlineStr">
+        <is>
+          <t>giovane samuel</t>
+        </is>
+      </c>
+      <c r="ED7" t="inlineStr">
+        <is>
+          <t>AgoFEXP9</t>
+        </is>
+      </c>
+      <c r="EE7" t="inlineStr">
+        <is>
+          <t>giovane samuel</t>
+        </is>
+      </c>
+      <c r="EF7" t="inlineStr">
+        <is>
+          <t>dne3gePB</t>
+        </is>
+      </c>
+      <c r="EG7" t="inlineStr">
+        <is>
+          <t>schiavi nicolas</t>
+        </is>
+      </c>
+      <c r="EH7" t="inlineStr">
+        <is>
+          <t>SEwp6Uhi</t>
+        </is>
+      </c>
+      <c r="EI7" t="inlineStr">
+        <is>
+          <t>belloni niccolo</t>
+        </is>
+      </c>
+      <c r="EJ7" t="inlineStr">
+        <is>
+          <t>SEwp6Uhi</t>
+        </is>
+      </c>
+      <c r="EK7" t="inlineStr">
+        <is>
+          <t>belloni niccolo</t>
+        </is>
+      </c>
+      <c r="EL7" t="inlineStr">
+        <is>
+          <t>hn4q1pAA</t>
+        </is>
+      </c>
+      <c r="EM7" t="inlineStr">
+        <is>
+          <t>cicconi manuel</t>
+        </is>
+      </c>
+      <c r="EN7" t="inlineStr">
+        <is>
+          <t>dfo0RTSJ</t>
+        </is>
+      </c>
+      <c r="EO7" t="inlineStr">
+        <is>
+          <t>capello alessandro</t>
+        </is>
+      </c>
+      <c r="EP7" t="inlineStr">
+        <is>
+          <t>dfo0RTSJ</t>
+        </is>
+      </c>
+      <c r="EQ7" t="inlineStr">
+        <is>
+          <t>capello alessandro</t>
+        </is>
+      </c>
+      <c r="ER7" t="inlineStr">
+        <is>
+          <t>ddvz0tcQ</t>
+        </is>
+      </c>
+      <c r="ES7" t="inlineStr">
+        <is>
+          <t>capezzi leonardo</t>
+        </is>
+      </c>
+      <c r="ET7" t="inlineStr">
+        <is>
+          <t>z92952s6</t>
+        </is>
+      </c>
+      <c r="EU7" t="inlineStr">
+        <is>
+          <t>cerri leonardo</t>
+        </is>
+      </c>
+      <c r="EV7" t="inlineStr">
+        <is>
+          <t>z92952s6</t>
+        </is>
+      </c>
+      <c r="EW7" t="inlineStr">
+        <is>
+          <t>cerri leonardo</t>
+        </is>
+      </c>
+      <c r="EX7" t="inlineStr">
+        <is>
+          <t>C0IePhv1</t>
+        </is>
+      </c>
+      <c r="EY7" t="inlineStr">
+        <is>
+          <t>finotto mattia</t>
+        </is>
+      </c>
+      <c r="EZ7" t="inlineStr"/>
+      <c r="FA7" t="inlineStr"/>
+      <c r="FB7" t="inlineStr"/>
+      <c r="FC7" t="inlineStr"/>
+      <c r="FD7" t="inlineStr"/>
+      <c r="FE7" t="inlineStr"/>
+      <c r="FF7" t="inlineStr"/>
+      <c r="FG7" t="inlineStr"/>
+      <c r="FH7" t="inlineStr"/>
+      <c r="FI7" t="inlineStr"/>
+      <c r="FJ7" t="inlineStr"/>
+      <c r="FK7" t="inlineStr"/>
+      <c r="FL7" t="inlineStr"/>
+      <c r="FM7" t="inlineStr"/>
+      <c r="FN7" t="inlineStr"/>
+      <c r="FO7" t="inlineStr"/>
+      <c r="FP7" t="inlineStr"/>
+      <c r="FQ7" t="inlineStr"/>
+      <c r="FR7" t="inlineStr"/>
+      <c r="FS7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>hEY0fdTF</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>semper adrian</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>hQKJwYnd</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>canestrelli simone</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>xrpkAADs</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>caracciolo antonio</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>hrJODeQE</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>bonfanti giovanni</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>hYIzCDnT</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>toure idrissa</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>S4Gdo5p3</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>piccinini gabriele</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>IeO9PQjK</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>marin marius</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>nyOeW0BU</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>beruatto pietro</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>6uk6H0Ai</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>leris mehdi</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>zFFYexZK</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>moreo stefano</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>n3dSutCc</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>tramoni matteo</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>bVXYRoIt</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>desplanches sebastiano</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>WSOBy5mn</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>diakite salim</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>MqNVQa4o</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>nedelcearu ionut</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>MiTDJFqG</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>nikolaou dimitrios</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>SzFjYRlO</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>pierozzi niccolo</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>rLETyaHe</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>saric dario</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>6q1EW3gj</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>blin alexis</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>44OHk9di</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>ranocchia filippo</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>QRxD5fN5</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>insigne roberto</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>jJFZiKyI</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>di francesco federico</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>xAQAwbhk</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>brunori matteo</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>ANXh14xc</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>angori samuele</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>pr02pCCG</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>arena alessandro</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>dGAt06R5</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>bonfanti nicholas</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>dMiNmDpr</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>calabresi arturo</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>CYcsJc7H</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>hojholt malthe</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>pSDZ73wA</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>jevsenak zan</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>trNqVCBI</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>loria leonardo</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>hA80raLj</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>mlakar jan</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>ULMctLS6</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>nicolas andrade</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>OnR1j6mM</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>raychev adrian</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>tQ9LN1fh</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>rus adrian</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>xhLRqrX3</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>vignato emanuel</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>jXsDx65M</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>appuah stredair</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>p6lid052</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>buttaro alessio</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>dIqrhHoE</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>ceccaroni pietro</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>8SAIZdh5</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>cutrona francesco</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>fivMxYck</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>di mariano francesco</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>AcX8a9pK</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>gomes claudio</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>Slv0QNjF</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>henry thomas</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>hIreZGmE</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>hansen kristoffer</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>tz6uZNmt</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>nespola manfredi</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>S0zo50w7</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>peda patryk</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>d8ybAOqJ</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>vasic vasic</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>EPCv63wE</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>verre valerio</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr"/>
+      <c r="CQ8" t="inlineStr"/>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>ANXh14xc</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>angori samuele</t>
+        </is>
+      </c>
+      <c r="CT8" t="inlineStr">
+        <is>
+          <t>ANXh14xc</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>angori samuele</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>nyOeW0BU</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>beruatto pietro</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>dGAt06R5</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>bonfanti nicholas</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>dGAt06R5</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>bonfanti nicholas</t>
+        </is>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
+          <t>hYIzCDnT</t>
+        </is>
+      </c>
+      <c r="DC8" t="inlineStr">
+        <is>
+          <t>toure idrissa</t>
+        </is>
+      </c>
+      <c r="DD8" t="inlineStr">
+        <is>
+          <t>CYcsJc7H</t>
+        </is>
+      </c>
+      <c r="DE8" t="inlineStr">
+        <is>
+          <t>hojholt malthe</t>
+        </is>
+      </c>
+      <c r="DF8" t="inlineStr">
+        <is>
+          <t>CYcsJc7H</t>
+        </is>
+      </c>
+      <c r="DG8" t="inlineStr">
+        <is>
+          <t>hojholt malthe</t>
+        </is>
+      </c>
+      <c r="DH8" t="inlineStr">
+        <is>
+          <t>n3dSutCc</t>
+        </is>
+      </c>
+      <c r="DI8" t="inlineStr">
+        <is>
+          <t>tramoni matteo</t>
+        </is>
+      </c>
+      <c r="DJ8" t="inlineStr">
+        <is>
+          <t>dMiNmDpr</t>
+        </is>
+      </c>
+      <c r="DK8" t="inlineStr">
+        <is>
+          <t>calabresi arturo</t>
+        </is>
+      </c>
+      <c r="DL8" t="inlineStr">
+        <is>
+          <t>dMiNmDpr</t>
+        </is>
+      </c>
+      <c r="DM8" t="inlineStr">
+        <is>
+          <t>calabresi arturo</t>
+        </is>
+      </c>
+      <c r="DN8" t="inlineStr">
+        <is>
+          <t>6uk6H0Ai</t>
+        </is>
+      </c>
+      <c r="DO8" t="inlineStr">
+        <is>
+          <t>leris mehdi</t>
+        </is>
+      </c>
+      <c r="DP8" t="inlineStr">
+        <is>
+          <t>xhLRqrX3</t>
+        </is>
+      </c>
+      <c r="DQ8" t="inlineStr">
+        <is>
+          <t>vignato emanuel</t>
+        </is>
+      </c>
+      <c r="DR8" t="inlineStr">
+        <is>
+          <t>xhLRqrX3</t>
+        </is>
+      </c>
+      <c r="DS8" t="inlineStr">
+        <is>
+          <t>vignato emanuel</t>
+        </is>
+      </c>
+      <c r="DT8" t="inlineStr">
+        <is>
+          <t>zFFYexZK</t>
+        </is>
+      </c>
+      <c r="DU8" t="inlineStr">
+        <is>
+          <t>moreo stefano</t>
+        </is>
+      </c>
+      <c r="DV8" t="inlineStr">
+        <is>
+          <t>d8ybAOqJ</t>
+        </is>
+      </c>
+      <c r="DW8" t="inlineStr">
+        <is>
+          <t>vasic vasic</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>d8ybAOqJ</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>vasic vasic</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>QRxD5fN5</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>insigne roberto</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>S0zo50w7</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>peda patryk</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr">
+        <is>
+          <t>S0zo50w7</t>
+        </is>
+      </c>
+      <c r="EE8" t="inlineStr">
+        <is>
+          <t>peda patryk</t>
+        </is>
+      </c>
+      <c r="EF8" t="inlineStr">
+        <is>
+          <t>MqNVQa4o</t>
+        </is>
+      </c>
+      <c r="EG8" t="inlineStr">
+        <is>
+          <t>nedelcearu ionut</t>
+        </is>
+      </c>
+      <c r="EH8" t="inlineStr">
+        <is>
+          <t>Slv0QNjF</t>
+        </is>
+      </c>
+      <c r="EI8" t="inlineStr">
+        <is>
+          <t>henry thomas</t>
+        </is>
+      </c>
+      <c r="EJ8" t="inlineStr">
+        <is>
+          <t>Slv0QNjF</t>
+        </is>
+      </c>
+      <c r="EK8" t="inlineStr">
+        <is>
+          <t>henry thomas</t>
+        </is>
+      </c>
+      <c r="EL8" t="inlineStr">
+        <is>
+          <t>jJFZiKyI</t>
+        </is>
+      </c>
+      <c r="EM8" t="inlineStr">
+        <is>
+          <t>di francesco federico</t>
+        </is>
+      </c>
+      <c r="EN8" t="inlineStr">
+        <is>
+          <t>AcX8a9pK</t>
+        </is>
+      </c>
+      <c r="EO8" t="inlineStr">
+        <is>
+          <t>gomes claudio</t>
+        </is>
+      </c>
+      <c r="EP8" t="inlineStr">
+        <is>
+          <t>AcX8a9pK</t>
+        </is>
+      </c>
+      <c r="EQ8" t="inlineStr">
+        <is>
+          <t>gomes claudio</t>
+        </is>
+      </c>
+      <c r="ER8" t="inlineStr">
+        <is>
+          <t>rLETyaHe</t>
+        </is>
+      </c>
+      <c r="ES8" t="inlineStr">
+        <is>
+          <t>saric dario</t>
+        </is>
+      </c>
+      <c r="ET8" t="inlineStr">
+        <is>
+          <t>hIreZGmE</t>
+        </is>
+      </c>
+      <c r="EU8" t="inlineStr">
+        <is>
+          <t>hansen kristoffer</t>
+        </is>
+      </c>
+      <c r="EV8" t="inlineStr">
+        <is>
+          <t>hIreZGmE</t>
+        </is>
+      </c>
+      <c r="EW8" t="inlineStr">
+        <is>
+          <t>hansen kristoffer</t>
+        </is>
+      </c>
+      <c r="EX8" t="inlineStr">
+        <is>
+          <t>SzFjYRlO</t>
+        </is>
+      </c>
+      <c r="EY8" t="inlineStr">
+        <is>
+          <t>pierozzi niccolo</t>
+        </is>
+      </c>
+      <c r="EZ8" t="inlineStr"/>
+      <c r="FA8" t="inlineStr"/>
+      <c r="FB8" t="inlineStr"/>
+      <c r="FC8" t="inlineStr"/>
+      <c r="FD8" t="inlineStr"/>
+      <c r="FE8" t="inlineStr"/>
+      <c r="FF8" t="inlineStr"/>
+      <c r="FG8" t="inlineStr"/>
+      <c r="FH8" t="inlineStr"/>
+      <c r="FI8" t="inlineStr"/>
+      <c r="FJ8" t="inlineStr"/>
+      <c r="FK8" t="inlineStr"/>
+      <c r="FL8" t="inlineStr"/>
+      <c r="FM8" t="inlineStr"/>
+      <c r="FN8" t="inlineStr"/>
+      <c r="FO8" t="inlineStr"/>
+      <c r="FP8" t="inlineStr"/>
+      <c r="FQ8" t="inlineStr"/>
+      <c r="FR8" t="inlineStr"/>
+      <c r="FS8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fTynsh49</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ghidotti simone</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>rmvDqIY7</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>bereszynski bartosz</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Q7fl3yYg</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>romagnoli simone</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>xSd0xhgK</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>vulikic stipe</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dpMPW6zh</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>venuti lorenzo</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>GKxv62wr</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>akinsanmiro ebenezer</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>6qpSLKkb</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>yepes gerard</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>dpI0AACN</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>bellemo alessandro</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>IooZNoIP</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>giordano simone</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>tAqEMK0a</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>coda massimo</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>WpuYwQHd</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>tutino gennaro</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6wVqSqO0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>bardi francesco</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>bkpO1UAs</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>fiamozzi riccardo</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>baFaIqPm</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>meroni andrea</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Ug0GqtE0</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>rozzio paolo</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>08RKxF9J</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>libutti lorenzo</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>AwsyawQ1</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>portanova manolo</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>67w6mUGh</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>reinhart tobias</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>jumC8deM</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>sersanti alessandro</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0bwMG5SF</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>vergara antonio</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>QqCsQcU5</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>gondo cedric</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>UZADb54K</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>maggio matteo</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>6XMPoYMf</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>barreca antonio</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>2PcLSPHS</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>benedetti leonardo</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>rDl88SSs</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>depaoli fabio</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>p6nuqtZG</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>ferrari alex</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>tp0ewToo</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>girelli stefano</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>KrODGzyo</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>kasami pajtim</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>hxFdb12n</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>la gumina antonio</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>x2S7DucC</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>meulensteen melle</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>p49C8BCr</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>sekulov nikola</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>jeW6mAhJ</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>veroli davide</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>tUw2S8Tb</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>vieira ronaldo</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>6B2hAjdT</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>vismara paolo</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>46jUu380</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>cavallini giacomo</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>lfpEEa5J</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>cigarini luca</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>SpsFliY4</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>ignacchiti lorenzo</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>ATMse0OQ</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>motta edoardo</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>8WxIdbec</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>nahounou yannis</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>ALmM5Mbm</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>sampirisi mario</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>UenvOQL5</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>sposito alex</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>dh1QqfhO</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>stramaccioni diego</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>ziYCoya3</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>stulac leo</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>zPvo9nZ2</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>urso oliver</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>d0WK1pb6</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>vido luca</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr"/>
+      <c r="CO9" t="inlineStr"/>
+      <c r="CP9" t="inlineStr"/>
+      <c r="CQ9" t="inlineStr"/>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>6B2hAjdT</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>vismara paolo</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
+          <t>6B2hAjdT</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>vismara paolo</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>fTynsh49</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>ghidotti simone</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>rDl88SSs</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>depaoli fabio</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>rDl88SSs</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>depaoli fabio</t>
+        </is>
+      </c>
+      <c r="DB9" t="inlineStr">
+        <is>
+          <t>IooZNoIP</t>
+        </is>
+      </c>
+      <c r="DC9" t="inlineStr">
+        <is>
+          <t>giordano simone</t>
+        </is>
+      </c>
+      <c r="DD9" t="inlineStr">
+        <is>
+          <t>2PcLSPHS</t>
+        </is>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
+          <t>benedetti leonardo</t>
+        </is>
+      </c>
+      <c r="DF9" t="inlineStr">
+        <is>
+          <t>2PcLSPHS</t>
+        </is>
+      </c>
+      <c r="DG9" t="inlineStr">
+        <is>
+          <t>benedetti leonardo</t>
+        </is>
+      </c>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>GKxv62wr</t>
+        </is>
+      </c>
+      <c r="DI9" t="inlineStr">
+        <is>
+          <t>akinsanmiro ebenezer</t>
+        </is>
+      </c>
+      <c r="DJ9" t="inlineStr">
+        <is>
+          <t>p49C8BCr</t>
+        </is>
+      </c>
+      <c r="DK9" t="inlineStr">
+        <is>
+          <t>sekulov nikola</t>
+        </is>
+      </c>
+      <c r="DL9" t="inlineStr">
+        <is>
+          <t>p49C8BCr</t>
+        </is>
+      </c>
+      <c r="DM9" t="inlineStr">
+        <is>
+          <t>sekulov nikola</t>
+        </is>
+      </c>
+      <c r="DN9" t="inlineStr">
+        <is>
+          <t>dpI0AACN</t>
+        </is>
+      </c>
+      <c r="DO9" t="inlineStr">
+        <is>
+          <t>bellemo alessandro</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr">
+        <is>
+          <t>tUw2S8Tb</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
+        <is>
+          <t>vieira ronaldo</t>
+        </is>
+      </c>
+      <c r="DR9" t="inlineStr">
+        <is>
+          <t>tUw2S8Tb</t>
+        </is>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
+          <t>vieira ronaldo</t>
+        </is>
+      </c>
+      <c r="DT9" t="inlineStr">
+        <is>
+          <t>WpuYwQHd</t>
+        </is>
+      </c>
+      <c r="DU9" t="inlineStr">
+        <is>
+          <t>tutino gennaro</t>
+        </is>
+      </c>
+      <c r="DV9" t="inlineStr">
+        <is>
+          <t>SpsFliY4</t>
+        </is>
+      </c>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>ignacchiti lorenzo</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>SpsFliY4</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>ignacchiti lorenzo</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>UZADb54K</t>
+        </is>
+      </c>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>maggio matteo</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>lfpEEa5J</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>cigarini luca</t>
+        </is>
+      </c>
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t>lfpEEa5J</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>cigarini luca</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr">
+        <is>
+          <t>AwsyawQ1</t>
+        </is>
+      </c>
+      <c r="EG9" t="inlineStr">
+        <is>
+          <t>portanova manolo</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
+          <t>d0WK1pb6</t>
+        </is>
+      </c>
+      <c r="EI9" t="inlineStr">
+        <is>
+          <t>vido luca</t>
+        </is>
+      </c>
+      <c r="EJ9" t="inlineStr">
+        <is>
+          <t>d0WK1pb6</t>
+        </is>
+      </c>
+      <c r="EK9" t="inlineStr">
+        <is>
+          <t>vido luca</t>
+        </is>
+      </c>
+      <c r="EL9" t="inlineStr">
+        <is>
+          <t>QqCsQcU5</t>
+        </is>
+      </c>
+      <c r="EM9" t="inlineStr">
+        <is>
+          <t>gondo cedric</t>
+        </is>
+      </c>
+      <c r="EN9" t="inlineStr">
+        <is>
+          <t>ALmM5Mbm</t>
+        </is>
+      </c>
+      <c r="EO9" t="inlineStr">
+        <is>
+          <t>sampirisi mario</t>
+        </is>
+      </c>
+      <c r="EP9" t="inlineStr">
+        <is>
+          <t>ALmM5Mbm</t>
+        </is>
+      </c>
+      <c r="EQ9" t="inlineStr">
+        <is>
+          <t>sampirisi mario</t>
+        </is>
+      </c>
+      <c r="ER9" t="inlineStr">
+        <is>
+          <t>jumC8deM</t>
+        </is>
+      </c>
+      <c r="ES9" t="inlineStr">
+        <is>
+          <t>sersanti alessandro</t>
+        </is>
+      </c>
+      <c r="ET9" t="inlineStr"/>
+      <c r="EU9" t="inlineStr"/>
+      <c r="EV9" t="inlineStr"/>
+      <c r="EW9" t="inlineStr"/>
+      <c r="EX9" t="inlineStr"/>
+      <c r="EY9" t="inlineStr"/>
+      <c r="EZ9" t="inlineStr"/>
+      <c r="FA9" t="inlineStr"/>
+      <c r="FB9" t="inlineStr"/>
+      <c r="FC9" t="inlineStr"/>
+      <c r="FD9" t="inlineStr"/>
+      <c r="FE9" t="inlineStr"/>
+      <c r="FF9" t="inlineStr"/>
+      <c r="FG9" t="inlineStr"/>
+      <c r="FH9" t="inlineStr"/>
+      <c r="FI9" t="inlineStr"/>
+      <c r="FJ9" t="inlineStr"/>
+      <c r="FK9" t="inlineStr"/>
+      <c r="FL9" t="inlineStr"/>
+      <c r="FM9" t="inlineStr"/>
+      <c r="FN9" t="inlineStr"/>
+      <c r="FO9" t="inlineStr"/>
+      <c r="FP9" t="inlineStr"/>
+      <c r="FQ9" t="inlineStr"/>
+      <c r="FR9" t="inlineStr"/>
+      <c r="FS9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>d2BR3Upb</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>satalino giacomo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>IJwHBntK</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>paz yeferson</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>M5l0hplp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>odenthal cas</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ILuvGx81</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>romagna filippo</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dQ1Evunq</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>doig josh</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>retVSWHL</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>kumi justin</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>jPrEU8Tr</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>boloca daniel</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>6392aYqP</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>caligara fabrizio</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4Of5akc5</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>antiste janis</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Q1wMNrxU</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>bajrami nedim</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>f3tdpb62</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>mulattieri samuele</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>tlSr8Yco</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>pisseri matteo</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>xIKq8Lhb</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>curto marco</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2k9zUaAa</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ciofi andrea</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>EBw91VL5</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>mangraviti massimiliano</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>pnI8ZjZr</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>ceesay joseph</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>hjLa97a7</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>berti tommaso</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>8vhUYvNN</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>calo giacomo</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>n7piqBuG</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>bastoni simone</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>tnsZtqGu</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>donnarumma daniele</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>4MMcPxki</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>shpendi cristian</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>WrbFYwR8</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>kargbo augustus</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>2FVwCcx2</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>bruno kevin</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>2ZalbHv9</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>knezovic borna</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>z5gWeVo8</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>leone kevin</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>t4NSHrlh</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>lipani luca</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>QiWQsVa5</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>lovato matteo</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>KpyQQSsm</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>miranda kevin</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>UmzKM5tM</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>missori filippo</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>fDRMwkTQ</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>moro luca</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>nodnKnAs</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>obiang pedro</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>C0qz46Jj</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>pieragnolo edoardo</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>MLQScsMb</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>russo alessandro</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>prHV7Xpt</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>russo flavio</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>2qAN5836</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>adamo emanuele</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>ADBJ4OrH</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>antonucci mirko</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>nmdCa7Ds</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>celia raffaele</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>fiJmaURn</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>coveri valentino</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>hrgu7eZM</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>francesconi matteo</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>dG0Lm68C</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>klinsmann jonathan</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>GtGjeC0b</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>manetti giulio</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>2J6W9OsT</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>piacentini matteo</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>8CpA5o79</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>pieraccini simone</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>rwjsRUCI</t>
+        </is>
+      </c>
+      <c r="CK10" t="inlineStr">
+        <is>
+          <t>siano alessandro</t>
+        </is>
+      </c>
+      <c r="CL10" t="inlineStr"/>
+      <c r="CM10" t="inlineStr"/>
+      <c r="CN10" t="inlineStr"/>
+      <c r="CO10" t="inlineStr"/>
+      <c r="CP10" t="inlineStr"/>
+      <c r="CQ10" t="inlineStr"/>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>QiWQsVa5</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>lovato matteo</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr">
+        <is>
+          <t>QiWQsVa5</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>lovato matteo</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>IJwHBntK</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>paz yeferson</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>prHV7Xpt</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>russo flavio</t>
+        </is>
+      </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>prHV7Xpt</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>russo flavio</t>
+        </is>
+      </c>
+      <c r="DB10" t="inlineStr">
+        <is>
+          <t>Q1wMNrxU</t>
+        </is>
+      </c>
+      <c r="DC10" t="inlineStr">
+        <is>
+          <t>bajrami nedim</t>
+        </is>
+      </c>
+      <c r="DD10" t="inlineStr">
+        <is>
+          <t>nodnKnAs</t>
+        </is>
+      </c>
+      <c r="DE10" t="inlineStr">
+        <is>
+          <t>obiang pedro</t>
+        </is>
+      </c>
+      <c r="DF10" t="inlineStr">
+        <is>
+          <t>nodnKnAs</t>
+        </is>
+      </c>
+      <c r="DG10" t="inlineStr">
+        <is>
+          <t>obiang pedro</t>
+        </is>
+      </c>
+      <c r="DH10" t="inlineStr">
+        <is>
+          <t>6392aYqP</t>
+        </is>
+      </c>
+      <c r="DI10" t="inlineStr">
+        <is>
+          <t>caligara fabrizio</t>
+        </is>
+      </c>
+      <c r="DJ10" t="inlineStr">
+        <is>
+          <t>UmzKM5tM</t>
+        </is>
+      </c>
+      <c r="DK10" t="inlineStr">
+        <is>
+          <t>missori filippo</t>
+        </is>
+      </c>
+      <c r="DL10" t="inlineStr">
+        <is>
+          <t>UmzKM5tM</t>
+        </is>
+      </c>
+      <c r="DM10" t="inlineStr">
+        <is>
+          <t>missori filippo</t>
+        </is>
+      </c>
+      <c r="DN10" t="inlineStr">
+        <is>
+          <t>4Of5akc5</t>
+        </is>
+      </c>
+      <c r="DO10" t="inlineStr">
+        <is>
+          <t>antiste janis</t>
+        </is>
+      </c>
+      <c r="DP10" t="inlineStr">
+        <is>
+          <t>t4NSHrlh</t>
+        </is>
+      </c>
+      <c r="DQ10" t="inlineStr">
+        <is>
+          <t>lipani luca</t>
+        </is>
+      </c>
+      <c r="DR10" t="inlineStr">
+        <is>
+          <t>t4NSHrlh</t>
+        </is>
+      </c>
+      <c r="DS10" t="inlineStr">
+        <is>
+          <t>lipani luca</t>
+        </is>
+      </c>
+      <c r="DT10" t="inlineStr">
+        <is>
+          <t>retVSWHL</t>
+        </is>
+      </c>
+      <c r="DU10" t="inlineStr">
+        <is>
+          <t>kumi justin</t>
+        </is>
+      </c>
+      <c r="DV10" t="inlineStr">
+        <is>
+          <t>2qAN5836</t>
+        </is>
+      </c>
+      <c r="DW10" t="inlineStr">
+        <is>
+          <t>adamo emanuele</t>
+        </is>
+      </c>
+      <c r="DX10" t="inlineStr">
+        <is>
+          <t>2qAN5836</t>
+        </is>
+      </c>
+      <c r="DY10" t="inlineStr">
+        <is>
+          <t>adamo emanuele</t>
+        </is>
+      </c>
+      <c r="DZ10" t="inlineStr">
+        <is>
+          <t>pnI8ZjZr</t>
+        </is>
+      </c>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>ceesay joseph</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>ADBJ4OrH</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
+          <t>antonucci mirko</t>
+        </is>
+      </c>
+      <c r="ED10" t="inlineStr">
+        <is>
+          <t>ADBJ4OrH</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>antonucci mirko</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
+        <is>
+          <t>8vhUYvNN</t>
+        </is>
+      </c>
+      <c r="EG10" t="inlineStr">
+        <is>
+          <t>calo giacomo</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>2J6W9OsT</t>
+        </is>
+      </c>
+      <c r="EI10" t="inlineStr">
+        <is>
+          <t>piacentini matteo</t>
+        </is>
+      </c>
+      <c r="EJ10" t="inlineStr">
+        <is>
+          <t>2J6W9OsT</t>
+        </is>
+      </c>
+      <c r="EK10" t="inlineStr">
+        <is>
+          <t>piacentini matteo</t>
+        </is>
+      </c>
+      <c r="EL10" t="inlineStr">
+        <is>
+          <t>xIKq8Lhb</t>
+        </is>
+      </c>
+      <c r="EM10" t="inlineStr">
+        <is>
+          <t>curto marco</t>
+        </is>
+      </c>
+      <c r="EN10" t="inlineStr">
+        <is>
+          <t>nmdCa7Ds</t>
+        </is>
+      </c>
+      <c r="EO10" t="inlineStr">
+        <is>
+          <t>celia raffaele</t>
+        </is>
+      </c>
+      <c r="EP10" t="inlineStr">
+        <is>
+          <t>nmdCa7Ds</t>
+        </is>
+      </c>
+      <c r="EQ10" t="inlineStr">
+        <is>
+          <t>celia raffaele</t>
+        </is>
+      </c>
+      <c r="ER10" t="inlineStr">
+        <is>
+          <t>tnsZtqGu</t>
+        </is>
+      </c>
+      <c r="ES10" t="inlineStr">
+        <is>
+          <t>donnarumma daniele</t>
+        </is>
+      </c>
+      <c r="ET10" t="inlineStr">
+        <is>
+          <t>hrgu7eZM</t>
+        </is>
+      </c>
+      <c r="EU10" t="inlineStr">
+        <is>
+          <t>francesconi matteo</t>
+        </is>
+      </c>
+      <c r="EV10" t="inlineStr">
+        <is>
+          <t>hrgu7eZM</t>
+        </is>
+      </c>
+      <c r="EW10" t="inlineStr">
+        <is>
+          <t>francesconi matteo</t>
+        </is>
+      </c>
+      <c r="EX10" t="inlineStr">
+        <is>
+          <t>hjLa97a7</t>
+        </is>
+      </c>
+      <c r="EY10" t="inlineStr">
+        <is>
+          <t>berti tommaso</t>
+        </is>
+      </c>
+      <c r="EZ10" t="inlineStr"/>
+      <c r="FA10" t="inlineStr"/>
+      <c r="FB10" t="inlineStr"/>
+      <c r="FC10" t="inlineStr"/>
+      <c r="FD10" t="inlineStr"/>
+      <c r="FE10" t="inlineStr"/>
+      <c r="FF10" t="inlineStr"/>
+      <c r="FG10" t="inlineStr"/>
+      <c r="FH10" t="inlineStr"/>
+      <c r="FI10" t="inlineStr"/>
+      <c r="FJ10" t="inlineStr"/>
+      <c r="FK10" t="inlineStr"/>
+      <c r="FL10" t="inlineStr"/>
+      <c r="FM10" t="inlineStr"/>
+      <c r="FN10" t="inlineStr"/>
+      <c r="FO10" t="inlineStr"/>
+      <c r="FP10" t="inlineStr"/>
+      <c r="FQ10" t="inlineStr"/>
+      <c r="FR10" t="inlineStr"/>
+      <c r="FS10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4ry5sueR</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sarr mouhamadou</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>QcPURnA3</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>mateju ales</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>xIj2TcyE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>hristov petko</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>OUZiJhvh</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>bertola nicolo</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>EgfizWFr</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vignali luca</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>vZM5mg5N</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>esposito salvatore</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>lpbxLFLT</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>nagy adam</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>WEIpbflm</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>bandinelli filippo</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>vs1w0sCd</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>elia salvatore</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>dKXxEOKj</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>esposito francesco</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>tCvX7iBP</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>falcinelli diego</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>bNZfXB2q</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>cerofolini michele</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>W6Uqcx1k</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monterisi ilario</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>fL14Xe6b</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>marchizza riccardo</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>xbr7uc5g</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>biraschi davide</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>hjatkmbP</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>oyono jeremy</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>lAAgG4hD</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>cichella matteo</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>G0q0g1Mp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>darboe ebrima</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>4UlxnksM</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>oyono anthony</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>fDYy3Ls1</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>ghedjemis fares</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>KrttNVLt</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>ambrosino giuseppe</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>CC0GVwI9</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>cuni marvin</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>t04rL0bG</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>aurelio giuseppe</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>AkjDhEk0</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>benvenuto mattia</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>CvWHSNg0</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>candelari pietro</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>YTuQ6xad</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>cassata francesco</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>KCtXlKaH</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>degli duccio</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>MTtBqQfl</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>di serio guiseppe</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>r34Klsm2</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>giorgeschi simone</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>OpOdOpiR</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>mascardi diego</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>2kJoCbl9</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>reca arkadiusz</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>zDHydpk5</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>salvador ferrer</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>nRUWcY4c</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>soleri edoardo</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>AaYOi9YT</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>wisniewski przemyslaw</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>bVCSvTzl</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>bracaglia gabriele</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>YTpHlpak</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>di stefano filippo</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>U5ueIFMC</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>frattali pierluigi</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>4pxhfOad</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>garritano luca</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>4AXvWzji</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>kalaj sergio</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>b7dng8al</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>kvernadze giorgi</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>OSvubCVd</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>mateus lusuardi</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>zum0lPdH</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>pecorino emanuele</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>tdixkni3</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>selvini alessandro</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>n79iW0sd</t>
+        </is>
+      </c>
+      <c r="CK11" t="inlineStr">
+        <is>
+          <t>sene fallou</t>
+        </is>
+      </c>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>4t7kEi2t</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>vural isak</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>Q3JMhYxU</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>zaknic lazar</t>
+        </is>
+      </c>
+      <c r="CP11" t="inlineStr"/>
+      <c r="CQ11" t="inlineStr"/>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>CvWHSNg0</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
+          <t>candelari pietro</t>
+        </is>
+      </c>
+      <c r="CT11" t="inlineStr">
+        <is>
+          <t>CvWHSNg0</t>
+        </is>
+      </c>
+      <c r="CU11" t="inlineStr">
+        <is>
+          <t>candelari pietro</t>
+        </is>
+      </c>
+      <c r="CV11" t="inlineStr">
+        <is>
+          <t>WEIpbflm</t>
+        </is>
+      </c>
+      <c r="CW11" t="inlineStr">
+        <is>
+          <t>bandinelli filippo</t>
+        </is>
+      </c>
+      <c r="CX11" t="inlineStr">
+        <is>
+          <t>nRUWcY4c</t>
+        </is>
+      </c>
+      <c r="CY11" t="inlineStr">
+        <is>
+          <t>soleri edoardo</t>
+        </is>
+      </c>
+      <c r="CZ11" t="inlineStr">
+        <is>
+          <t>nRUWcY4c</t>
+        </is>
+      </c>
+      <c r="DA11" t="inlineStr">
+        <is>
+          <t>soleri edoardo</t>
+        </is>
+      </c>
+      <c r="DB11" t="inlineStr">
+        <is>
+          <t>tCvX7iBP</t>
+        </is>
+      </c>
+      <c r="DC11" t="inlineStr">
+        <is>
+          <t>falcinelli diego</t>
+        </is>
+      </c>
+      <c r="DD11" t="inlineStr">
+        <is>
+          <t>MTtBqQfl</t>
+        </is>
+      </c>
+      <c r="DE11" t="inlineStr">
+        <is>
+          <t>di serio guiseppe</t>
+        </is>
+      </c>
+      <c r="DF11" t="inlineStr">
+        <is>
+          <t>MTtBqQfl</t>
+        </is>
+      </c>
+      <c r="DG11" t="inlineStr">
+        <is>
+          <t>di serio guiseppe</t>
+        </is>
+      </c>
+      <c r="DH11" t="inlineStr">
+        <is>
+          <t>dKXxEOKj</t>
+        </is>
+      </c>
+      <c r="DI11" t="inlineStr">
+        <is>
+          <t>esposito francesco</t>
+        </is>
+      </c>
+      <c r="DJ11" t="inlineStr">
+        <is>
+          <t>t04rL0bG</t>
+        </is>
+      </c>
+      <c r="DK11" t="inlineStr">
+        <is>
+          <t>aurelio giuseppe</t>
+        </is>
+      </c>
+      <c r="DL11" t="inlineStr">
+        <is>
+          <t>t04rL0bG</t>
+        </is>
+      </c>
+      <c r="DM11" t="inlineStr">
+        <is>
+          <t>aurelio giuseppe</t>
+        </is>
+      </c>
+      <c r="DN11" t="inlineStr">
+        <is>
+          <t>EgfizWFr</t>
+        </is>
+      </c>
+      <c r="DO11" t="inlineStr">
+        <is>
+          <t>vignali luca</t>
+        </is>
+      </c>
+      <c r="DP11" t="inlineStr">
+        <is>
+          <t>YTuQ6xad</t>
+        </is>
+      </c>
+      <c r="DQ11" t="inlineStr">
+        <is>
+          <t>cassata francesco</t>
+        </is>
+      </c>
+      <c r="DR11" t="inlineStr">
+        <is>
+          <t>YTuQ6xad</t>
+        </is>
+      </c>
+      <c r="DS11" t="inlineStr">
+        <is>
+          <t>cassata francesco</t>
+        </is>
+      </c>
+      <c r="DT11" t="inlineStr">
+        <is>
+          <t>lpbxLFLT</t>
+        </is>
+      </c>
+      <c r="DU11" t="inlineStr">
+        <is>
+          <t>nagy adam</t>
+        </is>
+      </c>
+      <c r="DV11" t="inlineStr">
+        <is>
+          <t>4pxhfOad</t>
+        </is>
+      </c>
+      <c r="DW11" t="inlineStr">
+        <is>
+          <t>garritano luca</t>
+        </is>
+      </c>
+      <c r="DX11" t="inlineStr">
+        <is>
+          <t>4pxhfOad</t>
+        </is>
+      </c>
+      <c r="DY11" t="inlineStr">
+        <is>
+          <t>garritano luca</t>
+        </is>
+      </c>
+      <c r="DZ11" t="inlineStr">
+        <is>
+          <t>G0q0g1Mp</t>
+        </is>
+      </c>
+      <c r="EA11" t="inlineStr">
+        <is>
+          <t>darboe ebrima</t>
+        </is>
+      </c>
+      <c r="EB11" t="inlineStr">
+        <is>
+          <t>YTpHlpak</t>
+        </is>
+      </c>
+      <c r="EC11" t="inlineStr">
+        <is>
+          <t>di stefano filippo</t>
+        </is>
+      </c>
+      <c r="ED11" t="inlineStr">
+        <is>
+          <t>YTpHlpak</t>
+        </is>
+      </c>
+      <c r="EE11" t="inlineStr">
+        <is>
+          <t>di stefano filippo</t>
+        </is>
+      </c>
+      <c r="EF11" t="inlineStr">
+        <is>
+          <t>fDYy3Ls1</t>
+        </is>
+      </c>
+      <c r="EG11" t="inlineStr">
+        <is>
+          <t>ghedjemis fares</t>
+        </is>
+      </c>
+      <c r="EH11" t="inlineStr">
+        <is>
+          <t>zum0lPdH</t>
+        </is>
+      </c>
+      <c r="EI11" t="inlineStr">
+        <is>
+          <t>pecorino emanuele</t>
+        </is>
+      </c>
+      <c r="EJ11" t="inlineStr">
+        <is>
+          <t>zum0lPdH</t>
+        </is>
+      </c>
+      <c r="EK11" t="inlineStr">
+        <is>
+          <t>pecorino emanuele</t>
+        </is>
+      </c>
+      <c r="EL11" t="inlineStr">
+        <is>
+          <t>CC0GVwI9</t>
+        </is>
+      </c>
+      <c r="EM11" t="inlineStr">
+        <is>
+          <t>cuni marvin</t>
+        </is>
+      </c>
+      <c r="EN11" t="inlineStr">
+        <is>
+          <t>b7dng8al</t>
+        </is>
+      </c>
+      <c r="EO11" t="inlineStr">
+        <is>
+          <t>kvernadze giorgi</t>
+        </is>
+      </c>
+      <c r="EP11" t="inlineStr">
+        <is>
+          <t>b7dng8al</t>
+        </is>
+      </c>
+      <c r="EQ11" t="inlineStr">
+        <is>
+          <t>kvernadze giorgi</t>
+        </is>
+      </c>
+      <c r="ER11" t="inlineStr">
+        <is>
+          <t>KrttNVLt</t>
+        </is>
+      </c>
+      <c r="ES11" t="inlineStr">
+        <is>
+          <t>ambrosino giuseppe</t>
+        </is>
+      </c>
+      <c r="ET11" t="inlineStr">
+        <is>
+          <t>bVCSvTzl</t>
+        </is>
+      </c>
+      <c r="EU11" t="inlineStr">
+        <is>
+          <t>bracaglia gabriele</t>
+        </is>
+      </c>
+      <c r="EV11" t="inlineStr">
+        <is>
+          <t>bVCSvTzl</t>
+        </is>
+      </c>
+      <c r="EW11" t="inlineStr">
+        <is>
+          <t>bracaglia gabriele</t>
+        </is>
+      </c>
+      <c r="EX11" t="inlineStr">
+        <is>
+          <t>4UlxnksM</t>
+        </is>
+      </c>
+      <c r="EY11" t="inlineStr">
+        <is>
+          <t>oyono anthony</t>
+        </is>
+      </c>
+      <c r="EZ11" t="inlineStr"/>
+      <c r="FA11" t="inlineStr"/>
+      <c r="FB11" t="inlineStr"/>
+      <c r="FC11" t="inlineStr"/>
+      <c r="FD11" t="inlineStr"/>
+      <c r="FE11" t="inlineStr"/>
+      <c r="FF11" t="inlineStr"/>
+      <c r="FG11" t="inlineStr"/>
+      <c r="FH11" t="inlineStr"/>
+      <c r="FI11" t="inlineStr"/>
+      <c r="FJ11" t="inlineStr"/>
+      <c r="FK11" t="inlineStr"/>
+      <c r="FL11" t="inlineStr"/>
+      <c r="FM11" t="inlineStr"/>
+      <c r="FN11" t="inlineStr"/>
+      <c r="FO11" t="inlineStr"/>
+      <c r="FP11" t="inlineStr"/>
+      <c r="FQ11" t="inlineStr"/>
+      <c r="FR11" t="inlineStr"/>
+      <c r="FS11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG10"/>
+  <dimension ref="A1:FE9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,7577 +781,6590 @@
       </c>
       <c r="BT1" s="1" t="inlineStr">
         <is>
+          <t>id_player_sub_home_14</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_14</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_15</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_15</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
           <t>id_player_sub_away_1</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_1</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_2</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_2</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_3</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_3</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_4</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_4</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_5</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_5</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_6</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_6</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_7</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_7</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_8</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_8</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_9</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_9</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_10</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_10</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_11</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_11</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_12</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_12</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_13</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_13</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_14</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_14</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_1</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_1</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_2</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_2</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_3</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_3</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_4</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_4</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_5</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_5</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_6</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_6</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_7</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_7</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_8</t>
-        </is>
-      </c>
-      <c r="DK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_8</t>
-        </is>
-      </c>
-      <c r="DL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_9</t>
-        </is>
-      </c>
-      <c r="DM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_9</t>
-        </is>
-      </c>
-      <c r="DN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_10</t>
-        </is>
-      </c>
-      <c r="DO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_10</t>
-        </is>
-      </c>
-      <c r="DP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_11</t>
-        </is>
-      </c>
-      <c r="DQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_11</t>
-        </is>
-      </c>
-      <c r="DR1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_12</t>
-        </is>
-      </c>
-      <c r="DS1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_12</t>
-        </is>
-      </c>
-      <c r="DT1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="DU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="DV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="DW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="DX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_15</t>
-        </is>
-      </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_15</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_1</t>
-        </is>
-      </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_1</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_2</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_2</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_3</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_3</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_4</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_4</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_5</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_5</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_6</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_6</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_7</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_7</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_8</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_8</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_9</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_9</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_10</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_10</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_11</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_11</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_12</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_12</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_13</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_13</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_14</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_14</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_15</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_15</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_home_14</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_home_14</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_home_15</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_home_15</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OAeKROjD</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>SYbhvYs3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>skorupski lukasz</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>nsVWqZE2</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>posch stefan</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>xAzIxa5n</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>beukema sam</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>O8NaVz3G</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>lucumi jhon</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>hxdzXUCO</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>lykogiannis charalampos</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>MiXFJwit</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>aebischer michel</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>pETNY4Qt</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>freuler remo</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>bkJ9njyQ</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>fabbian giovanni</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>bRV808wb</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>orsolini riccardo</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>6BYm6GqL</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>castro santiago</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>EmmpFCXN</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>ndoye dan</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
           <t>8WujtCJF</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>carnesecchi marco</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>SzDIipZ9</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>kossounou odilon</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>pW01mTt9</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>djimsiti berat</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>8xFYnbEi</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>kolasinac sead</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>6BgYlqqU</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>bellanova raoul</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>fqEsbNyA</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>ederson</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>SUUtwXea</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>de roon marten</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0WPEP3LT</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>ruggeri matteo</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>lt87Q6nj</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>brescianini marco</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>2eOa3r1T</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>de ketelaere charles</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>8QK1SO5g</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>lookman ademola</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>I52azhH8</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>bagnolini nicola</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>WAb3qgda</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>casale nicolo</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>tEYzXR62</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>corazza tommaso</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>6kW9PX8r</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>dallinga thijs</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>A9WpvRff</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>de silvestri lorenzo</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0CMCQTH6</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>dominguez benjamin</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>n9FYAE96</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>erlic martin</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>ANr5qAci</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>holm emil</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>QXDbCvep</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>iling samuel</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>xUfM6nJ2</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>karlsson jesper</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>xOw55vy0</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>miranda juan</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>SOva7ZCL</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>moro nikola</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>xbCDeKRm</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>odgaard jens</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>219bD5Kr</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>ravaglia federico</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>4SFU8b8f</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>urbanski kacper</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>AFefBpwI</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>cuadrado juan</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>jivNliqi</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>del lungo tommaso</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>nD7QhgLn</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>godfrey ben</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>Y3DYaDdP</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>palestra marco</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>ld4iyqYa</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>pasalic mario</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>44sSdBl6</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>patricio rui</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>Grhjz8pS</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>retegui mateo</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>tdfrZ6nG</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>rossi francesco</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>ba7y6F3c</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>samardzic lazar</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>rRf9f5UA</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>suleiman ibrahim</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>0G7MtHBl</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>zaniolo nicolo</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
         <is>
           <t>G6AuiwvH</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>zappacosta davide</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>4SFU8b8f</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>urbanski kacper</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>4SFU8b8f</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>urbanski kacper</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>bkJ9njyQ</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>fabbian giovanni</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>WAb3qgda</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>casale nicolo</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>WAb3qgda</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>casale nicolo</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>bRV808wb</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>orsolini riccardo</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>6kW9PX8r</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>dallinga thijs</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>6kW9PX8r</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>dallinga thijs</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>6BYm6GqL</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>castro santiago</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>n9FYAE96</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>erlic martin</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>n9FYAE96</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>erlic martin</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>MiXFJwit</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>aebischer michel</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>ANr5qAci</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>holm emil</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>ANr5qAci</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>holm emil</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>EmmpFCXN</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>ndoye dan</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>ba7y6F3c</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>samardzic lazar</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>ba7y6F3c</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>samardzic lazar</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>lt87Q6nj</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>brescianini marco</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>Grhjz8pS</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>retegui mateo</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>Grhjz8pS</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>retegui mateo</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>SzDIipZ9</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>kossounou odilon</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>AFefBpwI</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>cuadrado juan</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>AFefBpwI</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>cuadrado juan</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>6BgYlqqU</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>bellanova raoul</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr">
         <is>
           <t>ld4iyqYa</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="ES2" t="inlineStr">
         <is>
           <t>pasalic mario</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2eOa3r1T</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>de ketelaere charles</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Grhjz8pS</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>retegui mateo</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>fwyieeh8</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>audero emil</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Uaabio2H</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>van der brempt ignace</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>4j96wYs7</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>dossena alberto</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>AR2PqO6h</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>kempf marc oliver</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>pdBI3oS8</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>moreno alberto</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>zR7umNy4</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>strefezza gabriel</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>W2R804U4</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>roberto sergi</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>vmcGpMJM</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>perrone maximo</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>YclDapI5</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>fadera alieu</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>GG6EYRT0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>paz martinez nicolas</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>vB6l1nu7</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>cutrone patrick</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>lt87Q6nj</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>brescianini marco</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>AFefBpwI</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>cuadrado juan</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>jivNliqi</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>del lungo tommaso</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>hz4zWEIG</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>hien isak</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>8QK1SO5g</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>lookman ademola</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>Y3DYaDdP</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>palestra marco</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>44sSdBl6</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>patricio rui</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>tdfrZ6nG</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>rossi francesco</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>ld4iyqYa</t>
+        </is>
+      </c>
+      <c r="EU2" t="inlineStr">
+        <is>
+          <t>pasalic mario</t>
+        </is>
+      </c>
+      <c r="EV2" t="inlineStr">
         <is>
           <t>0WPEP3LT</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="EW2" t="inlineStr">
         <is>
           <t>ruggeri matteo</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>ba7y6F3c</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>samardzic lazar</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>rRf9f5UA</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>suleiman ibrahim</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>llm7waHJ</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>vlahovic vanja</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
+      <c r="EX2" t="inlineStr">
         <is>
           <t>0G7MtHBl</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="EY2" t="inlineStr">
         <is>
           <t>zaniolo nicolo</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>nmCTZrFD</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>baselli daniele</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>W6UTbSDR</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>belotti andrea</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>vkRv24dh</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>braunoder matthias</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>IXqHAIWJ</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>da cunha lucas</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>S2gIJM28</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>engelhardt yannik</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>xzWqt9uL</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>gabrielloni alessandro</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>CxCzIfHK</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>goldaniga edoardo</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>UieHuD3i</t>
-        </is>
-      </c>
-      <c r="CI2" t="inlineStr">
-        <is>
-          <t>lovino alessio</t>
-        </is>
-      </c>
-      <c r="CJ2" t="inlineStr">
-        <is>
-          <t>4bKWOzzb</t>
-        </is>
-      </c>
-      <c r="CK2" t="inlineStr">
-        <is>
-          <t>jack fellipe</t>
-        </is>
-      </c>
-      <c r="CL2" t="inlineStr">
-        <is>
-          <t>MqKDIKSH</t>
-        </is>
-      </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>jasim ali</t>
-        </is>
-      </c>
-      <c r="CN2" t="inlineStr">
-        <is>
-          <t>0zd8jKI5</t>
-        </is>
-      </c>
-      <c r="CO2" t="inlineStr">
-        <is>
-          <t>mazzitelli luca</t>
-        </is>
-      </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>KrEhnvkN</t>
-        </is>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>reina pepe</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>lG6NBuFm</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>sala marco</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>rP6cESXb</t>
-        </is>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>verdi simone</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>lt87Q6nj</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>brescianini marco</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>lt87Q6nj</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>brescianini marco</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>ld4iyqYa</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>pasalic mario</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>8QK1SO5g</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>lookman ademola</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>8QK1SO5g</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>lookman ademola</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>Grhjz8pS</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>retegui mateo</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>AFefBpwI</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>cuadrado juan</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>AFefBpwI</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>cuadrado juan</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>G6AuiwvH</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>zappacosta davide</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>ba7y6F3c</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>samardzic lazar</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>ba7y6F3c</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>samardzic lazar</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>2eOa3r1T</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>de ketelaere charles</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>llm7waHJ</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>vlahovic vanja</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>llm7waHJ</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>vlahovic vanja</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>fqEsbNyA</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>ederson</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>0zd8jKI5</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>mazzitelli luca</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>0zd8jKI5</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>mazzitelli luca</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>YclDapI5</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>fadera alieu</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>xzWqt9uL</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>gabrielloni alessandro</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>xzWqt9uL</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>gabrielloni alessandro</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>vB6l1nu7</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>cutrone patrick</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>CxCzIfHK</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>goldaniga edoardo</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>CxCzIfHK</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>goldaniga edoardo</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>vmcGpMJM</t>
-        </is>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>perrone maximo</t>
-        </is>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>lG6NBuFm</t>
-        </is>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>sala marco</t>
-        </is>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>lG6NBuFm</t>
-        </is>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>sala marco</t>
-        </is>
-      </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>GG6EYRT0</t>
-        </is>
-      </c>
-      <c r="EW2" t="inlineStr">
-        <is>
-          <t>paz martinez nicolas</t>
-        </is>
-      </c>
-      <c r="EX2" t="inlineStr">
-        <is>
-          <t>S2gIJM28</t>
-        </is>
-      </c>
-      <c r="EY2" t="inlineStr">
-        <is>
-          <t>engelhardt yannik</t>
-        </is>
-      </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>S2gIJM28</t>
+          <t>0G7MtHBl</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>engelhardt yannik</t>
+          <t>zaniolo nicolo</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>zR7umNy4</t>
+          <t>8xFYnbEi</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>strefezza gabriel</t>
+          <t>kolasinac sead</t>
         </is>
       </c>
       <c r="FD2" t="inlineStr"/>
       <c r="FE2" t="inlineStr"/>
-      <c r="FF2" t="inlineStr"/>
-      <c r="FG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>h8xCR9dC</t>
+          <t>KIQjmWIj</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>rBsmDlYq</t>
+          <t>vZY7FZwP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>caprile elia</t>
+          <t>gollini pierluigi</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>xr29B9AI</t>
+          <t>EFmPm0Qo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>mazzocchi pasquale</t>
+          <t>de winter koni</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KIwYY1AC</t>
+          <t>vgmL526e</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>marin rafa</t>
+          <t>bani mattia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>StHeGfTT</t>
+          <t>Qydfoeer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>juan jesus</t>
+          <t>vasquez johan</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>UgYYWt1i</t>
+          <t>xjWe0TTo</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>spinazzola leonardo</t>
+          <t>zanoli alessandro</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0Qcw6Yy1</t>
+          <t>2XPmtx2l</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lobotka stanislav</t>
+          <t>frendrup morten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MPhh66QA</t>
+          <t>4InuIizr</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>gilmour billy</t>
+          <t>badelj milan</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>r9dHjC84</t>
+          <t>tSUumbUT</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>david neres</t>
+          <t>miretti fabio</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>GlZEnTQr</t>
+          <t>Q1Sl1XK4</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>raspadori giacomo</t>
+          <t>ahanor honest</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>URgTM07o</t>
+          <t>O4qi5hfc</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>ngonge cyril</t>
+          <t>pinamonti andrea</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>6m566fII</t>
+          <t>AazXYT3h</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>simeone giovanni</t>
+          <t>vitinha</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>A3ywEtVi</t>
+          <t>A3ZJNQg1</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>sirigu salvatore</t>
+          <t>perin mattia</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>p6lid052</t>
+          <t>KUjvgUhB</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>buttaro alessio</t>
+          <t>danilo</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>S0zo50w7</t>
+          <t>E5UKRKOH</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>peda patryk</t>
+          <t>kalulu kyatengwa piere</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>CMVcN419</t>
+          <t>INWVBb0R</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>baniya rayyan</t>
+          <t>bremer</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>dIqrhHoE</t>
+          <t>bsVzbV2I</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>ceccaroni pietro</t>
+          <t>rouhi jonas</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>d8ybAOqJ</t>
+          <t>4rFy4PRQ</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>vasic vasic</t>
+          <t>fagioli nicolo</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>44OHk9di</t>
+          <t>jZHxRi2A</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>ranocchia filippo</t>
+          <t>mckennie weston</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>rLETyaHe</t>
+          <t>filNjPIq</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>saric dario</t>
+          <t>gonzalez nicolas ivan</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>MZLNAdYj</t>
+          <t>lOCjQkeo</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>le douaron jeremy</t>
+          <t>koopmeiners teun</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>xAQAwbhk</t>
+          <t>0EgOZVie</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>brunori matteo</t>
+          <t>yildiz kenan</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>hIreZGmE</t>
+          <t>Ct0rhfn7</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>hansen kristoffer</t>
+          <t>vlahovic dusan</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>OtLZCB8S</t>
+          <t>fTOU6yR2</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>anguissa andre zambo</t>
+          <t>ankeye david</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>UDMnkfdo</t>
+          <t>25uHtnwl</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>buongiorno alessandro</t>
+          <t>bohinen emil</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>GUUR3bc3</t>
+          <t>QopKhlIm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>contini nikita</t>
+          <t>ekhator jeff</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>MP69NX2i</t>
+          <t>vw0NcNnU</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>di lorenzo giovanni</t>
+          <t>kasa lior</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>bNuGt0hE</t>
+          <t>MHD6IelJ</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>kvaratskhelia khvicha</t>
+          <t>leali nicola</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>dCkG0Iw0</t>
+          <t>6BUzxLAe</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>lukaku romelu</t>
+          <t>marcandalli alessandro</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>A7S3y397</t>
+          <t>l4xhn6hC</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>mctominay scott</t>
+          <t>caricol aaron</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>bwAJqLBt</t>
+          <t>WOffNMWA</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>olivera mathias</t>
+          <t>matturro romero alan</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>lxWZKRDD</t>
+          <t>zLlOcqw4</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>politano matteo</t>
+          <t>sabelli stefano</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>8Sw4X8wk</t>
+          <t>MsjFcjtJ</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>rrahmani amir</t>
+          <t>sommariva daniele</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>f9btzvmR</t>
+          <t>Ei7zkE0o</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>turi claudio</t>
+          <t>thorsby morten</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>2R03aynj</t>
+          <t>tW6pCCm8</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>zerbin alessio</t>
+          <t>vogliacco alessandro</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr"/>
       <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>jXsDx65M</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>appuah stredair</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>bVXYRoIt</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>desplanches sebastiano</t>
-        </is>
-      </c>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>WSOBy5mn</t>
+          <t>bNJ7fStk</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>diakite salim</t>
+          <t>cabal juan david</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>fivMxYck</t>
+          <t>vRzeXq5h</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>di mariano francesco</t>
+          <t>cambiaso andrea</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>AcX8a9pK</t>
+          <t>n53v4sSd</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>gomes claudio</t>
+          <t>chico conceicao</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>Slv0QNjF</t>
+          <t>dUJmgXia</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>henry thomas</t>
+          <t>di gregorio michele</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>QRxD5fN5</t>
+          <t>IZxlmmuF</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>insigne roberto</t>
+          <t>douglas luiz</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>Cvyu7pen</t>
+          <t>SCvJDma8</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>lucioni fabio</t>
+          <t>gatti federico</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>tz6uZNmt</t>
+          <t>6RgXRdd8</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>nespola manfredi</t>
+          <t>locatelli manuel</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>MiTDJFqG</t>
+          <t>0EjeWH5q</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>nikolaou dimitrios</t>
+          <t>mbangula tshifunda samuel</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>SzFjYRlO</t>
+          <t>Uii1AJuK</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>pierozzi niccolo</t>
+          <t>pinsoglio carlo</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>fa6CHtxA</t>
+          <t>juQzl8Zj</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>segre jacopo</t>
-        </is>
-      </c>
-      <c r="CR3" t="inlineStr"/>
-      <c r="CS3" t="inlineStr"/>
+          <t>savona nicolo</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>bDU1sgDT</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>thuram kephren</t>
+        </is>
+      </c>
       <c r="CT3" t="inlineStr"/>
       <c r="CU3" t="inlineStr"/>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>OtLZCB8S</t>
+          <t>25uHtnwl</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>anguissa andre zambo</t>
+          <t>bohinen emil</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>OtLZCB8S</t>
+          <t>25uHtnwl</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>anguissa andre zambo</t>
+          <t>bohinen emil</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>0Qcw6Yy1</t>
+          <t>4InuIizr</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>lobotka stanislav</t>
+          <t>badelj milan</t>
         </is>
       </c>
       <c r="DB3" t="inlineStr">
         <is>
-          <t>2R03aynj</t>
+          <t>WOffNMWA</t>
         </is>
       </c>
       <c r="DC3" t="inlineStr">
         <is>
-          <t>zerbin alessio</t>
+          <t>matturro romero alan</t>
         </is>
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>2R03aynj</t>
+          <t>WOffNMWA</t>
         </is>
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>zerbin alessio</t>
+          <t>matturro romero alan</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr">
         <is>
-          <t>URgTM07o</t>
+          <t>Q1Sl1XK4</t>
         </is>
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>ngonge cyril</t>
+          <t>ahanor honest</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>bNuGt0hE</t>
+          <t>vw0NcNnU</t>
         </is>
       </c>
       <c r="DI3" t="inlineStr">
         <is>
-          <t>kvaratskhelia khvicha</t>
+          <t>kasa lior</t>
         </is>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>bNuGt0hE</t>
+          <t>vw0NcNnU</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>kvaratskhelia khvicha</t>
+          <t>kasa lior</t>
         </is>
       </c>
       <c r="DL3" t="inlineStr">
         <is>
-          <t>r9dHjC84</t>
+          <t>tSUumbUT</t>
         </is>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>david neres</t>
+          <t>miretti fabio</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>dCkG0Iw0</t>
+          <t>fTOU6yR2</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>lukaku romelu</t>
+          <t>ankeye david</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>dCkG0Iw0</t>
+          <t>fTOU6yR2</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
-          <t>lukaku romelu</t>
+          <t>ankeye david</t>
         </is>
       </c>
       <c r="DR3" t="inlineStr">
         <is>
-          <t>6m566fII</t>
+          <t>AazXYT3h</t>
         </is>
       </c>
       <c r="DS3" t="inlineStr">
         <is>
-          <t>simeone giovanni</t>
+          <t>vitinha</t>
         </is>
       </c>
       <c r="DT3" t="inlineStr">
         <is>
-          <t>A7S3y397</t>
+          <t>zLlOcqw4</t>
         </is>
       </c>
       <c r="DU3" t="inlineStr">
         <is>
-          <t>mctominay scott</t>
+          <t>sabelli stefano</t>
         </is>
       </c>
       <c r="DV3" t="inlineStr">
         <is>
-          <t>A7S3y397</t>
+          <t>zLlOcqw4</t>
         </is>
       </c>
       <c r="DW3" t="inlineStr">
         <is>
-          <t>mctominay scott</t>
+          <t>sabelli stefano</t>
         </is>
       </c>
       <c r="DX3" t="inlineStr">
         <is>
-          <t>GlZEnTQr</t>
+          <t>xjWe0TTo</t>
         </is>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>raspadori giacomo</t>
+          <t>zanoli alessandro</t>
         </is>
       </c>
       <c r="DZ3" t="inlineStr">
         <is>
-          <t>QRxD5fN5</t>
+          <t>IZxlmmuF</t>
         </is>
       </c>
       <c r="EA3" t="inlineStr">
         <is>
-          <t>insigne roberto</t>
+          <t>douglas luiz</t>
         </is>
       </c>
       <c r="EB3" t="inlineStr">
         <is>
-          <t>QRxD5fN5</t>
+          <t>IZxlmmuF</t>
         </is>
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>insigne roberto</t>
+          <t>douglas luiz</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>MZLNAdYj</t>
+          <t>jZHxRi2A</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>le douaron jeremy</t>
+          <t>mckennie weston</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>AcX8a9pK</t>
+          <t>n53v4sSd</t>
         </is>
       </c>
       <c r="EG3" t="inlineStr">
         <is>
-          <t>gomes claudio</t>
+          <t>chico conceicao</t>
         </is>
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>AcX8a9pK</t>
+          <t>n53v4sSd</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
         <is>
-          <t>gomes claudio</t>
+          <t>chico conceicao</t>
         </is>
       </c>
       <c r="EJ3" t="inlineStr">
         <is>
-          <t>44OHk9di</t>
+          <t>filNjPIq</t>
         </is>
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>ranocchia filippo</t>
+          <t>gonzalez nicolas ivan</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr">
         <is>
-          <t>Cvyu7pen</t>
+          <t>vRzeXq5h</t>
         </is>
       </c>
       <c r="EM3" t="inlineStr">
         <is>
-          <t>lucioni fabio</t>
+          <t>cambiaso andrea</t>
         </is>
       </c>
       <c r="EN3" t="inlineStr">
         <is>
-          <t>Cvyu7pen</t>
+          <t>vRzeXq5h</t>
         </is>
       </c>
       <c r="EO3" t="inlineStr">
         <is>
-          <t>lucioni fabio</t>
+          <t>cambiaso andrea</t>
         </is>
       </c>
       <c r="EP3" t="inlineStr">
         <is>
-          <t>CMVcN419</t>
+          <t>bsVzbV2I</t>
         </is>
       </c>
       <c r="EQ3" t="inlineStr">
         <is>
-          <t>baniya rayyan</t>
+          <t>rouhi jonas</t>
         </is>
       </c>
       <c r="ER3" t="inlineStr">
         <is>
-          <t>fa6CHtxA</t>
+          <t>bDU1sgDT</t>
         </is>
       </c>
       <c r="ES3" t="inlineStr">
         <is>
-          <t>segre jacopo</t>
+          <t>thuram kephren</t>
         </is>
       </c>
       <c r="ET3" t="inlineStr">
         <is>
-          <t>fa6CHtxA</t>
+          <t>bDU1sgDT</t>
         </is>
       </c>
       <c r="EU3" t="inlineStr">
         <is>
-          <t>segre jacopo</t>
+          <t>thuram kephren</t>
         </is>
       </c>
       <c r="EV3" t="inlineStr">
         <is>
-          <t>rLETyaHe</t>
+          <t>0EgOZVie</t>
         </is>
       </c>
       <c r="EW3" t="inlineStr">
         <is>
-          <t>saric dario</t>
+          <t>yildiz kenan</t>
         </is>
       </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>SzFjYRlO</t>
+          <t>juQzl8Zj</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>pierozzi niccolo</t>
+          <t>savona nicolo</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>SzFjYRlO</t>
+          <t>juQzl8Zj</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
-          <t>pierozzi niccolo</t>
+          <t>savona nicolo</t>
         </is>
       </c>
       <c r="FB3" t="inlineStr">
         <is>
-          <t>hIreZGmE</t>
+          <t>E5UKRKOH</t>
         </is>
       </c>
       <c r="FC3" t="inlineStr">
         <is>
-          <t>hansen kristoffer</t>
+          <t>kalulu kyatengwa piere</t>
         </is>
       </c>
       <c r="FD3" t="inlineStr"/>
       <c r="FE3" t="inlineStr"/>
-      <c r="FF3" t="inlineStr"/>
-      <c r="FG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OE5MGhrf</t>
+          <t>pIgDNCf3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GbSDQoj8</t>
+          <t>Gr6T6rIt</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pizzignacco semuel</t>
+          <t>okoye maduks</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ShD3fHfH</t>
+          <t>42ADo7dd</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>d ambrosio danilo</t>
+          <t>kabasele christian</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>lOTx2Yho</t>
+          <t>0CykEP51</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>caldirola luca</t>
+          <t>bijol jaka</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>jBspTfmj</t>
+          <t>jaNZBJgT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>carboni andrea</t>
+          <t>toure souleymane</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0xrmbKZS</t>
+          <t>6XCZJG4M</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>martins kevin</t>
+          <t>ehizibue kingsley</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>vPBB8Jle</t>
+          <t>2oBl3y29</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>valoti mattia</t>
+          <t>lovric sandi</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Wj6lXM52</t>
+          <t>UDGFZQv8</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>pessina matteo</t>
+          <t>karlstrom jesper</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>dbshNo9J</t>
+          <t>QHRhjNJJ</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>kiriakopoulos giorgos</t>
+          <t>zarraga oier</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>lh4Ryd2l</t>
+          <t>GAzjxceh</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>forson omari</t>
+          <t>zemura jordan</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>hM9I17fh</t>
+          <t>SMbMSc26</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>caprari gianluca</t>
+          <t>thauvin florian</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>6i5Fwg4m</t>
+          <t>SKxz4XFS</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>maric mirko</t>
+          <t>davis keinan</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Kv1RND3R</t>
+          <t>4zA5n1UG</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>andrenacci lorenzo</t>
+          <t>sommer yann</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>d8G4xPEs</t>
+          <t>b3kUQZ4h</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dickmann lorenzo</t>
+          <t>bisseck yann aurel</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GA94QkW9</t>
+          <t>SrhnSpzL</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>calvani gabriele</t>
+          <t>acerbi francesco</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>OIah8ITR</t>
+          <t>On4TkPTN</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>papetti andrea</t>
+          <t>bastoni alessandro</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>6PM5vQQo</t>
+          <t>WbNknKk3</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>jallow alexander</t>
+          <t>darmian matteo</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>nH4bnBjF</t>
+          <t>WlVuvCqU</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>fogliata riccardo</t>
+          <t>frattesi davide</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Mw804hef</t>
+          <t>IRQeP5FJ</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>paghera fabrizio</t>
+          <t>calhanoglu hakan</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>UBJZLl4T</t>
+          <t>KKi1DwHC</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>bertagnoli massimo</t>
+          <t>mkhitaryan henrikh</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>pGN9fQkH</t>
+          <t>W6lypZn3</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>olzer giacomo</t>
+          <t>dimarco federico</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Kh4HwK0A</t>
+          <t>QHk1CXUh</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>borrelli gennaro</t>
+          <t>martinez lautaro</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>Czj6Fpfh</t>
+          <t>hMMX02Fm</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>juric ante matej</t>
+          <t>thuram marcus</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>4xwSQO9t</t>
+          <t>QgfEnOwH</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>berretta alessandro</t>
+          <t>abankwah james</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>r5YvrtEQ</t>
+          <t>Y3ooARhm</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>bianco alessandro</t>
+          <t>atta arthur</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>ABbkAWNr</t>
+          <t>b5XwSo4Q</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>bondo warren</t>
+          <t>bravo iker</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>ri4T3rvJ</t>
+          <t>2kXZSD2S</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>djuric milan</t>
+          <t>brenner</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>OrlLWHno</t>
+          <t>MXSXXNLr</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>izzo armando</t>
+          <t>ebosse enzo</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>txSCnXec</t>
+          <t>4W6Geckd</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>maldini daniel</t>
+          <t>ekkelenkamp jurgen</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>8hN0kFPe</t>
+          <t>UVyQpa9t</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>mari pablo</t>
+          <t>lucca lorenzo</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>EirLWWbG</t>
+          <t>xvD54OdB</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>mazza andrea</t>
+          <t>modesto rui</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>8t5OxIB9</t>
+          <t>dWZccSvp</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>pereira pedro</t>
+          <t>padelli daniele</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>f9YA97SK</t>
+          <t>pObeJZYN</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>postiglione nicolo</t>
+          <t>palma matteo</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>40k1HnYj</t>
+          <t>S4Y7hFZd</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>scaramelli endris</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>GdRRPoEK</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>turati stefano</t>
-        </is>
-      </c>
+          <t>sava razvan</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
       <c r="BR4" t="inlineStr"/>
       <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>SlzlBsGu</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>adorni davide</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>4tOV7HLj</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>avella michele</t>
-        </is>
-      </c>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>zaHOeeSS</t>
+          <t>WvR2ASLR</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>besaggio michele</t>
+          <t>arnautovic marko</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>xC9rbYUF</t>
+          <t>hzUi0u2S</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>bianchi flavio</t>
+          <t>asllani kristjan</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>SKC8z0LF</t>
+          <t>QZQkZOWj</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>bisoli dimitri</t>
+          <t>carlos augusto</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>tGcjYXdg</t>
+          <t>IkcGiQBb</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>bjarnason birkir</t>
+          <t>correa joaquin</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>bX0itvNd</t>
+          <t>8Cf0NM4a</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>buhagiar trent</t>
+          <t>de vrij stefan</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>WIETgwMu</t>
+          <t>IuWFfk7l</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>corrado niccolo</t>
+          <t>di gennaro raffaele</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>dSlBQwJe</t>
+          <t>QR0j1ejk</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>moncini gabriele</t>
+          <t>dumfries denzel</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>Ama1rbYr</t>
+          <t>n5XVsSqd</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>muca zylyf</t>
+          <t>martinez josep</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>bTRbEf8c</t>
+          <t>jwujRP9P</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>nuamah patrick</t>
+          <t>palacios tomas</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>dtE4EsL3</t>
+          <t>xxuEya3O</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>verreth matthias</t>
-        </is>
-      </c>
-      <c r="CR4" t="inlineStr"/>
-      <c r="CS4" t="inlineStr"/>
-      <c r="CT4" t="inlineStr"/>
-      <c r="CU4" t="inlineStr"/>
+          <t>pavard benjamin</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>E9UW7Gv8</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>taremi mehdi</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>dlFNZSvb</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>zielinski piotr</t>
+        </is>
+      </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>8hN0kFPe</t>
+          <t>4W6Geckd</t>
         </is>
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>mari pablo</t>
+          <t>ekkelenkamp jurgen</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>8hN0kFPe</t>
+          <t>4W6Geckd</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>mari pablo</t>
+          <t>ekkelenkamp jurgen</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>jBspTfmj</t>
+          <t>2oBl3y29</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>carboni andrea</t>
+          <t>lovric sandi</t>
         </is>
       </c>
       <c r="DB4" t="inlineStr">
         <is>
-          <t>r5YvrtEQ</t>
+          <t>UVyQpa9t</t>
         </is>
       </c>
       <c r="DC4" t="inlineStr">
         <is>
-          <t>bianco alessandro</t>
+          <t>lucca lorenzo</t>
         </is>
       </c>
       <c r="DD4" t="inlineStr">
         <is>
-          <t>r5YvrtEQ</t>
+          <t>UVyQpa9t</t>
         </is>
       </c>
       <c r="DE4" t="inlineStr">
         <is>
-          <t>bianco alessandro</t>
+          <t>lucca lorenzo</t>
         </is>
       </c>
       <c r="DF4" t="inlineStr">
         <is>
-          <t>Wj6lXM52</t>
+          <t>SKxz4XFS</t>
         </is>
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>pessina matteo</t>
+          <t>davis keinan</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>8t5OxIB9</t>
+          <t>Y3ooARhm</t>
         </is>
       </c>
       <c r="DI4" t="inlineStr">
         <is>
-          <t>pereira pedro</t>
+          <t>atta arthur</t>
         </is>
       </c>
       <c r="DJ4" t="inlineStr">
         <is>
-          <t>8t5OxIB9</t>
+          <t>Y3ooARhm</t>
         </is>
       </c>
       <c r="DK4" t="inlineStr">
         <is>
-          <t>pereira pedro</t>
+          <t>atta arthur</t>
         </is>
       </c>
       <c r="DL4" t="inlineStr">
         <is>
-          <t>dbshNo9J</t>
+          <t>UDGFZQv8</t>
         </is>
       </c>
       <c r="DM4" t="inlineStr">
         <is>
-          <t>kiriakopoulos giorgos</t>
+          <t>karlstrom jesper</t>
         </is>
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>OrlLWHno</t>
+          <t>2kXZSD2S</t>
         </is>
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>izzo armando</t>
+          <t>brenner</t>
         </is>
       </c>
       <c r="DP4" t="inlineStr">
         <is>
-          <t>OrlLWHno</t>
+          <t>2kXZSD2S</t>
         </is>
       </c>
       <c r="DQ4" t="inlineStr">
         <is>
-          <t>izzo armando</t>
+          <t>brenner</t>
         </is>
       </c>
       <c r="DR4" t="inlineStr">
         <is>
-          <t>lOTx2Yho</t>
+          <t>SMbMSc26</t>
         </is>
       </c>
       <c r="DS4" t="inlineStr">
         <is>
-          <t>caldirola luca</t>
+          <t>thauvin florian</t>
         </is>
       </c>
       <c r="DT4" t="inlineStr">
         <is>
-          <t>ABbkAWNr</t>
+          <t>b5XwSo4Q</t>
         </is>
       </c>
       <c r="DU4" t="inlineStr">
         <is>
-          <t>bondo warren</t>
+          <t>bravo iker</t>
         </is>
       </c>
       <c r="DV4" t="inlineStr">
         <is>
-          <t>ABbkAWNr</t>
+          <t>b5XwSo4Q</t>
         </is>
       </c>
       <c r="DW4" t="inlineStr">
         <is>
-          <t>bondo warren</t>
+          <t>bravo iker</t>
         </is>
       </c>
       <c r="DX4" t="inlineStr">
         <is>
-          <t>ShD3fHfH</t>
+          <t>QHRhjNJJ</t>
         </is>
       </c>
       <c r="DY4" t="inlineStr">
         <is>
-          <t>d ambrosio danilo</t>
+          <t>zarraga oier</t>
         </is>
       </c>
       <c r="DZ4" t="inlineStr">
         <is>
-          <t>dtE4EsL3</t>
+          <t>QZQkZOWj</t>
         </is>
       </c>
       <c r="EA4" t="inlineStr">
         <is>
-          <t>verreth matthias</t>
+          <t>carlos augusto</t>
         </is>
       </c>
       <c r="EB4" t="inlineStr">
         <is>
-          <t>dtE4EsL3</t>
+          <t>QZQkZOWj</t>
         </is>
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>verreth matthias</t>
+          <t>carlos augusto</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
         <is>
-          <t>Mw804hef</t>
+          <t>W6lypZn3</t>
         </is>
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>paghera fabrizio</t>
+          <t>dimarco federico</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>bTRbEf8c</t>
+          <t>E9UW7Gv8</t>
         </is>
       </c>
       <c r="EG4" t="inlineStr">
         <is>
-          <t>nuamah patrick</t>
+          <t>taremi mehdi</t>
         </is>
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>bTRbEf8c</t>
+          <t>E9UW7Gv8</t>
         </is>
       </c>
       <c r="EI4" t="inlineStr">
         <is>
-          <t>nuamah patrick</t>
+          <t>taremi mehdi</t>
         </is>
       </c>
       <c r="EJ4" t="inlineStr">
         <is>
-          <t>pGN9fQkH</t>
+          <t>hMMX02Fm</t>
         </is>
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>olzer giacomo</t>
+          <t>thuram marcus</t>
         </is>
       </c>
       <c r="EL4" t="inlineStr">
         <is>
-          <t>WIETgwMu</t>
+          <t>8Cf0NM4a</t>
         </is>
       </c>
       <c r="EM4" t="inlineStr">
         <is>
-          <t>corrado niccolo</t>
+          <t>de vrij stefan</t>
         </is>
       </c>
       <c r="EN4" t="inlineStr">
         <is>
-          <t>WIETgwMu</t>
+          <t>8Cf0NM4a</t>
         </is>
       </c>
       <c r="EO4" t="inlineStr">
         <is>
-          <t>corrado niccolo</t>
+          <t>de vrij stefan</t>
         </is>
       </c>
       <c r="EP4" t="inlineStr">
         <is>
-          <t>Kh4HwK0A</t>
+          <t>On4TkPTN</t>
         </is>
       </c>
       <c r="EQ4" t="inlineStr">
         <is>
-          <t>borrelli gennaro</t>
+          <t>bastoni alessandro</t>
         </is>
       </c>
       <c r="ER4" t="inlineStr">
         <is>
-          <t>dSlBQwJe</t>
+          <t>dlFNZSvb</t>
         </is>
       </c>
       <c r="ES4" t="inlineStr">
         <is>
-          <t>moncini gabriele</t>
+          <t>zielinski piotr</t>
         </is>
       </c>
       <c r="ET4" t="inlineStr">
         <is>
-          <t>dSlBQwJe</t>
+          <t>dlFNZSvb</t>
         </is>
       </c>
       <c r="EU4" t="inlineStr">
         <is>
-          <t>moncini gabriele</t>
+          <t>zielinski piotr</t>
         </is>
       </c>
       <c r="EV4" t="inlineStr">
         <is>
-          <t>Czj6Fpfh</t>
+          <t>WlVuvCqU</t>
         </is>
       </c>
       <c r="EW4" t="inlineStr">
         <is>
-          <t>juric ante matej</t>
+          <t>frattesi davide</t>
         </is>
       </c>
       <c r="EX4" t="inlineStr">
         <is>
-          <t>bX0itvNd</t>
+          <t>IkcGiQBb</t>
         </is>
       </c>
       <c r="EY4" t="inlineStr">
         <is>
-          <t>buhagiar trent</t>
+          <t>correa joaquin</t>
         </is>
       </c>
       <c r="EZ4" t="inlineStr">
         <is>
-          <t>bX0itvNd</t>
+          <t>IkcGiQBb</t>
         </is>
       </c>
       <c r="FA4" t="inlineStr">
         <is>
-          <t>buhagiar trent</t>
+          <t>correa joaquin</t>
         </is>
       </c>
       <c r="FB4" t="inlineStr">
         <is>
-          <t>nH4bnBjF</t>
+          <t>QHk1CXUh</t>
         </is>
       </c>
       <c r="FC4" t="inlineStr">
         <is>
-          <t>fogliata riccardo</t>
+          <t>martinez lautaro</t>
         </is>
       </c>
       <c r="FD4" t="inlineStr"/>
       <c r="FE4" t="inlineStr"/>
-      <c r="FF4" t="inlineStr"/>
-      <c r="FG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>baMp22np</t>
+          <t>CCDxBZAc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MHD6IelJ</t>
+          <t>S6gN2QNC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>leali nicola</t>
+          <t>maignan mike</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>tW6pCCm8</t>
+          <t>zBkSUAjf</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>vogliacco alessandro</t>
+          <t>emerson royal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>vgmL526e</t>
+          <t>Sl6O3rbN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>bani mattia</t>
+          <t>gabbia matteo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Qydfoeer</t>
+          <t>AZn3ZNeI</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>vasquez johan</t>
+          <t>tomori fikayo</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>zLlOcqw4</t>
+          <t>ATurLHr0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>sabelli stefano</t>
+          <t>hernandez theo</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2XPmtx2l</t>
+          <t>dn3cCK1H</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>frendrup morten</t>
+          <t>fofana youssouf</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4InuIizr</t>
+          <t>f17EnPl3</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>badelj milan</t>
+          <t>reijnders tijani</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ei7zkE0o</t>
+          <t>vTuaEfRq</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>thorsby morten</t>
+          <t>pulisic christian</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>l4xhn6hC</t>
+          <t>fmkHs3aU</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>caricol aaron</t>
+          <t>morata alvaro</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>O4qi5hfc</t>
+          <t>AqOPWN5s</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>pinamonti andrea</t>
+          <t>leao rafael</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>AazXYT3h</t>
+          <t>OYhxyduf</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>vitinha</t>
+          <t>abraham tammy</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>6JqatiEa</t>
+          <t>OCJ3DqzU</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>silvestri marco</t>
+          <t>falcone wladimiro</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>rmvDqIY7</t>
+          <t>Sf4eaXAH</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>bereszynski bartosz</t>
+          <t>dorgu patrick</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Q7fl3yYg</t>
+          <t>25Z8Kyb5</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>romagnoli simone</t>
+          <t>baschirotto federico</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>xSd0xhgK</t>
+          <t>QJJ3NUdE</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>vulikic stipe</t>
+          <t>gaspar kialonga</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>rDl88SSs</t>
+          <t>GxXIRkFl</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>depaoli fabio</t>
+          <t>gallo antonino</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>GKxv62wr</t>
+          <t>nccbKjdO</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>akinsanmiro ebenezer</t>
+          <t>coulibaly lassana</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>tUw2S8Tb</t>
+          <t>2PPgUVm4</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>vieira ronaldo</t>
+          <t>ramadani ylber</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>x2S7DucC</t>
+          <t>fZXLQLKC</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>meulensteen melle</t>
+          <t>pierret balthazar</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>E92vTtZA</t>
+          <t>lUc5MiUn</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>ioannou nicholas</t>
+          <t>tete morente</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>tAqEMK0a</t>
+          <t>4CvqRml2</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>coda massimo</t>
+          <t>krstovic nikola</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>hxFdb12n</t>
+          <t>GWSMlnRk</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>la gumina antonio</t>
+          <t>rebic ante</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>U5DbE1A7</t>
+          <t>UL36DwiA</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>accornero federico</t>
+          <t>bartesaghi davide</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>Q1Sl1XK4</t>
+          <t>niW1cP0k</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>ahanor honest</t>
+          <t>chukwueze samuel</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>fTOU6yR2</t>
+          <t>bRnH1txc</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>ankeye david</t>
+          <t>sanchez alejandro jimenez</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>25uHtnwl</t>
+          <t>viIS0FT7</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>bohinen emil</t>
+          <t>jovic luka</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>EFmPm0Qo</t>
+          <t>6DpURWF8</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>de winter koni</t>
+          <t>loftus cheek ruben</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>QopKhlIm</t>
+          <t>ETMctXs4</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>ekhator jeff</t>
+          <t>musah yunus</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>vZY7FZwP</t>
+          <t>Qm2DVwBO</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>gollini pierluigi</t>
+          <t>pavlovic strahinja</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>vw0NcNnU</t>
+          <t>bwgnNY5o</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>kasa lior</t>
+          <t>raveyre noah</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>6BUzxLAe</t>
+          <t>4lL9syGa</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>marcandalli alessandro</t>
+          <t>terracciano filippo</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>WOffNMWA</t>
+          <t>0vSsR1xI</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>matturro romero alan</t>
+          <t>thiaw malick</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>tSUumbUT</t>
+          <t>h8lbX15I</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>miretti fabio</t>
+          <t>torriani lorenzo</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>MsjFcjtJ</t>
+          <t>ppSIryD2</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>sommariva daniele</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>xjWe0TTo</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>zanoli alessandro</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>6XMPoYMf</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>barreca antonio</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>dpI0AACN</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>bellemo alessandro</t>
-        </is>
-      </c>
+          <t>zeroli kevin</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr"/>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>2PcLSPHS</t>
+          <t>IoRXiRdq</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>benedetti leonardo</t>
+          <t>banda lameck</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>vgf4LRaj</t>
+          <t>WEh0KZMT</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>borini fabio</t>
+          <t>borbei alexandru</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>IooZNoIP</t>
+          <t>vVyq9D0S</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>giordano simone</t>
+          <t>burnete catalin</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>KrODGzyo</t>
+          <t>I9wPkuuh</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>kasami pajtim</t>
+          <t>fruchtl christian</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>tOvdMMUq</t>
+          <t>4jKQUIgi</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>ravaglia nicola</t>
+          <t>hasa luis</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>E3RnK86O</t>
+          <t>riY6rQKH</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>riccio alessandro</t>
+          <t>jean gaby</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>p49C8BCr</t>
+          <t>bygrxvpg</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>sekulov nikola</t>
+          <t>marchwinski filip</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>WpuYwQHd</t>
+          <t>xOh4r9KI</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>tutino gennaro</t>
+          <t>mcjannet ed</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>dpMPW6zh</t>
+          <t>lQ1WQFtO</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>venuti lorenzo</t>
+          <t>oudin remi</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>jeW6mAhJ</t>
+          <t>04Pk3MMd</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>veroli davide</t>
+          <t>pelmard andy</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>6B2hAjdT</t>
+          <t>APPhFofM</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>vismara paolo</t>
+          <t>pierotti santiago</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>6qpSLKkb</t>
+          <t>bNNOGcFF</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>yepes gerard</t>
+          <t>rafia hamza</t>
         </is>
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>xjWe0TTo</t>
+          <t>6DpURWF8</t>
         </is>
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>zanoli alessandro</t>
+          <t>loftus cheek ruben</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>xjWe0TTo</t>
+          <t>6DpURWF8</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>zanoli alessandro</t>
+          <t>loftus cheek ruben</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>zLlOcqw4</t>
+          <t>fmkHs3aU</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>sabelli stefano</t>
+          <t>morata alvaro</t>
         </is>
       </c>
       <c r="DB5" t="inlineStr">
         <is>
-          <t>WOffNMWA</t>
+          <t>ETMctXs4</t>
         </is>
       </c>
       <c r="DC5" t="inlineStr">
         <is>
-          <t>matturro romero alan</t>
+          <t>musah yunus</t>
         </is>
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>WOffNMWA</t>
+          <t>ETMctXs4</t>
         </is>
       </c>
       <c r="DE5" t="inlineStr">
         <is>
-          <t>matturro romero alan</t>
+          <t>musah yunus</t>
         </is>
       </c>
       <c r="DF5" t="inlineStr">
         <is>
-          <t>l4xhn6hC</t>
+          <t>dn3cCK1H</t>
         </is>
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>caricol aaron</t>
+          <t>fofana youssouf</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>tSUumbUT</t>
+          <t>niW1cP0k</t>
         </is>
       </c>
       <c r="DI5" t="inlineStr">
         <is>
-          <t>miretti fabio</t>
+          <t>chukwueze samuel</t>
         </is>
       </c>
       <c r="DJ5" t="inlineStr">
         <is>
-          <t>tSUumbUT</t>
+          <t>niW1cP0k</t>
         </is>
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>miretti fabio</t>
+          <t>chukwueze samuel</t>
         </is>
       </c>
       <c r="DL5" t="inlineStr">
         <is>
-          <t>AazXYT3h</t>
+          <t>vTuaEfRq</t>
         </is>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>vitinha</t>
+          <t>pulisic christian</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>fTOU6yR2</t>
+          <t>UL36DwiA</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>ankeye david</t>
+          <t>bartesaghi davide</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
         <is>
-          <t>fTOU6yR2</t>
+          <t>UL36DwiA</t>
         </is>
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
-          <t>ankeye david</t>
+          <t>bartesaghi davide</t>
         </is>
       </c>
       <c r="DR5" t="inlineStr">
         <is>
-          <t>O4qi5hfc</t>
+          <t>ATurLHr0</t>
         </is>
       </c>
       <c r="DS5" t="inlineStr">
         <is>
-          <t>pinamonti andrea</t>
+          <t>hernandez theo</t>
         </is>
       </c>
       <c r="DT5" t="inlineStr">
         <is>
-          <t>25uHtnwl</t>
+          <t>viIS0FT7</t>
         </is>
       </c>
       <c r="DU5" t="inlineStr">
         <is>
-          <t>bohinen emil</t>
+          <t>jovic luka</t>
         </is>
       </c>
       <c r="DV5" t="inlineStr">
         <is>
-          <t>25uHtnwl</t>
+          <t>viIS0FT7</t>
         </is>
       </c>
       <c r="DW5" t="inlineStr">
         <is>
-          <t>bohinen emil</t>
+          <t>jovic luka</t>
         </is>
       </c>
       <c r="DX5" t="inlineStr">
         <is>
-          <t>4InuIizr</t>
+          <t>OYhxyduf</t>
         </is>
       </c>
       <c r="DY5" t="inlineStr">
         <is>
-          <t>badelj milan</t>
+          <t>abraham tammy</t>
         </is>
       </c>
       <c r="DZ5" t="inlineStr">
         <is>
-          <t>2PcLSPHS</t>
+          <t>IoRXiRdq</t>
         </is>
       </c>
       <c r="EA5" t="inlineStr">
         <is>
-          <t>benedetti leonardo</t>
+          <t>banda lameck</t>
         </is>
       </c>
       <c r="EB5" t="inlineStr">
         <is>
-          <t>2PcLSPHS</t>
+          <t>IoRXiRdq</t>
         </is>
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>benedetti leonardo</t>
+          <t>banda lameck</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>GKxv62wr</t>
+          <t>lUc5MiUn</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>akinsanmiro ebenezer</t>
+          <t>tete morente</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>WpuYwQHd</t>
+          <t>bNNOGcFF</t>
         </is>
       </c>
       <c r="EG5" t="inlineStr">
         <is>
-          <t>tutino gennaro</t>
+          <t>rafia hamza</t>
         </is>
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>WpuYwQHd</t>
+          <t>bNNOGcFF</t>
         </is>
       </c>
       <c r="EI5" t="inlineStr">
         <is>
-          <t>tutino gennaro</t>
+          <t>rafia hamza</t>
         </is>
       </c>
       <c r="EJ5" t="inlineStr">
         <is>
-          <t>tAqEMK0a</t>
+          <t>fZXLQLKC</t>
         </is>
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>coda massimo</t>
+          <t>pierret balthazar</t>
         </is>
       </c>
       <c r="EL5" t="inlineStr">
         <is>
-          <t>6XMPoYMf</t>
+          <t>APPhFofM</t>
         </is>
       </c>
       <c r="EM5" t="inlineStr">
         <is>
-          <t>barreca antonio</t>
+          <t>pierotti santiago</t>
         </is>
       </c>
       <c r="EN5" t="inlineStr">
         <is>
-          <t>6XMPoYMf</t>
+          <t>APPhFofM</t>
         </is>
       </c>
       <c r="EO5" t="inlineStr">
         <is>
-          <t>barreca antonio</t>
+          <t>pierotti santiago</t>
         </is>
       </c>
       <c r="EP5" t="inlineStr">
         <is>
-          <t>E92vTtZA</t>
+          <t>GWSMlnRk</t>
         </is>
       </c>
       <c r="EQ5" t="inlineStr">
         <is>
-          <t>ioannou nicholas</t>
+          <t>rebic ante</t>
         </is>
       </c>
       <c r="ER5" t="inlineStr">
         <is>
-          <t>vgf4LRaj</t>
+          <t>lQ1WQFtO</t>
         </is>
       </c>
       <c r="ES5" t="inlineStr">
         <is>
-          <t>borini fabio</t>
+          <t>oudin remi</t>
         </is>
       </c>
       <c r="ET5" t="inlineStr">
         <is>
-          <t>vgf4LRaj</t>
+          <t>lQ1WQFtO</t>
         </is>
       </c>
       <c r="EU5" t="inlineStr">
         <is>
-          <t>borini fabio</t>
+          <t>oudin remi</t>
         </is>
       </c>
       <c r="EV5" t="inlineStr">
         <is>
-          <t>hxFdb12n</t>
+          <t>nccbKjdO</t>
         </is>
       </c>
       <c r="EW5" t="inlineStr">
         <is>
-          <t>la gumina antonio</t>
-        </is>
-      </c>
-      <c r="EX5" t="inlineStr">
-        <is>
-          <t>p49C8BCr</t>
-        </is>
-      </c>
-      <c r="EY5" t="inlineStr">
-        <is>
-          <t>sekulov nikola</t>
-        </is>
-      </c>
-      <c r="EZ5" t="inlineStr">
-        <is>
-          <t>p49C8BCr</t>
-        </is>
-      </c>
-      <c r="FA5" t="inlineStr">
-        <is>
-          <t>sekulov nikola</t>
-        </is>
-      </c>
-      <c r="FB5" t="inlineStr">
-        <is>
-          <t>tUw2S8Tb</t>
-        </is>
-      </c>
-      <c r="FC5" t="inlineStr">
-        <is>
-          <t>vieira ronaldo</t>
-        </is>
-      </c>
-      <c r="FD5" t="inlineStr"/>
-      <c r="FE5" t="inlineStr"/>
-      <c r="FF5" t="inlineStr"/>
-      <c r="FG5" t="inlineStr"/>
+          <t>coulibaly lassana</t>
+        </is>
+      </c>
+      <c r="EX5" t="inlineStr"/>
+      <c r="EY5" t="inlineStr"/>
+      <c r="EZ5" t="inlineStr"/>
+      <c r="FA5" t="inlineStr"/>
+      <c r="FB5" t="inlineStr"/>
+      <c r="FC5" t="inlineStr"/>
+      <c r="FD5" t="inlineStr">
+        <is>
+          <t>xhN6Eae7</t>
+        </is>
+      </c>
+      <c r="FE5" t="inlineStr">
+        <is>
+          <t>samooja jasper</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>xCj1xWPj</t>
+          <t>jwmmlzio</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S4Y7hFZd</t>
+          <t>vJSWqc3U</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sava razvan</t>
+          <t>radunovic boris</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>QgfEnOwH</t>
+          <t>vRCJaryd</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>abankwah james</t>
+          <t>pucino raffaele</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0CykEP51</t>
+          <t>joCeChcm</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>bijol jaka</t>
+          <t>vicari francesco</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>jaNZBJgT</t>
+          <t>K4ftNDkl</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>toure souleymane</t>
+          <t>mantovani valerio</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>xvD54OdB</t>
+          <t>bFSFG3sT</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>modesto rui</t>
+          <t>olivieri andrea</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2oBl3y29</t>
+          <t>8EOkxnms</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lovric sandi</t>
+          <t>lella nunzio</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>QHRhjNJJ</t>
+          <t>Gl31cksa</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>zarraga oier</t>
+          <t>benali ahmad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>ChzBGkMR</t>
+          <t>UFsffxn9</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>payero martin</t>
+          <t>maita mattia</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>GAzjxceh</t>
+          <t>2DjEKsjr</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>zemura jordan</t>
+          <t>dorval mehdi</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>b5XwSo4Q</t>
+          <t>GCL4UYe3</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>bravo iker</t>
+          <t>falletti cesar</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>UVyQpa9t</t>
+          <t>lEiQbqRi</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>lucca lorenzo</t>
+          <t>lasagna kevin</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>l0e0BnSA</t>
+          <t>2ep1Q9sS</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>fiorillo vincenzo</t>
+          <t>micai alessandro</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Im8vPlLt</t>
+          <t>nPaTBKkJ</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>ghiglione paolo</t>
+          <t>venturi michael</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2uPbwswk</t>
+          <t>25OhQNhD</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ruggeri fabio</t>
+          <t>camporese michele</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>lWANALyo</t>
+          <t>WlJRaVcb</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>velthuis tijs</t>
+          <t>caporale alessandro</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>hCBiTrxs</t>
+          <t>GAjUdy0c</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>jaroszynski pavel</t>
+          <t>ricciardi manuel</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>phFkXFtU</t>
+          <t>GIIVeUW1</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>hrustic ajdin</t>
+          <t>mauri jose</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>KEdDR3M7</t>
+          <t>6q2NY0gd</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>soriano roberto</t>
+          <t>charlys</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0rM28Wn3</t>
+          <t>WMM2MKsk</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>tello andres</t>
+          <t>ricci giacomo</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>IiIBwl8s</t>
+          <t>0b0UNkXD</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>kallon yayah</t>
+          <t>mazzocchi simone</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>IN4rltwr</t>
+          <t>4CxkxV7L</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>simy</t>
+          <t>kouan christian</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>jcWKCztM</t>
+          <t>hhJIUYwm</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>dalmonte nicola</t>
+          <t>fumagalli tommaso</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>Y3ooARhm</t>
+          <t>zsBl6R0S</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>atta arthur</t>
+          <t>bellomo nicola</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2kXZSD2S</t>
+          <t>x4AiZlG7</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>brenner</t>
+          <t>favasuli costantino</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>SKxz4XFS</t>
+          <t>xlic3PnN</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>davis keinan</t>
+          <t>favilli andrea</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>MXSXXNLr</t>
+          <t>M9Jn9Zm9</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>ebosse enzo</t>
+          <t>maiello raffaele</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>6XCZJG4M</t>
+          <t>WAWziD2c</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>ehizibue kingsley</t>
+          <t>manzari giacomo</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4W6Geckd</t>
+          <t>Q9PDryv2</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>ekkelenkamp jurgen</t>
+          <t>novakovich andrija</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>42ADo7dd</t>
+          <t>2J5yEYd4</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>kabasele christian</t>
+          <t>obaretin nosa edward</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>UDGFZQv8</t>
+          <t>t0rMk0s7</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>karlstrom jesper</t>
+          <t>pissardo marco</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>Gr6T6rIt</t>
+          <t>xStvhMAR</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>okoye maduks</t>
+          <t>saco coli</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>dWZccSvp</t>
+          <t>YgsNSpKb</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>padelli daniele</t>
+          <t>sgarbi lorenzo</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>pObeJZYN</t>
+          <t>KKpjmCfA</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>palma matteo</t>
+          <t>sibilli giuseppe</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>SMbMSc26</t>
+          <t>4jyY67mb</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>thauvin florian</t>
+          <t>tripaldelli alessandro</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr"/>
       <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>4jCqyBoe</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>amatucci lorenzo</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>2NEiLzlK</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>braaf jayden</t>
-        </is>
-      </c>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>b5OLGEKk</t>
+          <t>rZC7dOvh</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>bronn dylan</t>
+          <t>ciervo riccardo</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>raWfPms5</t>
+          <t>Szz1Ydfm</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>corriere francesco</t>
+          <t>cimino baldovino</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>bX4esuFb</t>
+          <t>n5ugiXLC</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>ferrari gianmarco</t>
+          <t>d orazio tommaso</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>EFz3cpqf</t>
+          <t>MFTLnkXH</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>gentile davide</t>
+          <t>dalle mura christian</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>fmW4DLwJ</t>
+          <t>UaY4ZNC1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>maggiore giulio</t>
+          <t>florenz aldo</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>OMiJz5gi</t>
+          <t>CGriWp56</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>njoh lilian</t>
+          <t>hristov andrea</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>MTQaLOIC</t>
+          <t>GAnUo3OH</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>reine adelaide jeff</t>
+          <t>kourfalidis christos</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>dvzcWaun</t>
+          <t>xIWZdkGt</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>sepe luigi</t>
+          <t>rizzo pinna andrea</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>0npaWwAk</t>
+          <t>6kdfCmVL</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>stojanovic petar</t>
+          <t>sankoh mohamed</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>S8GkvmO5</t>
+          <t>0QAtZqHu</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>torregrossa ernesto</t>
+          <t>strizzolo luca</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>UkKychK3</t>
+          <t>8lySR7S9</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>verde daniele</t>
+          <t>vettorel thomas</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>QultNmNB</t>
+          <t>YmE6Aqul</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
         <is>
-          <t>wlodarczyk szymon</t>
+          <t>zilli massimo</t>
         </is>
       </c>
       <c r="CV6" t="inlineStr">
         <is>
-          <t>4W6Geckd</t>
+          <t>KKpjmCfA</t>
         </is>
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>ekkelenkamp jurgen</t>
+          <t>sibilli giuseppe</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>4W6Geckd</t>
+          <t>KKpjmCfA</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>ekkelenkamp jurgen</t>
+          <t>sibilli giuseppe</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>ChzBGkMR</t>
+          <t>GCL4UYe3</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>payero martin</t>
+          <t>falletti cesar</t>
         </is>
       </c>
       <c r="DB6" t="inlineStr">
         <is>
-          <t>Y3ooARhm</t>
+          <t>xStvhMAR</t>
         </is>
       </c>
       <c r="DC6" t="inlineStr">
         <is>
-          <t>atta arthur</t>
+          <t>saco coli</t>
         </is>
       </c>
       <c r="DD6" t="inlineStr">
         <is>
-          <t>Y3ooARhm</t>
+          <t>xStvhMAR</t>
         </is>
       </c>
       <c r="DE6" t="inlineStr">
         <is>
-          <t>atta arthur</t>
+          <t>saco coli</t>
         </is>
       </c>
       <c r="DF6" t="inlineStr">
         <is>
-          <t>2oBl3y29</t>
+          <t>UFsffxn9</t>
         </is>
       </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>lovric sandi</t>
+          <t>maita mattia</t>
         </is>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
-          <t>SKxz4XFS</t>
+          <t>2J5yEYd4</t>
         </is>
       </c>
       <c r="DI6" t="inlineStr">
         <is>
-          <t>davis keinan</t>
+          <t>obaretin nosa edward</t>
         </is>
       </c>
       <c r="DJ6" t="inlineStr">
         <is>
-          <t>SKxz4XFS</t>
+          <t>2J5yEYd4</t>
         </is>
       </c>
       <c r="DK6" t="inlineStr">
         <is>
-          <t>davis keinan</t>
+          <t>obaretin nosa edward</t>
         </is>
       </c>
       <c r="DL6" t="inlineStr">
         <is>
-          <t>UVyQpa9t</t>
+          <t>2DjEKsjr</t>
         </is>
       </c>
       <c r="DM6" t="inlineStr">
         <is>
-          <t>lucca lorenzo</t>
+          <t>dorval mehdi</t>
         </is>
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>MXSXXNLr</t>
+          <t>x4AiZlG7</t>
         </is>
       </c>
       <c r="DO6" t="inlineStr">
         <is>
-          <t>ebosse enzo</t>
+          <t>favasuli costantino</t>
         </is>
       </c>
       <c r="DP6" t="inlineStr">
         <is>
-          <t>MXSXXNLr</t>
+          <t>x4AiZlG7</t>
         </is>
       </c>
       <c r="DQ6" t="inlineStr">
         <is>
-          <t>ebosse enzo</t>
+          <t>favasuli costantino</t>
         </is>
       </c>
       <c r="DR6" t="inlineStr">
         <is>
-          <t>jaNZBJgT</t>
+          <t>bFSFG3sT</t>
         </is>
       </c>
       <c r="DS6" t="inlineStr">
         <is>
-          <t>toure souleymane</t>
+          <t>olivieri andrea</t>
         </is>
       </c>
       <c r="DT6" t="inlineStr">
         <is>
-          <t>pObeJZYN</t>
+          <t>Q9PDryv2</t>
         </is>
       </c>
       <c r="DU6" t="inlineStr">
         <is>
-          <t>palma matteo</t>
+          <t>novakovich andrija</t>
         </is>
       </c>
       <c r="DV6" t="inlineStr">
         <is>
-          <t>pObeJZYN</t>
+          <t>Q9PDryv2</t>
         </is>
       </c>
       <c r="DW6" t="inlineStr">
         <is>
-          <t>palma matteo</t>
+          <t>novakovich andrija</t>
         </is>
       </c>
       <c r="DX6" t="inlineStr">
         <is>
-          <t>QgfEnOwH</t>
+          <t>lEiQbqRi</t>
         </is>
       </c>
       <c r="DY6" t="inlineStr">
         <is>
-          <t>abankwah james</t>
+          <t>lasagna kevin</t>
         </is>
       </c>
       <c r="DZ6" t="inlineStr">
         <is>
-          <t>fmW4DLwJ</t>
+          <t>UaY4ZNC1</t>
         </is>
       </c>
       <c r="EA6" t="inlineStr">
         <is>
-          <t>maggiore giulio</t>
+          <t>florenz aldo</t>
         </is>
       </c>
       <c r="EB6" t="inlineStr">
         <is>
-          <t>fmW4DLwJ</t>
+          <t>UaY4ZNC1</t>
         </is>
       </c>
       <c r="EC6" t="inlineStr">
         <is>
-          <t>maggiore giulio</t>
+          <t>florenz aldo</t>
         </is>
       </c>
       <c r="ED6" t="inlineStr">
         <is>
-          <t>phFkXFtU</t>
+          <t>4CxkxV7L</t>
         </is>
       </c>
       <c r="EE6" t="inlineStr">
         <is>
-          <t>hrustic ajdin</t>
+          <t>kouan christian</t>
         </is>
       </c>
       <c r="EF6" t="inlineStr">
         <is>
-          <t>UkKychK3</t>
+          <t>0QAtZqHu</t>
         </is>
       </c>
       <c r="EG6" t="inlineStr">
         <is>
-          <t>verde daniele</t>
+          <t>strizzolo luca</t>
         </is>
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>UkKychK3</t>
+          <t>0QAtZqHu</t>
         </is>
       </c>
       <c r="EI6" t="inlineStr">
         <is>
-          <t>verde daniele</t>
+          <t>strizzolo luca</t>
         </is>
       </c>
       <c r="EJ6" t="inlineStr">
         <is>
-          <t>jcWKCztM</t>
+          <t>GIIVeUW1</t>
         </is>
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>dalmonte nicola</t>
+          <t>mauri jose</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
         <is>
-          <t>S8GkvmO5</t>
+          <t>rZC7dOvh</t>
         </is>
       </c>
       <c r="EM6" t="inlineStr">
         <is>
-          <t>torregrossa ernesto</t>
+          <t>ciervo riccardo</t>
         </is>
       </c>
       <c r="EN6" t="inlineStr">
         <is>
-          <t>S8GkvmO5</t>
+          <t>rZC7dOvh</t>
         </is>
       </c>
       <c r="EO6" t="inlineStr">
         <is>
-          <t>torregrossa ernesto</t>
+          <t>ciervo riccardo</t>
         </is>
       </c>
       <c r="EP6" t="inlineStr">
         <is>
-          <t>KEdDR3M7</t>
+          <t>WMM2MKsk</t>
         </is>
       </c>
       <c r="EQ6" t="inlineStr">
         <is>
-          <t>soriano roberto</t>
+          <t>ricci giacomo</t>
         </is>
       </c>
       <c r="ER6" t="inlineStr">
         <is>
-          <t>2NEiLzlK</t>
+          <t>xIWZdkGt</t>
         </is>
       </c>
       <c r="ES6" t="inlineStr">
         <is>
-          <t>braaf jayden</t>
+          <t>rizzo pinna andrea</t>
         </is>
       </c>
       <c r="ET6" t="inlineStr">
         <is>
-          <t>2NEiLzlK</t>
+          <t>xIWZdkGt</t>
         </is>
       </c>
       <c r="EU6" t="inlineStr">
         <is>
-          <t>braaf jayden</t>
+          <t>rizzo pinna andrea</t>
         </is>
       </c>
       <c r="EV6" t="inlineStr">
         <is>
-          <t>IiIBwl8s</t>
+          <t>0b0UNkXD</t>
         </is>
       </c>
       <c r="EW6" t="inlineStr">
         <is>
-          <t>kallon yayah</t>
+          <t>mazzocchi simone</t>
         </is>
       </c>
       <c r="EX6" t="inlineStr">
         <is>
-          <t>4jCqyBoe</t>
+          <t>YmE6Aqul</t>
         </is>
       </c>
       <c r="EY6" t="inlineStr">
         <is>
-          <t>amatucci lorenzo</t>
+          <t>zilli massimo</t>
         </is>
       </c>
       <c r="EZ6" t="inlineStr">
         <is>
-          <t>4jCqyBoe</t>
+          <t>YmE6Aqul</t>
         </is>
       </c>
       <c r="FA6" t="inlineStr">
         <is>
-          <t>amatucci lorenzo</t>
+          <t>zilli massimo</t>
         </is>
       </c>
       <c r="FB6" t="inlineStr">
         <is>
-          <t>IN4rltwr</t>
+          <t>GAjUdy0c</t>
         </is>
       </c>
       <c r="FC6" t="inlineStr">
         <is>
-          <t>simy</t>
+          <t>ricciardi manuel</t>
         </is>
       </c>
       <c r="FD6" t="inlineStr"/>
       <c r="FE6" t="inlineStr"/>
-      <c r="FF6" t="inlineStr"/>
-      <c r="FG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>h2uVDr1f</t>
+          <t>vaTsAHD4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ULMctLS6</t>
+          <t>QJM49URT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nicolas andrade</t>
+          <t>bleve marco</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>dMiNmDpr</t>
+          <t>GAOlIzwG</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>calabresi arturo</t>
+          <t>illanes julian</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>tQ9LN1fh</t>
+          <t>Am0oVUF6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>rus adrian</t>
+          <t>hermannsson hjortur</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>nyOeW0BU</t>
+          <t>tMqmOicE</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>beruatto pietro</t>
+          <t>imperiale marco</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>hYIzCDnT</t>
+          <t>f71DcoeK</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>toure idrissa</t>
+          <t>bouah devid eugene</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CYcsJc7H</t>
+          <t>ddvz0tcQ</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>hojholt malthe</t>
+          <t>capezzi leonardo</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>pSDZ73wA</t>
+          <t>dne3gePB</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>jevsenak zan</t>
+          <t>schiavi nicolas</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>ANXh14xc</t>
+          <t>hn4q1pAA</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>angori samuele</t>
+          <t>cicconi manuel</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>pr02pCCG</t>
+          <t>C0IePhv1</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>arena alessandro</t>
+          <t>finotto mattia</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>hA80raLj</t>
+          <t>dfo0RTSJ</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>mlakar jan</t>
+          <t>capello alessandro</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>S8AdeCEH</t>
+          <t>Kd5zFbti</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>lind alexander</t>
+          <t>cherubini luigi</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>dG0Lm68C</t>
+          <t>6wVqSqO0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>klinsmann jonathan</t>
+          <t>bardi francesco</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2J6W9OsT</t>
+          <t>bkpO1UAs</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>piacentini matteo</t>
+          <t>fiamozzi riccardo</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>fNkZk3Qs</t>
+          <t>baFaIqPm</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>prestia giuseppe</t>
+          <t>meroni andrea</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>8CpA5o79</t>
+          <t>Ug0GqtE0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>pieraccini simone</t>
+          <t>rozzio paolo</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2qAN5836</t>
+          <t>G0zPj5Ba</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>adamo emanuele</t>
+          <t>fontanarosa alessandro</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>hrgu7eZM</t>
+          <t>jumC8deM</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>francesconi matteo</t>
+          <t>sersanti alessandro</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>K4ZJo8cN</t>
+          <t>ziYCoya3</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>mendicino leonardo</t>
+          <t>stulac leo</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>nmdCa7Ds</t>
+          <t>67w6mUGh</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>celia raffaele</t>
+          <t>reinhart tobias</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>ADBJ4OrH</t>
+          <t>AwsyawQ1</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>antonucci mirko</t>
+          <t>portanova manolo</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>nLiu560a</t>
+          <t>0bwMG5SF</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>tavsan elayis</t>
+          <t>vergara antonio</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>hIdAwd5O</t>
+          <t>CEu5J6N8</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>van hooijdonk sydney</t>
+          <t>okwonkwo orji</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>d6546BZK</t>
+          <t>SEwp6Uhi</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>abildgaard oliver</t>
+          <t>belloni niccolo</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>hrJODeQE</t>
+          <t>z92952s6</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>bonfanti giovanni</t>
+          <t>cerri leonardo</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>dGAt06R5</t>
+          <t>xnMwyU45</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>bonfanti nicholas</t>
+          <t>chiorra niccolo</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>hQKJwYnd</t>
+          <t>bmwzhd5k</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>canestrelli simone</t>
+          <t>coppolaro mauro</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>xrpkAADs</t>
+          <t>2LTAy8I5</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>caracciolo antonio</t>
+          <t>falco filippo</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>rTL6MlyQ</t>
+          <t>AgoFEXP9</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>leoncini mattia</t>
+          <t>giovane samuel</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>trNqVCBI</t>
+          <t>0GYbO9xj</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>loria leonardo</t>
+          <t>guarino gabriele</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>IeO9PQjK</t>
+          <t>xM8qrrze</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>marin marius</t>
+          <t>oliana filippo</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>zFFYexZK</t>
+          <t>hpPoJ5jN</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>moreo stefano</t>
+          <t>palmieri riccardo</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>S4Gdo5p3</t>
+          <t>zPp0s4d5</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>piccinini gabriele</t>
+          <t>panico giuseppe</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>OnR1j6mM</t>
+          <t>AT5jymNl</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>raychev adrian</t>
+          <t>zanon simone</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>Q5dMN4HG</t>
+          <t>t6Pgd1eg</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>sapola motiejus</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>hEY0fdTF</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>semper adrian</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>n7piqBuG</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>bastoni simone</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>8vhUYvNN</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>calo giacomo</t>
-        </is>
-      </c>
+          <t>zuelli emanuele</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr"/>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>OQAZiTD2</t>
+          <t>46jUu380</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>chiarello riccardo</t>
+          <t>cavallini giacomo</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2k9zUaAa</t>
+          <t>lfpEEa5J</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>ciofi andrea</t>
+          <t>cigarini luca</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>xIKq8Lhb</t>
+          <t>YisAx5wl</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>curto marco</t>
+          <t>girma natan</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>tnsZtqGu</t>
+          <t>QqCsQcU5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>donnarumma daniele</t>
+          <t>gondo cedric</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4Eq1TORH</t>
+          <t>SpsFliY4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>hraiech saber</t>
+          <t>ignacchiti lorenzo</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>WrbFYwR8</t>
+          <t>08RKxF9J</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>kargbo augustus</t>
+          <t>libutti lorenzo</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>GtGjeC0b</t>
+          <t>M9Nbe4EG</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>manetti giulio</t>
+          <t>lucchesi lorenzo</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>EBw91VL5</t>
+          <t>UZADb54K</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>mangraviti massimiliano</t>
+          <t>maggio matteo</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>tlSr8Yco</t>
+          <t>AouSuCPP</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>pisseri matteo</t>
+          <t>marras manuel</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>4MMcPxki</t>
+          <t>ATMse0OQ</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>shpendi cristian</t>
+          <t>motta edoardo</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>rwjsRUCI</t>
+          <t>8WxIdbec</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>siano alessandro</t>
-        </is>
-      </c>
-      <c r="CT7" t="inlineStr"/>
-      <c r="CU7" t="inlineStr"/>
+          <t>nahounou yannis</t>
+        </is>
+      </c>
+      <c r="CT7" t="inlineStr">
+        <is>
+          <t>d0WK1pb6</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>vido luca</t>
+        </is>
+      </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>d6546BZK</t>
+          <t>zPp0s4d5</t>
         </is>
       </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>abildgaard oliver</t>
+          <t>panico giuseppe</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>d6546BZK</t>
+          <t>zPp0s4d5</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>abildgaard oliver</t>
+          <t>panico giuseppe</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>hA80raLj</t>
+          <t>dfo0RTSJ</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>mlakar jan</t>
+          <t>capello alessandro</t>
         </is>
       </c>
       <c r="DB7" t="inlineStr">
         <is>
-          <t>hrJODeQE</t>
+          <t>AgoFEXP9</t>
         </is>
       </c>
       <c r="DC7" t="inlineStr">
         <is>
-          <t>bonfanti giovanni</t>
+          <t>giovane samuel</t>
         </is>
       </c>
       <c r="DD7" t="inlineStr">
         <is>
-          <t>hrJODeQE</t>
+          <t>AgoFEXP9</t>
         </is>
       </c>
       <c r="DE7" t="inlineStr">
         <is>
-          <t>bonfanti giovanni</t>
+          <t>giovane samuel</t>
         </is>
       </c>
       <c r="DF7" t="inlineStr">
         <is>
-          <t>nyOeW0BU</t>
+          <t>ddvz0tcQ</t>
         </is>
       </c>
       <c r="DG7" t="inlineStr">
         <is>
-          <t>beruatto pietro</t>
+          <t>capezzi leonardo</t>
         </is>
       </c>
       <c r="DH7" t="inlineStr">
         <is>
-          <t>dGAt06R5</t>
+          <t>bmwzhd5k</t>
         </is>
       </c>
       <c r="DI7" t="inlineStr">
         <is>
-          <t>bonfanti nicholas</t>
+          <t>coppolaro mauro</t>
         </is>
       </c>
       <c r="DJ7" t="inlineStr">
         <is>
-          <t>dGAt06R5</t>
+          <t>bmwzhd5k</t>
         </is>
       </c>
       <c r="DK7" t="inlineStr">
         <is>
-          <t>bonfanti nicholas</t>
+          <t>coppolaro mauro</t>
         </is>
       </c>
       <c r="DL7" t="inlineStr">
         <is>
-          <t>hYIzCDnT</t>
+          <t>Am0oVUF6</t>
         </is>
       </c>
       <c r="DM7" t="inlineStr">
         <is>
-          <t>toure idrissa</t>
+          <t>hermannsson hjortur</t>
         </is>
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>xhLRqrX3</t>
+          <t>AT5jymNl</t>
         </is>
       </c>
       <c r="DO7" t="inlineStr">
         <is>
-          <t>vignato emanuel</t>
+          <t>zanon simone</t>
         </is>
       </c>
       <c r="DP7" t="inlineStr">
         <is>
-          <t>xhLRqrX3</t>
+          <t>AT5jymNl</t>
         </is>
       </c>
       <c r="DQ7" t="inlineStr">
         <is>
-          <t>vignato emanuel</t>
+          <t>zanon simone</t>
         </is>
       </c>
       <c r="DR7" t="inlineStr">
         <is>
-          <t>pSDZ73wA</t>
+          <t>f71DcoeK</t>
         </is>
       </c>
       <c r="DS7" t="inlineStr">
         <is>
-          <t>jevsenak zan</t>
+          <t>bouah devid eugene</t>
         </is>
       </c>
       <c r="DT7" t="inlineStr">
         <is>
-          <t>zFFYexZK</t>
+          <t>z92952s6</t>
         </is>
       </c>
       <c r="DU7" t="inlineStr">
         <is>
-          <t>moreo stefano</t>
+          <t>cerri leonardo</t>
         </is>
       </c>
       <c r="DV7" t="inlineStr">
         <is>
-          <t>zFFYexZK</t>
+          <t>z92952s6</t>
         </is>
       </c>
       <c r="DW7" t="inlineStr">
         <is>
-          <t>moreo stefano</t>
+          <t>cerri leonardo</t>
         </is>
       </c>
       <c r="DX7" t="inlineStr">
         <is>
-          <t>tQ9LN1fh</t>
+          <t>Kd5zFbti</t>
         </is>
       </c>
       <c r="DY7" t="inlineStr">
         <is>
-          <t>rus adrian</t>
+          <t>cherubini luigi</t>
         </is>
       </c>
       <c r="DZ7" t="inlineStr">
         <is>
-          <t>EBw91VL5</t>
+          <t>AouSuCPP</t>
         </is>
       </c>
       <c r="EA7" t="inlineStr">
         <is>
-          <t>mangraviti massimiliano</t>
+          <t>marras manuel</t>
         </is>
       </c>
       <c r="EB7" t="inlineStr">
         <is>
-          <t>EBw91VL5</t>
+          <t>AouSuCPP</t>
         </is>
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>mangraviti massimiliano</t>
+          <t>marras manuel</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
         <is>
-          <t>8CpA5o79</t>
+          <t>0bwMG5SF</t>
         </is>
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>pieraccini simone</t>
+          <t>vergara antonio</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>4Eq1TORH</t>
+          <t>d0WK1pb6</t>
         </is>
       </c>
       <c r="EG7" t="inlineStr">
         <is>
-          <t>hraiech saber</t>
+          <t>vido luca</t>
         </is>
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>4Eq1TORH</t>
+          <t>d0WK1pb6</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
         <is>
-          <t>hraiech saber</t>
+          <t>vido luca</t>
         </is>
       </c>
       <c r="EJ7" t="inlineStr">
         <is>
-          <t>K4ZJo8cN</t>
+          <t>bkpO1UAs</t>
         </is>
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>mendicino leonardo</t>
+          <t>fiamozzi riccardo</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>4MMcPxki</t>
+          <t>M9Nbe4EG</t>
         </is>
       </c>
       <c r="EM7" t="inlineStr">
         <is>
-          <t>shpendi cristian</t>
+          <t>lucchesi lorenzo</t>
         </is>
       </c>
       <c r="EN7" t="inlineStr">
         <is>
-          <t>4MMcPxki</t>
+          <t>M9Nbe4EG</t>
         </is>
       </c>
       <c r="EO7" t="inlineStr">
         <is>
-          <t>shpendi cristian</t>
+          <t>lucchesi lorenzo</t>
         </is>
       </c>
       <c r="EP7" t="inlineStr">
         <is>
-          <t>hIdAwd5O</t>
+          <t>jumC8deM</t>
         </is>
       </c>
       <c r="EQ7" t="inlineStr">
         <is>
-          <t>van hooijdonk sydney</t>
+          <t>sersanti alessandro</t>
         </is>
       </c>
       <c r="ER7" t="inlineStr">
         <is>
-          <t>2k9zUaAa</t>
+          <t>SpsFliY4</t>
         </is>
       </c>
       <c r="ES7" t="inlineStr">
         <is>
-          <t>ciofi andrea</t>
+          <t>ignacchiti lorenzo</t>
         </is>
       </c>
       <c r="ET7" t="inlineStr">
         <is>
-          <t>2k9zUaAa</t>
+          <t>SpsFliY4</t>
         </is>
       </c>
       <c r="EU7" t="inlineStr">
         <is>
-          <t>ciofi andrea</t>
+          <t>ignacchiti lorenzo</t>
         </is>
       </c>
       <c r="EV7" t="inlineStr">
         <is>
-          <t>2qAN5836</t>
+          <t>ziYCoya3</t>
         </is>
       </c>
       <c r="EW7" t="inlineStr">
         <is>
-          <t>adamo emanuele</t>
+          <t>stulac leo</t>
         </is>
       </c>
       <c r="EX7" t="inlineStr">
         <is>
-          <t>tnsZtqGu</t>
+          <t>QqCsQcU5</t>
         </is>
       </c>
       <c r="EY7" t="inlineStr">
         <is>
-          <t>donnarumma daniele</t>
+          <t>gondo cedric</t>
         </is>
       </c>
       <c r="EZ7" t="inlineStr">
         <is>
-          <t>tnsZtqGu</t>
+          <t>QqCsQcU5</t>
         </is>
       </c>
       <c r="FA7" t="inlineStr">
         <is>
-          <t>donnarumma daniele</t>
+          <t>gondo cedric</t>
         </is>
       </c>
       <c r="FB7" t="inlineStr">
         <is>
-          <t>nmdCa7Ds</t>
+          <t>CEu5J6N8</t>
         </is>
       </c>
       <c r="FC7" t="inlineStr">
         <is>
-          <t>celia raffaele</t>
-        </is>
-      </c>
-      <c r="FD7" t="inlineStr">
-        <is>
-          <t>WWMStvpn</t>
-        </is>
-      </c>
-      <c r="FE7" t="inlineStr">
-        <is>
-          <t>tosi lorenzo</t>
-        </is>
-      </c>
-      <c r="FF7" t="inlineStr">
-        <is>
-          <t>xhLRqrX3</t>
-        </is>
-      </c>
-      <c r="FG7" t="inlineStr">
-        <is>
-          <t>vignato emanuel</t>
-        </is>
-      </c>
+          <t>okwonkwo orji</t>
+        </is>
+      </c>
+      <c r="FD7" t="inlineStr"/>
+      <c r="FE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SG7bDmCr</t>
+          <t>4USV4sgM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mw0wd0xM</t>
+          <t>SxjadbLU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>milinkovic savic vanja</t>
+          <t>moldovan horatiu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>84cMABdJ</t>
+          <t>IJwHBntK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>walukiewicz sebastian</t>
+          <t>paz yeferson</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UZiNdd1Q</t>
+          <t>O0Ss5jSf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>maripan guillermo</t>
+          <t>muharemovic tarik</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4f3WP5vm</t>
+          <t>ILuvGx81</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>coco saul</t>
+          <t>romagna filippo</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ltnVl6l2</t>
+          <t>dQ1Evunq</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>pedersen marcus</t>
+          <t>doig josh</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>nRc0fR5f</t>
+          <t>rZYDo3K5</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>tameze adrien</t>
+          <t>iannoni edoardo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>KShlcp4N</t>
+          <t>jPrEU8Tr</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>linetty karol</t>
+          <t>boloca daniel</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>vkek8Ais</t>
+          <t>EF3UYlr3</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>gineitis gvidas</t>
+          <t>thorstvedt kristian</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>OvtFAISo</t>
+          <t>zNDPrjy8</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>lazaro valentino</t>
+          <t>pierini nicholas</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>OQYJ3VXT</t>
+          <t>f3tdpb62</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>karamoh yann</t>
+          <t>mulattieri samuele</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>4C0YmOaJ</t>
+          <t>EZVZoGs8</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>adams che</t>
+          <t>lauriente armand</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>KKXDLjg8</t>
+          <t>6Pbkbcv3</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>seghetti jacopo</t>
+          <t>gori stefano</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Ua5srQK6</t>
+          <t>QcPURnA3</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>de sciglio mattia</t>
+          <t>mateju ales</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>I52ibPrQ</t>
+          <t>AaYOi9YT</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>marianucci luca</t>
+          <t>wisniewski przemyslaw</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2eFCBn8A</t>
+          <t>OUZiJhvh</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>tosto lorenzo</t>
+          <t>bertola nicolo</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>GK1tPlKu</t>
+          <t>EgfizWFr</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>sambia solomon</t>
+          <t>vignali luca</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Q1sHUL1D</t>
+          <t>YTuQ6xad</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>haas nicolas</t>
+          <t>cassata francesco</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>YmvWlE1E</t>
+          <t>vZM5mg5N</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>henderson liam</t>
+          <t>esposito salvatore</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>4SWMMcZd</t>
+          <t>WEIpbflm</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>cacace liberato</t>
+          <t>bandinelli filippo</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>lYCSEEBl</t>
+          <t>2kJoCbl9</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>konate ismael</t>
+          <t>reca arkadiusz</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4pUDwSFI</t>
+          <t>MTtBqQfl</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>ekong emmanuel</t>
+          <t>di serio guiseppe</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>v3hpfVmF</t>
+          <t>dKXxEOKj</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>pellegri pietro</t>
+          <t>esposito francesco</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>GStMS8cB</t>
+          <t>4Of5akc5</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>bianay balcot come</t>
+          <t>antiste janis</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>hM1aIsWB</t>
+          <t>rJOfdpaA</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>ciammaglichella aaron</t>
+          <t>d andrea luca</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>AsEOFfdr</t>
+          <t>dxb0x43T</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>dembele ali</t>
+          <t>ghion andrea</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>zZcNEj5Q</t>
+          <t>t4NSHrlh</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>donnarumma antonio</t>
+          <t>lipani luca</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>vqZMiS0h</t>
+          <t>fDRMwkTQ</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>illic ivan</t>
+          <t>moro luca</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>fsw4UmgM</t>
+          <t>nodnKnAs</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>masina adam</t>
+          <t>obiang pedro</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>vwnI8wkF</t>
+          <t>M5l0hplp</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>nije eybi</t>
+          <t>odenthal cas</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>vR4315G2</t>
+          <t>C0qz46Jj</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>paleari alberto</t>
+          <t>pieragnolo edoardo</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>thdNLRpt</t>
+          <t>prHV7Xpt</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>ricci samuele</t>
+          <t>russo flavio</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>jNePUJ0b</t>
+          <t>d2BR3Upb</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>sanabria antonio</t>
+          <t>satalino giacomo</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>4vTK4LUr</t>
+          <t>IsGWKIMq</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>sosa borna</t>
+          <t>toljan jeremy</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>YirekWMs</t>
+          <t>2B5YqXFG</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>vojvoda mergim</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>v7zQxVoD</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>zapata duvan</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>jTWtnxud</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>anjorin faustino</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>dfcCpneb</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>brancolini federico</t>
-        </is>
-      </c>
+          <t>volpato cristian</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>YL741OaO</t>
+          <t>AkjDhEk0</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>colombo lorenzo</t>
+          <t>benvenuto mattia</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>WrbP1Sdg</t>
+          <t>CvWHSNg0</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>esposito sebastiano</t>
+          <t>candelari pietro</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>8lxchd9S</t>
+          <t>KWrHl314</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>goglichidze saba</t>
+          <t>colak antonio mirko</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>E7Jj74nK</t>
+          <t>KCtXlKaH</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>grassi alberto</t>
+          <t>degli duccio</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>jZgmSlM1</t>
+          <t>vs1w0sCd</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>gyasi emmanuel</t>
+          <t>elia salvatore</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>zJD6Mdr3</t>
+          <t>tCvX7iBP</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>pezzella giuseppe</t>
+          <t>falcinelli diego</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>8xn3Hfaq</t>
+          <t>r34Klsm2</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>popov bogdan</t>
+          <t>giorgeschi simone</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>U1piMQgC</t>
+          <t>xIj2TcyE</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>solbakken ola</t>
+          <t>hristov petko</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>4xCrFFMe</t>
+          <t>OpOdOpiR</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>vasquez devis</t>
+          <t>mascardi diego</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>bZmRuRzO</t>
+          <t>lpbxLFLT</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>viti mattia</t>
-        </is>
-      </c>
-      <c r="CR8" t="inlineStr"/>
-      <c r="CS8" t="inlineStr"/>
-      <c r="CT8" t="inlineStr"/>
-      <c r="CU8" t="inlineStr"/>
+          <t>nagy adam</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>zDHydpk5</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>salvador ferrer</t>
+        </is>
+      </c>
+      <c r="CT8" t="inlineStr">
+        <is>
+          <t>nRUWcY4c</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>soleri edoardo</t>
+        </is>
+      </c>
       <c r="CV8" t="inlineStr">
         <is>
-          <t>4vTK4LUr</t>
+          <t>IsGWKIMq</t>
         </is>
       </c>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>sosa borna</t>
+          <t>toljan jeremy</t>
         </is>
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>4vTK4LUr</t>
+          <t>IsGWKIMq</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>sosa borna</t>
+          <t>toljan jeremy</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>84cMABdJ</t>
+          <t>IJwHBntK</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>walukiewicz sebastian</t>
+          <t>paz yeferson</t>
         </is>
       </c>
       <c r="DB8" t="inlineStr">
         <is>
-          <t>v7zQxVoD</t>
+          <t>2B5YqXFG</t>
         </is>
       </c>
       <c r="DC8" t="inlineStr">
         <is>
-          <t>zapata duvan</t>
+          <t>volpato cristian</t>
         </is>
       </c>
       <c r="DD8" t="inlineStr">
         <is>
-          <t>v7zQxVoD</t>
+          <t>2B5YqXFG</t>
         </is>
       </c>
       <c r="DE8" t="inlineStr">
         <is>
-          <t>zapata duvan</t>
+          <t>volpato cristian</t>
         </is>
       </c>
       <c r="DF8" t="inlineStr">
         <is>
-          <t>vkek8Ais</t>
+          <t>zNDPrjy8</t>
         </is>
       </c>
       <c r="DG8" t="inlineStr">
         <is>
-          <t>gineitis gvidas</t>
+          <t>pierini nicholas</t>
         </is>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
-          <t>thdNLRpt</t>
+          <t>prHV7Xpt</t>
         </is>
       </c>
       <c r="DI8" t="inlineStr">
         <is>
-          <t>ricci samuele</t>
+          <t>russo flavio</t>
         </is>
       </c>
       <c r="DJ8" t="inlineStr">
         <is>
-          <t>thdNLRpt</t>
+          <t>prHV7Xpt</t>
         </is>
       </c>
       <c r="DK8" t="inlineStr">
         <is>
-          <t>ricci samuele</t>
+          <t>russo flavio</t>
         </is>
       </c>
       <c r="DL8" t="inlineStr">
         <is>
-          <t>nRc0fR5f</t>
+          <t>f3tdpb62</t>
         </is>
       </c>
       <c r="DM8" t="inlineStr">
         <is>
-          <t>tameze adrien</t>
+          <t>mulattieri samuele</t>
         </is>
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>vwnI8wkF</t>
+          <t>nodnKnAs</t>
         </is>
       </c>
       <c r="DO8" t="inlineStr">
         <is>
-          <t>nije eybi</t>
+          <t>obiang pedro</t>
         </is>
       </c>
       <c r="DP8" t="inlineStr">
         <is>
-          <t>vwnI8wkF</t>
+          <t>nodnKnAs</t>
         </is>
       </c>
       <c r="DQ8" t="inlineStr">
         <is>
-          <t>nije eybi</t>
+          <t>obiang pedro</t>
         </is>
       </c>
       <c r="DR8" t="inlineStr">
         <is>
-          <t>OQYJ3VXT</t>
+          <t>EF3UYlr3</t>
         </is>
       </c>
       <c r="DS8" t="inlineStr">
         <is>
-          <t>karamoh yann</t>
-        </is>
-      </c>
-      <c r="DT8" t="inlineStr">
-        <is>
-          <t>AsEOFfdr</t>
-        </is>
-      </c>
-      <c r="DU8" t="inlineStr">
-        <is>
-          <t>dembele ali</t>
-        </is>
-      </c>
-      <c r="DV8" t="inlineStr">
-        <is>
-          <t>AsEOFfdr</t>
-        </is>
-      </c>
-      <c r="DW8" t="inlineStr">
-        <is>
-          <t>dembele ali</t>
-        </is>
-      </c>
-      <c r="DX8" t="inlineStr">
-        <is>
-          <t>4f3WP5vm</t>
-        </is>
-      </c>
-      <c r="DY8" t="inlineStr">
-        <is>
-          <t>coco saul</t>
-        </is>
-      </c>
+          <t>thorstvedt kristian</t>
+        </is>
+      </c>
+      <c r="DT8" t="inlineStr"/>
+      <c r="DU8" t="inlineStr"/>
+      <c r="DV8" t="inlineStr"/>
+      <c r="DW8" t="inlineStr"/>
+      <c r="DX8" t="inlineStr"/>
+      <c r="DY8" t="inlineStr"/>
       <c r="DZ8" t="inlineStr">
         <is>
-          <t>U1piMQgC</t>
+          <t>nRUWcY4c</t>
         </is>
       </c>
       <c r="EA8" t="inlineStr">
         <is>
-          <t>solbakken ola</t>
+          <t>soleri edoardo</t>
         </is>
       </c>
       <c r="EB8" t="inlineStr">
         <is>
-          <t>U1piMQgC</t>
+          <t>nRUWcY4c</t>
         </is>
       </c>
       <c r="EC8" t="inlineStr">
         <is>
-          <t>solbakken ola</t>
+          <t>soleri edoardo</t>
         </is>
       </c>
       <c r="ED8" t="inlineStr">
         <is>
-          <t>lYCSEEBl</t>
+          <t>dKXxEOKj</t>
         </is>
       </c>
       <c r="EE8" t="inlineStr">
         <is>
-          <t>konate ismael</t>
+          <t>esposito francesco</t>
         </is>
       </c>
       <c r="EF8" t="inlineStr">
         <is>
-          <t>E7Jj74nK</t>
+          <t>lpbxLFLT</t>
         </is>
       </c>
       <c r="EG8" t="inlineStr">
         <is>
-          <t>grassi alberto</t>
+          <t>nagy adam</t>
         </is>
       </c>
       <c r="EH8" t="inlineStr">
         <is>
-          <t>E7Jj74nK</t>
+          <t>lpbxLFLT</t>
         </is>
       </c>
       <c r="EI8" t="inlineStr">
         <is>
-          <t>grassi alberto</t>
+          <t>nagy adam</t>
         </is>
       </c>
       <c r="EJ8" t="inlineStr">
         <is>
-          <t>YmvWlE1E</t>
+          <t>YTuQ6xad</t>
         </is>
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>henderson liam</t>
+          <t>cassata francesco</t>
         </is>
       </c>
       <c r="EL8" t="inlineStr">
         <is>
-          <t>YL741OaO</t>
+          <t>KWrHl314</t>
         </is>
       </c>
       <c r="EM8" t="inlineStr">
         <is>
-          <t>colombo lorenzo</t>
+          <t>colak antonio mirko</t>
         </is>
       </c>
       <c r="EN8" t="inlineStr">
         <is>
-          <t>YL741OaO</t>
+          <t>KWrHl314</t>
         </is>
       </c>
       <c r="EO8" t="inlineStr">
         <is>
-          <t>colombo lorenzo</t>
+          <t>colak antonio mirko</t>
         </is>
       </c>
       <c r="EP8" t="inlineStr">
         <is>
-          <t>v3hpfVmF</t>
+          <t>MTtBqQfl</t>
         </is>
       </c>
       <c r="EQ8" t="inlineStr">
         <is>
-          <t>pellegri pietro</t>
+          <t>di serio guiseppe</t>
         </is>
       </c>
       <c r="ER8" t="inlineStr">
         <is>
-          <t>jZgmSlM1</t>
+          <t>CvWHSNg0</t>
         </is>
       </c>
       <c r="ES8" t="inlineStr">
         <is>
-          <t>gyasi emmanuel</t>
+          <t>candelari pietro</t>
         </is>
       </c>
       <c r="ET8" t="inlineStr">
         <is>
-          <t>jZgmSlM1</t>
+          <t>CvWHSNg0</t>
         </is>
       </c>
       <c r="EU8" t="inlineStr">
         <is>
-          <t>gyasi emmanuel</t>
+          <t>candelari pietro</t>
         </is>
       </c>
       <c r="EV8" t="inlineStr">
         <is>
-          <t>GK1tPlKu</t>
+          <t>vZM5mg5N</t>
         </is>
       </c>
       <c r="EW8" t="inlineStr">
         <is>
-          <t>sambia solomon</t>
+          <t>esposito salvatore</t>
         </is>
       </c>
       <c r="EX8" t="inlineStr">
         <is>
-          <t>bZmRuRzO</t>
+          <t>vs1w0sCd</t>
         </is>
       </c>
       <c r="EY8" t="inlineStr">
         <is>
-          <t>viti mattia</t>
+          <t>elia salvatore</t>
         </is>
       </c>
       <c r="EZ8" t="inlineStr">
         <is>
-          <t>bZmRuRzO</t>
+          <t>vs1w0sCd</t>
         </is>
       </c>
       <c r="FA8" t="inlineStr">
         <is>
-          <t>viti mattia</t>
+          <t>elia salvatore</t>
         </is>
       </c>
       <c r="FB8" t="inlineStr">
         <is>
-          <t>2eFCBn8A</t>
+          <t>2kJoCbl9</t>
         </is>
       </c>
       <c r="FC8" t="inlineStr">
         <is>
-          <t>tosto lorenzo</t>
+          <t>reca arkadiusz</t>
         </is>
       </c>
       <c r="FD8" t="inlineStr"/>
       <c r="FE8" t="inlineStr"/>
-      <c r="FF8" t="inlineStr"/>
-      <c r="FG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WjBv9U0S</t>
+          <t>8vLb6ZCT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>zTdDPVna</t>
+          <t>GpcVQVTI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sherri alen</t>
+          <t>maniero luca</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6y7tiy6b</t>
+          <t>80gdKWOF</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>zappa gabriele</t>
+          <t>salvi alessandro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2c7LCGJR</t>
+          <t>KQJr2C6I</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>palomino jose</t>
+          <t>pavan nicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>YZEkc9qD</t>
+          <t>jiFEodbj</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>obert adam</t>
+          <t>angeli matteo</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>tnZd7uZQ</t>
+          <t>O4VaVa69</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>azzi paulo</t>
+          <t>carissoni lorenzo</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>thWJbHFE</t>
+          <t>EVzPaGzl</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>adopo michel</t>
+          <t>d alessio francesco</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>zaVrgWQt</t>
+          <t>l2Rt2EsD</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>makoumbou antoine</t>
+          <t>branca simone</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>pUpsjuw3</t>
+          <t>SnRbZOrK</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>augello tommaso</t>
+          <t>amatucci francesco</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>nNOKUM6f</t>
+          <t>K0AtvAAP</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>gaetano gianluca</t>
+          <t>desogus jacopo</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>69h4RBd7</t>
+          <t>Q741cgiO</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>felici mattia</t>
+          <t>ravasio mario</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>K0nUrV5K</t>
+          <t>dbk2r5CD</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>lapadula gianluca</t>
+          <t>pandolfi luca</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>8IlcJpOd</t>
+          <t>bNZfXB2q</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>saro gianluca</t>
+          <t>cerofolini michele</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>QD7M0ATr</t>
+          <t>fL14Xe6b</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>antov valentin</t>
+          <t>marchizza riccardo</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>r3yChj3j</t>
+          <t>4AXvWzji</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>moretti lorenzo</t>
+          <t>kalaj sergio</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>fLyWlO5j</t>
+          <t>W6Uqcx1k</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>lochoshvili luka</t>
+          <t>monterisi ilario</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>j7T2rzph</t>
+          <t>4UlxnksM</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>barbieri tommaso</t>
+          <t>oyono anthony</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>AoykjoMB</t>
+          <t>lAAgG4hD</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>pickel charles</t>
+          <t>cichella matteo</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>KI9lXC0P</t>
+          <t>Qga48RFm</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>majer zan</t>
+          <t>gelli francesco</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>UspinGse</t>
+          <t>4pxhfOad</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>milanese tommaso</t>
+          <t>garritano luca</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>pdJ2qg8l</t>
+          <t>YTpHlpak</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>quagliata giacomo</t>
+          <t>di stefano filippo</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>xpN4ICmj</t>
+          <t>QunHCDU2</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>johnsen dennis</t>
+          <t>tsadjout frank</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>MeskQr4l</t>
+          <t>AajjuPEj</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>de luca manuel</t>
+          <t>partipilo anthony</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>nBYARUG6</t>
+          <t>hUTyvgJA</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>ciocci giuseppe</t>
+          <t>cassano claudio</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>pIHBE5H5</t>
+          <t>v5Kz7B89</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>cogoni andrea</t>
+          <t>cecchetto andrea</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>E9t2kgz3</t>
+          <t>0dqCCCd6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>deiola alessandro</t>
+          <t>kastrati elhan</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>l6ZLUe9D</t>
+          <t>f3UWa8ss</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>luperto sebastiano</t>
+          <t>magrassi andrea</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>QZQ9DtPs</t>
+          <t>IooWgdIk</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>luvumbo zito</t>
+          <t>masciangelo edoardo</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>WYOcFAQk</t>
+          <t>KEyUOiHh</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>marin razvan</t>
+          <t>piccinini stefano</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>tvxzDyfa</t>
+          <t>2LoNIGf3</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>mutandwa kingstone</t>
+          <t>rabbi simone</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>CK8QgVjh</t>
+          <t>I3kYfG62</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>piccoli roberto</t>
+          <t>rizza alessio</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>0nQhrI82</t>
+          <t>tr0PFNGl</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>scuffet simone</t>
+          <t>scquizzato edoardo</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>40ggoSmN</t>
+          <t>Q7OEUsLS</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>viola nicolas</t>
+          <t>vita alessio</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>2csPLGHO</t>
+          <t>b1p7vpf3</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>zortea nadir</t>
+          <t>voltan davide</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr"/>
       <c r="BQ9" t="inlineStr"/>
       <c r="BR9" t="inlineStr"/>
       <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>8hcuiE2b</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>bianchetti matteo</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>jN7arfI0</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>buonaiuto cristian</t>
-        </is>
-      </c>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>4KEjxptI</t>
+          <t>KrttNVLt</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>castagnetti michele</t>
+          <t>ambrosino giuseppe</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>SnPwFapn</t>
+          <t>bJBRauoj</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>collocolo michele</t>
+          <t>begic tjas</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>pEUDpBZR</t>
+          <t>Ysk36pE4</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>fulignati andrea</t>
+          <t>bettella davide</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>rg2GWgeM</t>
+          <t>bVCSvTzl</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>jungdal andreas</t>
+          <t>bracaglia gabriele</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>tdJlhP53</t>
+          <t>2evqns7I</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>nasti marco</t>
+          <t>canotto luigi</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>xIUCaSh4</t>
+          <t>plNsoAhU</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>sernicola leonardo</t>
+          <t>haoudi hamza</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>zX8VztZq</t>
+          <t>b7dng8al</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>vandeputte jari</t>
+          <t>kvernadze giorgi</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>vJItNu2r</t>
+          <t>hfhlvfwf</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>vazquez franco</t>
-        </is>
-      </c>
-      <c r="CN9" t="inlineStr"/>
-      <c r="CO9" t="inlineStr"/>
-      <c r="CP9" t="inlineStr"/>
-      <c r="CQ9" t="inlineStr"/>
-      <c r="CR9" t="inlineStr"/>
-      <c r="CS9" t="inlineStr"/>
-      <c r="CT9" t="inlineStr"/>
-      <c r="CU9" t="inlineStr"/>
+          <t>machin jose</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>hjatkmbP</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>oyono jeremy</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>n79iW0sd</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>sene fallou</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>KWK0U27f</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>sorrentino alessandro</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
+          <t>YPwDDAst</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>szyminski przemyslaw</t>
+        </is>
+      </c>
       <c r="CV9" t="inlineStr">
         <is>
-          <t>CK8QgVjh</t>
+          <t>f3UWa8ss</t>
         </is>
       </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>piccoli roberto</t>
+          <t>magrassi andrea</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>CK8QgVjh</t>
+          <t>f3UWa8ss</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>piccoli roberto</t>
+          <t>magrassi andrea</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>69h4RBd7</t>
+          <t>Q741cgiO</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>felici mattia</t>
+          <t>ravasio mario</t>
         </is>
       </c>
       <c r="DB9" t="inlineStr">
         <is>
-          <t>40ggoSmN</t>
+          <t>Q7OEUsLS</t>
         </is>
       </c>
       <c r="DC9" t="inlineStr">
         <is>
-          <t>viola nicolas</t>
+          <t>vita alessio</t>
         </is>
       </c>
       <c r="DD9" t="inlineStr">
         <is>
-          <t>40ggoSmN</t>
+          <t>Q7OEUsLS</t>
         </is>
       </c>
       <c r="DE9" t="inlineStr">
         <is>
-          <t>viola nicolas</t>
+          <t>vita alessio</t>
         </is>
       </c>
       <c r="DF9" t="inlineStr">
         <is>
-          <t>nNOKUM6f</t>
+          <t>EVzPaGzl</t>
         </is>
       </c>
       <c r="DG9" t="inlineStr">
         <is>
-          <t>gaetano gianluca</t>
+          <t>d alessio francesco</t>
         </is>
       </c>
       <c r="DH9" t="inlineStr">
         <is>
-          <t>2csPLGHO</t>
+          <t>hUTyvgJA</t>
         </is>
       </c>
       <c r="DI9" t="inlineStr">
         <is>
-          <t>zortea nadir</t>
+          <t>cassano claudio</t>
         </is>
       </c>
       <c r="DJ9" t="inlineStr">
         <is>
-          <t>2csPLGHO</t>
+          <t>hUTyvgJA</t>
         </is>
       </c>
       <c r="DK9" t="inlineStr">
         <is>
-          <t>zortea nadir</t>
+          <t>cassano claudio</t>
         </is>
       </c>
       <c r="DL9" t="inlineStr">
         <is>
-          <t>pUpsjuw3</t>
+          <t>K0AtvAAP</t>
         </is>
       </c>
       <c r="DM9" t="inlineStr">
         <is>
-          <t>augello tommaso</t>
+          <t>desogus jacopo</t>
         </is>
       </c>
       <c r="DN9" t="inlineStr">
         <is>
-          <t>QZQ9DtPs</t>
+          <t>IooWgdIk</t>
         </is>
       </c>
       <c r="DO9" t="inlineStr">
         <is>
-          <t>luvumbo zito</t>
+          <t>masciangelo edoardo</t>
         </is>
       </c>
       <c r="DP9" t="inlineStr">
         <is>
-          <t>QZQ9DtPs</t>
+          <t>IooWgdIk</t>
         </is>
       </c>
       <c r="DQ9" t="inlineStr">
         <is>
-          <t>luvumbo zito</t>
+          <t>masciangelo edoardo</t>
         </is>
       </c>
       <c r="DR9" t="inlineStr">
         <is>
-          <t>K0nUrV5K</t>
+          <t>l2Rt2EsD</t>
         </is>
       </c>
       <c r="DS9" t="inlineStr">
         <is>
-          <t>lapadula gianluca</t>
+          <t>branca simone</t>
         </is>
       </c>
       <c r="DT9" t="inlineStr">
         <is>
-          <t>E9t2kgz3</t>
+          <t>2LoNIGf3</t>
         </is>
       </c>
       <c r="DU9" t="inlineStr">
         <is>
-          <t>deiola alessandro</t>
+          <t>rabbi simone</t>
         </is>
       </c>
       <c r="DV9" t="inlineStr">
         <is>
-          <t>E9t2kgz3</t>
+          <t>2LoNIGf3</t>
         </is>
       </c>
       <c r="DW9" t="inlineStr">
         <is>
-          <t>deiola alessandro</t>
+          <t>rabbi simone</t>
         </is>
       </c>
       <c r="DX9" t="inlineStr">
         <is>
-          <t>thWJbHFE</t>
+          <t>dbk2r5CD</t>
         </is>
       </c>
       <c r="DY9" t="inlineStr">
         <is>
-          <t>adopo michel</t>
+          <t>pandolfi luca</t>
         </is>
       </c>
       <c r="DZ9" t="inlineStr">
         <is>
-          <t>tdJlhP53</t>
+          <t>KrttNVLt</t>
         </is>
       </c>
       <c r="EA9" t="inlineStr">
         <is>
-          <t>nasti marco</t>
+          <t>ambrosino giuseppe</t>
         </is>
       </c>
       <c r="EB9" t="inlineStr">
         <is>
-          <t>tdJlhP53</t>
+          <t>KrttNVLt</t>
         </is>
       </c>
       <c r="EC9" t="inlineStr">
         <is>
-          <t>nasti marco</t>
+          <t>ambrosino giuseppe</t>
         </is>
       </c>
       <c r="ED9" t="inlineStr">
         <is>
-          <t>MeskQr4l</t>
+          <t>QunHCDU2</t>
         </is>
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>de luca manuel</t>
+          <t>tsadjout frank</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
         <is>
-          <t>vJItNu2r</t>
+          <t>b7dng8al</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
         <is>
-          <t>vazquez franco</t>
+          <t>kvernadze giorgi</t>
         </is>
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>vJItNu2r</t>
+          <t>b7dng8al</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
         <is>
-          <t>vazquez franco</t>
+          <t>kvernadze giorgi</t>
         </is>
       </c>
       <c r="EJ9" t="inlineStr">
         <is>
-          <t>UspinGse</t>
+          <t>YTpHlpak</t>
         </is>
       </c>
       <c r="EK9" t="inlineStr">
         <is>
-          <t>milanese tommaso</t>
+          <t>di stefano filippo</t>
         </is>
       </c>
       <c r="EL9" t="inlineStr">
         <is>
-          <t>xIUCaSh4</t>
+          <t>bJBRauoj</t>
         </is>
       </c>
       <c r="EM9" t="inlineStr">
         <is>
-          <t>sernicola leonardo</t>
+          <t>begic tjas</t>
         </is>
       </c>
       <c r="EN9" t="inlineStr">
         <is>
-          <t>xIUCaSh4</t>
+          <t>bJBRauoj</t>
         </is>
       </c>
       <c r="EO9" t="inlineStr">
         <is>
-          <t>sernicola leonardo</t>
+          <t>begic tjas</t>
         </is>
       </c>
       <c r="EP9" t="inlineStr">
         <is>
-          <t>j7T2rzph</t>
+          <t>AajjuPEj</t>
         </is>
       </c>
       <c r="EQ9" t="inlineStr">
         <is>
-          <t>barbieri tommaso</t>
+          <t>partipilo anthony</t>
         </is>
       </c>
       <c r="ER9" t="inlineStr">
         <is>
-          <t>zX8VztZq</t>
+          <t>Ysk36pE4</t>
         </is>
       </c>
       <c r="ES9" t="inlineStr">
         <is>
-          <t>vandeputte jari</t>
+          <t>bettella davide</t>
         </is>
       </c>
       <c r="ET9" t="inlineStr">
         <is>
-          <t>zX8VztZq</t>
+          <t>Ysk36pE4</t>
         </is>
       </c>
       <c r="EU9" t="inlineStr">
         <is>
-          <t>vandeputte jari</t>
+          <t>bettella davide</t>
         </is>
       </c>
       <c r="EV9" t="inlineStr">
         <is>
-          <t>r3yChj3j</t>
+          <t>4UlxnksM</t>
         </is>
       </c>
       <c r="EW9" t="inlineStr">
         <is>
-          <t>moretti lorenzo</t>
-        </is>
-      </c>
-      <c r="EX9" t="inlineStr">
-        <is>
-          <t>SnPwFapn</t>
-        </is>
-      </c>
-      <c r="EY9" t="inlineStr">
-        <is>
-          <t>collocolo michele</t>
-        </is>
-      </c>
-      <c r="EZ9" t="inlineStr">
-        <is>
-          <t>SnPwFapn</t>
-        </is>
-      </c>
-      <c r="FA9" t="inlineStr">
-        <is>
-          <t>collocolo michele</t>
-        </is>
-      </c>
-      <c r="FB9" t="inlineStr">
-        <is>
-          <t>AoykjoMB</t>
-        </is>
-      </c>
-      <c r="FC9" t="inlineStr">
-        <is>
-          <t>pickel charles</t>
-        </is>
-      </c>
+          <t>oyono anthony</t>
+        </is>
+      </c>
+      <c r="EX9" t="inlineStr"/>
+      <c r="EY9" t="inlineStr"/>
+      <c r="EZ9" t="inlineStr"/>
+      <c r="FA9" t="inlineStr"/>
+      <c r="FB9" t="inlineStr"/>
+      <c r="FC9" t="inlineStr"/>
       <c r="FD9" t="inlineStr"/>
       <c r="FE9" t="inlineStr"/>
-      <c r="FF9" t="inlineStr"/>
-      <c r="FG9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>O2Xm0vko</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>I9wPkuuh</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>fruchtl christian</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>6TtQuJeb</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>guilbert frederic</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>04Pk3MMd</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>pelmard andy</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>riY6rQKH</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>jean gaby</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Sf4eaXAH</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>dorgu patrick</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>fZXLQLKC</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>pierret balthazar</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>bNNOGcFF</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>rafia hamza</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>lQ1WQFtO</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>oudin remi</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>bygrxvpg</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>marchwinski filip</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>IoRXiRdq</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>banda lameck</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>APPhFofM</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>pierotti santiago</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>d2BR3Upb</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>satalino giacomo</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>IsGWKIMq</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>toljan jeremy</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>O0Ss5jSf</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>muharemovic tarik</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>M5l0hplp</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>odenthal cas</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>dQ1Evunq</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>doig josh</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>nodnKnAs</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>obiang pedro</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>t4NSHrlh</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>lipani luca</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>6392aYqP</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>caligara fabrizio</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>zNDPrjy8</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>pierini nicholas</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>prHV7Xpt</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>russo flavio</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>2B5YqXFG</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>volpato cristian</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>25Z8Kyb5</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>baschirotto federico</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>WEh0KZMT</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>borbei alexandru</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>vVyq9D0S</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>burnete catalin</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>nccbKjdO</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>coulibaly lassana</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>OCJ3DqzU</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>falcone wladimiro</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>GxXIRkFl</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>gallo antonino</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>QJJ3NUdE</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>gaspar kialonga</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>4jKQUIgi</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>hasa luis</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>QsP2aUC4</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>helgason thorir</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>4CvqRml2</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>krstovic nikola</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>xOh4r9KI</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>mcjannet ed</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>2PPgUVm4</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>ramadani ylber</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>GWSMlnRk</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>rebic ante</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>4Of5akc5</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>antiste janis</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>rJOfdpaA</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>d andrea luca</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>dxb0x43T</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>ghion andrea</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>rZYDo3K5</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>iannoni edoardo</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2ZalbHv9</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>knezovic borna</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>retVSWHL</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>kumi justin</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>EZVZoGs8</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>lauriente armand</t>
-        </is>
-      </c>
-      <c r="CH10" t="inlineStr">
-        <is>
-          <t>KpyQQSsm</t>
-        </is>
-      </c>
-      <c r="CI10" t="inlineStr">
-        <is>
-          <t>miranda kevin</t>
-        </is>
-      </c>
-      <c r="CJ10" t="inlineStr">
-        <is>
-          <t>UmzKM5tM</t>
-        </is>
-      </c>
-      <c r="CK10" t="inlineStr">
-        <is>
-          <t>missori filippo</t>
-        </is>
-      </c>
-      <c r="CL10" t="inlineStr">
-        <is>
-          <t>SxjadbLU</t>
-        </is>
-      </c>
-      <c r="CM10" t="inlineStr">
-        <is>
-          <t>moldovan horatiu</t>
-        </is>
-      </c>
-      <c r="CN10" t="inlineStr">
-        <is>
-          <t>fDRMwkTQ</t>
-        </is>
-      </c>
-      <c r="CO10" t="inlineStr">
-        <is>
-          <t>moro luca</t>
-        </is>
-      </c>
-      <c r="CP10" t="inlineStr">
-        <is>
-          <t>IJwHBntK</t>
-        </is>
-      </c>
-      <c r="CQ10" t="inlineStr">
-        <is>
-          <t>paz yeferson</t>
-        </is>
-      </c>
-      <c r="CR10" t="inlineStr">
-        <is>
-          <t>C0qz46Jj</t>
-        </is>
-      </c>
-      <c r="CS10" t="inlineStr">
-        <is>
-          <t>pieragnolo edoardo</t>
-        </is>
-      </c>
-      <c r="CT10" t="inlineStr">
-        <is>
-          <t>MLQScsMb</t>
-        </is>
-      </c>
-      <c r="CU10" t="inlineStr">
-        <is>
-          <t>russo alessandro</t>
-        </is>
-      </c>
-      <c r="CV10" t="inlineStr">
-        <is>
-          <t>GWSMlnRk</t>
-        </is>
-      </c>
-      <c r="CW10" t="inlineStr">
-        <is>
-          <t>rebic ante</t>
-        </is>
-      </c>
-      <c r="CX10" t="inlineStr">
-        <is>
-          <t>GWSMlnRk</t>
-        </is>
-      </c>
-      <c r="CY10" t="inlineStr">
-        <is>
-          <t>rebic ante</t>
-        </is>
-      </c>
-      <c r="CZ10" t="inlineStr">
-        <is>
-          <t>APPhFofM</t>
-        </is>
-      </c>
-      <c r="DA10" t="inlineStr">
-        <is>
-          <t>pierotti santiago</t>
-        </is>
-      </c>
-      <c r="DB10" t="inlineStr">
-        <is>
-          <t>GxXIRkFl</t>
-        </is>
-      </c>
-      <c r="DC10" t="inlineStr">
-        <is>
-          <t>gallo antonino</t>
-        </is>
-      </c>
-      <c r="DD10" t="inlineStr">
-        <is>
-          <t>GxXIRkFl</t>
-        </is>
-      </c>
-      <c r="DE10" t="inlineStr">
-        <is>
-          <t>gallo antonino</t>
-        </is>
-      </c>
-      <c r="DF10" t="inlineStr">
-        <is>
-          <t>IoRXiRdq</t>
-        </is>
-      </c>
-      <c r="DG10" t="inlineStr">
-        <is>
-          <t>banda lameck</t>
-        </is>
-      </c>
-      <c r="DH10" t="inlineStr">
-        <is>
-          <t>vVyq9D0S</t>
-        </is>
-      </c>
-      <c r="DI10" t="inlineStr">
-        <is>
-          <t>burnete catalin</t>
-        </is>
-      </c>
-      <c r="DJ10" t="inlineStr">
-        <is>
-          <t>vVyq9D0S</t>
-        </is>
-      </c>
-      <c r="DK10" t="inlineStr">
-        <is>
-          <t>burnete catalin</t>
-        </is>
-      </c>
-      <c r="DL10" t="inlineStr">
-        <is>
-          <t>bygrxvpg</t>
-        </is>
-      </c>
-      <c r="DM10" t="inlineStr">
-        <is>
-          <t>marchwinski filip</t>
-        </is>
-      </c>
-      <c r="DN10" t="inlineStr">
-        <is>
-          <t>QJJ3NUdE</t>
-        </is>
-      </c>
-      <c r="DO10" t="inlineStr">
-        <is>
-          <t>gaspar kialonga</t>
-        </is>
-      </c>
-      <c r="DP10" t="inlineStr">
-        <is>
-          <t>QJJ3NUdE</t>
-        </is>
-      </c>
-      <c r="DQ10" t="inlineStr">
-        <is>
-          <t>gaspar kialonga</t>
-        </is>
-      </c>
-      <c r="DR10" t="inlineStr">
-        <is>
-          <t>04Pk3MMd</t>
-        </is>
-      </c>
-      <c r="DS10" t="inlineStr">
-        <is>
-          <t>pelmard andy</t>
-        </is>
-      </c>
-      <c r="DT10" t="inlineStr">
-        <is>
-          <t>4jKQUIgi</t>
-        </is>
-      </c>
-      <c r="DU10" t="inlineStr">
-        <is>
-          <t>hasa luis</t>
-        </is>
-      </c>
-      <c r="DV10" t="inlineStr">
-        <is>
-          <t>4jKQUIgi</t>
-        </is>
-      </c>
-      <c r="DW10" t="inlineStr">
-        <is>
-          <t>hasa luis</t>
-        </is>
-      </c>
-      <c r="DX10" t="inlineStr">
-        <is>
-          <t>Sf4eaXAH</t>
-        </is>
-      </c>
-      <c r="DY10" t="inlineStr">
-        <is>
-          <t>dorgu patrick</t>
-        </is>
-      </c>
-      <c r="DZ10" t="inlineStr">
-        <is>
-          <t>dxb0x43T</t>
-        </is>
-      </c>
-      <c r="EA10" t="inlineStr">
-        <is>
-          <t>ghion andrea</t>
-        </is>
-      </c>
-      <c r="EB10" t="inlineStr">
-        <is>
-          <t>dxb0x43T</t>
-        </is>
-      </c>
-      <c r="EC10" t="inlineStr">
-        <is>
-          <t>ghion andrea</t>
-        </is>
-      </c>
-      <c r="ED10" t="inlineStr">
-        <is>
-          <t>zNDPrjy8</t>
-        </is>
-      </c>
-      <c r="EE10" t="inlineStr">
-        <is>
-          <t>pierini nicholas</t>
-        </is>
-      </c>
-      <c r="EF10" t="inlineStr">
-        <is>
-          <t>C0qz46Jj</t>
-        </is>
-      </c>
-      <c r="EG10" t="inlineStr">
-        <is>
-          <t>pieragnolo edoardo</t>
-        </is>
-      </c>
-      <c r="EH10" t="inlineStr">
-        <is>
-          <t>C0qz46Jj</t>
-        </is>
-      </c>
-      <c r="EI10" t="inlineStr">
-        <is>
-          <t>pieragnolo edoardo</t>
-        </is>
-      </c>
-      <c r="EJ10" t="inlineStr">
-        <is>
-          <t>dQ1Evunq</t>
-        </is>
-      </c>
-      <c r="EK10" t="inlineStr">
-        <is>
-          <t>doig josh</t>
-        </is>
-      </c>
-      <c r="EL10" t="inlineStr">
-        <is>
-          <t>rJOfdpaA</t>
-        </is>
-      </c>
-      <c r="EM10" t="inlineStr">
-        <is>
-          <t>d andrea luca</t>
-        </is>
-      </c>
-      <c r="EN10" t="inlineStr">
-        <is>
-          <t>rJOfdpaA</t>
-        </is>
-      </c>
-      <c r="EO10" t="inlineStr">
-        <is>
-          <t>d andrea luca</t>
-        </is>
-      </c>
-      <c r="EP10" t="inlineStr">
-        <is>
-          <t>2B5YqXFG</t>
-        </is>
-      </c>
-      <c r="EQ10" t="inlineStr">
-        <is>
-          <t>volpato cristian</t>
-        </is>
-      </c>
-      <c r="ER10" t="inlineStr">
-        <is>
-          <t>fDRMwkTQ</t>
-        </is>
-      </c>
-      <c r="ES10" t="inlineStr">
-        <is>
-          <t>moro luca</t>
-        </is>
-      </c>
-      <c r="ET10" t="inlineStr">
-        <is>
-          <t>fDRMwkTQ</t>
-        </is>
-      </c>
-      <c r="EU10" t="inlineStr">
-        <is>
-          <t>moro luca</t>
-        </is>
-      </c>
-      <c r="EV10" t="inlineStr">
-        <is>
-          <t>prHV7Xpt</t>
-        </is>
-      </c>
-      <c r="EW10" t="inlineStr">
-        <is>
-          <t>russo flavio</t>
-        </is>
-      </c>
-      <c r="EX10" t="inlineStr">
-        <is>
-          <t>4Of5akc5</t>
-        </is>
-      </c>
-      <c r="EY10" t="inlineStr">
-        <is>
-          <t>antiste janis</t>
-        </is>
-      </c>
-      <c r="EZ10" t="inlineStr">
-        <is>
-          <t>4Of5akc5</t>
-        </is>
-      </c>
-      <c r="FA10" t="inlineStr">
-        <is>
-          <t>antiste janis</t>
-        </is>
-      </c>
-      <c r="FB10" t="inlineStr">
-        <is>
-          <t>6392aYqP</t>
-        </is>
-      </c>
-      <c r="FC10" t="inlineStr">
-        <is>
-          <t>caligara fabrizio</t>
-        </is>
-      </c>
-      <c r="FD10" t="inlineStr">
-        <is>
-          <t>xhN6Eae7</t>
-        </is>
-      </c>
-      <c r="FE10" t="inlineStr">
-        <is>
-          <t>samooja jasper</t>
-        </is>
-      </c>
-      <c r="FF10" t="inlineStr">
-        <is>
-          <t>lUc5MiUn</t>
-        </is>
-      </c>
-      <c r="FG10" t="inlineStr">
-        <is>
-          <t>tete morente</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FE9"/>
+  <dimension ref="A1:GC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6590 +781,7861 @@
       </c>
       <c r="BT1" s="1" t="inlineStr">
         <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_10</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_10</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_11</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_11</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_12</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_12</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
           <t>id_player_sub_home_14</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_home_14</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_13</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_13</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="FR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="FS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="FT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="FU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_home_15</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_home_15</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_1</t>
-        </is>
-      </c>
-      <c r="BY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_1</t>
-        </is>
-      </c>
-      <c r="BZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_2</t>
-        </is>
-      </c>
-      <c r="CA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_2</t>
-        </is>
-      </c>
-      <c r="CB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_3</t>
-        </is>
-      </c>
-      <c r="CC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_3</t>
-        </is>
-      </c>
-      <c r="CD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_4</t>
-        </is>
-      </c>
-      <c r="CE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_4</t>
-        </is>
-      </c>
-      <c r="CF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_5</t>
-        </is>
-      </c>
-      <c r="CG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_5</t>
-        </is>
-      </c>
-      <c r="CH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_6</t>
-        </is>
-      </c>
-      <c r="CI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_6</t>
-        </is>
-      </c>
-      <c r="CJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_7</t>
-        </is>
-      </c>
-      <c r="CK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_7</t>
-        </is>
-      </c>
-      <c r="CL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_8</t>
-        </is>
-      </c>
-      <c r="CM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_8</t>
-        </is>
-      </c>
-      <c r="CN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_9</t>
-        </is>
-      </c>
-      <c r="CO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_9</t>
-        </is>
-      </c>
-      <c r="CP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_10</t>
-        </is>
-      </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_10</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_11</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_11</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_12</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_12</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_1</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_1</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_2</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_2</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_3</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_3</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_4</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_4</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_5</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_5</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_6</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_6</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_7</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_7</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_8</t>
-        </is>
-      </c>
-      <c r="DK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_8</t>
-        </is>
-      </c>
-      <c r="DL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_9</t>
-        </is>
-      </c>
-      <c r="DM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_9</t>
-        </is>
-      </c>
-      <c r="DN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_10</t>
-        </is>
-      </c>
-      <c r="DO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_10</t>
-        </is>
-      </c>
-      <c r="DP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_11</t>
-        </is>
-      </c>
-      <c r="DQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_11</t>
-        </is>
-      </c>
-      <c r="DR1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_12</t>
-        </is>
-      </c>
-      <c r="DS1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_12</t>
-        </is>
-      </c>
-      <c r="DT1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="DU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="DV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="DW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="DX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_15</t>
-        </is>
-      </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_15</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_1</t>
-        </is>
-      </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_1</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_2</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_2</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_3</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_3</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_4</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_4</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_5</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_5</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_6</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_6</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_7</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_7</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_8</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_8</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_9</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_9</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_10</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_10</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_11</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_11</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_12</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_12</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_13</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_13</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_14</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_14</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_15</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_15</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_13</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_13</t>
+      <c r="FX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_14</t>
+        </is>
+      </c>
+      <c r="FY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_14</t>
+        </is>
+      </c>
+      <c r="FZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_15</t>
+        </is>
+      </c>
+      <c r="GA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_15</t>
+        </is>
+      </c>
+      <c r="GB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="GC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SYbhvYs3</t>
+          <t>rBsmDlYq</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>skorupski lukasz</t>
+          <t>caprile elia</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>nsVWqZE2</t>
+          <t>MP69NX2i</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>posch stefan</t>
+          <t>di lorenzo giovanni</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>xAzIxa5n</t>
+          <t>8Sw4X8wk</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>beukema sam</t>
+          <t>rrahmani amir</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>O8NaVz3G</t>
+          <t>UDMnkfdo</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>lucumi jhon</t>
+          <t>buongiorno alessandro</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>hxdzXUCO</t>
+          <t>bwAJqLBt</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>lykogiannis charalampos</t>
+          <t>olivera mathias</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>MiXFJwit</t>
+          <t>OtLZCB8S</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>aebischer michel</t>
+          <t>anguissa andre zambo</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>pETNY4Qt</t>
+          <t>0Qcw6Yy1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>freuler remo</t>
+          <t>lobotka stanislav</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>bkJ9njyQ</t>
+          <t>A7S3y397</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>fabbian giovanni</t>
+          <t>mctominay scott</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>bRV808wb</t>
+          <t>lxWZKRDD</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>orsolini riccardo</t>
+          <t>politano matteo</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>6BYm6GqL</t>
+          <t>dCkG0Iw0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>castro santiago</t>
+          <t>lukaku romelu</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>EmmpFCXN</t>
+          <t>bNuGt0hE</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>ndoye dan</t>
+          <t>kvaratskhelia khvicha</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>8WujtCJF</t>
+          <t>GdRRPoEK</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>carnesecchi marco</t>
+          <t>turati stefano</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>SzDIipZ9</t>
+          <t>OrlLWHno</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>kossounou odilon</t>
+          <t>izzo armando</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>pW01mTt9</t>
+          <t>8hN0kFPe</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>djimsiti berat</t>
+          <t>mari pablo</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8xFYnbEi</t>
+          <t>jBspTfmj</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>kolasinac sead</t>
+          <t>carboni andrea</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>6BgYlqqU</t>
+          <t>8t5OxIB9</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>bellanova raoul</t>
+          <t>pereira pedro</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>fqEsbNyA</t>
+          <t>r5YvrtEQ</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>ederson</t>
+          <t>bianco alessandro</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>SUUtwXea</t>
+          <t>ABbkAWNr</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>de roon marten</t>
+          <t>bondo warren</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0WPEP3LT</t>
+          <t>dbshNo9J</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>ruggeri matteo</t>
+          <t>kiriakopoulos giorgos</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>lt87Q6nj</t>
+          <t>txSCnXec</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>brescianini marco</t>
+          <t>maldini daniel</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2eOa3r1T</t>
+          <t>Wj6lXM52</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>de ketelaere charles</t>
+          <t>pessina matteo</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>8QK1SO5g</t>
+          <t>ri4T3rvJ</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>lookman ademola</t>
+          <t>djuric milan</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>I52azhH8</t>
+          <t>GUUR3bc3</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>bagnolini nicola</t>
+          <t>contini nikita</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>WAb3qgda</t>
+          <t>r9dHjC84</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>casale nicolo</t>
+          <t>david neres</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>tEYzXR62</t>
+          <t>4GK1zMhd</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>corazza tommaso</t>
+          <t>folorunsho michael</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>6kW9PX8r</t>
+          <t>MPhh66QA</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>dallinga thijs</t>
+          <t>gilmour billy</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>A9WpvRff</t>
+          <t>StHeGfTT</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>de silvestri lorenzo</t>
+          <t>juan jesus</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0CMCQTH6</t>
+          <t>KIwYY1AC</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>dominguez benjamin</t>
+          <t>marin rafa</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>n9FYAE96</t>
+          <t>xr29B9AI</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>erlic martin</t>
+          <t>mazzocchi pasquale</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>ANr5qAci</t>
+          <t>URgTM07o</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>holm emil</t>
+          <t>ngonge cyril</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>QXDbCvep</t>
+          <t>GlZEnTQr</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>iling samuel</t>
+          <t>raspadori giacomo</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>xUfM6nJ2</t>
+          <t>6m566fII</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>karlsson jesper</t>
+          <t>simeone giovanni</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>xOw55vy0</t>
+          <t>UgYYWt1i</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>miranda juan</t>
+          <t>spinazzola leonardo</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>SOva7ZCL</t>
+          <t>f9btzvmR</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>moro nikola</t>
+          <t>turi claudio</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>xbCDeKRm</t>
+          <t>2R03aynj</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>odgaard jens</t>
+          <t>zerbin alessio</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>219bD5Kr</t>
+          <t>4xwSQO9t</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>ravaglia federico</t>
+          <t>berretta alessandro</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>4SFU8b8f</t>
+          <t>lb7jSwtb</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>urbanski kacper</t>
+          <t>birindelli samuele</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>AFefBpwI</t>
+          <t>lOTx2Yho</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>cuadrado juan</t>
+          <t>caldirola luca</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>jivNliqi</t>
+          <t>hM9I17fh</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>del lungo tommaso</t>
+          <t>caprari gianluca</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>nD7QhgLn</t>
+          <t>ShD3fHfH</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>godfrey ben</t>
+          <t>d ambrosio danilo</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>Y3DYaDdP</t>
+          <t>lh4Ryd2l</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>palestra marco</t>
+          <t>forson omari</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>ld4iyqYa</t>
+          <t>6i5Fwg4m</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>pasalic mario</t>
+          <t>maric mirko</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>44sSdBl6</t>
+          <t>0xrmbKZS</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>patricio rui</t>
+          <t>martins kevin</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>Grhjz8pS</t>
+          <t>EirLWWbG</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>retegui mateo</t>
+          <t>mazza andrea</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>tdfrZ6nG</t>
+          <t>GbSDQoj8</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>rossi francesco</t>
+          <t>pizzignacco semuel</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>ba7y6F3c</t>
+          <t>f9YA97SK</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>samardzic lazar</t>
+          <t>postiglione nicolo</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>rRf9f5UA</t>
+          <t>vPBB8Jle</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>suleiman ibrahim</t>
+          <t>valoti mattia</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>0G7MtHBl</t>
+          <t>xr29B9AI</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>zaniolo nicolo</t>
+          <t>mazzocchi pasquale</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>G6AuiwvH</t>
+          <t>xr29B9AI</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>zappacosta davide</t>
+          <t>mazzocchi pasquale</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>4SFU8b8f</t>
+          <t>bNuGt0hE</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>urbanski kacper</t>
+          <t>kvaratskhelia khvicha</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>4SFU8b8f</t>
+          <t>r9dHjC84</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>urbanski kacper</t>
+          <t>david neres</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>bkJ9njyQ</t>
+          <t>r9dHjC84</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>fabbian giovanni</t>
+          <t>david neres</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>WAb3qgda</t>
+          <t>lxWZKRDD</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>casale nicolo</t>
+          <t>politano matteo</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>WAb3qgda</t>
+          <t>GlZEnTQr</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>casale nicolo</t>
+          <t>raspadori giacomo</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>bRV808wb</t>
+          <t>GlZEnTQr</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>orsolini riccardo</t>
+          <t>raspadori giacomo</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>6kW9PX8r</t>
+          <t>dCkG0Iw0</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>dallinga thijs</t>
+          <t>lukaku romelu</t>
         </is>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>6kW9PX8r</t>
+          <t>UgYYWt1i</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>dallinga thijs</t>
+          <t>spinazzola leonardo</t>
         </is>
       </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>6BYm6GqL</t>
+          <t>UgYYWt1i</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>castro santiago</t>
+          <t>spinazzola leonardo</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>n9FYAE96</t>
+          <t>bwAJqLBt</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>erlic martin</t>
+          <t>olivera mathias</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>n9FYAE96</t>
+          <t>MPhh66QA</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>erlic martin</t>
+          <t>gilmour billy</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>MiXFJwit</t>
+          <t>MPhh66QA</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>aebischer michel</t>
+          <t>gilmour billy</t>
         </is>
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>ANr5qAci</t>
+          <t>0Qcw6Yy1</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
         <is>
-          <t>holm emil</t>
+          <t>lobotka stanislav</t>
         </is>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>ANr5qAci</t>
+          <t>ShD3fHfH</t>
         </is>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>holm emil</t>
+          <t>d ambrosio danilo</t>
         </is>
       </c>
       <c r="DX2" t="inlineStr">
         <is>
-          <t>EmmpFCXN</t>
+          <t>ShD3fHfH</t>
         </is>
       </c>
       <c r="DY2" t="inlineStr">
         <is>
-          <t>ndoye dan</t>
+          <t>d ambrosio danilo</t>
         </is>
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
-          <t>ba7y6F3c</t>
+          <t>OrlLWHno</t>
         </is>
       </c>
       <c r="EA2" t="inlineStr">
         <is>
-          <t>samardzic lazar</t>
+          <t>izzo armando</t>
         </is>
       </c>
       <c r="EB2" t="inlineStr">
         <is>
-          <t>ba7y6F3c</t>
+          <t>hM9I17fh</t>
         </is>
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>samardzic lazar</t>
+          <t>caprari gianluca</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
         <is>
-          <t>lt87Q6nj</t>
+          <t>hM9I17fh</t>
         </is>
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>brescianini marco</t>
+          <t>caprari gianluca</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>Grhjz8pS</t>
+          <t>r5YvrtEQ</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>retegui mateo</t>
+          <t>bianco alessandro</t>
         </is>
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>Grhjz8pS</t>
+          <t>0xrmbKZS</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
         <is>
-          <t>retegui mateo</t>
+          <t>martins kevin</t>
         </is>
       </c>
       <c r="EJ2" t="inlineStr">
         <is>
-          <t>SzDIipZ9</t>
+          <t>0xrmbKZS</t>
         </is>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>kossounou odilon</t>
+          <t>martins kevin</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>AFefBpwI</t>
+          <t>8t5OxIB9</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>cuadrado juan</t>
+          <t>pereira pedro</t>
         </is>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>AFefBpwI</t>
+          <t>EBsz2tTd</t>
         </is>
       </c>
       <c r="EO2" t="inlineStr">
         <is>
-          <t>cuadrado juan</t>
+          <t>meret alex</t>
         </is>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>6BgYlqqU</t>
+          <t>CnvwSKf9</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>bellanova raoul</t>
+          <t>rui mario</t>
         </is>
       </c>
       <c r="ER2" t="inlineStr">
         <is>
-          <t>ld4iyqYa</t>
+          <t>p8mcxZnq</t>
         </is>
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>pasalic mario</t>
+          <t>ciurria patrick</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>ld4iyqYa</t>
+          <t>ENDYjGK9</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
         <is>
-          <t>pasalic mario</t>
+          <t>cragno alessio</t>
         </is>
       </c>
       <c r="EV2" t="inlineStr">
         <is>
-          <t>0WPEP3LT</t>
+          <t>f1Ft78yl</t>
         </is>
       </c>
       <c r="EW2" t="inlineStr">
         <is>
-          <t>ruggeri matteo</t>
+          <t>gagliardini roberto</t>
         </is>
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>0G7MtHBl</t>
+          <t>0WK0EKMu</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>zaniolo nicolo</t>
-        </is>
-      </c>
-      <c r="EZ2" t="inlineStr">
-        <is>
-          <t>0G7MtHBl</t>
-        </is>
-      </c>
-      <c r="FA2" t="inlineStr">
-        <is>
-          <t>zaniolo nicolo</t>
-        </is>
-      </c>
-      <c r="FB2" t="inlineStr">
-        <is>
-          <t>8xFYnbEi</t>
-        </is>
-      </c>
-      <c r="FC2" t="inlineStr">
-        <is>
-          <t>kolasinac sead</t>
-        </is>
-      </c>
+          <t>vignato samuel</t>
+        </is>
+      </c>
+      <c r="EZ2" t="inlineStr"/>
+      <c r="FA2" t="inlineStr"/>
+      <c r="FB2" t="inlineStr"/>
+      <c r="FC2" t="inlineStr"/>
       <c r="FD2" t="inlineStr"/>
       <c r="FE2" t="inlineStr"/>
+      <c r="FF2" t="inlineStr"/>
+      <c r="FG2" t="inlineStr"/>
+      <c r="FH2" t="inlineStr"/>
+      <c r="FI2" t="inlineStr"/>
+      <c r="FJ2" t="inlineStr"/>
+      <c r="FK2" t="inlineStr"/>
+      <c r="FL2" t="inlineStr"/>
+      <c r="FM2" t="inlineStr"/>
+      <c r="FN2" t="inlineStr"/>
+      <c r="FO2" t="inlineStr"/>
+      <c r="FP2" t="inlineStr"/>
+      <c r="FQ2" t="inlineStr"/>
+      <c r="FR2" t="inlineStr"/>
+      <c r="FS2" t="inlineStr"/>
+      <c r="FT2" t="inlineStr"/>
+      <c r="FU2" t="inlineStr"/>
+      <c r="FV2" t="inlineStr"/>
+      <c r="FW2" t="inlineStr"/>
+      <c r="FX2" t="inlineStr"/>
+      <c r="FY2" t="inlineStr"/>
+      <c r="FZ2" t="inlineStr"/>
+      <c r="GA2" t="inlineStr"/>
+      <c r="GB2" t="inlineStr"/>
+      <c r="GC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>vZY7FZwP</t>
+          <t>4xCrFFMe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gollini pierluigi</t>
+          <t>vasquez devis</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EFmPm0Qo</t>
+          <t>8lxchd9S</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>de winter koni</t>
+          <t>goglichidze saba</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>vgmL526e</t>
+          <t>bZmRuRzO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>bani mattia</t>
+          <t>viti mattia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Qydfoeer</t>
+          <t>xtJXLSFe</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>vasquez johan</t>
+          <t>ismajli ardian</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>xjWe0TTo</t>
+          <t>jZgmSlM1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>zanoli alessandro</t>
+          <t>gyasi emmanuel</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2XPmtx2l</t>
+          <t>E7Jj74nK</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>frendrup morten</t>
+          <t>grassi alberto</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4InuIizr</t>
+          <t>YmvWlE1E</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>badelj milan</t>
+          <t>henderson liam</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>tSUumbUT</t>
+          <t>zJD6Mdr3</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>miretti fabio</t>
+          <t>pezzella giuseppe</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Q1Sl1XK4</t>
+          <t>jTWtnxud</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ahanor honest</t>
+          <t>anjorin faustino</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>O4qi5hfc</t>
+          <t>WrbP1Sdg</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>pinamonti andrea</t>
+          <t>esposito sebastiano</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>AazXYT3h</t>
+          <t>YL741OaO</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>vitinha</t>
+          <t>colombo lorenzo</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>A3ZJNQg1</t>
+          <t>d6AEQ6OD</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>perin mattia</t>
+          <t>de gea david</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>KUjvgUhB</t>
+          <t>6qJwoGCI</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>danilo</t>
+          <t>dodo</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>E5UKRKOH</t>
+          <t>xfB3Fqzl</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>kalulu kyatengwa piere</t>
+          <t>comuzzo pietro</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>INWVBb0R</t>
+          <t>boIt2f70</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>bremer</t>
+          <t>ranieri luca</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>bsVzbV2I</t>
+          <t>r1EFsksF</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>rouhi jonas</t>
+          <t>gosens robin</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4rFy4PRQ</t>
+          <t>YFjrlxDr</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>fagioli nicolo</t>
+          <t>bove edoardo</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>jZHxRi2A</t>
+          <t>IcuAZWW1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>mckennie weston</t>
+          <t>cataldi danilo</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>filNjPIq</t>
+          <t>d2DTOQlc</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>gonzalez nicolas ivan</t>
+          <t>colpani andrea</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>lOCjQkeo</t>
+          <t>bHCOu1Tl</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>koopmeiners teun</t>
+          <t>gudmundsson albert</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0EgOZVie</t>
+          <t>6ZevPMzQ</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>yildiz kenan</t>
+          <t>kouame cristian</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>Ct0rhfn7</t>
+          <t>QPclX9Uq</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>vlahovic dusan</t>
+          <t>kean moise</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>fTOU6yR2</t>
+          <t>dfcCpneb</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>ankeye david</t>
+          <t>brancolini federico</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>25uHtnwl</t>
+          <t>4SWMMcZd</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>bohinen emil</t>
+          <t>cacace liberato</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>QopKhlIm</t>
+          <t>Ua5srQK6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>ekhator jeff</t>
+          <t>de sciglio mattia</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>vw0NcNnU</t>
+          <t>4pUDwSFI</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>kasa lior</t>
+          <t>ekong emmanuel</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>MHD6IelJ</t>
+          <t>b3uylvFN</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>leali nicola</t>
+          <t>fazzini jacopo</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>6BUzxLAe</t>
+          <t>Q1sHUL1D</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>marcandalli alessandro</t>
+          <t>haas nicolas</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>l4xhn6hC</t>
+          <t>lYCSEEBl</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>caricol aaron</t>
+          <t>konate ismael</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>WOffNMWA</t>
+          <t>CnRzW1VM</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>matturro romero alan</t>
+          <t>maleh youssef</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>zLlOcqw4</t>
+          <t>I52ibPrQ</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>sabelli stefano</t>
+          <t>marianucci luca</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>MsjFcjtJ</t>
+          <t>v3hpfVmF</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>sommariva daniele</t>
+          <t>pellegri pietro</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>Ei7zkE0o</t>
+          <t>GK1tPlKu</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>thorsby morten</t>
+          <t>sambia solomon</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>tW6pCCm8</t>
+          <t>KKXDLjg8</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>vogliacco alessandro</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="inlineStr"/>
+          <t>seghetti jacopo</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>U1piMQgC</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>solbakken ola</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>6kCEy6hD</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>adli yacine</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>4jLAxE3g</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>beltran lucas</t>
+        </is>
+      </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>bNJ7fStk</t>
+          <t>h81ElhF9</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>cabal juan david</t>
+          <t>biraghi cristiano</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>vRzeXq5h</t>
+          <t>xGBNss8O</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>cambiaso andrea</t>
+          <t>ikone jonathan</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>n53v4sSd</t>
+          <t>CrxJQ1Q8</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>chico conceicao</t>
+          <t>kayode michael</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>dUJmgXia</t>
+          <t>v9oBM840</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>di gregorio michele</t>
+          <t>mandragora rolando</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>IZxlmmuF</t>
+          <t>OxtBmUSA</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>douglas luiz</t>
+          <t>martinelli tommaso</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>SCvJDma8</t>
+          <t>KOGWbJk6</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>gatti federico</t>
+          <t>martinez lucas</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>6RgXRdd8</t>
+          <t>2umQcqSu</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>locatelli manuel</t>
+          <t>moreno matias</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0EjeWH5q</t>
+          <t>Ghafo5hk</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>mbangula tshifunda samuel</t>
+          <t>parisi fabiano</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>Uii1AJuK</t>
+          <t>nc2mg7is</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>pinsoglio carlo</t>
+          <t>richardson amir</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>juQzl8Zj</t>
+          <t>rkQyXmLB</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>savona nicolo</t>
+          <t>sottil riccardo</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>bDU1sgDT</t>
+          <t>U1piMQgC</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>thuram kephren</t>
-        </is>
-      </c>
-      <c r="CT3" t="inlineStr"/>
-      <c r="CU3" t="inlineStr"/>
+          <t>solbakken ola</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>U1piMQgC</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>solbakken ola</t>
+        </is>
+      </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>25uHtnwl</t>
+          <t>YL741OaO</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>bohinen emil</t>
+          <t>colombo lorenzo</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>25uHtnwl</t>
+          <t>4pUDwSFI</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>bohinen emil</t>
+          <t>ekong emmanuel</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>4InuIizr</t>
+          <t>4pUDwSFI</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>badelj milan</t>
+          <t>ekong emmanuel</t>
         </is>
       </c>
       <c r="DB3" t="inlineStr">
         <is>
-          <t>WOffNMWA</t>
+          <t>YmvWlE1E</t>
         </is>
       </c>
       <c r="DC3" t="inlineStr">
         <is>
-          <t>matturro romero alan</t>
+          <t>henderson liam</t>
         </is>
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>WOffNMWA</t>
+          <t>v3hpfVmF</t>
         </is>
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>matturro romero alan</t>
+          <t>pellegri pietro</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr">
         <is>
-          <t>Q1Sl1XK4</t>
+          <t>v3hpfVmF</t>
         </is>
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>ahanor honest</t>
+          <t>pellegri pietro</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>vw0NcNnU</t>
+          <t>WrbP1Sdg</t>
         </is>
       </c>
       <c r="DI3" t="inlineStr">
         <is>
-          <t>kasa lior</t>
+          <t>esposito sebastiano</t>
         </is>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>vw0NcNnU</t>
+          <t>Q1sHUL1D</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>kasa lior</t>
+          <t>haas nicolas</t>
         </is>
       </c>
       <c r="DL3" t="inlineStr">
         <is>
-          <t>tSUumbUT</t>
+          <t>Q1sHUL1D</t>
         </is>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>miretti fabio</t>
+          <t>haas nicolas</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>fTOU6yR2</t>
+          <t>jTWtnxud</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>ankeye david</t>
-        </is>
-      </c>
-      <c r="DP3" t="inlineStr">
-        <is>
-          <t>fTOU6yR2</t>
-        </is>
-      </c>
-      <c r="DQ3" t="inlineStr">
-        <is>
-          <t>ankeye david</t>
-        </is>
-      </c>
-      <c r="DR3" t="inlineStr">
-        <is>
-          <t>AazXYT3h</t>
-        </is>
-      </c>
-      <c r="DS3" t="inlineStr">
-        <is>
-          <t>vitinha</t>
-        </is>
-      </c>
-      <c r="DT3" t="inlineStr">
-        <is>
-          <t>zLlOcqw4</t>
-        </is>
-      </c>
-      <c r="DU3" t="inlineStr">
-        <is>
-          <t>sabelli stefano</t>
-        </is>
-      </c>
+          <t>anjorin faustino</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr"/>
+      <c r="DQ3" t="inlineStr"/>
+      <c r="DR3" t="inlineStr"/>
+      <c r="DS3" t="inlineStr"/>
+      <c r="DT3" t="inlineStr"/>
+      <c r="DU3" t="inlineStr"/>
       <c r="DV3" t="inlineStr">
         <is>
-          <t>zLlOcqw4</t>
+          <t>4jLAxE3g</t>
         </is>
       </c>
       <c r="DW3" t="inlineStr">
         <is>
-          <t>sabelli stefano</t>
+          <t>beltran lucas</t>
         </is>
       </c>
       <c r="DX3" t="inlineStr">
         <is>
-          <t>xjWe0TTo</t>
+          <t>4jLAxE3g</t>
         </is>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>zanoli alessandro</t>
+          <t>beltran lucas</t>
         </is>
       </c>
       <c r="DZ3" t="inlineStr">
         <is>
-          <t>IZxlmmuF</t>
+          <t>bHCOu1Tl</t>
         </is>
       </c>
       <c r="EA3" t="inlineStr">
         <is>
-          <t>douglas luiz</t>
+          <t>gudmundsson albert</t>
         </is>
       </c>
       <c r="EB3" t="inlineStr">
         <is>
-          <t>IZxlmmuF</t>
+          <t>6kCEy6hD</t>
         </is>
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>douglas luiz</t>
+          <t>adli yacine</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>jZHxRi2A</t>
+          <t>6kCEy6hD</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>mckennie weston</t>
+          <t>adli yacine</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>n53v4sSd</t>
+          <t>IcuAZWW1</t>
         </is>
       </c>
       <c r="EG3" t="inlineStr">
         <is>
-          <t>chico conceicao</t>
+          <t>cataldi danilo</t>
         </is>
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>n53v4sSd</t>
+          <t>xGBNss8O</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
         <is>
-          <t>chico conceicao</t>
+          <t>ikone jonathan</t>
         </is>
       </c>
       <c r="EJ3" t="inlineStr">
         <is>
-          <t>filNjPIq</t>
+          <t>xGBNss8O</t>
         </is>
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>gonzalez nicolas ivan</t>
+          <t>ikone jonathan</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr">
         <is>
-          <t>vRzeXq5h</t>
+          <t>d2DTOQlc</t>
         </is>
       </c>
       <c r="EM3" t="inlineStr">
         <is>
-          <t>cambiaso andrea</t>
+          <t>colpani andrea</t>
         </is>
       </c>
       <c r="EN3" t="inlineStr">
         <is>
-          <t>vRzeXq5h</t>
+          <t>QiCirDVf</t>
         </is>
       </c>
       <c r="EO3" t="inlineStr">
         <is>
-          <t>cambiaso andrea</t>
+          <t>belardinelli luca</t>
         </is>
       </c>
       <c r="EP3" t="inlineStr">
         <is>
-          <t>bsVzbV2I</t>
+          <t>KbPlg3Fl</t>
         </is>
       </c>
       <c r="EQ3" t="inlineStr">
         <is>
-          <t>rouhi jonas</t>
+          <t>ebuehi tyronne</t>
         </is>
       </c>
       <c r="ER3" t="inlineStr">
         <is>
-          <t>bDU1sgDT</t>
+          <t>OSXlKkv9</t>
         </is>
       </c>
       <c r="ES3" t="inlineStr">
         <is>
-          <t>thuram kephren</t>
-        </is>
-      </c>
-      <c r="ET3" t="inlineStr">
-        <is>
-          <t>bDU1sgDT</t>
-        </is>
-      </c>
-      <c r="EU3" t="inlineStr">
-        <is>
-          <t>thuram kephren</t>
-        </is>
-      </c>
-      <c r="EV3" t="inlineStr">
-        <is>
-          <t>0EgOZVie</t>
-        </is>
-      </c>
-      <c r="EW3" t="inlineStr">
-        <is>
-          <t>yildiz kenan</t>
-        </is>
-      </c>
-      <c r="EX3" t="inlineStr">
-        <is>
-          <t>juQzl8Zj</t>
-        </is>
-      </c>
-      <c r="EY3" t="inlineStr">
-        <is>
-          <t>savona nicolo</t>
-        </is>
-      </c>
+          <t>pongracic marin</t>
+        </is>
+      </c>
+      <c r="ET3" t="inlineStr"/>
+      <c r="EU3" t="inlineStr"/>
+      <c r="EV3" t="inlineStr"/>
+      <c r="EW3" t="inlineStr"/>
+      <c r="EX3" t="inlineStr"/>
+      <c r="EY3" t="inlineStr"/>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>juQzl8Zj</t>
+          <t>2eFCBn8A</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
-          <t>savona nicolo</t>
+          <t>tosto lorenzo</t>
         </is>
       </c>
       <c r="FB3" t="inlineStr">
         <is>
-          <t>E5UKRKOH</t>
+          <t>Wz2bzMVI</t>
         </is>
       </c>
       <c r="FC3" t="inlineStr">
         <is>
-          <t>kalulu kyatengwa piere</t>
-        </is>
-      </c>
-      <c r="FD3" t="inlineStr"/>
-      <c r="FE3" t="inlineStr"/>
+          <t>terracciano pietro</t>
+        </is>
+      </c>
+      <c r="FD3" t="inlineStr">
+        <is>
+          <t>rkQyXmLB</t>
+        </is>
+      </c>
+      <c r="FE3" t="inlineStr">
+        <is>
+          <t>sottil riccardo</t>
+        </is>
+      </c>
+      <c r="FF3" t="inlineStr">
+        <is>
+          <t>rkQyXmLB</t>
+        </is>
+      </c>
+      <c r="FG3" t="inlineStr">
+        <is>
+          <t>sottil riccardo</t>
+        </is>
+      </c>
+      <c r="FH3" t="inlineStr">
+        <is>
+          <t>6ZevPMzQ</t>
+        </is>
+      </c>
+      <c r="FI3" t="inlineStr">
+        <is>
+          <t>kouame cristian</t>
+        </is>
+      </c>
+      <c r="FJ3" t="inlineStr">
+        <is>
+          <t>Ghafo5hk</t>
+        </is>
+      </c>
+      <c r="FK3" t="inlineStr">
+        <is>
+          <t>parisi fabiano</t>
+        </is>
+      </c>
+      <c r="FL3" t="inlineStr">
+        <is>
+          <t>Ghafo5hk</t>
+        </is>
+      </c>
+      <c r="FM3" t="inlineStr">
+        <is>
+          <t>parisi fabiano</t>
+        </is>
+      </c>
+      <c r="FN3" t="inlineStr">
+        <is>
+          <t>r1EFsksF</t>
+        </is>
+      </c>
+      <c r="FO3" t="inlineStr">
+        <is>
+          <t>gosens robin</t>
+        </is>
+      </c>
+      <c r="FP3" t="inlineStr">
+        <is>
+          <t>6HUZxS6p</t>
+        </is>
+      </c>
+      <c r="FQ3" t="inlineStr">
+        <is>
+          <t>perisan samuele</t>
+        </is>
+      </c>
+      <c r="FR3" t="inlineStr">
+        <is>
+          <t>t2MszR74</t>
+        </is>
+      </c>
+      <c r="FS3" t="inlineStr">
+        <is>
+          <t>sazonov saba</t>
+        </is>
+      </c>
+      <c r="FT3" t="inlineStr">
+        <is>
+          <t>Ees7JNmc</t>
+        </is>
+      </c>
+      <c r="FU3" t="inlineStr">
+        <is>
+          <t>zurkowski szymon</t>
+        </is>
+      </c>
+      <c r="FV3" t="inlineStr"/>
+      <c r="FW3" t="inlineStr"/>
+      <c r="FX3" t="inlineStr"/>
+      <c r="FY3" t="inlineStr"/>
+      <c r="FZ3" t="inlineStr"/>
+      <c r="GA3" t="inlineStr"/>
+      <c r="GB3" t="inlineStr"/>
+      <c r="GC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gr6T6rIt</t>
+          <t>xjK7spn1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>okoye maduks</t>
+          <t>svilar mile</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42ADo7dd</t>
+          <t>dMy1KKlG</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>kabasele christian</t>
+          <t>mancini gianluca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0CykEP51</t>
+          <t>0ORJzjri</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>bijol jaka</t>
+          <t>n dicka obite</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>jaNZBJgT</t>
+          <t>GEGCuSA8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>toure souleymane</t>
+          <t>angelino</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6XCZJG4M</t>
+          <t>KG2a47J4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ehizibue kingsley</t>
+          <t>celik zeki</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2oBl3y29</t>
+          <t>YDaoYZBS</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lovric sandi</t>
+          <t>kone kouadio</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>UDGFZQv8</t>
+          <t>t6u0o3h7</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>karlstrom jesper</t>
+          <t>cristante bryan</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>QHRhjNJJ</t>
+          <t>fFLge2V1</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>zarraga oier</t>
+          <t>el shaarawy stephan</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>GAzjxceh</t>
+          <t>fXK87Cpf</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>zemura jordan</t>
+          <t>soule matias</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>SMbMSc26</t>
+          <t>8GVcLWJk</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>thauvin florian</t>
+          <t>pellegrini lorenzo</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>SKxz4XFS</t>
+          <t>C63L6vqA</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>davis keinan</t>
+          <t>dovbyk artem</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>4zA5n1UG</t>
+          <t>Q7KOnM07</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>sommer yann</t>
+          <t>joronen jesse</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>b3kUQZ4h</t>
+          <t>nHot9WLH</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>bisseck yann aurel</t>
+          <t>candela antonio</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>SrhnSpzL</t>
+          <t>6PYQeLsa</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>acerbi francesco</t>
+          <t>idzes jay</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>On4TkPTN</t>
+          <t>d6gJghfB</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>bastoni alessandro</t>
+          <t>svoboda michael</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>WbNknKk3</t>
+          <t>SAVw0168</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>darmian matteo</t>
+          <t>zampano francesco</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>WlVuvCqU</t>
+          <t>rJcy0auH</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>frattesi davide</t>
+          <t>nicolussi hans</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>IRQeP5FJ</t>
+          <t>4EDOAeYC</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>calhanoglu hakan</t>
+          <t>ellertsson mikael egill</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>KKi1DwHC</t>
+          <t>h2WGwSuO</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>mkhitaryan henrikh</t>
+          <t>haps ridgeciano</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>W6lypZn3</t>
+          <t>EiLy1nCa</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>dimarco federico</t>
+          <t>oristanio gaetano</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>QHk1CXUh</t>
+          <t>bVamjfgm</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>martinez lautaro</t>
+          <t>busio gianluca</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>hMMX02Fm</t>
+          <t>WfrgzpCh</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>thuram marcus</t>
+          <t>pohjanpalo joel</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>QgfEnOwH</t>
+          <t>OOentN4R</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>abankwah james</t>
+          <t>abdulhamid saud</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>Y3ooARhm</t>
+          <t>QySTk0pB</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>atta arthur</t>
+          <t>baldanzi tommaso</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>b5XwSo4Q</t>
+          <t>OlrRMLsM</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>bravo iker</t>
+          <t>sangare aboubacar</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2kXZSD2S</t>
+          <t>QeUL1GtM</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>brenner</t>
+          <t>dahl samuel</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>MXSXXNLr</t>
+          <t>W4myUVXR</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>ebosse enzo</t>
+          <t>dybala paulo</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4W6Geckd</t>
+          <t>OUjnz4Ab</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>ekkelenkamp jurgen</t>
+          <t>hermoso mario</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>UVyQpa9t</t>
+          <t>2c4AueOM</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>lucca lorenzo</t>
+          <t>hummels mats</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>xvD54OdB</t>
+          <t>UwPcTSBl</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>modesto rui</t>
+          <t>marin renato</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>dWZccSvp</t>
+          <t>lbNnSBiA</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>padelli daniele</t>
+          <t>paredes leandro</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>pObeJZYN</t>
+          <t>8nDLItn7</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>palma matteo</t>
+          <t>pisilli niccolo</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>S4Y7hFZd</t>
+          <t>YBLvziIh</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>sava razvan</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
+          <t>ryan mathew</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>Ys7niGiq</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>shomurodov eldor</t>
+        </is>
+      </c>
       <c r="BR4" t="inlineStr"/>
       <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
-      <c r="BW4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>hpae2jw4</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>andersen magnus kofod</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>zeVLnJdb</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>bruno</t>
+        </is>
+      </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>WvR2ASLR</t>
+          <t>Qqmz8U8m</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>arnautovic marko</t>
+          <t>carboni franco</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>hzUi0u2S</t>
+          <t>UJyCwMHF</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>asllani kristjan</t>
+          <t>crnigoj domen</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>QZQkZOWj</t>
+          <t>dfIWSyf9</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>carlos augusto</t>
+          <t>doumbia issa</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>IkcGiQBb</t>
+          <t>dCPh9H60</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>correa joaquin</t>
+          <t>el haddad saad</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>8Cf0NM4a</t>
+          <t>M9b7IZRg</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>de vrij stefan</t>
+          <t>grandi matteo</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>IuWFfk7l</t>
+          <t>AcMGD9Nj</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>di gennaro raffaele</t>
+          <t>gytkjaer christian</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>QR0j1ejk</t>
+          <t>Yq9XdF2N</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>dumfries denzel</t>
+          <t>raimondo antonio</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>n5XVsSqd</t>
+          <t>lj2aOZGT</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>martinez josep</t>
+          <t>sagrado richie</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>jwujRP9P</t>
+          <t>KMlNAiAc</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>palacios tomas</t>
+          <t>schingtienne joel</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>xxuEya3O</t>
+          <t>vsFwl9Sg</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>pavard benjamin</t>
+          <t>stankovic filip</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>E9UW7Gv8</t>
+          <t>QySTk0pB</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>taremi mehdi</t>
+          <t>baldanzi tommaso</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>dlFNZSvb</t>
+          <t>QySTk0pB</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>zielinski piotr</t>
+          <t>baldanzi tommaso</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>4W6Geckd</t>
+          <t>dMy1KKlG</t>
         </is>
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>ekkelenkamp jurgen</t>
+          <t>mancini gianluca</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>4W6Geckd</t>
+          <t>8nDLItn7</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>ekkelenkamp jurgen</t>
+          <t>pisilli niccolo</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>2oBl3y29</t>
+          <t>8nDLItn7</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>lovric sandi</t>
+          <t>pisilli niccolo</t>
         </is>
       </c>
       <c r="DB4" t="inlineStr">
         <is>
-          <t>UVyQpa9t</t>
+          <t>YDaoYZBS</t>
         </is>
       </c>
       <c r="DC4" t="inlineStr">
         <is>
-          <t>lucca lorenzo</t>
+          <t>kone kouadio</t>
         </is>
       </c>
       <c r="DD4" t="inlineStr">
         <is>
-          <t>UVyQpa9t</t>
+          <t>lbNnSBiA</t>
         </is>
       </c>
       <c r="DE4" t="inlineStr">
         <is>
-          <t>lucca lorenzo</t>
+          <t>paredes leandro</t>
         </is>
       </c>
       <c r="DF4" t="inlineStr">
         <is>
-          <t>SKxz4XFS</t>
+          <t>lbNnSBiA</t>
         </is>
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>davis keinan</t>
+          <t>paredes leandro</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>Y3ooARhm</t>
+          <t>8GVcLWJk</t>
         </is>
       </c>
       <c r="DI4" t="inlineStr">
         <is>
-          <t>atta arthur</t>
+          <t>pellegrini lorenzo</t>
         </is>
       </c>
       <c r="DJ4" t="inlineStr">
         <is>
-          <t>Y3ooARhm</t>
+          <t>OUjnz4Ab</t>
         </is>
       </c>
       <c r="DK4" t="inlineStr">
         <is>
-          <t>atta arthur</t>
+          <t>hermoso mario</t>
         </is>
       </c>
       <c r="DL4" t="inlineStr">
         <is>
-          <t>UDGFZQv8</t>
+          <t>OUjnz4Ab</t>
         </is>
       </c>
       <c r="DM4" t="inlineStr">
         <is>
-          <t>karlstrom jesper</t>
+          <t>hermoso mario</t>
         </is>
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>2kXZSD2S</t>
+          <t>fXK87Cpf</t>
         </is>
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>brenner</t>
-        </is>
-      </c>
-      <c r="DP4" t="inlineStr">
-        <is>
-          <t>2kXZSD2S</t>
-        </is>
-      </c>
-      <c r="DQ4" t="inlineStr">
-        <is>
-          <t>brenner</t>
-        </is>
-      </c>
-      <c r="DR4" t="inlineStr">
-        <is>
-          <t>SMbMSc26</t>
-        </is>
-      </c>
-      <c r="DS4" t="inlineStr">
-        <is>
-          <t>thauvin florian</t>
-        </is>
-      </c>
-      <c r="DT4" t="inlineStr">
-        <is>
-          <t>b5XwSo4Q</t>
-        </is>
-      </c>
-      <c r="DU4" t="inlineStr">
-        <is>
-          <t>bravo iker</t>
-        </is>
-      </c>
+          <t>soule matias</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr"/>
+      <c r="DQ4" t="inlineStr"/>
+      <c r="DR4" t="inlineStr"/>
+      <c r="DS4" t="inlineStr"/>
+      <c r="DT4" t="inlineStr"/>
+      <c r="DU4" t="inlineStr"/>
       <c r="DV4" t="inlineStr">
         <is>
-          <t>b5XwSo4Q</t>
+          <t>dfIWSyf9</t>
         </is>
       </c>
       <c r="DW4" t="inlineStr">
         <is>
-          <t>bravo iker</t>
+          <t>doumbia issa</t>
         </is>
       </c>
       <c r="DX4" t="inlineStr">
         <is>
-          <t>QHRhjNJJ</t>
+          <t>dfIWSyf9</t>
         </is>
       </c>
       <c r="DY4" t="inlineStr">
         <is>
-          <t>zarraga oier</t>
+          <t>doumbia issa</t>
         </is>
       </c>
       <c r="DZ4" t="inlineStr">
         <is>
-          <t>QZQkZOWj</t>
+          <t>4EDOAeYC</t>
         </is>
       </c>
       <c r="EA4" t="inlineStr">
         <is>
-          <t>carlos augusto</t>
+          <t>ellertsson mikael egill</t>
         </is>
       </c>
       <c r="EB4" t="inlineStr">
         <is>
-          <t>QZQkZOWj</t>
+          <t>hpae2jw4</t>
         </is>
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>carlos augusto</t>
+          <t>andersen magnus kofod</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
         <is>
-          <t>W6lypZn3</t>
+          <t>hpae2jw4</t>
         </is>
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>dimarco federico</t>
+          <t>andersen magnus kofod</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>E9UW7Gv8</t>
+          <t>rJcy0auH</t>
         </is>
       </c>
       <c r="EG4" t="inlineStr">
         <is>
-          <t>taremi mehdi</t>
+          <t>nicolussi hans</t>
         </is>
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>E9UW7Gv8</t>
+          <t>UJyCwMHF</t>
         </is>
       </c>
       <c r="EI4" t="inlineStr">
         <is>
-          <t>taremi mehdi</t>
+          <t>crnigoj domen</t>
         </is>
       </c>
       <c r="EJ4" t="inlineStr">
         <is>
-          <t>hMMX02Fm</t>
+          <t>UJyCwMHF</t>
         </is>
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>thuram marcus</t>
+          <t>crnigoj domen</t>
         </is>
       </c>
       <c r="EL4" t="inlineStr">
         <is>
-          <t>8Cf0NM4a</t>
+          <t>EiLy1nCa</t>
         </is>
       </c>
       <c r="EM4" t="inlineStr">
         <is>
-          <t>de vrij stefan</t>
+          <t>oristanio gaetano</t>
         </is>
       </c>
       <c r="EN4" t="inlineStr">
         <is>
-          <t>8Cf0NM4a</t>
+          <t>hC5yfF2A</t>
         </is>
       </c>
       <c r="EO4" t="inlineStr">
         <is>
-          <t>de vrij stefan</t>
+          <t>le fee enzo</t>
         </is>
       </c>
       <c r="EP4" t="inlineStr">
         <is>
-          <t>On4TkPTN</t>
+          <t>n5cPVwks</t>
         </is>
       </c>
       <c r="EQ4" t="inlineStr">
         <is>
-          <t>bastoni alessandro</t>
+          <t>saelemaekers alexis</t>
         </is>
       </c>
       <c r="ER4" t="inlineStr">
         <is>
-          <t>dlFNZSvb</t>
+          <t>087BaXQf</t>
         </is>
       </c>
       <c r="ES4" t="inlineStr">
         <is>
-          <t>zielinski piotr</t>
+          <t>altare giorgio</t>
         </is>
       </c>
       <c r="ET4" t="inlineStr">
         <is>
-          <t>dlFNZSvb</t>
+          <t>tpMja0bC</t>
         </is>
       </c>
       <c r="EU4" t="inlineStr">
         <is>
-          <t>zielinski piotr</t>
-        </is>
-      </c>
-      <c r="EV4" t="inlineStr">
-        <is>
-          <t>WlVuvCqU</t>
-        </is>
-      </c>
-      <c r="EW4" t="inlineStr">
-        <is>
-          <t>frattesi davide</t>
-        </is>
-      </c>
-      <c r="EX4" t="inlineStr">
-        <is>
-          <t>IkcGiQBb</t>
-        </is>
-      </c>
-      <c r="EY4" t="inlineStr">
-        <is>
-          <t>correa joaquin</t>
-        </is>
-      </c>
-      <c r="EZ4" t="inlineStr">
-        <is>
-          <t>IkcGiQBb</t>
-        </is>
-      </c>
-      <c r="FA4" t="inlineStr">
-        <is>
-          <t>correa joaquin</t>
-        </is>
-      </c>
+          <t>bjarkason bjarki steinn</t>
+        </is>
+      </c>
+      <c r="EV4" t="inlineStr"/>
+      <c r="EW4" t="inlineStr"/>
+      <c r="EX4" t="inlineStr"/>
+      <c r="EY4" t="inlineStr"/>
+      <c r="EZ4" t="inlineStr"/>
+      <c r="FA4" t="inlineStr"/>
       <c r="FB4" t="inlineStr">
         <is>
-          <t>QHk1CXUh</t>
+          <t>h6p8JLua</t>
         </is>
       </c>
       <c r="FC4" t="inlineStr">
         <is>
-          <t>martinez lautaro</t>
-        </is>
-      </c>
-      <c r="FD4" t="inlineStr"/>
-      <c r="FE4" t="inlineStr"/>
+          <t>sverko marin</t>
+        </is>
+      </c>
+      <c r="FD4" t="inlineStr">
+        <is>
+          <t>AcMGD9Nj</t>
+        </is>
+      </c>
+      <c r="FE4" t="inlineStr">
+        <is>
+          <t>gytkjaer christian</t>
+        </is>
+      </c>
+      <c r="FF4" t="inlineStr">
+        <is>
+          <t>AcMGD9Nj</t>
+        </is>
+      </c>
+      <c r="FG4" t="inlineStr">
+        <is>
+          <t>gytkjaer christian</t>
+        </is>
+      </c>
+      <c r="FH4" t="inlineStr">
+        <is>
+          <t>nHot9WLH</t>
+        </is>
+      </c>
+      <c r="FI4" t="inlineStr">
+        <is>
+          <t>candela antonio</t>
+        </is>
+      </c>
+      <c r="FJ4" t="inlineStr">
+        <is>
+          <t>Yq9XdF2N</t>
+        </is>
+      </c>
+      <c r="FK4" t="inlineStr">
+        <is>
+          <t>raimondo antonio</t>
+        </is>
+      </c>
+      <c r="FL4" t="inlineStr">
+        <is>
+          <t>Yq9XdF2N</t>
+        </is>
+      </c>
+      <c r="FM4" t="inlineStr">
+        <is>
+          <t>raimondo antonio</t>
+        </is>
+      </c>
+      <c r="FN4" t="inlineStr">
+        <is>
+          <t>WfrgzpCh</t>
+        </is>
+      </c>
+      <c r="FO4" t="inlineStr">
+        <is>
+          <t>pohjanpalo joel</t>
+        </is>
+      </c>
+      <c r="FP4" t="inlineStr"/>
+      <c r="FQ4" t="inlineStr"/>
+      <c r="FR4" t="inlineStr"/>
+      <c r="FS4" t="inlineStr"/>
+      <c r="FT4" t="inlineStr"/>
+      <c r="FU4" t="inlineStr"/>
+      <c r="FV4" t="inlineStr"/>
+      <c r="FW4" t="inlineStr"/>
+      <c r="FX4" t="inlineStr"/>
+      <c r="FY4" t="inlineStr"/>
+      <c r="FZ4" t="inlineStr"/>
+      <c r="GA4" t="inlineStr"/>
+      <c r="GB4" t="inlineStr"/>
+      <c r="GC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S6gN2QNC</t>
+          <t>fwyieeh8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>maignan mike</t>
+          <t>audero emil</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>zBkSUAjf</t>
+          <t>Uaabio2H</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>emerson royal</t>
+          <t>van der brempt ignace</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sl6O3rbN</t>
+          <t>AR2PqO6h</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>gabbia matteo</t>
+          <t>kempf marc oliver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AZn3ZNeI</t>
+          <t>4j96wYs7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>tomori fikayo</t>
+          <t>dossena alberto</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ATurLHr0</t>
+          <t>pdBI3oS8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>hernandez theo</t>
+          <t>moreno alberto</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>dn3cCK1H</t>
+          <t>vmcGpMJM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>fofana youssouf</t>
+          <t>perrone maximo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>f17EnPl3</t>
+          <t>W2R804U4</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>reijnders tijani</t>
+          <t>roberto sergi</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>vTuaEfRq</t>
+          <t>zR7umNy4</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>pulisic christian</t>
+          <t>strefezza gabriel</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>fmkHs3aU</t>
+          <t>GG6EYRT0</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>morata alvaro</t>
+          <t>paz martinez nicolas</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>AqOPWN5s</t>
+          <t>YclDapI5</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>leao rafael</t>
+          <t>fadera alieu</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>OYhxyduf</t>
+          <t>vB6l1nu7</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>abraham tammy</t>
+          <t>cutrone patrick</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>OCJ3DqzU</t>
+          <t>WhLULVuN</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>falcone wladimiro</t>
+          <t>montipo lorenzo</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Sf4eaXAH</t>
+          <t>6w5hZnnM</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dorgu patrick</t>
+          <t>tchatchoua jackson</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>25Z8Kyb5</t>
+          <t>pW9YKtJc</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>baschirotto federico</t>
+          <t>daniliuc flavius</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>QJJ3NUdE</t>
+          <t>tdLvMbiM</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>gaspar kialonga</t>
+          <t>coppola diego</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>GxXIRkFl</t>
+          <t>CERvOK0k</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>gallo antonino</t>
+          <t>frese martin</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>nccbKjdO</t>
+          <t>Yc3A88m7</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>coulibaly lassana</t>
+          <t>silva daniel</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2PPgUVm4</t>
+          <t>8vDirdIn</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>ramadani ylber</t>
+          <t>belahyane reda</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>fZXLQLKC</t>
+          <t>CQDgdTbJ</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>pierret balthazar</t>
+          <t>suslov tomas</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>lUc5MiUn</t>
+          <t>pK1EjnC1</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>tete morente</t>
+          <t>kastanos grigoris</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>4CvqRml2</t>
+          <t>4QATUtMO</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>krstovic nikola</t>
+          <t>lazovic darko</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>GWSMlnRk</t>
+          <t>2gNPfEXb</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>rebic ante</t>
+          <t>tengstedt casper</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>UL36DwiA</t>
+          <t>KSz457vB</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>bartesaghi davide</t>
+          <t>barba federico</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>niW1cP0k</t>
+          <t>nmCTZrFD</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>chukwueze samuel</t>
+          <t>baselli daniele</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>bRnH1txc</t>
+          <t>W6UTbSDR</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>sanchez alejandro jimenez</t>
+          <t>belotti andrea</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>viIS0FT7</t>
+          <t>vkRv24dh</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>jovic luka</t>
+          <t>braunoder matthias</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>6DpURWF8</t>
+          <t>IXqHAIWJ</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>loftus cheek ruben</t>
+          <t>da cunha lucas</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>ETMctXs4</t>
+          <t>S2gIJM28</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>musah yunus</t>
+          <t>engelhardt yannik</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>Qm2DVwBO</t>
+          <t>xzWqt9uL</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>pavlovic strahinja</t>
+          <t>gabrielloni alessandro</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>bwgnNY5o</t>
+          <t>CxCzIfHK</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>raveyre noah</t>
+          <t>goldaniga edoardo</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>4lL9syGa</t>
+          <t>UieHuD3i</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>terracciano filippo</t>
+          <t>lovino alessio</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0vSsR1xI</t>
+          <t>4bKWOzzb</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>thiaw malick</t>
+          <t>jack fellipe</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>h8lbX15I</t>
+          <t>MqKDIKSH</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>torriani lorenzo</t>
+          <t>jasim ali</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>ppSIryD2</t>
+          <t>0zd8jKI5</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>zeroli kevin</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
-      <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr"/>
-      <c r="BW5" t="inlineStr"/>
+          <t>mazzitelli luca</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>KrEhnvkN</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>reina pepe</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>rBlR9dl1</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>ajayi junior</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>nuvpd81D</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>berardi alessandro</t>
+        </is>
+      </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>IoRXiRdq</t>
+          <t>GGJ3Opji</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>banda lameck</t>
+          <t>bradaric domagoj</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>WEh0KZMT</t>
+          <t>WOEPeZlj</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>borbei alexandru</t>
+          <t>cisse alphadjo</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>vVyq9D0S</t>
+          <t>6JBYdeU4</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>burnete catalin</t>
+          <t>duda ondrej</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>I9wPkuuh</t>
+          <t>zPszNclq</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>fruchtl christian</t>
+          <t>faraoni davide</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4jKQUIgi</t>
+          <t>rsXIkA0l</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>hasa luis</t>
+          <t>ghilardi daniele</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>riY6rQKH</t>
+          <t>A1vJjksK</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>jean gaby</t>
+          <t>lambourde mathis</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>bygrxvpg</t>
+          <t>WYdXC95U</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>marchwinski filip</t>
+          <t>magnani giangiacomo</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>xOh4r9KI</t>
+          <t>M7SEoxVE</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>mcjannet ed</t>
+          <t>mosquera daniel</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>lQ1WQFtO</t>
+          <t>fuwlkDxt</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>oudin remi</t>
+          <t>okou yllan</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>04Pk3MMd</t>
+          <t>p4FWIWw5</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>pelmard andy</t>
+          <t>perilli simone</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>APPhFofM</t>
+          <t>IXqHAIWJ</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>pierotti santiago</t>
+          <t>da cunha lucas</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>bNNOGcFF</t>
+          <t>IXqHAIWJ</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>rafia hamza</t>
+          <t>da cunha lucas</t>
         </is>
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>6DpURWF8</t>
+          <t>zR7umNy4</t>
         </is>
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>loftus cheek ruben</t>
+          <t>strefezza gabriel</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>6DpURWF8</t>
+          <t>W6UTbSDR</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>loftus cheek ruben</t>
+          <t>belotti andrea</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>fmkHs3aU</t>
+          <t>W6UTbSDR</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>morata alvaro</t>
+          <t>belotti andrea</t>
         </is>
       </c>
       <c r="DB5" t="inlineStr">
         <is>
-          <t>ETMctXs4</t>
+          <t>vB6l1nu7</t>
         </is>
       </c>
       <c r="DC5" t="inlineStr">
         <is>
-          <t>musah yunus</t>
+          <t>cutrone patrick</t>
         </is>
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>ETMctXs4</t>
+          <t>0zd8jKI5</t>
         </is>
       </c>
       <c r="DE5" t="inlineStr">
         <is>
-          <t>musah yunus</t>
+          <t>mazzitelli luca</t>
         </is>
       </c>
       <c r="DF5" t="inlineStr">
         <is>
-          <t>dn3cCK1H</t>
+          <t>0zd8jKI5</t>
         </is>
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>fofana youssouf</t>
+          <t>mazzitelli luca</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>niW1cP0k</t>
+          <t>YclDapI5</t>
         </is>
       </c>
       <c r="DI5" t="inlineStr">
         <is>
-          <t>chukwueze samuel</t>
+          <t>fadera alieu</t>
         </is>
       </c>
       <c r="DJ5" t="inlineStr">
         <is>
-          <t>niW1cP0k</t>
+          <t>MqKDIKSH</t>
         </is>
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>chukwueze samuel</t>
+          <t>jasim ali</t>
         </is>
       </c>
       <c r="DL5" t="inlineStr">
         <is>
-          <t>vTuaEfRq</t>
+          <t>MqKDIKSH</t>
         </is>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>pulisic christian</t>
+          <t>jasim ali</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>UL36DwiA</t>
+          <t>vmcGpMJM</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>bartesaghi davide</t>
+          <t>perrone maximo</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
         <is>
-          <t>UL36DwiA</t>
+          <t>nmCTZrFD</t>
         </is>
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
-          <t>bartesaghi davide</t>
+          <t>baselli daniele</t>
         </is>
       </c>
       <c r="DR5" t="inlineStr">
         <is>
-          <t>ATurLHr0</t>
+          <t>nmCTZrFD</t>
         </is>
       </c>
       <c r="DS5" t="inlineStr">
         <is>
-          <t>hernandez theo</t>
+          <t>baselli daniele</t>
         </is>
       </c>
       <c r="DT5" t="inlineStr">
         <is>
-          <t>viIS0FT7</t>
+          <t>GG6EYRT0</t>
         </is>
       </c>
       <c r="DU5" t="inlineStr">
         <is>
-          <t>jovic luka</t>
+          <t>paz martinez nicolas</t>
         </is>
       </c>
       <c r="DV5" t="inlineStr">
         <is>
-          <t>viIS0FT7</t>
+          <t>6JBYdeU4</t>
         </is>
       </c>
       <c r="DW5" t="inlineStr">
         <is>
-          <t>jovic luka</t>
+          <t>duda ondrej</t>
         </is>
       </c>
       <c r="DX5" t="inlineStr">
         <is>
-          <t>OYhxyduf</t>
+          <t>6JBYdeU4</t>
         </is>
       </c>
       <c r="DY5" t="inlineStr">
         <is>
-          <t>abraham tammy</t>
+          <t>duda ondrej</t>
         </is>
       </c>
       <c r="DZ5" t="inlineStr">
         <is>
-          <t>IoRXiRdq</t>
+          <t>Yc3A88m7</t>
         </is>
       </c>
       <c r="EA5" t="inlineStr">
         <is>
-          <t>banda lameck</t>
+          <t>silva daniel</t>
         </is>
       </c>
       <c r="EB5" t="inlineStr">
         <is>
-          <t>IoRXiRdq</t>
+          <t>M7SEoxVE</t>
         </is>
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>banda lameck</t>
+          <t>mosquera daniel</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>lUc5MiUn</t>
+          <t>M7SEoxVE</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>tete morente</t>
+          <t>mosquera daniel</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>bNNOGcFF</t>
+          <t>pK1EjnC1</t>
         </is>
       </c>
       <c r="EG5" t="inlineStr">
         <is>
-          <t>rafia hamza</t>
+          <t>kastanos grigoris</t>
         </is>
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>bNNOGcFF</t>
+          <t>WYdXC95U</t>
         </is>
       </c>
       <c r="EI5" t="inlineStr">
         <is>
-          <t>rafia hamza</t>
+          <t>magnani giangiacomo</t>
         </is>
       </c>
       <c r="EJ5" t="inlineStr">
         <is>
-          <t>fZXLQLKC</t>
+          <t>WYdXC95U</t>
         </is>
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>pierret balthazar</t>
+          <t>magnani giangiacomo</t>
         </is>
       </c>
       <c r="EL5" t="inlineStr">
         <is>
-          <t>APPhFofM</t>
+          <t>2gNPfEXb</t>
         </is>
       </c>
       <c r="EM5" t="inlineStr">
         <is>
-          <t>pierotti santiago</t>
-        </is>
-      </c>
-      <c r="EN5" t="inlineStr">
-        <is>
-          <t>APPhFofM</t>
-        </is>
-      </c>
-      <c r="EO5" t="inlineStr">
-        <is>
-          <t>pierotti santiago</t>
-        </is>
-      </c>
-      <c r="EP5" t="inlineStr">
-        <is>
-          <t>GWSMlnRk</t>
-        </is>
-      </c>
-      <c r="EQ5" t="inlineStr">
-        <is>
-          <t>rebic ante</t>
-        </is>
-      </c>
+          <t>tengstedt casper</t>
+        </is>
+      </c>
+      <c r="EN5" t="inlineStr"/>
+      <c r="EO5" t="inlineStr"/>
+      <c r="EP5" t="inlineStr"/>
+      <c r="EQ5" t="inlineStr"/>
       <c r="ER5" t="inlineStr">
         <is>
-          <t>lQ1WQFtO</t>
+          <t>AZfDAIPf</t>
         </is>
       </c>
       <c r="ES5" t="inlineStr">
         <is>
-          <t>oudin remi</t>
+          <t>alidou faride</t>
         </is>
       </c>
       <c r="ET5" t="inlineStr">
         <is>
-          <t>lQ1WQFtO</t>
+          <t>ImoJ2c3M</t>
         </is>
       </c>
       <c r="EU5" t="inlineStr">
         <is>
-          <t>oudin remi</t>
+          <t>cruz juan</t>
         </is>
       </c>
       <c r="EV5" t="inlineStr">
         <is>
-          <t>nccbKjdO</t>
+          <t>hh5m41l6</t>
         </is>
       </c>
       <c r="EW5" t="inlineStr">
         <is>
-          <t>coulibaly lassana</t>
-        </is>
-      </c>
-      <c r="EX5" t="inlineStr"/>
-      <c r="EY5" t="inlineStr"/>
-      <c r="EZ5" t="inlineStr"/>
-      <c r="FA5" t="inlineStr"/>
-      <c r="FB5" t="inlineStr"/>
-      <c r="FC5" t="inlineStr"/>
+          <t>dawidowicz pawel</t>
+        </is>
+      </c>
+      <c r="EX5" t="inlineStr">
+        <is>
+          <t>nJ2Rd9i9</t>
+        </is>
+      </c>
+      <c r="EY5" t="inlineStr">
+        <is>
+          <t>harroui abdou</t>
+        </is>
+      </c>
+      <c r="EZ5" t="inlineStr">
+        <is>
+          <t>lG6NBuFm</t>
+        </is>
+      </c>
+      <c r="FA5" t="inlineStr">
+        <is>
+          <t>sala marco</t>
+        </is>
+      </c>
+      <c r="FB5" t="inlineStr">
+        <is>
+          <t>Aiy63dji</t>
+        </is>
+      </c>
+      <c r="FC5" t="inlineStr">
+        <is>
+          <t>rocha livramento dailon</t>
+        </is>
+      </c>
       <c r="FD5" t="inlineStr">
         <is>
-          <t>xhN6Eae7</t>
+          <t>Aiy63dji</t>
         </is>
       </c>
       <c r="FE5" t="inlineStr">
         <is>
-          <t>samooja jasper</t>
+          <t>rocha livramento dailon</t>
+        </is>
+      </c>
+      <c r="FF5" t="inlineStr">
+        <is>
+          <t>Aiy63dji</t>
+        </is>
+      </c>
+      <c r="FG5" t="inlineStr">
+        <is>
+          <t>rocha livramento dailon</t>
+        </is>
+      </c>
+      <c r="FH5" t="inlineStr">
+        <is>
+          <t>4QATUtMO</t>
+        </is>
+      </c>
+      <c r="FI5" t="inlineStr">
+        <is>
+          <t>lazovic darko</t>
+        </is>
+      </c>
+      <c r="FJ5" t="inlineStr">
+        <is>
+          <t>A1vJjksK</t>
+        </is>
+      </c>
+      <c r="FK5" t="inlineStr">
+        <is>
+          <t>lambourde mathis</t>
+        </is>
+      </c>
+      <c r="FL5" t="inlineStr">
+        <is>
+          <t>A1vJjksK</t>
+        </is>
+      </c>
+      <c r="FM5" t="inlineStr">
+        <is>
+          <t>lambourde mathis</t>
+        </is>
+      </c>
+      <c r="FN5" t="inlineStr">
+        <is>
+          <t>pW9YKtJc</t>
+        </is>
+      </c>
+      <c r="FO5" t="inlineStr">
+        <is>
+          <t>daniliuc flavius</t>
+        </is>
+      </c>
+      <c r="FP5" t="inlineStr"/>
+      <c r="FQ5" t="inlineStr"/>
+      <c r="FR5" t="inlineStr"/>
+      <c r="FS5" t="inlineStr"/>
+      <c r="FT5" t="inlineStr"/>
+      <c r="FU5" t="inlineStr"/>
+      <c r="FV5" t="inlineStr">
+        <is>
+          <t>rP6cESXb</t>
+        </is>
+      </c>
+      <c r="FW5" t="inlineStr">
+        <is>
+          <t>verdi simone</t>
+        </is>
+      </c>
+      <c r="FX5" t="inlineStr">
+        <is>
+          <t>2HYYjAtD</t>
+        </is>
+      </c>
+      <c r="FY5" t="inlineStr">
+        <is>
+          <t>sarr amin</t>
+        </is>
+      </c>
+      <c r="FZ5" t="inlineStr">
+        <is>
+          <t>Y3Pr63Lm</t>
+        </is>
+      </c>
+      <c r="GA5" t="inlineStr">
+        <is>
+          <t>sishuba ayanda</t>
+        </is>
+      </c>
+      <c r="GB5" t="inlineStr">
+        <is>
+          <t>WrzFSvEm</t>
+        </is>
+      </c>
+      <c r="GC5" t="inlineStr">
+        <is>
+          <t>serdar suat</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jwmmlzio</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>vJSWqc3U</t>
+          <t>vR4315G2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>radunovic boris</t>
+          <t>paleari alberto</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>vRCJaryd</t>
+          <t>YirekWMs</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>pucino raffaele</t>
+          <t>vojvoda mergim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>joCeChcm</t>
+          <t>4f3WP5vm</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>vicari francesco</t>
+          <t>coco saul</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>K4ftNDkl</t>
+          <t>fsw4UmgM</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>mantovani valerio</t>
+          <t>masina adam</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bFSFG3sT</t>
+          <t>OvtFAISo</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>olivieri andrea</t>
+          <t>lazaro valentino</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8EOkxnms</t>
+          <t>nRc0fR5f</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lella nunzio</t>
+          <t>tameze adrien</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Gl31cksa</t>
+          <t>thdNLRpt</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>benali ahmad</t>
+          <t>ricci samuele</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>UFsffxn9</t>
+          <t>vqZMiS0h</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>maita mattia</t>
+          <t>illic ivan</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2DjEKsjr</t>
+          <t>4vTK4LUr</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>dorval mehdi</t>
+          <t>sosa borna</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>GCL4UYe3</t>
+          <t>jNePUJ0b</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>falletti cesar</t>
+          <t>sanabria antonio</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>lEiQbqRi</t>
+          <t>v7zQxVoD</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>lasagna kevin</t>
+          <t>zapata duvan</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2ep1Q9sS</t>
+          <t>C6m92DF7</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>micai alessandro</t>
+          <t>provedel ivan</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>nPaTBKkJ</t>
+          <t>WlqJxlIT</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>venturi michael</t>
+          <t>lazzari manuel</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>25OhQNhD</t>
+          <t>dQqXDhtf</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>camporese michele</t>
+          <t>gila mario</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>WlJRaVcb</t>
+          <t>Wr49C0j4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>caporale alessandro</t>
+          <t>romagnoli alessio</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>GAjUdy0c</t>
+          <t>pY6E7S2D</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>ricciardi manuel</t>
+          <t>tavares nuno</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>GIIVeUW1</t>
+          <t>6ZesE86o</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>mauri jose</t>
+          <t>guendouzi matteo</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6q2NY0gd</t>
+          <t>bPQZKve0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>charlys</t>
+          <t>rovella nicolo</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>WMM2MKsk</t>
+          <t>d0vohCHH</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>ricci giacomo</t>
+          <t>isaksen gustav</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0b0UNkXD</t>
+          <t>zk0Q52W2</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>mazzocchi simone</t>
+          <t>dia boulaye</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>4CxkxV7L</t>
+          <t>MJ7sACQ8</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>kouan christian</t>
+          <t>zaccagni mattia</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>hhJIUYwm</t>
+          <t>ET4rsqIP</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>fumagalli tommaso</t>
+          <t>castellanos valentin</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>zsBl6R0S</t>
+          <t>4C0YmOaJ</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>bellomo nicola</t>
+          <t>adams che</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>x4AiZlG7</t>
+          <t>AsEOFfdr</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>favasuli costantino</t>
+          <t>dembele ali</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>xlic3PnN</t>
+          <t>zZcNEj5Q</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>favilli andrea</t>
+          <t>donnarumma antonio</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>M9Jn9Zm9</t>
+          <t>vkek8Ais</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>maiello raffaele</t>
+          <t>gineitis gvidas</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>WAWziD2c</t>
+          <t>OQYJ3VXT</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>manzari giacomo</t>
+          <t>karamoh yann</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>Q9PDryv2</t>
+          <t>KShlcp4N</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>novakovich andrija</t>
+          <t>linetty karol</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2J5yEYd4</t>
+          <t>UZiNdd1Q</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>obaretin nosa edward</t>
+          <t>maripan guillermo</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>t0rMk0s7</t>
+          <t>vwnI8wkF</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>pissardo marco</t>
+          <t>nije eybi</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>xStvhMAR</t>
+          <t>ltnVl6l2</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>saco coli</t>
+          <t>pedersen marcus</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>YgsNSpKb</t>
+          <t>4vGR45j3</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>sgarbi lorenzo</t>
+          <t>plaia francesco</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>KKpjmCfA</t>
+          <t>4ryWOtME</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>sibilli giuseppe</t>
+          <t>vlasic nikola</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>4jyY67mb</t>
+          <t>84cMABdJ</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>tripaldelli alessandro</t>
+          <t>walukiewicz sebastian</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr"/>
       <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
-      <c r="BW6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>ALBpOZPH</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>castrovilli gaetano</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>AF8BqWgI</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>dele bashiru fisayo</t>
+        </is>
+      </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>rZC7dOvh</t>
+          <t>2PZTBiII</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>ciervo riccardo</t>
+          <t>furlanetto alessio</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>Szz1Ydfm</t>
+          <t>vVGAhOFI</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>cimino baldovino</t>
+          <t>mandas christos</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>n5ugiXLC</t>
+          <t>tC46HZrA</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>d orazio tommaso</t>
+          <t>marusic adam</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>MFTLnkXH</t>
+          <t>Uma3vLeI</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>dalle mura christian</t>
+          <t>noslin tijjani</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>UaY4ZNC1</t>
+          <t>YXwSY2Ef</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>florenz aldo</t>
+          <t>patric</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>CGriWp56</t>
+          <t>0f1tMqQl</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>hristov andrea</t>
+          <t>pedro</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>GAnUo3OH</t>
+          <t>WKey0InR</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>kourfalidis christos</t>
+          <t>pellegrini luca</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>xIWZdkGt</t>
+          <t>vij66lN7</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>rizzo pinna andrea</t>
+          <t>tchaouna loum</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>6kdfCmVL</t>
+          <t>AVysqrBE</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>sankoh mohamed</t>
-        </is>
-      </c>
-      <c r="CP6" t="inlineStr">
-        <is>
-          <t>0QAtZqHu</t>
-        </is>
-      </c>
-      <c r="CQ6" t="inlineStr">
-        <is>
-          <t>strizzolo luca</t>
-        </is>
-      </c>
+          <t>vecino matias</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr"/>
+      <c r="CQ6" t="inlineStr"/>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>8lySR7S9</t>
+          <t>ltnVl6l2</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>vettorel thomas</t>
+          <t>pedersen marcus</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>YmE6Aqul</t>
+          <t>ltnVl6l2</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
         <is>
-          <t>zilli massimo</t>
+          <t>pedersen marcus</t>
         </is>
       </c>
       <c r="CV6" t="inlineStr">
         <is>
-          <t>KKpjmCfA</t>
+          <t>4vTK4LUr</t>
         </is>
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>sibilli giuseppe</t>
+          <t>sosa borna</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>KKpjmCfA</t>
+          <t>4C0YmOaJ</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>sibilli giuseppe</t>
+          <t>adams che</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>GCL4UYe3</t>
+          <t>4C0YmOaJ</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>falletti cesar</t>
+          <t>adams che</t>
         </is>
       </c>
       <c r="DB6" t="inlineStr">
         <is>
-          <t>xStvhMAR</t>
+          <t>nRc0fR5f</t>
         </is>
       </c>
       <c r="DC6" t="inlineStr">
         <is>
-          <t>saco coli</t>
+          <t>tameze adrien</t>
         </is>
       </c>
       <c r="DD6" t="inlineStr">
         <is>
-          <t>xStvhMAR</t>
+          <t>4ryWOtME</t>
         </is>
       </c>
       <c r="DE6" t="inlineStr">
         <is>
-          <t>saco coli</t>
+          <t>vlasic nikola</t>
         </is>
       </c>
       <c r="DF6" t="inlineStr">
         <is>
-          <t>UFsffxn9</t>
+          <t>4ryWOtME</t>
         </is>
       </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>maita mattia</t>
+          <t>vlasic nikola</t>
         </is>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
-          <t>2J5yEYd4</t>
+          <t>jNePUJ0b</t>
         </is>
       </c>
       <c r="DI6" t="inlineStr">
         <is>
-          <t>obaretin nosa edward</t>
+          <t>sanabria antonio</t>
         </is>
       </c>
       <c r="DJ6" t="inlineStr">
         <is>
-          <t>2J5yEYd4</t>
+          <t>vwnI8wkF</t>
         </is>
       </c>
       <c r="DK6" t="inlineStr">
         <is>
-          <t>obaretin nosa edward</t>
+          <t>nije eybi</t>
         </is>
       </c>
       <c r="DL6" t="inlineStr">
         <is>
-          <t>2DjEKsjr</t>
+          <t>vwnI8wkF</t>
         </is>
       </c>
       <c r="DM6" t="inlineStr">
         <is>
-          <t>dorval mehdi</t>
+          <t>nije eybi</t>
         </is>
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>x4AiZlG7</t>
+          <t>OvtFAISo</t>
         </is>
       </c>
       <c r="DO6" t="inlineStr">
         <is>
-          <t>favasuli costantino</t>
+          <t>lazaro valentino</t>
         </is>
       </c>
       <c r="DP6" t="inlineStr">
         <is>
-          <t>x4AiZlG7</t>
+          <t>UZiNdd1Q</t>
         </is>
       </c>
       <c r="DQ6" t="inlineStr">
         <is>
-          <t>favasuli costantino</t>
+          <t>maripan guillermo</t>
         </is>
       </c>
       <c r="DR6" t="inlineStr">
         <is>
-          <t>bFSFG3sT</t>
+          <t>UZiNdd1Q</t>
         </is>
       </c>
       <c r="DS6" t="inlineStr">
         <is>
-          <t>olivieri andrea</t>
+          <t>maripan guillermo</t>
         </is>
       </c>
       <c r="DT6" t="inlineStr">
         <is>
-          <t>Q9PDryv2</t>
+          <t>YirekWMs</t>
         </is>
       </c>
       <c r="DU6" t="inlineStr">
         <is>
-          <t>novakovich andrija</t>
+          <t>vojvoda mergim</t>
         </is>
       </c>
       <c r="DV6" t="inlineStr">
         <is>
-          <t>Q9PDryv2</t>
+          <t>AVysqrBE</t>
         </is>
       </c>
       <c r="DW6" t="inlineStr">
         <is>
-          <t>novakovich andrija</t>
+          <t>vecino matias</t>
         </is>
       </c>
       <c r="DX6" t="inlineStr">
         <is>
-          <t>lEiQbqRi</t>
+          <t>AVysqrBE</t>
         </is>
       </c>
       <c r="DY6" t="inlineStr">
         <is>
-          <t>lasagna kevin</t>
+          <t>vecino matias</t>
         </is>
       </c>
       <c r="DZ6" t="inlineStr">
         <is>
-          <t>UaY4ZNC1</t>
+          <t>zk0Q52W2</t>
         </is>
       </c>
       <c r="EA6" t="inlineStr">
         <is>
-          <t>florenz aldo</t>
+          <t>dia boulaye</t>
         </is>
       </c>
       <c r="EB6" t="inlineStr">
         <is>
-          <t>UaY4ZNC1</t>
+          <t>WKey0InR</t>
         </is>
       </c>
       <c r="EC6" t="inlineStr">
         <is>
-          <t>florenz aldo</t>
+          <t>pellegrini luca</t>
         </is>
       </c>
       <c r="ED6" t="inlineStr">
         <is>
-          <t>4CxkxV7L</t>
+          <t>WKey0InR</t>
         </is>
       </c>
       <c r="EE6" t="inlineStr">
         <is>
-          <t>kouan christian</t>
+          <t>pellegrini luca</t>
         </is>
       </c>
       <c r="EF6" t="inlineStr">
         <is>
-          <t>0QAtZqHu</t>
+          <t>pY6E7S2D</t>
         </is>
       </c>
       <c r="EG6" t="inlineStr">
         <is>
-          <t>strizzolo luca</t>
+          <t>tavares nuno</t>
         </is>
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>0QAtZqHu</t>
+          <t>vij66lN7</t>
         </is>
       </c>
       <c r="EI6" t="inlineStr">
         <is>
-          <t>strizzolo luca</t>
+          <t>tchaouna loum</t>
         </is>
       </c>
       <c r="EJ6" t="inlineStr">
         <is>
-          <t>GIIVeUW1</t>
+          <t>vij66lN7</t>
         </is>
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>mauri jose</t>
+          <t>tchaouna loum</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
         <is>
-          <t>rZC7dOvh</t>
+          <t>d0vohCHH</t>
         </is>
       </c>
       <c r="EM6" t="inlineStr">
         <is>
-          <t>ciervo riccardo</t>
+          <t>isaksen gustav</t>
         </is>
       </c>
       <c r="EN6" t="inlineStr">
         <is>
-          <t>rZC7dOvh</t>
+          <t>CS7XFNwq</t>
         </is>
       </c>
       <c r="EO6" t="inlineStr">
         <is>
-          <t>ciervo riccardo</t>
+          <t>ilkhan emirhan</t>
         </is>
       </c>
       <c r="EP6" t="inlineStr">
         <is>
-          <t>WMM2MKsk</t>
+          <t>bmU7ExmH</t>
         </is>
       </c>
       <c r="EQ6" t="inlineStr">
         <is>
-          <t>ricci giacomo</t>
+          <t>savva zannetos</t>
         </is>
       </c>
       <c r="ER6" t="inlineStr">
         <is>
-          <t>xIWZdkGt</t>
+          <t>G8cfGd8h</t>
         </is>
       </c>
       <c r="ES6" t="inlineStr">
         <is>
-          <t>rizzo pinna andrea</t>
-        </is>
-      </c>
-      <c r="ET6" t="inlineStr">
-        <is>
-          <t>xIWZdkGt</t>
-        </is>
-      </c>
-      <c r="EU6" t="inlineStr">
-        <is>
-          <t>rizzo pinna andrea</t>
-        </is>
-      </c>
-      <c r="EV6" t="inlineStr">
-        <is>
-          <t>0b0UNkXD</t>
-        </is>
-      </c>
-      <c r="EW6" t="inlineStr">
-        <is>
-          <t>mazzocchi simone</t>
-        </is>
-      </c>
-      <c r="EX6" t="inlineStr">
-        <is>
-          <t>YmE6Aqul</t>
-        </is>
-      </c>
-      <c r="EY6" t="inlineStr">
-        <is>
-          <t>zilli massimo</t>
-        </is>
-      </c>
-      <c r="EZ6" t="inlineStr">
-        <is>
-          <t>YmE6Aqul</t>
-        </is>
-      </c>
-      <c r="FA6" t="inlineStr">
-        <is>
-          <t>zilli massimo</t>
-        </is>
-      </c>
-      <c r="FB6" t="inlineStr">
-        <is>
-          <t>GAjUdy0c</t>
-        </is>
-      </c>
-      <c r="FC6" t="inlineStr">
-        <is>
-          <t>ricciardi manuel</t>
-        </is>
-      </c>
-      <c r="FD6" t="inlineStr"/>
-      <c r="FE6" t="inlineStr"/>
+          <t>gigot samuel</t>
+        </is>
+      </c>
+      <c r="ET6" t="inlineStr"/>
+      <c r="EU6" t="inlineStr"/>
+      <c r="EV6" t="inlineStr"/>
+      <c r="EW6" t="inlineStr"/>
+      <c r="EX6" t="inlineStr"/>
+      <c r="EY6" t="inlineStr"/>
+      <c r="EZ6" t="inlineStr"/>
+      <c r="FA6" t="inlineStr"/>
+      <c r="FB6" t="inlineStr"/>
+      <c r="FC6" t="inlineStr"/>
+      <c r="FD6" t="inlineStr">
+        <is>
+          <t>tC46HZrA</t>
+        </is>
+      </c>
+      <c r="FE6" t="inlineStr">
+        <is>
+          <t>marusic adam</t>
+        </is>
+      </c>
+      <c r="FF6" t="inlineStr">
+        <is>
+          <t>tC46HZrA</t>
+        </is>
+      </c>
+      <c r="FG6" t="inlineStr">
+        <is>
+          <t>marusic adam</t>
+        </is>
+      </c>
+      <c r="FH6" t="inlineStr">
+        <is>
+          <t>WlqJxlIT</t>
+        </is>
+      </c>
+      <c r="FI6" t="inlineStr">
+        <is>
+          <t>lazzari manuel</t>
+        </is>
+      </c>
+      <c r="FJ6" t="inlineStr">
+        <is>
+          <t>Uma3vLeI</t>
+        </is>
+      </c>
+      <c r="FK6" t="inlineStr">
+        <is>
+          <t>noslin tijjani</t>
+        </is>
+      </c>
+      <c r="FL6" t="inlineStr">
+        <is>
+          <t>Uma3vLeI</t>
+        </is>
+      </c>
+      <c r="FM6" t="inlineStr">
+        <is>
+          <t>noslin tijjani</t>
+        </is>
+      </c>
+      <c r="FN6" t="inlineStr">
+        <is>
+          <t>ET4rsqIP</t>
+        </is>
+      </c>
+      <c r="FO6" t="inlineStr">
+        <is>
+          <t>castellanos valentin</t>
+        </is>
+      </c>
+      <c r="FP6" t="inlineStr">
+        <is>
+          <t>ARdXOcOJ</t>
+        </is>
+      </c>
+      <c r="FQ6" t="inlineStr">
+        <is>
+          <t>schuurs perr</t>
+        </is>
+      </c>
+      <c r="FR6" t="inlineStr"/>
+      <c r="FS6" t="inlineStr"/>
+      <c r="FT6" t="inlineStr"/>
+      <c r="FU6" t="inlineStr"/>
+      <c r="FV6" t="inlineStr"/>
+      <c r="FW6" t="inlineStr"/>
+      <c r="FX6" t="inlineStr"/>
+      <c r="FY6" t="inlineStr"/>
+      <c r="FZ6" t="inlineStr"/>
+      <c r="GA6" t="inlineStr"/>
+      <c r="GB6" t="inlineStr"/>
+      <c r="GC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vaTsAHD4</t>
+          <t>nPWk8erH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>QJM49URT</t>
+          <t>tlSr8Yco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bleve marco</t>
+          <t>pisseri matteo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GAOlIzwG</t>
+          <t>2k9zUaAa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>illanes julian</t>
+          <t>ciofi andrea</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Am0oVUF6</t>
+          <t>fNkZk3Qs</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>hermannsson hjortur</t>
+          <t>prestia giuseppe</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>tMqmOicE</t>
+          <t>EBw91VL5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>imperiale marco</t>
+          <t>mangraviti massimiliano</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>f71DcoeK</t>
+          <t>2qAN5836</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>bouah devid eugene</t>
+          <t>adamo emanuele</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ddvz0tcQ</t>
+          <t>8vhUYvNN</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>capezzi leonardo</t>
+          <t>calo giacomo</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>dne3gePB</t>
+          <t>n7piqBuG</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>schiavi nicolas</t>
+          <t>bastoni simone</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>hn4q1pAA</t>
+          <t>tnsZtqGu</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>cicconi manuel</t>
+          <t>donnarumma daniele</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>C0IePhv1</t>
+          <t>ADBJ4OrH</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>finotto mattia</t>
+          <t>antonucci mirko</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>dfo0RTSJ</t>
+          <t>WrbFYwR8</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>capello alessandro</t>
+          <t>kargbo augustus</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Kd5zFbti</t>
+          <t>4MMcPxki</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>cherubini luigi</t>
+          <t>shpendi cristian</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>6wVqSqO0</t>
+          <t>ppkkwoIq</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>bardi francesco</t>
+          <t>festa marco</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>bkpO1UAs</t>
+          <t>S6rP7VQf</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>fiamozzi riccardo</t>
+          <t>radaelli nicolo</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>baFaIqPm</t>
+          <t>ngBZLdIk</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>meroni andrea</t>
+          <t>brignani fabrizio</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Ug0GqtE0</t>
+          <t>rqTURYfL</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>rozzio paolo</t>
+          <t>redolfi alex</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>G0zPj5Ba</t>
+          <t>jLhOHa57</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>fontanarosa alessandro</t>
+          <t>panizzi erik</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>jumC8deM</t>
+          <t>dfLh9Nso</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>sersanti alessandro</t>
+          <t>trimboli simone</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>ziYCoya3</t>
+          <t>ERIznhBT</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>stulac leo</t>
+          <t>burrai salvatore</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>67w6mUGh</t>
+          <t>ULHzNvxG</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>reinhart tobias</t>
+          <t>bragantini davide</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>AwsyawQ1</t>
+          <t>CxdWXum0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>portanova manolo</t>
+          <t>aramu mattia</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>0bwMG5SF</t>
+          <t>8rHEthHl</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>vergara antonio</t>
+          <t>fiori antonio</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>CEu5J6N8</t>
+          <t>llxIMxss</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>okwonkwo orji</t>
+          <t>mensah davis</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>SEwp6Uhi</t>
+          <t>hjLa97a7</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>belloni niccolo</t>
+          <t>berti tommaso</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>z92952s6</t>
+          <t>pnI8ZjZr</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>cerri leonardo</t>
+          <t>ceesay joseph</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>xnMwyU45</t>
+          <t>nmdCa7Ds</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>chiorra niccolo</t>
+          <t>celia raffaele</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>bmwzhd5k</t>
+          <t>OQAZiTD2</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>coppolaro mauro</t>
+          <t>chiarello riccardo</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>2LTAy8I5</t>
+          <t>xIKq8Lhb</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>falco filippo</t>
+          <t>curto marco</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>AgoFEXP9</t>
+          <t>hrgu7eZM</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>giovane samuel</t>
+          <t>francesconi matteo</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0GYbO9xj</t>
+          <t>dG0Lm68C</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>guarino gabriele</t>
+          <t>klinsmann jonathan</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>xM8qrrze</t>
+          <t>K4ZJo8cN</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>oliana filippo</t>
+          <t>mendicino leonardo</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>hpPoJ5jN</t>
+          <t>2J6W9OsT</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>palmieri riccardo</t>
+          <t>piacentini matteo</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>zPp0s4d5</t>
+          <t>8CpA5o79</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>panico giuseppe</t>
+          <t>pieraccini simone</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>AT5jymNl</t>
+          <t>nLiu560a</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>zanon simone</t>
+          <t>tavsan elayis</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>t6Pgd1eg</t>
+          <t>hIdAwd5O</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>zuelli emanuele</t>
+          <t>van hooijdonk sydney</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr"/>
       <c r="BS7" t="inlineStr"/>
-      <c r="BT7" t="inlineStr"/>
-      <c r="BU7" t="inlineStr"/>
-      <c r="BV7" t="inlineStr"/>
-      <c r="BW7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>SzgxNIFd</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>artioli federico</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>nFKFHQYJ</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>bani cristiano</t>
+        </is>
+      </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>46jUu380</t>
+          <t>v1cJQRlH</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>cavallini giacomo</t>
+          <t>cella stefano</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>lfpEEa5J</t>
+          <t>zabBo8TD</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>cigarini luca</t>
+          <t>debenedetti alessandro</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>YisAx5wl</t>
+          <t>vwQdsuRJ</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>girma natan</t>
+          <t>de maio sebastian</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>QqCsQcU5</t>
+          <t>SULw1d9h</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>gondo cedric</t>
+          <t>galuppini francesco</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>SpsFliY4</t>
+          <t>dj7ewEp6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>ignacchiti lorenzo</t>
+          <t>maggioni tommaso</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>08RKxF9J</t>
+          <t>r96jf7K7</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>libutti lorenzo</t>
+          <t>mancuso leonardo</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>M9Nbe4EG</t>
+          <t>nPDWBMl9</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>lucchesi lorenzo</t>
+          <t>muroni mattia</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>UZADb54K</t>
+          <t>dCTZFBZK</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>maggio matteo</t>
+          <t>ruocco francesco</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>AouSuCPP</t>
+          <t>j1TwYY8F</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>marras manuel</t>
+          <t>sonzogni luca</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>ATMse0OQ</t>
+          <t>I1MCXHlA</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>motta edoardo</t>
+          <t>wieser david</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>8WxIdbec</t>
+          <t>nLiu560a</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>nahounou yannis</t>
+          <t>tavsan elayis</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>d0WK1pb6</t>
+          <t>nLiu560a</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
         <is>
-          <t>vido luca</t>
+          <t>tavsan elayis</t>
         </is>
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>zPp0s4d5</t>
+          <t>WrbFYwR8</t>
         </is>
       </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>panico giuseppe</t>
+          <t>kargbo augustus</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>zPp0s4d5</t>
+          <t>K4ZJo8cN</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>panico giuseppe</t>
+          <t>mendicino leonardo</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>dfo0RTSJ</t>
+          <t>K4ZJo8cN</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>capello alessandro</t>
+          <t>mendicino leonardo</t>
         </is>
       </c>
       <c r="DB7" t="inlineStr">
         <is>
-          <t>AgoFEXP9</t>
+          <t>8vhUYvNN</t>
         </is>
       </c>
       <c r="DC7" t="inlineStr">
         <is>
-          <t>giovane samuel</t>
+          <t>calo giacomo</t>
         </is>
       </c>
       <c r="DD7" t="inlineStr">
         <is>
-          <t>AgoFEXP9</t>
+          <t>xIKq8Lhb</t>
         </is>
       </c>
       <c r="DE7" t="inlineStr">
         <is>
-          <t>giovane samuel</t>
+          <t>curto marco</t>
         </is>
       </c>
       <c r="DF7" t="inlineStr">
         <is>
-          <t>ddvz0tcQ</t>
+          <t>xIKq8Lhb</t>
         </is>
       </c>
       <c r="DG7" t="inlineStr">
         <is>
-          <t>capezzi leonardo</t>
+          <t>curto marco</t>
         </is>
       </c>
       <c r="DH7" t="inlineStr">
         <is>
-          <t>bmwzhd5k</t>
+          <t>2qAN5836</t>
         </is>
       </c>
       <c r="DI7" t="inlineStr">
         <is>
-          <t>coppolaro mauro</t>
+          <t>adamo emanuele</t>
         </is>
       </c>
       <c r="DJ7" t="inlineStr">
         <is>
-          <t>bmwzhd5k</t>
+          <t>hIdAwd5O</t>
         </is>
       </c>
       <c r="DK7" t="inlineStr">
         <is>
-          <t>coppolaro mauro</t>
+          <t>van hooijdonk sydney</t>
         </is>
       </c>
       <c r="DL7" t="inlineStr">
         <is>
-          <t>Am0oVUF6</t>
+          <t>hIdAwd5O</t>
         </is>
       </c>
       <c r="DM7" t="inlineStr">
         <is>
-          <t>hermannsson hjortur</t>
+          <t>van hooijdonk sydney</t>
         </is>
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>AT5jymNl</t>
+          <t>4MMcPxki</t>
         </is>
       </c>
       <c r="DO7" t="inlineStr">
         <is>
-          <t>zanon simone</t>
+          <t>shpendi cristian</t>
         </is>
       </c>
       <c r="DP7" t="inlineStr">
         <is>
-          <t>AT5jymNl</t>
+          <t>hrgu7eZM</t>
         </is>
       </c>
       <c r="DQ7" t="inlineStr">
         <is>
-          <t>zanon simone</t>
+          <t>francesconi matteo</t>
         </is>
       </c>
       <c r="DR7" t="inlineStr">
         <is>
-          <t>f71DcoeK</t>
+          <t>hrgu7eZM</t>
         </is>
       </c>
       <c r="DS7" t="inlineStr">
         <is>
-          <t>bouah devid eugene</t>
+          <t>francesconi matteo</t>
         </is>
       </c>
       <c r="DT7" t="inlineStr">
         <is>
-          <t>z92952s6</t>
+          <t>n7piqBuG</t>
         </is>
       </c>
       <c r="DU7" t="inlineStr">
         <is>
-          <t>cerri leonardo</t>
+          <t>bastoni simone</t>
         </is>
       </c>
       <c r="DV7" t="inlineStr">
         <is>
-          <t>z92952s6</t>
+          <t>dj7ewEp6</t>
         </is>
       </c>
       <c r="DW7" t="inlineStr">
         <is>
-          <t>cerri leonardo</t>
+          <t>maggioni tommaso</t>
         </is>
       </c>
       <c r="DX7" t="inlineStr">
         <is>
-          <t>Kd5zFbti</t>
+          <t>dj7ewEp6</t>
         </is>
       </c>
       <c r="DY7" t="inlineStr">
         <is>
-          <t>cherubini luigi</t>
+          <t>maggioni tommaso</t>
         </is>
       </c>
       <c r="DZ7" t="inlineStr">
         <is>
-          <t>AouSuCPP</t>
+          <t>S6rP7VQf</t>
         </is>
       </c>
       <c r="EA7" t="inlineStr">
         <is>
-          <t>marras manuel</t>
+          <t>radaelli nicolo</t>
         </is>
       </c>
       <c r="EB7" t="inlineStr">
         <is>
-          <t>AouSuCPP</t>
+          <t>r96jf7K7</t>
         </is>
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>marras manuel</t>
+          <t>mancuso leonardo</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
         <is>
-          <t>0bwMG5SF</t>
+          <t>r96jf7K7</t>
         </is>
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>vergara antonio</t>
+          <t>mancuso leonardo</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>d0WK1pb6</t>
+          <t>CxdWXum0</t>
         </is>
       </c>
       <c r="EG7" t="inlineStr">
         <is>
-          <t>vido luca</t>
+          <t>aramu mattia</t>
         </is>
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>d0WK1pb6</t>
+          <t>zabBo8TD</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
         <is>
-          <t>vido luca</t>
+          <t>debenedetti alessandro</t>
         </is>
       </c>
       <c r="EJ7" t="inlineStr">
         <is>
-          <t>bkpO1UAs</t>
+          <t>zabBo8TD</t>
         </is>
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>fiamozzi riccardo</t>
+          <t>debenedetti alessandro</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>M9Nbe4EG</t>
+          <t>llxIMxss</t>
         </is>
       </c>
       <c r="EM7" t="inlineStr">
         <is>
-          <t>lucchesi lorenzo</t>
-        </is>
-      </c>
-      <c r="EN7" t="inlineStr">
-        <is>
-          <t>M9Nbe4EG</t>
-        </is>
-      </c>
-      <c r="EO7" t="inlineStr">
-        <is>
-          <t>lucchesi lorenzo</t>
-        </is>
-      </c>
-      <c r="EP7" t="inlineStr">
-        <is>
-          <t>jumC8deM</t>
-        </is>
-      </c>
-      <c r="EQ7" t="inlineStr">
-        <is>
-          <t>sersanti alessandro</t>
-        </is>
-      </c>
-      <c r="ER7" t="inlineStr">
-        <is>
-          <t>SpsFliY4</t>
-        </is>
-      </c>
-      <c r="ES7" t="inlineStr">
-        <is>
-          <t>ignacchiti lorenzo</t>
-        </is>
-      </c>
-      <c r="ET7" t="inlineStr">
-        <is>
-          <t>SpsFliY4</t>
-        </is>
-      </c>
-      <c r="EU7" t="inlineStr">
-        <is>
-          <t>ignacchiti lorenzo</t>
-        </is>
-      </c>
-      <c r="EV7" t="inlineStr">
-        <is>
-          <t>ziYCoya3</t>
-        </is>
-      </c>
-      <c r="EW7" t="inlineStr">
-        <is>
-          <t>stulac leo</t>
-        </is>
-      </c>
-      <c r="EX7" t="inlineStr">
-        <is>
-          <t>QqCsQcU5</t>
-        </is>
-      </c>
-      <c r="EY7" t="inlineStr">
-        <is>
-          <t>gondo cedric</t>
-        </is>
-      </c>
-      <c r="EZ7" t="inlineStr">
-        <is>
-          <t>QqCsQcU5</t>
-        </is>
-      </c>
-      <c r="FA7" t="inlineStr">
-        <is>
-          <t>gondo cedric</t>
-        </is>
-      </c>
-      <c r="FB7" t="inlineStr">
-        <is>
-          <t>CEu5J6N8</t>
-        </is>
-      </c>
-      <c r="FC7" t="inlineStr">
-        <is>
-          <t>okwonkwo orji</t>
-        </is>
-      </c>
-      <c r="FD7" t="inlineStr"/>
-      <c r="FE7" t="inlineStr"/>
+          <t>mensah davis</t>
+        </is>
+      </c>
+      <c r="EN7" t="inlineStr"/>
+      <c r="EO7" t="inlineStr"/>
+      <c r="EP7" t="inlineStr"/>
+      <c r="EQ7" t="inlineStr"/>
+      <c r="ER7" t="inlineStr"/>
+      <c r="ES7" t="inlineStr"/>
+      <c r="ET7" t="inlineStr"/>
+      <c r="EU7" t="inlineStr"/>
+      <c r="EV7" t="inlineStr"/>
+      <c r="EW7" t="inlineStr"/>
+      <c r="EX7" t="inlineStr"/>
+      <c r="EY7" t="inlineStr"/>
+      <c r="EZ7" t="inlineStr"/>
+      <c r="FA7" t="inlineStr"/>
+      <c r="FB7" t="inlineStr"/>
+      <c r="FC7" t="inlineStr"/>
+      <c r="FD7" t="inlineStr">
+        <is>
+          <t>SULw1d9h</t>
+        </is>
+      </c>
+      <c r="FE7" t="inlineStr">
+        <is>
+          <t>galuppini francesco</t>
+        </is>
+      </c>
+      <c r="FF7" t="inlineStr">
+        <is>
+          <t>SULw1d9h</t>
+        </is>
+      </c>
+      <c r="FG7" t="inlineStr">
+        <is>
+          <t>galuppini francesco</t>
+        </is>
+      </c>
+      <c r="FH7" t="inlineStr">
+        <is>
+          <t>ULHzNvxG</t>
+        </is>
+      </c>
+      <c r="FI7" t="inlineStr">
+        <is>
+          <t>bragantini davide</t>
+        </is>
+      </c>
+      <c r="FJ7" t="inlineStr">
+        <is>
+          <t>dCTZFBZK</t>
+        </is>
+      </c>
+      <c r="FK7" t="inlineStr">
+        <is>
+          <t>ruocco francesco</t>
+        </is>
+      </c>
+      <c r="FL7" t="inlineStr">
+        <is>
+          <t>dCTZFBZK</t>
+        </is>
+      </c>
+      <c r="FM7" t="inlineStr">
+        <is>
+          <t>ruocco francesco</t>
+        </is>
+      </c>
+      <c r="FN7" t="inlineStr">
+        <is>
+          <t>8rHEthHl</t>
+        </is>
+      </c>
+      <c r="FO7" t="inlineStr">
+        <is>
+          <t>fiori antonio</t>
+        </is>
+      </c>
+      <c r="FP7" t="inlineStr"/>
+      <c r="FQ7" t="inlineStr"/>
+      <c r="FR7" t="inlineStr"/>
+      <c r="FS7" t="inlineStr"/>
+      <c r="FT7" t="inlineStr"/>
+      <c r="FU7" t="inlineStr"/>
+      <c r="FV7" t="inlineStr"/>
+      <c r="FW7" t="inlineStr"/>
+      <c r="FX7" t="inlineStr"/>
+      <c r="FY7" t="inlineStr"/>
+      <c r="FZ7" t="inlineStr"/>
+      <c r="GA7" t="inlineStr"/>
+      <c r="GB7" t="inlineStr"/>
+      <c r="GC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4USV4sgM</t>
+          <t>ID6U0Dzi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SxjadbLU</t>
+          <t>Sbgy5Y2h</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>moldovan horatiu</t>
+          <t>ngagne demba thiam</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IJwHBntK</t>
+          <t>ANCHAv7b</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>paz yeferson</t>
+          <t>folino francesco</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>O0Ss5jSf</t>
+          <t>lYD8hHV2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>muharemovic tarik</t>
+          <t>varnier marco</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ILuvGx81</t>
+          <t>On46eNg0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>romagna filippo</t>
+          <t>ruggero marco</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dQ1Evunq</t>
+          <t>4vpyISi8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>doig josh</t>
+          <t>floriani romano</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>rZYDo3K5</t>
+          <t>APo2PW3H</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>iannoni edoardo</t>
+          <t>buglio davide</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>jPrEU8Tr</t>
+          <t>YwNkUuc0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>boloca daniel</t>
+          <t>pierobon christian</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>EF3UYlr3</t>
+          <t>0fXqxXmN</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>thorstvedt kristian</t>
+          <t>rocchetti yuri</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>zNDPrjy8</t>
+          <t>dhjiV3mt</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>pierini nicholas</t>
+          <t>maistro fabio</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>f3tdpb62</t>
+          <t>xCsi3lKT</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>mulattieri samuele</t>
+          <t>candellone leonardo</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>EZVZoGs8</t>
+          <t>l6TZ4fzb</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>lauriente armand</t>
+          <t>adorante andrea</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>6Pbkbcv3</t>
+          <t>hEY0fdTF</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>gori stefano</t>
+          <t>semper adrian</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>QcPURnA3</t>
+          <t>hQKJwYnd</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>mateju ales</t>
+          <t>canestrelli simone</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>AaYOi9YT</t>
+          <t>xrpkAADs</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>wisniewski przemyslaw</t>
+          <t>caracciolo antonio</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>OUZiJhvh</t>
+          <t>hrJODeQE</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>bertola nicolo</t>
+          <t>bonfanti giovanni</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>EgfizWFr</t>
+          <t>S4Gdo5p3</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>vignali luca</t>
+          <t>piccinini gabriele</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>YTuQ6xad</t>
+          <t>IeO9PQjK</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>cassata francesco</t>
+          <t>marin marius</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>vZM5mg5N</t>
+          <t>d6546BZK</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>esposito salvatore</t>
+          <t>abildgaard oliver</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>WEIpbflm</t>
+          <t>nyOeW0BU</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>bandinelli filippo</t>
+          <t>beruatto pietro</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2kJoCbl9</t>
+          <t>zFFYexZK</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>reca arkadiusz</t>
+          <t>moreo stefano</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>MTtBqQfl</t>
+          <t>hYIzCDnT</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>di serio guiseppe</t>
+          <t>toure idrissa</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>dKXxEOKj</t>
+          <t>dGAt06R5</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>esposito francesco</t>
+          <t>bonfanti nicholas</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>4Of5akc5</t>
+          <t>lbJUZPxb</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>antiste janis</t>
+          <t>artistico gabriele</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>rJOfdpaA</t>
+          <t>jRW1tUsI</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>d andrea luca</t>
+          <t>baldi matteo</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>dxb0x43T</t>
+          <t>KSk57mgG</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>ghion andrea</t>
+          <t>di marco tommaso</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>t4NSHrlh</t>
+          <t>bHF8YI0f</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>lipani luca</t>
+          <t>fortini niccolo</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>fDRMwkTQ</t>
+          <t>S8fFGCzE</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>moro luca</t>
+          <t>gerbo alberto</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>nodnKnAs</t>
+          <t>OKLO0yfk</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>obiang pedro</t>
+          <t>leone giuseppe</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>M5l0hplp</t>
+          <t>xSoLBf8J</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>odenthal cas</t>
+          <t>meli marco</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>C0qz46Jj</t>
+          <t>nFKiZwej</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>pieragnolo edoardo</t>
+          <t>mosti nicola</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>prHV7Xpt</t>
+          <t>hMU3UYLc</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>russo flavio</t>
+          <t>piovanello enrico</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>d2BR3Upb</t>
+          <t>KAVGuGeo</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>satalino giacomo</t>
+          <t>piscopo kevin</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>IsGWKIMq</t>
+          <t>KUj8H9z1</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>toljan jeremy</t>
+          <t>signorini alessandro</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>2B5YqXFG</t>
+          <t>ImM7rIxo</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>volpato cristian</t>
+          <t>zuccon federico</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr"/>
       <c r="BS8" t="inlineStr"/>
-      <c r="BT8" t="inlineStr"/>
-      <c r="BU8" t="inlineStr"/>
-      <c r="BV8" t="inlineStr"/>
-      <c r="BW8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>ANXh14xc</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>angori samuele</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>pr02pCCG</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>arena alessandro</t>
+        </is>
+      </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>AkjDhEk0</t>
+          <t>dMiNmDpr</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>benvenuto mattia</t>
+          <t>calabresi arturo</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>CvWHSNg0</t>
+          <t>CYcsJc7H</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>candelari pietro</t>
+          <t>hojholt malthe</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>KWrHl314</t>
+          <t>pSDZ73wA</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>colak antonio mirko</t>
+          <t>jevsenak zan</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>KCtXlKaH</t>
+          <t>rTL6MlyQ</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>degli duccio</t>
+          <t>leoncini mattia</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>vs1w0sCd</t>
+          <t>S8AdeCEH</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>elia salvatore</t>
+          <t>lind alexander</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>tCvX7iBP</t>
+          <t>trNqVCBI</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>falcinelli diego</t>
+          <t>loria leonardo</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>r34Klsm2</t>
+          <t>ULMctLS6</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>giorgeschi simone</t>
+          <t>nicolas andrade</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>xIj2TcyE</t>
+          <t>tQ9LN1fh</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>hristov petko</t>
+          <t>rus adrian</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>OpOdOpiR</t>
+          <t>WWMStvpn</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>mascardi diego</t>
+          <t>tosi lorenzo</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>lpbxLFLT</t>
+          <t>xhLRqrX3</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>nagy adam</t>
+          <t>vignato emanuel</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>zDHydpk5</t>
+          <t>xSoLBf8J</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>salvador ferrer</t>
+          <t>meli marco</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>nRUWcY4c</t>
+          <t>xSoLBf8J</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
         <is>
-          <t>soleri edoardo</t>
+          <t>meli marco</t>
         </is>
       </c>
       <c r="CV8" t="inlineStr">
         <is>
-          <t>IsGWKIMq</t>
+          <t>dhjiV3mt</t>
         </is>
       </c>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>toljan jeremy</t>
+          <t>maistro fabio</t>
         </is>
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>IsGWKIMq</t>
+          <t>lbJUZPxb</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>toljan jeremy</t>
+          <t>artistico gabriele</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>IJwHBntK</t>
+          <t>lbJUZPxb</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>paz yeferson</t>
+          <t>artistico gabriele</t>
         </is>
       </c>
       <c r="DB8" t="inlineStr">
         <is>
-          <t>2B5YqXFG</t>
+          <t>l6TZ4fzb</t>
         </is>
       </c>
       <c r="DC8" t="inlineStr">
         <is>
-          <t>volpato cristian</t>
+          <t>adorante andrea</t>
         </is>
       </c>
       <c r="DD8" t="inlineStr">
         <is>
-          <t>2B5YqXFG</t>
+          <t>KAVGuGeo</t>
         </is>
       </c>
       <c r="DE8" t="inlineStr">
         <is>
-          <t>volpato cristian</t>
+          <t>piscopo kevin</t>
         </is>
       </c>
       <c r="DF8" t="inlineStr">
         <is>
-          <t>zNDPrjy8</t>
+          <t>KAVGuGeo</t>
         </is>
       </c>
       <c r="DG8" t="inlineStr">
         <is>
-          <t>pierini nicholas</t>
+          <t>piscopo kevin</t>
         </is>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
-          <t>prHV7Xpt</t>
+          <t>xCsi3lKT</t>
         </is>
       </c>
       <c r="DI8" t="inlineStr">
         <is>
-          <t>russo flavio</t>
+          <t>candellone leonardo</t>
         </is>
       </c>
       <c r="DJ8" t="inlineStr">
         <is>
-          <t>prHV7Xpt</t>
+          <t>jRW1tUsI</t>
         </is>
       </c>
       <c r="DK8" t="inlineStr">
         <is>
-          <t>russo flavio</t>
+          <t>baldi matteo</t>
         </is>
       </c>
       <c r="DL8" t="inlineStr">
         <is>
-          <t>f3tdpb62</t>
+          <t>jRW1tUsI</t>
         </is>
       </c>
       <c r="DM8" t="inlineStr">
         <is>
-          <t>mulattieri samuele</t>
+          <t>baldi matteo</t>
         </is>
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>nodnKnAs</t>
+          <t>0fXqxXmN</t>
         </is>
       </c>
       <c r="DO8" t="inlineStr">
         <is>
-          <t>obiang pedro</t>
+          <t>rocchetti yuri</t>
         </is>
       </c>
       <c r="DP8" t="inlineStr">
         <is>
-          <t>nodnKnAs</t>
+          <t>ImM7rIxo</t>
         </is>
       </c>
       <c r="DQ8" t="inlineStr">
         <is>
-          <t>obiang pedro</t>
+          <t>zuccon federico</t>
         </is>
       </c>
       <c r="DR8" t="inlineStr">
         <is>
-          <t>EF3UYlr3</t>
+          <t>ImM7rIxo</t>
         </is>
       </c>
       <c r="DS8" t="inlineStr">
         <is>
-          <t>thorstvedt kristian</t>
-        </is>
-      </c>
-      <c r="DT8" t="inlineStr"/>
-      <c r="DU8" t="inlineStr"/>
-      <c r="DV8" t="inlineStr"/>
-      <c r="DW8" t="inlineStr"/>
-      <c r="DX8" t="inlineStr"/>
-      <c r="DY8" t="inlineStr"/>
+          <t>zuccon federico</t>
+        </is>
+      </c>
+      <c r="DT8" t="inlineStr">
+        <is>
+          <t>YwNkUuc0</t>
+        </is>
+      </c>
+      <c r="DU8" t="inlineStr">
+        <is>
+          <t>pierobon christian</t>
+        </is>
+      </c>
+      <c r="DV8" t="inlineStr">
+        <is>
+          <t>ANXh14xc</t>
+        </is>
+      </c>
+      <c r="DW8" t="inlineStr">
+        <is>
+          <t>angori samuele</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>ANXh14xc</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>angori samuele</t>
+        </is>
+      </c>
       <c r="DZ8" t="inlineStr">
         <is>
-          <t>nRUWcY4c</t>
+          <t>hYIzCDnT</t>
         </is>
       </c>
       <c r="EA8" t="inlineStr">
         <is>
-          <t>soleri edoardo</t>
+          <t>toure idrissa</t>
         </is>
       </c>
       <c r="EB8" t="inlineStr">
         <is>
-          <t>nRUWcY4c</t>
+          <t>xhLRqrX3</t>
         </is>
       </c>
       <c r="EC8" t="inlineStr">
         <is>
-          <t>soleri edoardo</t>
+          <t>vignato emanuel</t>
         </is>
       </c>
       <c r="ED8" t="inlineStr">
         <is>
-          <t>dKXxEOKj</t>
+          <t>xhLRqrX3</t>
         </is>
       </c>
       <c r="EE8" t="inlineStr">
         <is>
-          <t>esposito francesco</t>
+          <t>vignato emanuel</t>
         </is>
       </c>
       <c r="EF8" t="inlineStr">
         <is>
-          <t>lpbxLFLT</t>
+          <t>nyOeW0BU</t>
         </is>
       </c>
       <c r="EG8" t="inlineStr">
         <is>
-          <t>nagy adam</t>
+          <t>beruatto pietro</t>
         </is>
       </c>
       <c r="EH8" t="inlineStr">
         <is>
-          <t>lpbxLFLT</t>
+          <t>CYcsJc7H</t>
         </is>
       </c>
       <c r="EI8" t="inlineStr">
         <is>
-          <t>nagy adam</t>
+          <t>hojholt malthe</t>
         </is>
       </c>
       <c r="EJ8" t="inlineStr">
         <is>
-          <t>YTuQ6xad</t>
+          <t>CYcsJc7H</t>
         </is>
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>cassata francesco</t>
+          <t>hojholt malthe</t>
         </is>
       </c>
       <c r="EL8" t="inlineStr">
         <is>
-          <t>KWrHl314</t>
+          <t>d6546BZK</t>
         </is>
       </c>
       <c r="EM8" t="inlineStr">
         <is>
-          <t>colak antonio mirko</t>
-        </is>
-      </c>
-      <c r="EN8" t="inlineStr">
-        <is>
-          <t>KWrHl314</t>
-        </is>
-      </c>
-      <c r="EO8" t="inlineStr">
-        <is>
-          <t>colak antonio mirko</t>
-        </is>
-      </c>
-      <c r="EP8" t="inlineStr">
-        <is>
-          <t>MTtBqQfl</t>
-        </is>
-      </c>
-      <c r="EQ8" t="inlineStr">
-        <is>
-          <t>di serio guiseppe</t>
-        </is>
-      </c>
-      <c r="ER8" t="inlineStr">
-        <is>
-          <t>CvWHSNg0</t>
-        </is>
-      </c>
-      <c r="ES8" t="inlineStr">
-        <is>
-          <t>candelari pietro</t>
-        </is>
-      </c>
-      <c r="ET8" t="inlineStr">
-        <is>
-          <t>CvWHSNg0</t>
-        </is>
-      </c>
-      <c r="EU8" t="inlineStr">
-        <is>
-          <t>candelari pietro</t>
-        </is>
-      </c>
-      <c r="EV8" t="inlineStr">
-        <is>
-          <t>vZM5mg5N</t>
-        </is>
-      </c>
-      <c r="EW8" t="inlineStr">
-        <is>
-          <t>esposito salvatore</t>
-        </is>
-      </c>
-      <c r="EX8" t="inlineStr">
-        <is>
-          <t>vs1w0sCd</t>
-        </is>
-      </c>
-      <c r="EY8" t="inlineStr">
-        <is>
-          <t>elia salvatore</t>
-        </is>
-      </c>
-      <c r="EZ8" t="inlineStr">
-        <is>
-          <t>vs1w0sCd</t>
-        </is>
-      </c>
-      <c r="FA8" t="inlineStr">
-        <is>
-          <t>elia salvatore</t>
-        </is>
-      </c>
-      <c r="FB8" t="inlineStr">
-        <is>
-          <t>2kJoCbl9</t>
-        </is>
-      </c>
-      <c r="FC8" t="inlineStr">
-        <is>
-          <t>reca arkadiusz</t>
-        </is>
-      </c>
-      <c r="FD8" t="inlineStr"/>
-      <c r="FE8" t="inlineStr"/>
+          <t>abildgaard oliver</t>
+        </is>
+      </c>
+      <c r="EN8" t="inlineStr"/>
+      <c r="EO8" t="inlineStr"/>
+      <c r="EP8" t="inlineStr"/>
+      <c r="EQ8" t="inlineStr"/>
+      <c r="ER8" t="inlineStr"/>
+      <c r="ES8" t="inlineStr"/>
+      <c r="ET8" t="inlineStr"/>
+      <c r="EU8" t="inlineStr"/>
+      <c r="EV8" t="inlineStr"/>
+      <c r="EW8" t="inlineStr"/>
+      <c r="EX8" t="inlineStr"/>
+      <c r="EY8" t="inlineStr"/>
+      <c r="EZ8" t="inlineStr"/>
+      <c r="FA8" t="inlineStr"/>
+      <c r="FB8" t="inlineStr"/>
+      <c r="FC8" t="inlineStr"/>
+      <c r="FD8" t="inlineStr">
+        <is>
+          <t>pr02pCCG</t>
+        </is>
+      </c>
+      <c r="FE8" t="inlineStr">
+        <is>
+          <t>arena alessandro</t>
+        </is>
+      </c>
+      <c r="FF8" t="inlineStr">
+        <is>
+          <t>pr02pCCG</t>
+        </is>
+      </c>
+      <c r="FG8" t="inlineStr">
+        <is>
+          <t>arena alessandro</t>
+        </is>
+      </c>
+      <c r="FH8" t="inlineStr">
+        <is>
+          <t>hrJODeQE</t>
+        </is>
+      </c>
+      <c r="FI8" t="inlineStr">
+        <is>
+          <t>bonfanti giovanni</t>
+        </is>
+      </c>
+      <c r="FJ8" t="inlineStr">
+        <is>
+          <t>S8AdeCEH</t>
+        </is>
+      </c>
+      <c r="FK8" t="inlineStr">
+        <is>
+          <t>lind alexander</t>
+        </is>
+      </c>
+      <c r="FL8" t="inlineStr">
+        <is>
+          <t>S8AdeCEH</t>
+        </is>
+      </c>
+      <c r="FM8" t="inlineStr">
+        <is>
+          <t>lind alexander</t>
+        </is>
+      </c>
+      <c r="FN8" t="inlineStr">
+        <is>
+          <t>dGAt06R5</t>
+        </is>
+      </c>
+      <c r="FO8" t="inlineStr">
+        <is>
+          <t>bonfanti nicholas</t>
+        </is>
+      </c>
+      <c r="FP8" t="inlineStr"/>
+      <c r="FQ8" t="inlineStr"/>
+      <c r="FR8" t="inlineStr"/>
+      <c r="FS8" t="inlineStr"/>
+      <c r="FT8" t="inlineStr"/>
+      <c r="FU8" t="inlineStr"/>
+      <c r="FV8" t="inlineStr"/>
+      <c r="FW8" t="inlineStr"/>
+      <c r="FX8" t="inlineStr"/>
+      <c r="FY8" t="inlineStr"/>
+      <c r="FZ8" t="inlineStr"/>
+      <c r="GA8" t="inlineStr"/>
+      <c r="GB8" t="inlineStr"/>
+      <c r="GC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8vLb6ZCT</t>
+          <t>zkyF8Pgc</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GpcVQVTI</t>
+          <t>zVciSbuM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>maniero luca</t>
+          <t>gagno riccardo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>80gdKWOF</t>
+          <t>0KOxlW5f</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>salvi alessandro</t>
+          <t>dellavalle alessandro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KQJr2C6I</t>
+          <t>lrTyTrDK</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>pavan nicola</t>
+          <t>zaro giovanni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>jiFEodbj</t>
+          <t>h2x8H16h</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>angeli matteo</t>
+          <t>caldara mattia</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O4VaVa69</t>
+          <t>GxGwdpWd</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>carissoni lorenzo</t>
+          <t>idrissi riyad</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>EVzPaGzl</t>
+          <t>dnZSvEME</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>d alessio francesco</t>
+          <t>magnino luca</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>l2Rt2EsD</t>
+          <t>4IL28fC8</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>branca simone</t>
+          <t>santoro simone</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SnRbZOrK</t>
+          <t>K2oPRv02</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>amatucci francesco</t>
+          <t>palumbo antonio</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>K0AtvAAP</t>
+          <t>f1smwzJc</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>desogus jacopo</t>
+          <t>duca edoardo</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Q741cgiO</t>
+          <t>hfvxnHLb</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>ravasio mario</t>
+          <t>bozhanaj kleis</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>dbk2r5CD</t>
+          <t>ldqJAYF7</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>pandolfi luca</t>
+          <t>abiuso fabio</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>bNZfXB2q</t>
+          <t>6JqatiEa</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>cerofolini michele</t>
+          <t>silvestri marco</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>fL14Xe6b</t>
+          <t>rmvDqIY7</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>marchizza riccardo</t>
+          <t>bereszynski bartosz</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>4AXvWzji</t>
+          <t>Q7fl3yYg</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>kalaj sergio</t>
+          <t>romagnoli simone</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>W6Uqcx1k</t>
+          <t>xSd0xhgK</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>monterisi ilario</t>
+          <t>vulikic stipe</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>4UlxnksM</t>
+          <t>dpMPW6zh</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>oyono anthony</t>
+          <t>venuti lorenzo</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>lAAgG4hD</t>
+          <t>2PcLSPHS</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>cichella matteo</t>
+          <t>benedetti leonardo</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>Qga48RFm</t>
+          <t>6qpSLKkb</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>gelli francesco</t>
+          <t>yepes gerard</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>4pxhfOad</t>
+          <t>dpI0AACN</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>garritano luca</t>
+          <t>bellemo alessandro</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>YTpHlpak</t>
+          <t>E92vTtZA</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>di stefano filippo</t>
+          <t>ioannou nicholas</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>QunHCDU2</t>
+          <t>WpuYwQHd</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>tsadjout frank</t>
+          <t>tutino gennaro</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>AajjuPEj</t>
+          <t>tAqEMK0a</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>partipilo anthony</t>
+          <t>coda massimo</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>hUTyvgJA</t>
+          <t>UR5FxyQD</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>cassano claudio</t>
+          <t>bagheria fabrizio</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>v5Kz7B89</t>
+          <t>6PTxZBhB</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>cecchetto andrea</t>
+          <t>beyuku bowutankoyi gady pierre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>0dqCCCd6</t>
+          <t>nivZo5js</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>kastrati elhan</t>
+          <t>caso giuseppe</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>f3UWa8ss</t>
+          <t>AcHn4RA5</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>magrassi andrea</t>
+          <t>cauz cristian</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>IooWgdIk</t>
+          <t>n5TCLpkU</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>masciangelo edoardo</t>
+          <t>cotali matteo</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>KEyUOiHh</t>
+          <t>6RC0qtx6</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>piccinini stefano</t>
+          <t>oliva marco</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2LoNIGf3</t>
+          <t>IDD8ySMl</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>rabbi simone</t>
+          <t>pergreffi antonio</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>I3kYfG62</t>
+          <t>8fN5kj02</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>rizza alessio</t>
+          <t>sarros ioannis</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>tr0PFNGl</t>
+          <t>ChuL5A4p</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>scquizzato edoardo</t>
+          <t>sassi jacopo</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>Q7OEUsLS</t>
+          <t>Qctgw5of</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>vita alessio</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>b1p7vpf3</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>voltan davide</t>
-        </is>
-      </c>
+          <t>zidouh taha</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr"/>
       <c r="BQ9" t="inlineStr"/>
       <c r="BR9" t="inlineStr"/>
       <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>GKxv62wr</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>akinsanmiro ebenezer</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>6XMPoYMf</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>barreca antonio</t>
+        </is>
+      </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>KrttNVLt</t>
+          <t>rDl88SSs</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>ambrosino giuseppe</t>
+          <t>depaoli fabio</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>bJBRauoj</t>
+          <t>IooZNoIP</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>begic tjas</t>
+          <t>giordano simone</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>Ysk36pE4</t>
+          <t>KrODGzyo</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>bettella davide</t>
+          <t>kasami pajtim</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>bVCSvTzl</t>
+          <t>hxFdb12n</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>bracaglia gabriele</t>
+          <t>la gumina antonio</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>2evqns7I</t>
+          <t>x2S7DucC</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>canotto luigi</t>
+          <t>meulensteen melle</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>plNsoAhU</t>
+          <t>E3RnK86O</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>haoudi hamza</t>
+          <t>riccio alessandro</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>b7dng8al</t>
+          <t>p49C8BCr</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>kvernadze giorgi</t>
+          <t>sekulov nikola</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>hfhlvfwf</t>
+          <t>jeW6mAhJ</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>machin jose</t>
+          <t>veroli davide</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>hjatkmbP</t>
+          <t>tUw2S8Tb</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>oyono jeremy</t>
+          <t>vieira ronaldo</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>n79iW0sd</t>
+          <t>6B2hAjdT</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>sene fallou</t>
+          <t>vismara paolo</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>KWK0U27f</t>
+          <t>nivZo5js</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>sorrentino alessandro</t>
+          <t>caso giuseppe</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>YPwDDAst</t>
+          <t>nivZo5js</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
         <is>
-          <t>szyminski przemyslaw</t>
+          <t>caso giuseppe</t>
         </is>
       </c>
       <c r="CV9" t="inlineStr">
         <is>
-          <t>f3UWa8ss</t>
+          <t>f1smwzJc</t>
         </is>
       </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>magrassi andrea</t>
+          <t>duca edoardo</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>f3UWa8ss</t>
+          <t>6PTxZBhB</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>magrassi andrea</t>
+          <t>beyuku bowutankoyi gady pierre</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>Q741cgiO</t>
+          <t>6PTxZBhB</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>ravasio mario</t>
+          <t>beyuku bowutankoyi gady pierre</t>
         </is>
       </c>
       <c r="DB9" t="inlineStr">
         <is>
-          <t>Q7OEUsLS</t>
+          <t>0KOxlW5f</t>
         </is>
       </c>
       <c r="DC9" t="inlineStr">
         <is>
-          <t>vita alessio</t>
+          <t>dellavalle alessandro</t>
         </is>
       </c>
       <c r="DD9" t="inlineStr">
         <is>
-          <t>Q7OEUsLS</t>
+          <t>Qctgw5of</t>
         </is>
       </c>
       <c r="DE9" t="inlineStr">
         <is>
-          <t>vita alessio</t>
+          <t>zidouh taha</t>
         </is>
       </c>
       <c r="DF9" t="inlineStr">
         <is>
-          <t>EVzPaGzl</t>
+          <t>Qctgw5of</t>
         </is>
       </c>
       <c r="DG9" t="inlineStr">
         <is>
-          <t>d alessio francesco</t>
+          <t>zidouh taha</t>
         </is>
       </c>
       <c r="DH9" t="inlineStr">
         <is>
-          <t>hUTyvgJA</t>
+          <t>dnZSvEME</t>
         </is>
       </c>
       <c r="DI9" t="inlineStr">
         <is>
-          <t>cassano claudio</t>
+          <t>magnino luca</t>
         </is>
       </c>
       <c r="DJ9" t="inlineStr">
         <is>
-          <t>hUTyvgJA</t>
+          <t>AcHn4RA5</t>
         </is>
       </c>
       <c r="DK9" t="inlineStr">
         <is>
-          <t>cassano claudio</t>
+          <t>cauz cristian</t>
         </is>
       </c>
       <c r="DL9" t="inlineStr">
         <is>
-          <t>K0AtvAAP</t>
+          <t>AcHn4RA5</t>
         </is>
       </c>
       <c r="DM9" t="inlineStr">
         <is>
-          <t>desogus jacopo</t>
+          <t>cauz cristian</t>
         </is>
       </c>
       <c r="DN9" t="inlineStr">
         <is>
-          <t>IooWgdIk</t>
+          <t>hfvxnHLb</t>
         </is>
       </c>
       <c r="DO9" t="inlineStr">
         <is>
-          <t>masciangelo edoardo</t>
-        </is>
-      </c>
-      <c r="DP9" t="inlineStr">
-        <is>
-          <t>IooWgdIk</t>
-        </is>
-      </c>
-      <c r="DQ9" t="inlineStr">
-        <is>
-          <t>masciangelo edoardo</t>
-        </is>
-      </c>
-      <c r="DR9" t="inlineStr">
-        <is>
-          <t>l2Rt2EsD</t>
-        </is>
-      </c>
-      <c r="DS9" t="inlineStr">
-        <is>
-          <t>branca simone</t>
-        </is>
-      </c>
-      <c r="DT9" t="inlineStr">
-        <is>
-          <t>2LoNIGf3</t>
-        </is>
-      </c>
-      <c r="DU9" t="inlineStr">
-        <is>
-          <t>rabbi simone</t>
-        </is>
-      </c>
+          <t>bozhanaj kleis</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr"/>
+      <c r="DQ9" t="inlineStr"/>
+      <c r="DR9" t="inlineStr"/>
+      <c r="DS9" t="inlineStr"/>
+      <c r="DT9" t="inlineStr"/>
+      <c r="DU9" t="inlineStr"/>
       <c r="DV9" t="inlineStr">
         <is>
-          <t>2LoNIGf3</t>
+          <t>E3RnK86O</t>
         </is>
       </c>
       <c r="DW9" t="inlineStr">
         <is>
-          <t>rabbi simone</t>
+          <t>riccio alessandro</t>
         </is>
       </c>
       <c r="DX9" t="inlineStr">
         <is>
-          <t>dbk2r5CD</t>
+          <t>E3RnK86O</t>
         </is>
       </c>
       <c r="DY9" t="inlineStr">
         <is>
-          <t>pandolfi luca</t>
+          <t>riccio alessandro</t>
         </is>
       </c>
       <c r="DZ9" t="inlineStr">
         <is>
-          <t>KrttNVLt</t>
+          <t>Q7fl3yYg</t>
         </is>
       </c>
       <c r="EA9" t="inlineStr">
         <is>
-          <t>ambrosino giuseppe</t>
+          <t>romagnoli simone</t>
         </is>
       </c>
       <c r="EB9" t="inlineStr">
         <is>
-          <t>KrttNVLt</t>
+          <t>KrODGzyo</t>
         </is>
       </c>
       <c r="EC9" t="inlineStr">
         <is>
-          <t>ambrosino giuseppe</t>
+          <t>kasami pajtim</t>
         </is>
       </c>
       <c r="ED9" t="inlineStr">
         <is>
-          <t>QunHCDU2</t>
+          <t>KrODGzyo</t>
         </is>
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>tsadjout frank</t>
+          <t>kasami pajtim</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
         <is>
-          <t>b7dng8al</t>
+          <t>2PcLSPHS</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
         <is>
-          <t>kvernadze giorgi</t>
+          <t>benedetti leonardo</t>
         </is>
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>b7dng8al</t>
+          <t>rDl88SSs</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
         <is>
-          <t>kvernadze giorgi</t>
+          <t>depaoli fabio</t>
         </is>
       </c>
       <c r="EJ9" t="inlineStr">
         <is>
-          <t>YTpHlpak</t>
+          <t>rDl88SSs</t>
         </is>
       </c>
       <c r="EK9" t="inlineStr">
         <is>
-          <t>di stefano filippo</t>
+          <t>depaoli fabio</t>
         </is>
       </c>
       <c r="EL9" t="inlineStr">
         <is>
-          <t>bJBRauoj</t>
+          <t>E92vTtZA</t>
         </is>
       </c>
       <c r="EM9" t="inlineStr">
         <is>
-          <t>begic tjas</t>
-        </is>
-      </c>
-      <c r="EN9" t="inlineStr">
-        <is>
-          <t>bJBRauoj</t>
-        </is>
-      </c>
-      <c r="EO9" t="inlineStr">
-        <is>
-          <t>begic tjas</t>
-        </is>
-      </c>
-      <c r="EP9" t="inlineStr">
-        <is>
-          <t>AajjuPEj</t>
-        </is>
-      </c>
-      <c r="EQ9" t="inlineStr">
-        <is>
-          <t>partipilo anthony</t>
-        </is>
-      </c>
-      <c r="ER9" t="inlineStr">
-        <is>
-          <t>Ysk36pE4</t>
-        </is>
-      </c>
-      <c r="ES9" t="inlineStr">
-        <is>
-          <t>bettella davide</t>
-        </is>
-      </c>
-      <c r="ET9" t="inlineStr">
-        <is>
-          <t>Ysk36pE4</t>
-        </is>
-      </c>
-      <c r="EU9" t="inlineStr">
-        <is>
-          <t>bettella davide</t>
-        </is>
-      </c>
-      <c r="EV9" t="inlineStr">
-        <is>
-          <t>4UlxnksM</t>
-        </is>
-      </c>
-      <c r="EW9" t="inlineStr">
-        <is>
-          <t>oyono anthony</t>
-        </is>
-      </c>
+          <t>ioannou nicholas</t>
+        </is>
+      </c>
+      <c r="EN9" t="inlineStr"/>
+      <c r="EO9" t="inlineStr"/>
+      <c r="EP9" t="inlineStr"/>
+      <c r="EQ9" t="inlineStr"/>
+      <c r="ER9" t="inlineStr"/>
+      <c r="ES9" t="inlineStr"/>
+      <c r="ET9" t="inlineStr"/>
+      <c r="EU9" t="inlineStr"/>
+      <c r="EV9" t="inlineStr"/>
+      <c r="EW9" t="inlineStr"/>
       <c r="EX9" t="inlineStr"/>
       <c r="EY9" t="inlineStr"/>
       <c r="EZ9" t="inlineStr"/>
       <c r="FA9" t="inlineStr"/>
       <c r="FB9" t="inlineStr"/>
       <c r="FC9" t="inlineStr"/>
-      <c r="FD9" t="inlineStr"/>
-      <c r="FE9" t="inlineStr"/>
+      <c r="FD9" t="inlineStr">
+        <is>
+          <t>tUw2S8Tb</t>
+        </is>
+      </c>
+      <c r="FE9" t="inlineStr">
+        <is>
+          <t>vieira ronaldo</t>
+        </is>
+      </c>
+      <c r="FF9" t="inlineStr">
+        <is>
+          <t>tUw2S8Tb</t>
+        </is>
+      </c>
+      <c r="FG9" t="inlineStr">
+        <is>
+          <t>vieira ronaldo</t>
+        </is>
+      </c>
+      <c r="FH9" t="inlineStr">
+        <is>
+          <t>dpI0AACN</t>
+        </is>
+      </c>
+      <c r="FI9" t="inlineStr">
+        <is>
+          <t>bellemo alessandro</t>
+        </is>
+      </c>
+      <c r="FJ9" t="inlineStr">
+        <is>
+          <t>GKxv62wr</t>
+        </is>
+      </c>
+      <c r="FK9" t="inlineStr">
+        <is>
+          <t>akinsanmiro ebenezer</t>
+        </is>
+      </c>
+      <c r="FL9" t="inlineStr">
+        <is>
+          <t>GKxv62wr</t>
+        </is>
+      </c>
+      <c r="FM9" t="inlineStr">
+        <is>
+          <t>akinsanmiro ebenezer</t>
+        </is>
+      </c>
+      <c r="FN9" t="inlineStr">
+        <is>
+          <t>tUw2S8Tb</t>
+        </is>
+      </c>
+      <c r="FO9" t="inlineStr">
+        <is>
+          <t>vieira ronaldo</t>
+        </is>
+      </c>
+      <c r="FP9" t="inlineStr"/>
+      <c r="FQ9" t="inlineStr"/>
+      <c r="FR9" t="inlineStr"/>
+      <c r="FS9" t="inlineStr"/>
+      <c r="FT9" t="inlineStr"/>
+      <c r="FU9" t="inlineStr"/>
+      <c r="FV9" t="inlineStr"/>
+      <c r="FW9" t="inlineStr"/>
+      <c r="FX9" t="inlineStr"/>
+      <c r="FY9" t="inlineStr"/>
+      <c r="FZ9" t="inlineStr"/>
+      <c r="GA9" t="inlineStr"/>
+      <c r="GB9" t="inlineStr"/>
+      <c r="GC9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>82ZM63O9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dvzcWaun</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>sepe luigi</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0npaWwAk</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>stojanovic petar</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>b5OLGEKk</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>bronn dylan</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>bX4esuFb</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ferrari gianmarco</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>OMiJz5gi</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>njoh lilian</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>fmW4DLwJ</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>maggiore giulio</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4jCqyBoe</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>amatucci lorenzo</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>MTQaLOIC</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>reine adelaide jeff</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>UkKychK3</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>verde daniele</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>QultNmNB</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>wlodarczyk szymon</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2NEiLzlK</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>braaf jayden</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Cd8PlZLP</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>pigliacelli mirko</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Cn5hGkJ1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>cassandro tommaso</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>ULlJRUuq</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>brighenti niccolo</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>lSjS9dZq</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>scognamillo stefano</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>4YukEqvc</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>bonini federico</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>2wV1KjZe</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>petriccione jacopo</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tYR5Dxf7</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>pompetti marco</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>I1gxHFqD</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>compagnon mattia</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>6sEtrQRT</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>koutsoupias ilias</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>AuwJZqXT</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>d alessandro marco</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>rewFYbKs</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>pittarello filippo</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>raWfPms5</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>corriere francesco</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>l0e0BnSA</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>fiorillo vincenzo</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>EFz3cpqf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>gentile davide</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>Im8vPlLt</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>ghiglione paolo</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>phFkXFtU</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>hrustic ajdin</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>hCBiTrxs</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>jaroszynski pavel</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>2uPbwswk</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>ruggeri fabio</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>IN4rltwr</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>simy</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>KEdDR3M7</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>soriano roberto</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>0rM28Wn3</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>tello andres</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>S8GkvmO5</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>torregrossa ernesto</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>lWANALyo</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>velthuis tijs</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>hSplSpIO</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>antonini lui matias</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>EoMTY8PS</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>biasci tommaso</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>lAib9q3o</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>buso nicolo</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>xrKwy1VH</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>ceresoli andrea</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>QJ45wC35</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>coulibaly mamadou</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>z9KbqiQG</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>dini andrea</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>Y3jLWCwC</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>la mantia andrea</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>WMPydjjC</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>piras marcello</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>jesSF9Ls</t>
+        </is>
+      </c>
+      <c r="CK10" t="inlineStr">
+        <is>
+          <t>seck demba</t>
+        </is>
+      </c>
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>Sz8BErOG</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>situm mario</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>OGQMciXh</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>turicchia riccardo</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
+        <is>
+          <t>nPTeq3L6</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>volpe giovanni</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>KEdDR3M7</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>soriano roberto</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr">
+        <is>
+          <t>KEdDR3M7</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>soriano roberto</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>MTQaLOIC</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>reine adelaide jeff</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>0rM28Wn3</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>tello andres</t>
+        </is>
+      </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>0rM28Wn3</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>tello andres</t>
+        </is>
+      </c>
+      <c r="DB10" t="inlineStr">
+        <is>
+          <t>4jCqyBoe</t>
+        </is>
+      </c>
+      <c r="DC10" t="inlineStr">
+        <is>
+          <t>amatucci lorenzo</t>
+        </is>
+      </c>
+      <c r="DD10" t="inlineStr">
+        <is>
+          <t>S8GkvmO5</t>
+        </is>
+      </c>
+      <c r="DE10" t="inlineStr">
+        <is>
+          <t>torregrossa ernesto</t>
+        </is>
+      </c>
+      <c r="DF10" t="inlineStr">
+        <is>
+          <t>S8GkvmO5</t>
+        </is>
+      </c>
+      <c r="DG10" t="inlineStr">
+        <is>
+          <t>torregrossa ernesto</t>
+        </is>
+      </c>
+      <c r="DH10" t="inlineStr">
+        <is>
+          <t>QultNmNB</t>
+        </is>
+      </c>
+      <c r="DI10" t="inlineStr">
+        <is>
+          <t>wlodarczyk szymon</t>
+        </is>
+      </c>
+      <c r="DJ10" t="inlineStr">
+        <is>
+          <t>phFkXFtU</t>
+        </is>
+      </c>
+      <c r="DK10" t="inlineStr">
+        <is>
+          <t>hrustic ajdin</t>
+        </is>
+      </c>
+      <c r="DL10" t="inlineStr">
+        <is>
+          <t>phFkXFtU</t>
+        </is>
+      </c>
+      <c r="DM10" t="inlineStr">
+        <is>
+          <t>hrustic ajdin</t>
+        </is>
+      </c>
+      <c r="DN10" t="inlineStr">
+        <is>
+          <t>2NEiLzlK</t>
+        </is>
+      </c>
+      <c r="DO10" t="inlineStr">
+        <is>
+          <t>braaf jayden</t>
+        </is>
+      </c>
+      <c r="DP10" t="inlineStr"/>
+      <c r="DQ10" t="inlineStr"/>
+      <c r="DR10" t="inlineStr"/>
+      <c r="DS10" t="inlineStr"/>
+      <c r="DT10" t="inlineStr"/>
+      <c r="DU10" t="inlineStr"/>
+      <c r="DV10" t="inlineStr">
+        <is>
+          <t>Sz8BErOG</t>
+        </is>
+      </c>
+      <c r="DW10" t="inlineStr">
+        <is>
+          <t>situm mario</t>
+        </is>
+      </c>
+      <c r="DX10" t="inlineStr">
+        <is>
+          <t>Sz8BErOG</t>
+        </is>
+      </c>
+      <c r="DY10" t="inlineStr">
+        <is>
+          <t>situm mario</t>
+        </is>
+      </c>
+      <c r="DZ10" t="inlineStr">
+        <is>
+          <t>AuwJZqXT</t>
+        </is>
+      </c>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>d alessandro marco</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>EoMTY8PS</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
+          <t>biasci tommaso</t>
+        </is>
+      </c>
+      <c r="ED10" t="inlineStr">
+        <is>
+          <t>EoMTY8PS</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>biasci tommaso</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
+        <is>
+          <t>6sEtrQRT</t>
+        </is>
+      </c>
+      <c r="EG10" t="inlineStr">
+        <is>
+          <t>koutsoupias ilias</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>QJ45wC35</t>
+        </is>
+      </c>
+      <c r="EI10" t="inlineStr">
+        <is>
+          <t>coulibaly mamadou</t>
+        </is>
+      </c>
+      <c r="EJ10" t="inlineStr">
+        <is>
+          <t>QJ45wC35</t>
+        </is>
+      </c>
+      <c r="EK10" t="inlineStr">
+        <is>
+          <t>coulibaly mamadou</t>
+        </is>
+      </c>
+      <c r="EL10" t="inlineStr">
+        <is>
+          <t>I1gxHFqD</t>
+        </is>
+      </c>
+      <c r="EM10" t="inlineStr">
+        <is>
+          <t>compagnon mattia</t>
+        </is>
+      </c>
+      <c r="EN10" t="inlineStr"/>
+      <c r="EO10" t="inlineStr"/>
+      <c r="EP10" t="inlineStr"/>
+      <c r="EQ10" t="inlineStr"/>
+      <c r="ER10" t="inlineStr"/>
+      <c r="ES10" t="inlineStr"/>
+      <c r="ET10" t="inlineStr"/>
+      <c r="EU10" t="inlineStr"/>
+      <c r="EV10" t="inlineStr"/>
+      <c r="EW10" t="inlineStr"/>
+      <c r="EX10" t="inlineStr"/>
+      <c r="EY10" t="inlineStr"/>
+      <c r="EZ10" t="inlineStr"/>
+      <c r="FA10" t="inlineStr"/>
+      <c r="FB10" t="inlineStr"/>
+      <c r="FC10" t="inlineStr"/>
+      <c r="FD10" t="inlineStr">
+        <is>
+          <t>Y3jLWCwC</t>
+        </is>
+      </c>
+      <c r="FE10" t="inlineStr">
+        <is>
+          <t>la mantia andrea</t>
+        </is>
+      </c>
+      <c r="FF10" t="inlineStr">
+        <is>
+          <t>Y3jLWCwC</t>
+        </is>
+      </c>
+      <c r="FG10" t="inlineStr">
+        <is>
+          <t>la mantia andrea</t>
+        </is>
+      </c>
+      <c r="FH10" t="inlineStr">
+        <is>
+          <t>rewFYbKs</t>
+        </is>
+      </c>
+      <c r="FI10" t="inlineStr">
+        <is>
+          <t>pittarello filippo</t>
+        </is>
+      </c>
+      <c r="FJ10" t="inlineStr"/>
+      <c r="FK10" t="inlineStr"/>
+      <c r="FL10" t="inlineStr"/>
+      <c r="FM10" t="inlineStr"/>
+      <c r="FN10" t="inlineStr"/>
+      <c r="FO10" t="inlineStr"/>
+      <c r="FP10" t="inlineStr"/>
+      <c r="FQ10" t="inlineStr"/>
+      <c r="FR10" t="inlineStr"/>
+      <c r="FS10" t="inlineStr"/>
+      <c r="FT10" t="inlineStr"/>
+      <c r="FU10" t="inlineStr"/>
+      <c r="FV10" t="inlineStr"/>
+      <c r="FW10" t="inlineStr"/>
+      <c r="FX10" t="inlineStr"/>
+      <c r="FY10" t="inlineStr"/>
+      <c r="FZ10" t="inlineStr"/>
+      <c r="GA10" t="inlineStr"/>
+      <c r="GB10" t="inlineStr"/>
+      <c r="GC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,3569 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:GK4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_10</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_10</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_10</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_10</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_11</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_11</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_12</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_12</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_13</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_13</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_14</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_14</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_15</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_15</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="FR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="FS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="FT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="FU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="FV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_11</t>
+        </is>
+      </c>
+      <c r="FW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_11</t>
+        </is>
+      </c>
+      <c r="FX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_12</t>
+        </is>
+      </c>
+      <c r="FY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_12</t>
+        </is>
+      </c>
+      <c r="FZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_13</t>
+        </is>
+      </c>
+      <c r="GA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_13</t>
+        </is>
+      </c>
+      <c r="GB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="GC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="GD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="GE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="GF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="GG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="GH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="GI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
+        </is>
+      </c>
+      <c r="GJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_9</t>
+        </is>
+      </c>
+      <c r="GK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_9</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C6m92DF7</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>provedel ivan</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>WlqJxlIT</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lazzari manuel</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>dQqXDhtf</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>gila mario</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Wr49C0j4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>romagnoli alessio</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>WKey0InR</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>pellegrini luca</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>bPQZKve0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>rovella nicolo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>6ZesE86o</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>guendouzi matteo</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Uma3vLeI</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>noslin tijjani</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>zk0Q52W2</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>dia boulaye</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>d0vohCHH</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>isaksen gustav</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>ET4rsqIP</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>castellanos valentin</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0nQhrI82</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>scuffet simone</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>6y7tiy6b</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>zappa gabriele</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0hqx5eWc</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>mina yerry</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>l6ZLUe9D</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>luperto sebastiano</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>pUpsjuw3</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>augello tommaso</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>thWJbHFE</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>adopo michel</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>zaVrgWQt</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>makoumbou antoine</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>2csPLGHO</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>zortea nadir</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>nNOKUM6f</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>gaetano gianluca</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>QZQ9DtPs</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>luvumbo zito</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>CK8QgVjh</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>piccoli roberto</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>ALBpOZPH</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>castrovilli gaetano</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>AF8BqWgI</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>dele bashiru fisayo</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>2PZTBiII</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>furlanetto alessio</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>G8cfGd8h</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>gigot samuel</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>vVGAhOFI</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>mandas christos</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>tC46HZrA</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>marusic adam</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0f1tMqQl</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>pedro</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>vij66lN7</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>tchaouna loum</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>AVysqrBE</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>vecino matias</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>MJ7sACQ8</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>zaccagni mattia</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>tnZd7uZQ</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>azzi paulo</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>nBYARUG6</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>ciocci giuseppe</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>E9t2kgz3</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>deiola alessandro</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>69h4RBd7</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>felici mattia</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>6kvbBHqr</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>jankto jakub</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>K0nUrV5K</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>lapadula gianluca</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>WYOcFAQk</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>marin razvan</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>tvxzDyfa</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>mutandwa kingstone</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>YZEkc9qD</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>obert adam</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>2c7LCGJR</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>palomino jose</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>xrQ22VYn</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>pavoletti leonardo</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>WMeojevP</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>prati matteo</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>zTdDPVna</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>sherri alen</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>40ggoSmN</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>viola nicolas</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>8xR8lIU9</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>wieteska mateusz</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>AVysqrBE</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>vecino matias</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>AVysqrBE</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>vecino matias</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>Uma3vLeI</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>noslin tijjani</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>0f1tMqQl</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>pedro</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>0f1tMqQl</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>pedro</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>d0vohCHH</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>isaksen gustav</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>MJ7sACQ8</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>zaccagni mattia</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>MJ7sACQ8</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>zaccagni mattia</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>6ZesE86o</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>guendouzi matteo</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>AF8BqWgI</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>dele bashiru fisayo</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>AF8BqWgI</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>dele bashiru fisayo</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>zk0Q52W2</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>dia boulaye</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>tC46HZrA</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>marusic adam</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>tC46HZrA</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>marusic adam</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>WlqJxlIT</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>lazzari manuel</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>40ggoSmN</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>viola nicolas</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>40ggoSmN</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>viola nicolas</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>nNOKUM6f</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>gaetano gianluca</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>YZEkc9qD</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>obert adam</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>YZEkc9qD</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>obert adam</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>pUpsjuw3</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>augello tommaso</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>69h4RBd7</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>felici mattia</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>69h4RBd7</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>felici mattia</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>2csPLGHO</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>zortea nadir</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>2c7LCGJR</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>palomino jose</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>2c7LCGJR</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>palomino jose</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>QZQ9DtPs</t>
+        </is>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>luvumbo zito</t>
+        </is>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>E9t2kgz3</t>
+        </is>
+      </c>
+      <c r="EU2" t="inlineStr">
+        <is>
+          <t>deiola alessandro</t>
+        </is>
+      </c>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>E9t2kgz3</t>
+        </is>
+      </c>
+      <c r="EW2" t="inlineStr">
+        <is>
+          <t>deiola alessandro</t>
+        </is>
+      </c>
+      <c r="EX2" t="inlineStr">
+        <is>
+          <t>CK8QgVjh</t>
+        </is>
+      </c>
+      <c r="EY2" t="inlineStr">
+        <is>
+          <t>piccoli roberto</t>
+        </is>
+      </c>
+      <c r="EZ2" t="inlineStr">
+        <is>
+          <t>pY6E7S2D</t>
+        </is>
+      </c>
+      <c r="FA2" t="inlineStr">
+        <is>
+          <t>tavares nuno</t>
+        </is>
+      </c>
+      <c r="FB2" t="inlineStr"/>
+      <c r="FC2" t="inlineStr"/>
+      <c r="FD2" t="inlineStr"/>
+      <c r="FE2" t="inlineStr"/>
+      <c r="FF2" t="inlineStr"/>
+      <c r="FG2" t="inlineStr"/>
+      <c r="FH2" t="inlineStr"/>
+      <c r="FI2" t="inlineStr"/>
+      <c r="FJ2" t="inlineStr"/>
+      <c r="FK2" t="inlineStr"/>
+      <c r="FL2" t="inlineStr"/>
+      <c r="FM2" t="inlineStr"/>
+      <c r="FN2" t="inlineStr"/>
+      <c r="FO2" t="inlineStr"/>
+      <c r="FP2" t="inlineStr"/>
+      <c r="FQ2" t="inlineStr"/>
+      <c r="FR2" t="inlineStr"/>
+      <c r="FS2" t="inlineStr"/>
+      <c r="FT2" t="inlineStr"/>
+      <c r="FU2" t="inlineStr"/>
+      <c r="FV2" t="inlineStr"/>
+      <c r="FW2" t="inlineStr"/>
+      <c r="FX2" t="inlineStr"/>
+      <c r="FY2" t="inlineStr"/>
+      <c r="FZ2" t="inlineStr"/>
+      <c r="GA2" t="inlineStr"/>
+      <c r="GB2" t="inlineStr"/>
+      <c r="GC2" t="inlineStr"/>
+      <c r="GD2" t="inlineStr"/>
+      <c r="GE2" t="inlineStr"/>
+      <c r="GF2" t="inlineStr"/>
+      <c r="GG2" t="inlineStr"/>
+      <c r="GH2" t="inlineStr"/>
+      <c r="GI2" t="inlineStr"/>
+      <c r="GJ2" t="inlineStr"/>
+      <c r="GK2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4xCrFFMe</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>vasquez devis</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ua5srQK6</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>de sciglio mattia</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>xtJXLSFe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ismajli ardian</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>bZmRuRzO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>viti mattia</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>jZgmSlM1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>gyasi emmanuel</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>YmvWlE1E</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>henderson liam</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Q1sHUL1D</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>haas nicolas</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CnRzW1VM</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>maleh youssef</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>zJD6Mdr3</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>pezzella giuseppe</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>U1piMQgC</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>solbakken ola</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>v3hpfVmF</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>pellegri pietro</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>KrEhnvkN</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>reina pepe</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>CxCzIfHK</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>goldaniga edoardo</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>4j96wYs7</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>dossena alberto</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>KSz457vB</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>barba federico</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>pdBI3oS8</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>moreno alberto</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>S2gIJM28</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>engelhardt yannik</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>AR2PqO6h</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>kempf marc oliver</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>YclDapI5</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>fadera alieu</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>IXqHAIWJ</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>da cunha lucas</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>zR7umNy4</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>strefezza gabriel</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>W6UTbSDR</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>belotti andrea</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>jTWtnxud</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>anjorin faustino</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>dfcCpneb</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>brancolini federico</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>4SWMMcZd</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>cacace liberato</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>YL741OaO</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>colombo lorenzo</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>4pUDwSFI</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>ekong emmanuel</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>lYCSEEBl</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>konate ismael</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>I52ibPrQ</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>marianucci luca</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>GK1tPlKu</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>sambia solomon</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>KKXDLjg8</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>seghetti jacopo</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>2eFCBn8A</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>tosto lorenzo</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>23LftUaB</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>andrealli francesco</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>fwyieeh8</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>audero emil</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>IBUaxPl6</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>cerri alberto</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>vB6l1nu7</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>cutrone patrick</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>xzWqt9uL</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>gabrielloni alessandro</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>UieHuD3i</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>lovino alessio</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>4bKWOzzb</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>jack fellipe</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>MqKDIKSH</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>jasim ali</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>CWsfUXG2</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>mazzaglia giuseppe</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>GG6EYRT0</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>paz martinez nicolas</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>lG6NBuFm</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>sala marco</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>rP6cESXb</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>verdi simone</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr"/>
+      <c r="CM3" t="inlineStr"/>
+      <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="inlineStr"/>
+      <c r="CP3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr"/>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>YL741OaO</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>colombo lorenzo</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>YL741OaO</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>colombo lorenzo</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>U1piMQgC</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>solbakken ola</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>jTWtnxud</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>anjorin faustino</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>jTWtnxud</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>anjorin faustino</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>Q1sHUL1D</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>haas nicolas</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>4pUDwSFI</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>ekong emmanuel</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>4pUDwSFI</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>ekong emmanuel</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>v3hpfVmF</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>pellegri pietro</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>I52ibPrQ</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>marianucci luca</t>
+        </is>
+      </c>
+      <c r="DL3" t="inlineStr">
+        <is>
+          <t>I52ibPrQ</t>
+        </is>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>marianucci luca</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>YmvWlE1E</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>henderson liam</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>4SWMMcZd</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
+          <t>cacace liberato</t>
+        </is>
+      </c>
+      <c r="DR3" t="inlineStr">
+        <is>
+          <t>4SWMMcZd</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
+          <t>cacace liberato</t>
+        </is>
+      </c>
+      <c r="DT3" t="inlineStr">
+        <is>
+          <t>zJD6Mdr3</t>
+        </is>
+      </c>
+      <c r="DU3" t="inlineStr">
+        <is>
+          <t>pezzella giuseppe</t>
+        </is>
+      </c>
+      <c r="DV3" t="inlineStr">
+        <is>
+          <t>GG6EYRT0</t>
+        </is>
+      </c>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>paz martinez nicolas</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>GG6EYRT0</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>paz martinez nicolas</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>KSz457vB</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>barba federico</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>vB6l1nu7</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>cutrone patrick</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>vB6l1nu7</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>cutrone patrick</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>zR7umNy4</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>strefezza gabriel</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>rP6cESXb</t>
+        </is>
+      </c>
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>verdi simone</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>rP6cESXb</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>verdi simone</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
+        <is>
+          <t>YclDapI5</t>
+        </is>
+      </c>
+      <c r="EM3" t="inlineStr">
+        <is>
+          <t>fadera alieu</t>
+        </is>
+      </c>
+      <c r="EN3" t="inlineStr">
+        <is>
+          <t>xzWqt9uL</t>
+        </is>
+      </c>
+      <c r="EO3" t="inlineStr">
+        <is>
+          <t>gabrielloni alessandro</t>
+        </is>
+      </c>
+      <c r="EP3" t="inlineStr">
+        <is>
+          <t>xzWqt9uL</t>
+        </is>
+      </c>
+      <c r="EQ3" t="inlineStr">
+        <is>
+          <t>gabrielloni alessandro</t>
+        </is>
+      </c>
+      <c r="ER3" t="inlineStr">
+        <is>
+          <t>W6UTbSDR</t>
+        </is>
+      </c>
+      <c r="ES3" t="inlineStr">
+        <is>
+          <t>belotti andrea</t>
+        </is>
+      </c>
+      <c r="ET3" t="inlineStr">
+        <is>
+          <t>IBUaxPl6</t>
+        </is>
+      </c>
+      <c r="EU3" t="inlineStr">
+        <is>
+          <t>cerri alberto</t>
+        </is>
+      </c>
+      <c r="EV3" t="inlineStr">
+        <is>
+          <t>IBUaxPl6</t>
+        </is>
+      </c>
+      <c r="EW3" t="inlineStr">
+        <is>
+          <t>cerri alberto</t>
+        </is>
+      </c>
+      <c r="EX3" t="inlineStr">
+        <is>
+          <t>IXqHAIWJ</t>
+        </is>
+      </c>
+      <c r="EY3" t="inlineStr">
+        <is>
+          <t>da cunha lucas</t>
+        </is>
+      </c>
+      <c r="EZ3" t="inlineStr">
+        <is>
+          <t>KbPlg3Fl</t>
+        </is>
+      </c>
+      <c r="FA3" t="inlineStr">
+        <is>
+          <t>ebuehi tyronne</t>
+        </is>
+      </c>
+      <c r="FB3" t="inlineStr">
+        <is>
+          <t>WrbP1Sdg</t>
+        </is>
+      </c>
+      <c r="FC3" t="inlineStr">
+        <is>
+          <t>esposito sebastiano</t>
+        </is>
+      </c>
+      <c r="FD3" t="inlineStr">
+        <is>
+          <t>8lxchd9S</t>
+        </is>
+      </c>
+      <c r="FE3" t="inlineStr">
+        <is>
+          <t>goglichidze saba</t>
+        </is>
+      </c>
+      <c r="FF3" t="inlineStr">
+        <is>
+          <t>E7Jj74nK</t>
+        </is>
+      </c>
+      <c r="FG3" t="inlineStr">
+        <is>
+          <t>grassi alberto</t>
+        </is>
+      </c>
+      <c r="FH3" t="inlineStr">
+        <is>
+          <t>6HUZxS6p</t>
+        </is>
+      </c>
+      <c r="FI3" t="inlineStr">
+        <is>
+          <t>perisan samuele</t>
+        </is>
+      </c>
+      <c r="FJ3" t="inlineStr">
+        <is>
+          <t>t2MszR74</t>
+        </is>
+      </c>
+      <c r="FK3" t="inlineStr">
+        <is>
+          <t>sazonov saba</t>
+        </is>
+      </c>
+      <c r="FL3" t="inlineStr">
+        <is>
+          <t>Ees7JNmc</t>
+        </is>
+      </c>
+      <c r="FM3" t="inlineStr">
+        <is>
+          <t>zurkowski szymon</t>
+        </is>
+      </c>
+      <c r="FN3" t="inlineStr">
+        <is>
+          <t>vkRv24dh</t>
+        </is>
+      </c>
+      <c r="FO3" t="inlineStr">
+        <is>
+          <t>braunoder matthias</t>
+        </is>
+      </c>
+      <c r="FP3" t="inlineStr">
+        <is>
+          <t>vmcGpMJM</t>
+        </is>
+      </c>
+      <c r="FQ3" t="inlineStr">
+        <is>
+          <t>perrone maximo</t>
+        </is>
+      </c>
+      <c r="FR3" t="inlineStr">
+        <is>
+          <t>W2R804U4</t>
+        </is>
+      </c>
+      <c r="FS3" t="inlineStr">
+        <is>
+          <t>roberto sergi</t>
+        </is>
+      </c>
+      <c r="FT3" t="inlineStr">
+        <is>
+          <t>Uaabio2H</t>
+        </is>
+      </c>
+      <c r="FU3" t="inlineStr">
+        <is>
+          <t>van der brempt ignace</t>
+        </is>
+      </c>
+      <c r="FV3" t="inlineStr"/>
+      <c r="FW3" t="inlineStr"/>
+      <c r="FX3" t="inlineStr"/>
+      <c r="FY3" t="inlineStr"/>
+      <c r="FZ3" t="inlineStr"/>
+      <c r="GA3" t="inlineStr"/>
+      <c r="GB3" t="inlineStr"/>
+      <c r="GC3" t="inlineStr"/>
+      <c r="GD3" t="inlineStr"/>
+      <c r="GE3" t="inlineStr"/>
+      <c r="GF3" t="inlineStr"/>
+      <c r="GG3" t="inlineStr"/>
+      <c r="GH3" t="inlineStr"/>
+      <c r="GI3" t="inlineStr"/>
+      <c r="GJ3" t="inlineStr"/>
+      <c r="GK3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4bDDVvmT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>suzuki zion</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SUqEqOY3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>coulibaly woyo</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>b7eKMEEo</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>del prato enrico</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6RV5Qaot</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>balogh botond</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>l8UQT6rE</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>valeri emanuele</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>UevlGWN5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>keita mandela</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Qw9q7XhE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>bernabe adrian</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>zwvX5g6l</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>man dennis</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ITcHEtOG</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>sohm simon</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>OOFN5OX4</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>mihaila valentin</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>08MpRWg8</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>bonny ange yoan</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>MHD6IelJ</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>leali nicola</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>tW6pCCm8</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>vogliacco alessandro</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Qydfoeer</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>vasquez johan</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>WOffNMWA</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>matturro romero alan</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>xjWe0TTo</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>zanoli alessandro</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Ei7zkE0o</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>thorsby morten</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>4InuIizr</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>badelj milan</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2XPmtx2l</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>frendrup morten</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>l4xhn6hC</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>caricol aaron</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>QopKhlIm</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>ekhator jeff</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>O4qi5hfc</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>pinamonti andrea</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>vL30lp6C</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>almqvist pontus</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>KSn7To32</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>benedyczak adrian</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>zm9nBPNL</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>camara drissa</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>GvtmmdSl</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>cancellieri matteo</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>fNdypn5G</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>charpentier gabriel</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>ba10fZZI</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>chichizola leandro</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>j33di9cK</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>corvi edoardo</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>Sv3By8Ki</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>di chiara gianluca</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>6NqFKJLp</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>estevez nahuel</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>hO2RGEGC</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>hainaut antoine</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>U5DbE1A7</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>accornero federico</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>Q1Sl1XK4</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>ahanor honest</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>rcRIhsUH</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>balotelli mario</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>25uHtnwl</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>bohinen emil</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>vw0NcNnU</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>kasa lior</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>6BUzxLAe</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>marcandalli alessandro</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>fwaRyAka</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>masini patrizio</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>nT9hAjIK</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>melegoni filippo</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>tSUumbUT</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>miretti fabio</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>txlUkIne</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>pereiro gaston</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>zLlOcqw4</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>sabelli stefano</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>MsjFcjtJ</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>sommariva daniele</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>OUQ7cgE0</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>stolz franz</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr"/>
+      <c r="CO4" t="inlineStr"/>
+      <c r="CP4" t="inlineStr"/>
+      <c r="CQ4" t="inlineStr"/>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>Eo7P7oks</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>haj mohamed</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>Eo7P7oks</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>haj mohamed</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>Qw9q7XhE</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>bernabe adrian</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>6NqFKJLp</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>estevez nahuel</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>6NqFKJLp</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>estevez nahuel</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
+          <t>Eo7P7oks</t>
+        </is>
+      </c>
+      <c r="DC4" t="inlineStr">
+        <is>
+          <t>haj mohamed</t>
+        </is>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>vL30lp6C</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>almqvist pontus</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
+        <is>
+          <t>vL30lp6C</t>
+        </is>
+      </c>
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>almqvist pontus</t>
+        </is>
+      </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>UevlGWN5</t>
+        </is>
+      </c>
+      <c r="DI4" t="inlineStr">
+        <is>
+          <t>keita mandela</t>
+        </is>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>fNdypn5G</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>charpentier gabriel</t>
+        </is>
+      </c>
+      <c r="DL4" t="inlineStr">
+        <is>
+          <t>fNdypn5G</t>
+        </is>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>charpentier gabriel</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>08MpRWg8</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>bonny ange yoan</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>KSn7To32</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
+          <t>benedyczak adrian</t>
+        </is>
+      </c>
+      <c r="DR4" t="inlineStr">
+        <is>
+          <t>KSn7To32</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
+          <t>benedyczak adrian</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>OOFN5OX4</t>
+        </is>
+      </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t>mihaila valentin</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
+          <t>zLlOcqw4</t>
+        </is>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>sabelli stefano</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>zLlOcqw4</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>sabelli stefano</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>xjWe0TTo</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>zanoli alessandro</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>Q1Sl1XK4</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
+          <t>ahanor honest</t>
+        </is>
+      </c>
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t>Q1Sl1XK4</t>
+        </is>
+      </c>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t>ahanor honest</t>
+        </is>
+      </c>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>l4xhn6hC</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>caricol aaron</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>rcRIhsUH</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>balotelli mario</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
+        <is>
+          <t>rcRIhsUH</t>
+        </is>
+      </c>
+      <c r="EK4" t="inlineStr">
+        <is>
+          <t>balotelli mario</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
+        <is>
+          <t>QopKhlIm</t>
+        </is>
+      </c>
+      <c r="EM4" t="inlineStr">
+        <is>
+          <t>ekhator jeff</t>
+        </is>
+      </c>
+      <c r="EN4" t="inlineStr">
+        <is>
+          <t>fwaRyAka</t>
+        </is>
+      </c>
+      <c r="EO4" t="inlineStr">
+        <is>
+          <t>masini patrizio</t>
+        </is>
+      </c>
+      <c r="EP4" t="inlineStr">
+        <is>
+          <t>fwaRyAka</t>
+        </is>
+      </c>
+      <c r="EQ4" t="inlineStr">
+        <is>
+          <t>masini patrizio</t>
+        </is>
+      </c>
+      <c r="ER4" t="inlineStr">
+        <is>
+          <t>4InuIizr</t>
+        </is>
+      </c>
+      <c r="ES4" t="inlineStr">
+        <is>
+          <t>badelj milan</t>
+        </is>
+      </c>
+      <c r="ET4" t="inlineStr"/>
+      <c r="EU4" t="inlineStr"/>
+      <c r="EV4" t="inlineStr"/>
+      <c r="EW4" t="inlineStr"/>
+      <c r="EX4" t="inlineStr"/>
+      <c r="EY4" t="inlineStr"/>
+      <c r="EZ4" t="inlineStr">
+        <is>
+          <t>x0EJsbc8</t>
+        </is>
+      </c>
+      <c r="FA4" t="inlineStr">
+        <is>
+          <t>circati alessandro</t>
+        </is>
+      </c>
+      <c r="FB4" t="inlineStr">
+        <is>
+          <t>bcZkPxo4</t>
+        </is>
+      </c>
+      <c r="FC4" t="inlineStr">
+        <is>
+          <t>hernani</t>
+        </is>
+      </c>
+      <c r="FD4" t="inlineStr">
+        <is>
+          <t>WU5civJO</t>
+        </is>
+      </c>
+      <c r="FE4" t="inlineStr">
+        <is>
+          <t>kowalski mateusz</t>
+        </is>
+      </c>
+      <c r="FF4" t="inlineStr"/>
+      <c r="FG4" t="inlineStr"/>
+      <c r="FH4" t="inlineStr"/>
+      <c r="FI4" t="inlineStr"/>
+      <c r="FJ4" t="inlineStr"/>
+      <c r="FK4" t="inlineStr"/>
+      <c r="FL4" t="inlineStr"/>
+      <c r="FM4" t="inlineStr"/>
+      <c r="FN4" t="inlineStr">
+        <is>
+          <t>fTOU6yR2</t>
+        </is>
+      </c>
+      <c r="FO4" t="inlineStr">
+        <is>
+          <t>ankeye david</t>
+        </is>
+      </c>
+      <c r="FP4" t="inlineStr">
+        <is>
+          <t>vgmL526e</t>
+        </is>
+      </c>
+      <c r="FQ4" t="inlineStr">
+        <is>
+          <t>bani mattia</t>
+        </is>
+      </c>
+      <c r="FR4" t="inlineStr">
+        <is>
+          <t>EFmPm0Qo</t>
+        </is>
+      </c>
+      <c r="FS4" t="inlineStr">
+        <is>
+          <t>de winter koni</t>
+        </is>
+      </c>
+      <c r="FT4" t="inlineStr">
+        <is>
+          <t>CtdcoETk</t>
+        </is>
+      </c>
+      <c r="FU4" t="inlineStr">
+        <is>
+          <t>ekuban caleb</t>
+        </is>
+      </c>
+      <c r="FV4" t="inlineStr">
+        <is>
+          <t>Eo7P7oks</t>
+        </is>
+      </c>
+      <c r="FW4" t="inlineStr">
+        <is>
+          <t>haj mohamed</t>
+        </is>
+      </c>
+      <c r="FX4" t="inlineStr">
+        <is>
+          <t>GdON0JjJ</t>
+        </is>
+      </c>
+      <c r="FY4" t="inlineStr">
+        <is>
+          <t>leoni giovanni</t>
+        </is>
+      </c>
+      <c r="FZ4" t="inlineStr">
+        <is>
+          <t>48K74eTp</t>
+        </is>
+      </c>
+      <c r="GA4" t="inlineStr">
+        <is>
+          <t>osorio yordan</t>
+        </is>
+      </c>
+      <c r="GB4" t="inlineStr">
+        <is>
+          <t>vZY7FZwP</t>
+        </is>
+      </c>
+      <c r="GC4" t="inlineStr">
+        <is>
+          <t>gollini pierluigi</t>
+        </is>
+      </c>
+      <c r="GD4" t="inlineStr">
+        <is>
+          <t>GGkyU0bT</t>
+        </is>
+      </c>
+      <c r="GE4" t="inlineStr">
+        <is>
+          <t>malinovsky ruslan</t>
+        </is>
+      </c>
+      <c r="GF4" t="inlineStr">
+        <is>
+          <t>8l36RdAF</t>
+        </is>
+      </c>
+      <c r="GG4" t="inlineStr">
+        <is>
+          <t>messias junior</t>
+        </is>
+      </c>
+      <c r="GH4" t="inlineStr">
+        <is>
+          <t>63jp0ZJd</t>
+        </is>
+      </c>
+      <c r="GI4" t="inlineStr">
+        <is>
+          <t>norton cuffy brooke</t>
+        </is>
+      </c>
+      <c r="GJ4" t="inlineStr">
+        <is>
+          <t>AazXYT3h</t>
+        </is>
+      </c>
+      <c r="GK4" t="inlineStr">
+        <is>
+          <t>vitinha</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>